--- a/base_personnages_fictifs.xlsx
+++ b/base_personnages_fictifs.xlsx
@@ -9,11 +9,9 @@
   <sheets>
     <sheet name="Personnages" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Lisez-moi" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Narration" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$O$174</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Narration'!$A$1:$G$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$P$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -150,12 +148,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O174"/>
+  <dimension ref="A1:P174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -538,7 +530,8 @@
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="44" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -614,6 +607,11 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Branche</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Parenté</t>
         </is>
       </c>
@@ -683,7 +681,8 @@
           <t>Benali</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Époux de Nadia</t>
         </is>
@@ -747,10 +746,15 @@
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>Côté (poste)</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -818,10 +822,15 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Tremblay (Alex)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Fils de Sonia</t>
         </is>
@@ -889,10 +898,15 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>Lavoie (JP)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>Fils cadet de Robert et Diane — petit frère de JP</t>
         </is>
@@ -960,10 +974,15 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Côté (ruelle)</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>ruelle</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Célibataire — tourne autour du Spot</t>
         </is>
@@ -1031,10 +1050,15 @@
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>Gagnon (hockey)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -1098,10 +1122,15 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Tremblay (Gratien)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Gratien</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Mère de Gratien Tremblay</t>
         </is>
@@ -1168,7 +1197,8 @@
           <t>Traoré</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -1235,7 +1265,8 @@
           <t>Martel</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Sœur de Julie Martel</t>
         </is>
@@ -1306,7 +1337,8 @@
           <t>Desrosiers-Simard</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>Conjointe de Marc-André</t>
         </is>
@@ -1373,7 +1405,8 @@
           <t>Girard</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>Épouse de Louis Girard</t>
         </is>
@@ -1440,7 +1473,8 @@
           <t>Lacroix</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>Neveu de Lucien et Thérèse Lacroix</t>
         </is>
@@ -1508,10 +1542,15 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Tremblay (bunker)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>bunker</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>Célibataire — vend des stocks à Dévon</t>
         </is>
@@ -1575,10 +1614,15 @@
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>Gagnon (immobilier)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>immobilier</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>Ex-mari de Sylvie Gagnon</t>
         </is>
@@ -1649,7 +1693,8 @@
           <t>Bérubé</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>Cousin de Kevin et Jessy Bérubé — travaille pour Dévon</t>
         </is>
@@ -1717,10 +1762,15 @@
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>Gagnon (motards)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>motards</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>Cousin de Karine et Rock Gagnon</t>
         </is>
@@ -1787,7 +1837,8 @@
           <t>Dubé</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>Frère de Mélanie Dubé</t>
         </is>
@@ -1851,10 +1902,15 @@
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>Gauthier (Tim)</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -1922,10 +1978,15 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Lavoie (Chantal)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Chantal</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>Fille de Gaétan</t>
         </is>
@@ -1993,10 +2054,15 @@
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>Bouchard (Chloé)</t>
+          <t>Bouchard</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>Chloé</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>Fille de Nathalie</t>
         </is>
@@ -2064,10 +2130,15 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Tremblay (Gratien)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Gratien</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>Fille de Manon Lavoie — estafette de Gratien</t>
         </is>
@@ -2131,10 +2202,15 @@
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>Lavoie (Michel)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>Père de Michel Lavoie</t>
         </is>
@@ -2205,7 +2281,8 @@
           <t>Noël</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>Célibataire — fournit Sam Aubin en motifs</t>
         </is>
@@ -2272,7 +2349,8 @@
           <t>Truchon</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>Mère d’Yvan Truchon</t>
         </is>
@@ -2339,7 +2417,8 @@
           <t>Pedneault</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>Épouse de Réjean Pedneault</t>
         </is>
@@ -2410,7 +2489,8 @@
           <t>Cloutier</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>Fils de Manon</t>
         </is>
@@ -2474,10 +2554,15 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Lavoie (JP)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>Mère de JP</t>
         </is>
@@ -2548,7 +2633,8 @@
           <t>Audet</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -2619,7 +2705,8 @@
           <t>Boucher</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>Fils de Fernande Boucher — frère d’Éric</t>
         </is>
@@ -2690,7 +2777,8 @@
           <t>Al-Hassan</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="inlineStr">
         <is>
           <t>Épouse de Karim</t>
         </is>
@@ -2758,10 +2846,15 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Côté (Victoria)</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>Époux de Lucie Côté</t>
         </is>
@@ -2832,7 +2925,8 @@
           <t>Boucher</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="inlineStr">
         <is>
           <t>Mère de Dévon, Éric et tante de Normand</t>
         </is>
@@ -2899,7 +2993,8 @@
           <t>Boivin</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>Sœur de Maxime Boivin</t>
         </is>
@@ -2970,7 +3065,8 @@
           <t>Harvey</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -3041,7 +3137,8 @@
           <t>Lacroix</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>Célibataire — harcèle Lucien Lacroix</t>
         </is>
@@ -3112,7 +3209,8 @@
           <t>Otis</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>Neveu de Jeanne Otis</t>
         </is>
@@ -3183,7 +3281,8 @@
           <t>Ha! Ha!</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>Célibataire — vit pour la Pyramide</t>
         </is>
@@ -3251,10 +3350,15 @@
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>Pelletier (bar)</t>
+          <t>Pelletier</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
         <is>
           <t>Père d’Hugo Pelletier — grand-père de Léa</t>
         </is>
@@ -3322,10 +3426,15 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Lavoie (Chantal)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Chantal</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>Père de Chantal Lavoie</t>
         </is>
@@ -3396,7 +3505,8 @@
           <t>Bergeron</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="inlineStr">
         <is>
           <t>Père d’Isabelle</t>
         </is>
@@ -3467,7 +3577,8 @@
           <t>Roy</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>Épouse de Réjean</t>
         </is>
@@ -3534,7 +3645,8 @@
           <t>Truchon</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>Conjointe d’Yvan Truchon</t>
         </is>
@@ -3602,10 +3714,15 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Tremblay (Gratien)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Gratien</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>Fils d’Aline Tremblay — conjoint de Linda</t>
         </is>
@@ -3676,7 +3793,8 @@
           <t>Truchon</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>Relais d’Yvan Truchon</t>
         </is>
@@ -3744,10 +3862,15 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Lapointe (Marco)</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>Père de Marco</t>
         </is>
@@ -3814,7 +3937,8 @@
           <t>Benali</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>Fils d’Ahmed et Nadia Benali</t>
         </is>
@@ -3882,10 +4006,15 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Pelletier (bar)</t>
+          <t>Pelletier</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>Fils de Gaston Pelletier — époux de Sarah</t>
         </is>
@@ -3952,7 +4081,8 @@
           <t>Blackburn</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="inlineStr">
         <is>
           <t>Sœur de Lise Blackburn</t>
         </is>
@@ -4019,7 +4149,8 @@
           <t>Chicoine</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>Mère de Réal Chicoine</t>
         </is>
@@ -4086,7 +4217,8 @@
           <t>Bergeron</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="inlineStr">
         <is>
           <t>Fille de Gilles Bergeron</t>
         </is>
@@ -4153,7 +4285,8 @@
           <t>Maltais</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -4221,10 +4354,15 @@
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>Lavoie (JP)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr">
         <is>
           <t>Fils de Robert et Diane</t>
         </is>
@@ -4288,10 +4426,15 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Gagnon (immobilier)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>immobilier</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>Mère de Sylvie Gagnon</t>
         </is>
@@ -4358,7 +4501,8 @@
           <t>Otis</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -4429,7 +4573,8 @@
           <t>Paradis</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>Locataire de Sylvie Gagnon</t>
         </is>
@@ -4500,7 +4645,8 @@
           <t>Bérubé</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="inlineStr">
         <is>
           <t>Fils de Lucie Bérubé — frère de Kevin</t>
         </is>
@@ -4568,10 +4714,15 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Tremblay (Johanne)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>Johanne</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>Conjointe de Sylvain Gagné</t>
         </is>
@@ -4638,7 +4789,8 @@
           <t>Langlois</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="inlineStr">
         <is>
           <t>Épouse de Steve Langlois</t>
         </is>
@@ -4705,7 +4857,8 @@
           <t>Martel</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -4772,7 +4925,8 @@
           <t>Fortin</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="inlineStr">
         <is>
           <t>Nièce d’Yves et Pauline Fortin</t>
         </is>
@@ -4839,7 +4993,8 @@
           <t>Al-Hassan</t>
         </is>
       </c>
-      <c r="O62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="n"/>
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>Époux de Fatima Al-Hassan</t>
         </is>
@@ -4910,7 +5065,8 @@
           <t>Desrosiers-Simard</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="inlineStr">
         <is>
           <t>Cousine d’Anik Desrosiers</t>
         </is>
@@ -4978,10 +5134,15 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Gagnon (motards)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>motards</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>Fille de Thérèse Gagnon — sœur de Rock</t>
         </is>
@@ -5052,7 +5213,8 @@
           <t>Bérubé</t>
         </is>
       </c>
-      <c r="O65" s="5" t="inlineStr">
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="inlineStr">
         <is>
           <t>Fils de Lucie Bérubé — frère de Jessy</t>
         </is>
@@ -5119,7 +5281,8 @@
           <t>Boudreault</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -5183,10 +5346,15 @@
       </c>
       <c r="N67" s="5" t="inlineStr">
         <is>
-          <t>Tremblay (Gratien)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>Gratien</t>
+        </is>
+      </c>
+      <c r="P67" s="5" t="inlineStr">
         <is>
           <t>Conjointe de Gratien Tremblay</t>
         </is>
@@ -5253,7 +5421,8 @@
           <t>Blackburn</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr">
+      <c r="O68" s="2" t="n"/>
+      <c r="P68" s="2" t="inlineStr">
         <is>
           <t>Collègue de Ginette Roy</t>
         </is>
@@ -5320,7 +5489,8 @@
           <t>Girard</t>
         </is>
       </c>
-      <c r="O69" s="5" t="inlineStr">
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="inlineStr">
         <is>
           <t>Époux d’Anne Girard</t>
         </is>
@@ -5388,10 +5558,15 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Villeneuve (ciel)</t>
+          <t>Villeneuve</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>ciel</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
         <is>
           <t>Célibataire — croise William McKenzie</t>
         </is>
@@ -5458,7 +5633,8 @@
           <t>Bérubé</t>
         </is>
       </c>
-      <c r="O71" s="5" t="inlineStr">
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="inlineStr">
         <is>
           <t>Mère de Kevin, Jessy et tante de Big Jo</t>
         </is>
@@ -5522,10 +5698,15 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Côté (Victoria)</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
         <is>
           <t>Épouse de Fernand Côté</t>
         </is>
@@ -5596,7 +5777,8 @@
           <t>Lacroix</t>
         </is>
       </c>
-      <c r="O73" s="5" t="inlineStr">
+      <c r="O73" s="5" t="n"/>
+      <c r="P73" s="5" t="inlineStr">
         <is>
           <t>Frère de Thérèse</t>
         </is>
@@ -5660,10 +5842,15 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Pelletier (bar)</t>
+          <t>Pelletier</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
         <is>
           <t>Fille d’Hugo et Sarah Pelletier</t>
         </is>
@@ -5734,7 +5921,8 @@
           <t>Cloutier</t>
         </is>
       </c>
-      <c r="O75" s="5" t="inlineStr">
+      <c r="O75" s="5" t="n"/>
+      <c r="P75" s="5" t="inlineStr">
         <is>
           <t>Fils de Manon Cloutier — petit frère de Dave</t>
         </is>
@@ -5801,7 +5989,8 @@
           <t>Cloutier</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
+      <c r="O76" s="2" t="n"/>
+      <c r="P76" s="2" t="inlineStr">
         <is>
           <t>Mère de Dave Cloutier</t>
         </is>
@@ -5865,10 +6054,15 @@
       </c>
       <c r="N77" s="5" t="inlineStr">
         <is>
-          <t>Tremblay (Gratien)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
+        <is>
+          <t>Gratien</t>
+        </is>
+      </c>
+      <c r="P77" s="5" t="inlineStr">
         <is>
           <t>Mère de Cindy Lavoie</t>
         </is>
@@ -5936,10 +6130,15 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Gagnon (motards)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>motards</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>Bras droit de Karine Gagnon</t>
         </is>
@@ -6010,7 +6209,8 @@
           <t>Desrosiers-Simard</t>
         </is>
       </c>
-      <c r="O79" s="5" t="inlineStr">
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="5" t="inlineStr">
         <is>
           <t>Conjoint d’Anik Desrosiers</t>
         </is>
@@ -6078,10 +6278,15 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Bouchard (ruelle)</t>
+          <t>Bouchard</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>ruelle</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
         <is>
           <t>Célibataire — Dévon lui doit</t>
         </is>
@@ -6149,10 +6354,15 @@
       </c>
       <c r="N81" s="5" t="inlineStr">
         <is>
-          <t>Lapointe (Marco)</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="O81" s="5" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="P81" s="5" t="inlineStr">
         <is>
           <t>Fils de Gérard et Monique</t>
         </is>
@@ -6223,7 +6433,8 @@
           <t>Brassard</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr">
+      <c r="O82" s="2" t="n"/>
+      <c r="P82" s="2" t="inlineStr">
         <is>
           <t>Épouse d’Émile Brassard</t>
         </is>
@@ -6287,10 +6498,15 @@
       </c>
       <c r="N83" s="5" t="inlineStr">
         <is>
-          <t>Lavoie (école)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O83" s="5" t="inlineStr">
+        <is>
+          <t>école</t>
+        </is>
+      </c>
+      <c r="P83" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -6357,7 +6573,8 @@
           <t>Boivin</t>
         </is>
       </c>
-      <c r="O84" s="2" t="inlineStr">
+      <c r="O84" s="2" t="n"/>
+      <c r="P84" s="2" t="inlineStr">
         <is>
           <t>Célibataire — véto du quartier</t>
         </is>
@@ -6425,10 +6642,15 @@
       </c>
       <c r="N85" s="5" t="inlineStr">
         <is>
-          <t>Lavoie (Michel)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O85" s="5" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="P85" s="5" t="inlineStr">
         <is>
           <t>Fils de Claude</t>
         </is>
@@ -6499,7 +6721,8 @@
           <t>Joseph</t>
         </is>
       </c>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="O86" s="2" t="n"/>
+      <c r="P86" s="2" t="inlineStr">
         <is>
           <t>Mère de Samuel</t>
         </is>
@@ -6563,10 +6786,15 @@
       </c>
       <c r="N87" s="5" t="inlineStr">
         <is>
-          <t>Lapointe (Marco)</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="O87" s="5" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="P87" s="5" t="inlineStr">
         <is>
           <t>Mère de Marco</t>
         </is>
@@ -6637,7 +6865,8 @@
           <t>Dubé</t>
         </is>
       </c>
-      <c r="O88" s="2" t="inlineStr">
+      <c r="O88" s="2" t="n"/>
+      <c r="P88" s="2" t="inlineStr">
         <is>
           <t>Sœur de Carl</t>
         </is>
@@ -6704,7 +6933,8 @@
           <t>Benali</t>
         </is>
       </c>
-      <c r="O89" s="5" t="inlineStr">
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="inlineStr">
         <is>
           <t>Épouse d’Ahmed Benali</t>
         </is>
@@ -6771,7 +7001,8 @@
           <t>Dubois</t>
         </is>
       </c>
-      <c r="O90" s="2" t="inlineStr">
+      <c r="O90" s="2" t="n"/>
+      <c r="P90" s="2" t="inlineStr">
         <is>
           <t>Sœur de Patrice Dubois</t>
         </is>
@@ -6838,7 +7069,8 @@
           <t>Vollant</t>
         </is>
       </c>
-      <c r="O91" s="5" t="inlineStr">
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -6902,10 +7134,15 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Bouchard (Chloé)</t>
+          <t>Bouchard</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Chloé</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
         <is>
           <t>Mère de Chloé Bouchard</t>
         </is>
@@ -6976,7 +7213,8 @@
           <t>Boucher</t>
         </is>
       </c>
-      <c r="O93" s="5" t="inlineStr">
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="inlineStr">
         <is>
           <t>Cousin de Dévon et Éric Boucher</t>
         </is>
@@ -7043,7 +7281,8 @@
           <t>Benali</t>
         </is>
       </c>
-      <c r="O94" s="2" t="inlineStr">
+      <c r="O94" s="2" t="n"/>
+      <c r="P94" s="2" t="inlineStr">
         <is>
           <t>Fille d’Ahmed et Nadia Benali — sœur d’Hassan</t>
         </is>
@@ -7114,7 +7353,8 @@
           <t>Dubois</t>
         </is>
       </c>
-      <c r="O95" s="5" t="inlineStr">
+      <c r="O95" s="5" t="n"/>
+      <c r="P95" s="5" t="inlineStr">
         <is>
           <t>Frère de Nancy</t>
         </is>
@@ -7181,7 +7421,8 @@
           <t>Desbiens</t>
         </is>
       </c>
-      <c r="O96" s="2" t="inlineStr">
+      <c r="O96" s="2" t="n"/>
+      <c r="P96" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -7248,7 +7489,8 @@
           <t>Fortin</t>
         </is>
       </c>
-      <c r="O97" s="5" t="inlineStr">
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="inlineStr">
         <is>
           <t>Épouse d’Yves Fortin</t>
         </is>
@@ -7316,10 +7558,15 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Villeneuve (hôpital)</t>
+          <t>Villeneuve</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>hôpital</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -7386,7 +7633,8 @@
           <t>Desrosiers-Simard</t>
         </is>
       </c>
-      <c r="O99" s="5" t="inlineStr">
+      <c r="O99" s="5" t="n"/>
+      <c r="P99" s="5" t="inlineStr">
         <is>
           <t>Mère de Marc-André Simard</t>
         </is>
@@ -7450,10 +7698,15 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Lapointe (Marco)</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
         <is>
           <t>Chat du 427 Victoria</t>
         </is>
@@ -7521,10 +7774,15 @@
       </c>
       <c r="N101" s="5" t="inlineStr">
         <is>
-          <t>Gagnon (complot)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O101" s="5" t="inlineStr">
+        <is>
+          <t>complot</t>
+        </is>
+      </c>
+      <c r="P101" s="5" t="inlineStr">
         <is>
           <t>Célibataire — écoute Alex Tremblay</t>
         </is>
@@ -7592,10 +7850,15 @@
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Villeneuve (bus)</t>
+          <t>Villeneuve</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -7666,7 +7929,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O103" s="5" t="inlineStr">
+      <c r="O103" s="5" t="n"/>
+      <c r="P103" s="5" t="inlineStr">
         <is>
           <t>Travaille pour Tony — croise Big Jo</t>
         </is>
@@ -7734,10 +7998,15 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Lavoie (JP)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
         <is>
           <t>Père de JP</t>
         </is>
@@ -7805,10 +8074,15 @@
       </c>
       <c r="N105" s="5" t="inlineStr">
         <is>
-          <t>Côté (port)</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O105" s="5" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="P105" s="5" t="inlineStr">
         <is>
           <t>Filleul de Fernand Côté</t>
         </is>
@@ -7876,10 +8150,15 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Gagnon (motards)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>motards</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
         <is>
           <t>Fils de Thérèse Gagnon — frère de Karine</t>
         </is>
@@ -7946,7 +8225,8 @@
           <t>Bontemps</t>
         </is>
       </c>
-      <c r="O107" s="5" t="inlineStr">
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="inlineStr">
         <is>
           <t>Époux de Valette</t>
         </is>
@@ -8017,7 +8297,8 @@
           <t>Chicoine</t>
         </is>
       </c>
-      <c r="O108" s="2" t="inlineStr">
+      <c r="O108" s="2" t="n"/>
+      <c r="P108" s="2" t="inlineStr">
         <is>
           <t>Fils d’Hélène</t>
         </is>
@@ -8088,7 +8369,8 @@
           <t>Pedneault</t>
         </is>
       </c>
-      <c r="O109" s="5" t="inlineStr">
+      <c r="O109" s="5" t="n"/>
+      <c r="P109" s="5" t="inlineStr">
         <is>
           <t>Époux de Céline Pedneault</t>
         </is>
@@ -8159,7 +8441,8 @@
           <t>Roy</t>
         </is>
       </c>
-      <c r="O110" s="2" t="inlineStr">
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="2" t="inlineStr">
         <is>
           <t>Mari de Ginette Roy</t>
         </is>
@@ -8230,7 +8513,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O111" s="5" t="inlineStr">
+      <c r="O111" s="5" t="n"/>
+      <c r="P111" s="5" t="inlineStr">
         <is>
           <t>Relais portuaire — croise Yvan Truchon</t>
         </is>
@@ -8301,7 +8585,8 @@
           <t>Joseph</t>
         </is>
       </c>
-      <c r="O112" s="2" t="inlineStr">
+      <c r="O112" s="2" t="n"/>
+      <c r="P112" s="2" t="inlineStr">
         <is>
           <t>Fils de Mireille Joseph</t>
         </is>
@@ -8365,10 +8650,15 @@
       </c>
       <c r="N113" s="5" t="inlineStr">
         <is>
-          <t>Pelletier (bar)</t>
+          <t>Pelletier</t>
         </is>
       </c>
       <c r="O113" s="5" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="P113" s="5" t="inlineStr">
         <is>
           <t>Épouse d’Hugo Pelletier</t>
         </is>
@@ -8439,7 +8729,8 @@
           <t>Potvin</t>
         </is>
       </c>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="O114" s="2" t="n"/>
+      <c r="P114" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -8507,10 +8798,15 @@
       </c>
       <c r="N115" s="5" t="inlineStr">
         <is>
-          <t>Bouchard (couronne)</t>
+          <t>Bouchard</t>
         </is>
       </c>
       <c r="O115" s="5" t="inlineStr">
+        <is>
+          <t>couronne</t>
+        </is>
+      </c>
+      <c r="P115" s="5" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -8574,10 +8870,15 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Tremblay (Alex)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
         <is>
           <t>Mère d’Alex Tremblay</t>
         </is>
@@ -8645,10 +8946,15 @@
       </c>
       <c r="N117" s="5" t="inlineStr">
         <is>
-          <t>Gauthier (casse)</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="O117" s="5" t="inlineStr">
+        <is>
+          <t>casse</t>
+        </is>
+      </c>
+      <c r="P117" s="5" t="inlineStr">
         <is>
           <t>Célibataire — fournit Bobby</t>
         </is>
@@ -8719,7 +9025,8 @@
           <t>Langlois</t>
         </is>
       </c>
-      <c r="O118" s="2" t="inlineStr">
+      <c r="O118" s="2" t="n"/>
+      <c r="P118" s="2" t="inlineStr">
         <is>
           <t>Époux de Josée</t>
         </is>
@@ -8787,10 +9094,15 @@
       </c>
       <c r="N119" s="5" t="inlineStr">
         <is>
-          <t>Lapointe (Marco)</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="O119" s="5" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="P119" s="5" t="inlineStr">
         <is>
           <t>Sœur de Marco</t>
         </is>
@@ -8858,10 +9170,15 @@
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Bouchard (hockey)</t>
+          <t>Bouchard</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -8925,10 +9242,15 @@
       </c>
       <c r="N121" s="5" t="inlineStr">
         <is>
-          <t>Tremblay (Johanne)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O121" s="5" t="inlineStr">
+        <is>
+          <t>Johanne</t>
+        </is>
+      </c>
+      <c r="P121" s="5" t="inlineStr">
         <is>
           <t>Conjoint de Johanne Tremblay</t>
         </is>
@@ -8996,10 +9318,15 @@
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Gagnon (immobilier)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>immobilier</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
         <is>
           <t>Fille de Jeanne Gagnon — ex-épouse de Bertrand</t>
         </is>
@@ -9067,10 +9394,15 @@
       </c>
       <c r="N123" s="5" t="inlineStr">
         <is>
-          <t>Gagnon (motards)</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O123" s="5" t="inlineStr">
+        <is>
+          <t>motards</t>
+        </is>
+      </c>
+      <c r="P123" s="5" t="inlineStr">
         <is>
           <t>Mère de Karine et Rock Gagnon</t>
         </is>
@@ -9137,7 +9469,8 @@
           <t>Lacroix</t>
         </is>
       </c>
-      <c r="O124" s="2" t="inlineStr">
+      <c r="O124" s="2" t="n"/>
+      <c r="P124" s="2" t="inlineStr">
         <is>
           <t>Sœur de Lucien Lacroix</t>
         </is>
@@ -9205,10 +9538,15 @@
       </c>
       <c r="N125" s="5" t="inlineStr">
         <is>
-          <t>Côté (ruelle)</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O125" s="5" t="inlineStr">
+        <is>
+          <t>ruelle</t>
+        </is>
+      </c>
+      <c r="P125" s="5" t="inlineStr">
         <is>
           <t>Célibataire — copain de Réal Chicoine</t>
         </is>
@@ -9275,7 +9613,8 @@
           <t>Fortin</t>
         </is>
       </c>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="O126" s="2" t="n"/>
+      <c r="P126" s="2" t="inlineStr">
         <is>
           <t>Fils d’Yves et Pauline Fortin</t>
         </is>
@@ -9346,7 +9685,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O127" s="5" t="inlineStr">
+      <c r="O127" s="5" t="n"/>
+      <c r="P127" s="5" t="inlineStr">
         <is>
           <t>Neveu de Vittorio — parle à Bobby Gagnon</t>
         </is>
@@ -9413,7 +9753,8 @@
           <t>Bontemps</t>
         </is>
       </c>
-      <c r="O128" s="2" t="inlineStr">
+      <c r="O128" s="2" t="n"/>
+      <c r="P128" s="2" t="inlineStr">
         <is>
           <t>Épouse de Roger</t>
         </is>
@@ -9481,10 +9822,15 @@
       </c>
       <c r="N129" s="5" t="inlineStr">
         <is>
-          <t>Côté (CPE)</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O129" s="5" t="inlineStr">
+        <is>
+          <t>CPE</t>
+        </is>
+      </c>
+      <c r="P129" s="5" t="inlineStr">
         <is>
           <t>Collègue de Mélanie Dubé</t>
         </is>
@@ -9555,7 +9901,8 @@
           <t>McKenzie</t>
         </is>
       </c>
-      <c r="O130" s="2" t="inlineStr">
+      <c r="O130" s="2" t="n"/>
+      <c r="P130" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -9622,7 +9969,8 @@
           <t>Couture</t>
         </is>
       </c>
-      <c r="O131" s="5" t="inlineStr">
+      <c r="O131" s="5" t="n"/>
+      <c r="P131" s="5" t="inlineStr">
         <is>
           <t>Célibataire — joue au bingo de Michel</t>
         </is>
@@ -9693,7 +10041,8 @@
           <t>Truchon</t>
         </is>
       </c>
-      <c r="O132" s="2" t="inlineStr">
+      <c r="O132" s="2" t="n"/>
+      <c r="P132" s="2" t="inlineStr">
         <is>
           <t>Fils de Cécile Truchon — conjoint de Gisèle</t>
         </is>
@@ -9760,7 +10109,8 @@
           <t>Fortin</t>
         </is>
       </c>
-      <c r="O133" s="5" t="inlineStr">
+      <c r="O133" s="5" t="n"/>
+      <c r="P133" s="5" t="inlineStr">
         <is>
           <t>Époux de Pauline Fortin</t>
         </is>
@@ -9827,7 +10177,8 @@
           <t>Martel</t>
         </is>
       </c>
-      <c r="O134" s="2" t="inlineStr">
+      <c r="O134" s="2" t="n"/>
+      <c r="P134" s="2" t="inlineStr">
         <is>
           <t>Cousine de Julie et Amélie Martel</t>
         </is>
@@ -9894,7 +10245,8 @@
           <t>Brassard</t>
         </is>
       </c>
-      <c r="O135" s="5" t="inlineStr">
+      <c r="O135" s="5" t="n"/>
+      <c r="P135" s="5" t="inlineStr">
         <is>
           <t>Époux de Marie-Claude Brassard</t>
         </is>
@@ -9961,7 +10313,8 @@
           <t>Gauthier</t>
         </is>
       </c>
-      <c r="O136" s="2" t="inlineStr">
+      <c r="O136" s="2" t="n"/>
+      <c r="P136" s="2" t="inlineStr">
         <is>
           <t>Supérieure de Stéphanie Lapointe</t>
         </is>
@@ -10032,7 +10385,8 @@
           <t>Boucher</t>
         </is>
       </c>
-      <c r="O137" s="5" t="inlineStr">
+      <c r="O137" s="5" t="n"/>
+      <c r="P137" s="5" t="inlineStr">
         <is>
           <t>Fils de Fernande — frère de Dévon</t>
         </is>
@@ -10096,10 +10450,15 @@
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>Dufour (hôtel de ville)</t>
+          <t>Dufour</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>hôtel de ville</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
         <is>
           <t>Père du maire Gilles Dufour</t>
         </is>
@@ -10167,10 +10526,15 @@
       </c>
       <c r="N139" s="5" t="inlineStr">
         <is>
-          <t>Simard (police)</t>
+          <t>Simard</t>
         </is>
       </c>
       <c r="O139" s="5" t="inlineStr">
+        <is>
+          <t>police</t>
+        </is>
+      </c>
+      <c r="P139" s="5" t="inlineStr">
         <is>
           <t>Supérieur de Pierre Samson</t>
         </is>
@@ -10237,7 +10601,8 @@
           <t>Otis</t>
         </is>
       </c>
-      <c r="O140" s="2" t="inlineStr">
+      <c r="O140" s="2" t="n"/>
+      <c r="P140" s="2" t="inlineStr">
         <is>
           <t>Nièce de Jeanne Otis</t>
         </is>
@@ -10304,7 +10669,8 @@
           <t>Samson</t>
         </is>
       </c>
-      <c r="O141" s="5" t="inlineStr">
+      <c r="O141" s="5" t="n"/>
+      <c r="P141" s="5" t="inlineStr">
         <is>
           <t>Épouse de Pierre Samson</t>
         </is>
@@ -10375,7 +10741,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O142" s="2" t="inlineStr">
+      <c r="O142" s="2" t="n"/>
+      <c r="P142" s="2" t="inlineStr">
         <is>
           <t>Façade du clan — croise Lady Dynamite</t>
         </is>
@@ -10446,7 +10813,8 @@
           <t>Pedneault</t>
         </is>
       </c>
-      <c r="O143" s="5" t="inlineStr">
+      <c r="O143" s="5" t="n"/>
+      <c r="P143" s="5" t="inlineStr">
         <is>
           <t>Cousin de Réjean Pedneault</t>
         </is>
@@ -10517,7 +10885,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O144" s="2" t="inlineStr">
+      <c r="O144" s="2" t="n"/>
+      <c r="P144" s="2" t="inlineStr">
         <is>
           <t>Conseiller de Vittorio</t>
         </is>
@@ -10581,10 +10950,15 @@
       </c>
       <c r="N145" s="5" t="inlineStr">
         <is>
-          <t>Côté (presse)</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O145" s="5" t="inlineStr">
+        <is>
+          <t>presse</t>
+        </is>
+      </c>
+      <c r="P145" s="5" t="inlineStr">
         <is>
           <t>Patron d’Olivier Savard — ex-patron de JP</t>
         </is>
@@ -10652,10 +11026,15 @@
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>Dufour (hôtel de ville)</t>
+          <t>Dufour</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>hôtel de ville</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
         <is>
           <t>Fils d’Albert Dufour — maire de Saguenay</t>
         </is>
@@ -10722,7 +11101,8 @@
           <t>Samson</t>
         </is>
       </c>
-      <c r="O147" s="5" t="inlineStr">
+      <c r="O147" s="5" t="n"/>
+      <c r="P147" s="5" t="inlineStr">
         <is>
           <t>Mère de Pierre Samson</t>
         </is>
@@ -10786,10 +11166,15 @@
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Gagné (politique)</t>
+          <t>Gagné</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>politique</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
         <is>
           <t>Célibataire</t>
         </is>
@@ -10857,10 +11242,15 @@
       </c>
       <c r="N149" s="5" t="inlineStr">
         <is>
-          <t>Roy (arnaque)</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="O149" s="5" t="inlineStr">
+        <is>
+          <t>arnaque</t>
+        </is>
+      </c>
+      <c r="P149" s="5" t="inlineStr">
         <is>
           <t>Célibataire — croise Alex Tremblay</t>
         </is>
@@ -10931,7 +11321,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O150" s="2" t="inlineStr">
+      <c r="O150" s="2" t="n"/>
+      <c r="P150" s="2" t="inlineStr">
         <is>
           <t>Chauffeur de Vittorio</t>
         </is>
@@ -11002,7 +11393,8 @@
           <t>Chen</t>
         </is>
       </c>
-      <c r="O151" s="5" t="inlineStr">
+      <c r="O151" s="5" t="n"/>
+      <c r="P151" s="5" t="inlineStr">
         <is>
           <t>Fils de Mei</t>
         </is>
@@ -11066,10 +11458,15 @@
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>Lavoie (JP)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
         <is>
           <t>Sœur de JP</t>
         </is>
@@ -11133,10 +11530,15 @@
       </c>
       <c r="N153" s="5" t="inlineStr">
         <is>
-          <t>Villeneuve (palais)</t>
+          <t>Villeneuve</t>
         </is>
       </c>
       <c r="O153" s="5" t="inlineStr">
+        <is>
+          <t>palais</t>
+        </is>
+      </c>
+      <c r="P153" s="5" t="inlineStr">
         <is>
           <t>Collègue de Catherine Samson</t>
         </is>
@@ -11207,7 +11609,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O154" s="2" t="inlineStr">
+      <c r="O154" s="2" t="n"/>
+      <c r="P154" s="2" t="inlineStr">
         <is>
           <t>Épouse de Vittorio</t>
         </is>
@@ -11274,7 +11677,8 @@
           <t>Chen</t>
         </is>
       </c>
-      <c r="O155" s="5" t="inlineStr">
+      <c r="O155" s="5" t="n"/>
+      <c r="P155" s="5" t="inlineStr">
         <is>
           <t>Mère de Justin Chen</t>
         </is>
@@ -11342,10 +11746,15 @@
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Tremblay (Église)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
         <is>
           <t>Supérieur de Lucien Lacroix</t>
         </is>
@@ -11416,7 +11825,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O157" s="5" t="inlineStr">
+      <c r="O157" s="5" t="n"/>
+      <c r="P157" s="5" t="inlineStr">
         <is>
           <t>Fils de Vittorio et Maria</t>
         </is>
@@ -11483,7 +11893,8 @@
           <t>Savard</t>
         </is>
       </c>
-      <c r="O158" s="2" t="inlineStr">
+      <c r="O158" s="2" t="n"/>
+      <c r="P158" s="2" t="inlineStr">
         <is>
           <t>Célibataire — ex-collègue de JP</t>
         </is>
@@ -11551,10 +11962,15 @@
       </c>
       <c r="N159" s="5" t="inlineStr">
         <is>
-          <t>Lapointe (Marco)</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="O159" s="5" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="P159" s="5" t="inlineStr">
         <is>
           <t>Frère de Marco</t>
         </is>
@@ -11625,7 +12041,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O160" s="2" t="inlineStr">
+      <c r="O160" s="2" t="n"/>
+      <c r="P160" s="2" t="inlineStr">
         <is>
           <t>Comptable du clan — croise Bertrand Gagnon</t>
         </is>
@@ -11696,7 +12113,8 @@
           <t>Samson</t>
         </is>
       </c>
-      <c r="O161" s="5" t="inlineStr">
+      <c r="O161" s="5" t="n"/>
+      <c r="P161" s="5" t="inlineStr">
         <is>
           <t>Fils d’Hélène Samson — époux de Catherine</t>
         </is>
@@ -11763,7 +12181,8 @@
           <t>Labbé</t>
         </is>
       </c>
-      <c r="O162" s="2" t="inlineStr">
+      <c r="O162" s="2" t="n"/>
+      <c r="P162" s="2" t="inlineStr">
         <is>
           <t>Célibataire — collègue de Laurie Lavoie</t>
         </is>
@@ -11834,7 +12253,8 @@
           <t>Santini</t>
         </is>
       </c>
-      <c r="O163" s="5" t="inlineStr">
+      <c r="O163" s="5" t="n"/>
+      <c r="P163" s="5" t="inlineStr">
         <is>
           <t>Époux de Maria — tient Dévon à distance</t>
         </is>
@@ -11905,7 +12325,8 @@
           <t>Chen</t>
         </is>
       </c>
-      <c r="O164" s="2" t="inlineStr">
+      <c r="O164" s="2" t="n"/>
+      <c r="P164" s="2" t="inlineStr">
         <is>
           <t>Colocataire de Justin Chen</t>
         </is>
@@ -11976,7 +12397,8 @@
           <t>Lefèvre</t>
         </is>
       </c>
-      <c r="O165" s="5" t="inlineStr">
+      <c r="O165" s="5" t="n"/>
+      <c r="P165" s="5" t="inlineStr">
         <is>
           <t>Frère de Camille</t>
         </is>
@@ -12043,7 +12465,8 @@
           <t>Larouche</t>
         </is>
       </c>
-      <c r="O166" s="2" t="inlineStr">
+      <c r="O166" s="2" t="n"/>
+      <c r="P166" s="2" t="inlineStr">
         <is>
           <t>Prof d’Antoine Lefèvre</t>
         </is>
@@ -12110,7 +12533,8 @@
           <t>Lefèvre</t>
         </is>
       </c>
-      <c r="O167" s="5" t="inlineStr">
+      <c r="O167" s="5" t="n"/>
+      <c r="P167" s="5" t="inlineStr">
         <is>
           <t>Sœur d’Antoine Lefèvre</t>
         </is>
@@ -12177,7 +12601,8 @@
           <t>Aubin</t>
         </is>
       </c>
-      <c r="O168" s="2" t="inlineStr">
+      <c r="O168" s="2" t="n"/>
+      <c r="P168" s="2" t="inlineStr">
         <is>
           <t>Frère de Sam Aubin</t>
         </is>
@@ -12245,10 +12670,15 @@
       </c>
       <c r="N169" s="5" t="inlineStr">
         <is>
-          <t>Tremblay (syndicat)</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O169" s="5" t="inlineStr">
+        <is>
+          <t>syndicat</t>
+        </is>
+      </c>
+      <c r="P169" s="5" t="inlineStr">
         <is>
           <t>Collègue de Mathieu Lavoie</t>
         </is>
@@ -12312,10 +12742,15 @@
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>Fortin (industrie)</t>
+          <t>Fortin</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>industrie</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
         <is>
           <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
         </is>
@@ -12383,10 +12818,15 @@
       </c>
       <c r="N171" s="5" t="inlineStr">
         <is>
-          <t>Lavoie (JP)</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O171" s="5" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="P171" s="5" t="inlineStr">
         <is>
           <t>Frère aîné de JP</t>
         </is>
@@ -12453,7 +12893,8 @@
           <t>Harvey</t>
         </is>
       </c>
-      <c r="O172" s="2" t="inlineStr">
+      <c r="O172" s="2" t="n"/>
+      <c r="P172" s="2" t="inlineStr">
         <is>
           <t>Nièce de François Harvey</t>
         </is>
@@ -12517,10 +12958,15 @@
       </c>
       <c r="N173" s="5" t="inlineStr">
         <is>
-          <t>Gagné (Arvida)</t>
+          <t>Gagné</t>
         </is>
       </c>
       <c r="O173" s="5" t="inlineStr">
+        <is>
+          <t>Arvida</t>
+        </is>
+      </c>
+      <c r="P173" s="5" t="inlineStr">
         <is>
           <t>Collègue de Mathieu Lavoie</t>
         </is>
@@ -12591,14 +13037,15 @@
           <t>Aubin</t>
         </is>
       </c>
-      <c r="O174" s="2" t="inlineStr">
+      <c r="O174" s="2" t="n"/>
+      <c r="P174" s="2" t="inlineStr">
         <is>
           <t>Frère de Dany</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O174"/>
+  <autoFilter ref="A1:P174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12609,7 +13056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -12634,7 +13081,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>173 entrées · 15 colonnes · région du Saguenay (Québec)</t>
+          <t>173 entrées · 16 colonnes · région du Saguenay (Québec)</t>
         </is>
       </c>
     </row>
@@ -12685,7 +13132,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Vide = la personne n'en a pas. Ce n'est PAS un oubli : dans la base, l'absence de surnom signale un personnage « rangé » (famille, voisins, institutions), par opposition aux personnages de la marge qui en ont tous un.</t>
+          <t>Vide = la personne n’en a pas. Ce n’est PAS un oubli : dans la base, l’absence de surnom signale un personnage « rangé » (famille, voisins, institutions), par opposition aux personnages de la marge qui en ont tous un.</t>
         </is>
       </c>
     </row>
@@ -12702,7 +13149,7 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Humain | Animal. Permet de filtrer et d'appliquer des règles différentes (la colonne Vêtements ne se lit pas pareil pour un animal).</t>
+          <t>Humain | Animal. Permet de filtrer et d’appliquer des règles différentes (la colonne Vêtements ne se lit pas pareil pour un animal).</t>
         </is>
       </c>
     </row>
@@ -12736,7 +13183,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Métier ou occupation autonome. Format recommandé : « Métier — précision ». Ne doit référencer ni un autre personnage, ni un lieu de l'intrigue, ni une faction / un clan (ex. interdit : « — clan Santini ») : le clan va dans la colonne Famille, la faction dans la feuille Narration.</t>
+          <t>Métier ou occupation autonome. Format recommandé : « Métier — précision ». Ne doit référencer ni un autre personnage, ni un lieu de l’intrigue, ni une faction / un clan (ex. interdit : « — clan Santini ») : le clan va dans la colonne Famille, la faction dans la source Narration.</t>
         </is>
       </c>
     </row>
@@ -12770,7 +13217,7 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Par défaut « Numéro, Rue » : les NUMÉROS SONT FICTIFS, les RUES sont réelles (extraites d'OpenStreetMap via l'API Overpass). Pour un lieu non adressable (plein air, sentier, base militaire), écrire « Lieu-dit : … » : ce préfixe signale volontairement l'absence de numéro civique.</t>
+          <t>Par défaut « Numéro, Rue » : les NUMÉROS SONT FICTIFS, les RUES sont réelles (extraites d’OpenStreetMap via l’API Overpass). Pour un lieu non adressable (plein air, sentier, base militaire), écrire « Lieu-dit : … » : ce préfixe signale volontairement l’absence de numéro civique.</t>
         </is>
       </c>
     </row>
@@ -12787,7 +13234,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>WGS84, 6 décimales. APPROXIMATIVE : centroïde réel de la rue + décalage déterministe de ±400 m. Précision au quartier, pas au bâtiment.</t>
+          <t>WGS84. APPROXIMATIVE : centroïde réel de la rue + décalage déterministe de ±400 m. Précision au quartier, pas au bâtiment.</t>
         </is>
       </c>
     </row>
@@ -12804,7 +13251,7 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>WGS84, 6 décimales. Même précision que Latitude.</t>
+          <t>WGS84. Même précision que Latitude.</t>
         </is>
       </c>
     </row>
@@ -12872,7 +13319,7 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Chemin relatif du WebP gabarit « -web » (~80 à 150 Ko). Vide = pas encore photographié. Deux gabarits par personnage dans portraits/ : -web.webp (le référencé ici) et -vignette.webp (400 px, utilisé par la carte et la planche contact). Découverts automatiquement par slug du nom. L’ancien gabarit « archive » (.webp sans suffixe) n’est référencé par rien : il ne doit pas être versionné (voir .gitignore). Toutes les vignettes sont assemblées dans portraits/planche-contact-generale.webp.</t>
+          <t>Chemin relatif du WebP gabarit « -web » (~80 à 150 Ko). Vide = pas encore illustré. Deux gabarits par personnage dans portraits/ : -web.webp (le référencé ici) et -vignette.webp (400 px, carte et planche contact). Découverts automatiquement par slug du nom. Toutes les vignettes sont assemblées dans portraits/planche-contact-generale.webp.</t>
         </is>
       </c>
     </row>
@@ -12889,120 +13336,179 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Nom du clan / foyer. Permet de grouper les proches sur la carte.</t>
+          <t>Nom du clan / foyer, SANS qualificatif : deux foyers homonymes (les Côté de la ruelle et ceux de la poste) se distinguent par la colonne Branche.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
+          <t>Branche</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Texte</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Précision au sein de la Famille : « JP », « ruelle », « motards », « hôtel de ville »… Vide = le foyer est seul de son nom. La paire Famille + Branche identifie un foyer de façon unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
           <t>Parenté</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Texte</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Lien familial explicite (père de, épouse de, etc.).</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Conventions générales</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>• Cellule VIDE  = information applicable mais absente, ou choix assumé (voir Surnom).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>• « s.o. »       = sans objet : la colonne ne s'applique pas à cette entrée (ex. Vêtements d'un animal).</t>
+          <t>• Cellule VIDE  = information applicable mais absente, ou choix assumé (voir Surnom).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>• Unicité        : la colonne Nom est la clé. Aucune entrée en double ; le surnom ne s’écrit JAMAIS dans Nom (il a sa colonne, sans « »).</t>
+          <t>• « s.o. »       = sans objet : la colonne ne s’applique pas à cette entrée (ex. Vêtements d’un animal).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>• Coordonnées    : WGS84. Fictives au bâtiment près — voir la précision dans la fiche Longitude.</t>
+          <t>• Unicité        : la colonne Nom est la clé. Aucune entrée en double ; le surnom ne s’écrit JAMAIS dans Nom (il a sa colonne, sans « »).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>• Adresses       : numéros inventés, rues réelles issues d'OpenStreetMap ; les lieux non adressables s’écrivent « Lieu-dit : … » (pas de numéro civique).</t>
+          <t>• Famille + Branche : la paire identifie un foyer. Deux foyers homonymes (Côté de la ruelle / Côté de la poste) partagent la Famille et se distinguent par la Branche.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>• Narration      : feuille séparée (Faction, Lien Spot, Quote joual, Arc S1), couverte à 100 % — mais jamais exportée dans les fichiers publics (json / geojson / carte).</t>
+          <t>• Coordonnées    : WGS84. Fictives au bâtiment près — voir la précision dans la fiche Longitude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>• Adresses       : numéros inventés, rues réelles issues d’OpenStreetMap ; les lieux non adressables s’écrivent « Lieu-dit : … » (pas de numéro civique).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>• Source         : data/personnages.csv est la source de vérité (texte, diffable). Ce classeur est un livrable régénéré par construire_base.py : ne pas l’éditer à la main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Narration</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>• Couverture      : 100 % des entrées (faction, lien au Spot, réplique, arc S1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>• Statut          : source PRIVÉE (data/narration.csv, non versionnée).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>• Ce classeur     : la narration est VOLONTAIREMENT ABSENTE — diffusion publique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>• Faction         : vocabulaire contrôlé de 17 valeurs (data/factions.txt) ; la nuance d’origine est conservée dans « Faction (détail) ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>• Jamais exportée : ni dans le CSV / JSON / GeoJSON publics, ni dans la carte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Provenance</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>• Rues et coordonnées  : OpenStreetMap (ODbL), via les API Overpass et Nominatim.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>• Vérifications locales : UQAC (bac en psychologie), Cégep de Jonquière — école ATM</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (cinéma et télévision), aluminerie Rio Tinto à Arvida, boulevard Talbot (Chicoutimi-Sud).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>• Vérifications locales : UQAC (bac en psychologie), Cégep de Jonquière — école ATM   (cinéma et télévision), aluminerie Rio Tinto à Arvida, boulevard Talbot (Chicoutimi-Sud).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>• Carte interactive    : Leaflet 1.9.4 (BSD-2), vendorié dans carte/vendor/ (le code de la carte fonctionne hors ligne ; seules les tuiles restent en ligne).</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>• Portraits            : images générées par IA ; fiction intégrale. Statut distinct dans LICENSE-DONNEES.md.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>• Généré le            : 2026-09-11 (date figée pour la reproductibilité)</t>
         </is>
@@ -13011,5816 +13517,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G174"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Surnom</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Faction</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Lien Spot</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Quote joual</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Arc S1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Age apparent</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>Jean-Philippe Lavoie</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>Sous-sol</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>Squatte chez Marco</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>Ferme ta gueule, JP. Tu respires trop fort.</t>
-        </is>
-      </c>
-      <c r="F2" s="18" t="inlineStr">
-        <is>
-          <t>Doit choisir entre rester ou partir chez Mélo</t>
-        </is>
-      </c>
-      <c r="G2" s="18" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>Marco Lapointe</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>Le Proprio du Spot</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>Sous-sol</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>Propriétaire 3½</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>Chut! Roger gratte!</t>
-        </is>
-      </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>Perd son bloc</t>
-        </is>
-      </c>
-      <c r="G3" s="19" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>Réal Chicoine</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Chicoine</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>Sous-sol</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>Meuble du Spot</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>Disparait</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Gratien Tremblay</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Crackhouse</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>Ruelle</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>Fournisseur</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>J'arrive, 5 min!</t>
-        </is>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>Se fait tasser</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Roger Bontemps</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n"/>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>1er étage</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Note tout</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>J'appelle la Ville!</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>Délateur</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>Valette Bontemps</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>1er étage</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>Méprise sous-sol</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>Ça sent la mort!</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>Alliance avec Sylvie</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>Pierre Samson</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>L'Enquêteur</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Loi</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>Enquête</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>On va jaser.</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>Veut Dévon</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>Chantal Lavoie</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>La Biche</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>Sous-sol</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Cherche divan</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>C'est à moi astheure!</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>Pète une coche</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Dévon Boucher</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Le Snake</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle d'en Face</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>Veut spot</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>Vous avez 24h.</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>Ultimatum</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>Kevin Bérubé</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>Ti-Boeuf</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>Ruelle d'en Face</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>Bras droit Dévon</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>Ouvre la porte!</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>Passe à l'acte</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Yvan Truchon</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>Cartoune</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle / Neutre</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>Fournit indiennes</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>J'ai du Next...</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>Source info</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>Pisse-Feu</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n"/>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>Sous-sol</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>Seul pas de dette</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>Miaou</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>Disparait = danger</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>Sylvie Gagnon</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>La Proprio</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Argent</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>Veut évincer</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>Ça fait 3 mois!</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>7 jours pour payer</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Ahmed Benali</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>Le Dépanneur</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>Neutre</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>Tout le monde lui doit 20$</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>Pas de crédit.</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>Footage</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>Mélanie Dubé</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>Mélo</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Propre</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>Ex JP</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>Si tu veux voir Léo, sois straight.</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>Offre divan clean</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>Dave Cloutier</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>Ti-Coune</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>Ruelle</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Livre pour Gratien</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>Yo j'ai ça!</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>Se fait pogner</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Ginette Roy</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Gigi</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>Connait Marco 10 ans</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>T'as-tu mangé?</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>Doit signaler</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>Steve Langlois</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>Le Plombier</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>1er étage</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>Dégât d'eau</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>C'est celle d'en bas qui coule!</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>Photo plafond</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>Anik Desrosiers</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>La Veilleuse</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Bloc d'en face</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>Voit tout</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>J'mêle pas de ça.</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>Témoignage clé</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>Antoine Lefèvre</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>Le Français</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>Art</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>Veut filmer Marco</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>C'est très raw.</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>Se fait voler caméra</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Johanne Tremblay</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Jo</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>Protège Gratien</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>C'est MON frère cave.</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>Passe côté Marco</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>Lucien Lacroix</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>Abbé Lacroix / Le Curé</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>Église</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>A baptisé Marco 1987</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>Ton père serait pas fier...</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>Offre sous-sol église</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>Michel Lavoie</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>Lady Dynamite</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>Bar du Coin / Louche</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>Loge Chantal</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>Les boules! B-12!</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>Levée fonds</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>Sam Aubin</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>Ink</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>Au-dessus Dépanneur / Louche</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>Entend via plancher</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>Je tatoue pas de face gratis.</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>Couvre tattoo Snake</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>Karine Gagnon</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>K-Town</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle / Louche</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>Dévon lui doit 3000$</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>La ruelle est à personne.</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>Back ou crisse Dévon</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>Justin Chen</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>Junior Westmount</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>Westmount / Louche naïf</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>Veut cred</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>J'ai 400 piasses!</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>Kidnapping gentil</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Mireille Joseph</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>Mamie Mireille</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Bloc d'à côté / Louche sage</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>A gardé Marco petit</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>Ils ont faim dans tête aussi.</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>Cache Ti-Coune</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>Alex Tremblay</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>Le Fantôme</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>3e étage / Louche numérique</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>Pirate caméra Marco</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>3,99$ par clip.</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>Preuve Roger vole courrier</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>Fatima Al-Hassan</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>Fatima Poutine</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Rue / Louche entrepreneure</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>Nourrit quartier</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>Pas d'argent, tu laves vaisselle.</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>QG neutre</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>Patrice Dubois</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>P'tit Pat</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>Bar du Coin / Louche</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>Refuse Ti-Boeuf</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>Dehors.</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>Garde corps Dynamite</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>Chloé Bouchard</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Chlo</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>2e étage / Louche numérique</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>Vole Wi-Fi Spot</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>C'est gratis.</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>Stream chicane viral</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>Gilles Bergeron</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>La Fouine</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>Sécurité / Louche ex-loi</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>Connait Samson jeune</t>
-        </is>
-      </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>J'ai tout vu.</t>
-        </is>
-      </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>Donne dossier Dévon</t>
-        </is>
-      </c>
-      <c r="G33" s="19" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>Robert Lavoie</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>Famille JP</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>Père JP</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>Arrange-toé.</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>Vient chercher JP</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>Diane Tremblay</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>Famille JP</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>Mère JP</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>T'as-tu mangé?</t>
-        </is>
-      </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>Menace débarquer</t>
-        </is>
-      </c>
-      <c r="G35" s="19" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>Mathieu Lavoie</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>Mat</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>Famille JP</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>Frère aîné</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>J't'ai déjà donné 500$.</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>Refuse aider</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>Laurie Lavoie</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>Famille JP</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>Petite soeur</t>
-        </is>
-      </c>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t>T'étais mon héros.</t>
-        </is>
-      </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>Amène Gigi</t>
-        </is>
-      </c>
-      <c r="G37" s="19" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>Gérard Lapointe</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>Gerry</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>Famille Marco</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>A laissé bloc</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>Regarde ce que vous avez fait!</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>CHSLD, guerre héritage</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>Monique Bouchard</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>Famille Marco</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>Mère Marco</t>
-        </is>
-      </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>Prie le petit Jésus.</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>Appelle Sylvie</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>Patrick Lapointe</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>Pat</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>Famille Marco</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>Veut vendre bloc</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>Réveille!</t>
-        </is>
-      </c>
-      <c r="F40" s="18" t="inlineStr">
-        <is>
-          <t>S'allie Sylvie</t>
-        </is>
-      </c>
-      <c r="G40" s="18" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>Stéphanie Lapointe</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>Steph</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>Famille Marco</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>Soeur Marco</t>
-        </is>
-      </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>Ça sent bizarre.</t>
-        </is>
-      </c>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>Veut chambre</t>
-        </is>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>Alain Côté</t>
-        </is>
-      </c>
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>Poste / Neutre</t>
-        </is>
-      </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>Passe au 427 chaque midi</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>J'livre le courrier, pas les secrets.</t>
-        </is>
-      </c>
-      <c r="F42" s="18" t="inlineStr">
-        <is>
-          <t>Voit Roger fouiller les boîtes</t>
-        </is>
-      </c>
-      <c r="G42" s="18" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>Alexis Côté</t>
-        </is>
-      </c>
-      <c r="B43" s="19" t="inlineStr">
-        <is>
-          <t>Ficelle</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="inlineStr">
-        <is>
-          <t>Ruelle</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>Fait les rez-de-chaussée du bloc</t>
-        </is>
-      </c>
-      <c r="E43" s="19" t="inlineStr">
-        <is>
-          <t>Une porte barrée, c’est juste une opinion.</t>
-        </is>
-      </c>
-      <c r="F43" s="19" t="inlineStr">
-        <is>
-          <t>Se fait acheter par Dévon puis dérape</t>
-        </is>
-      </c>
-      <c r="G43" s="19" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>Alexis Gagnon</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>Lex</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>Aréna / Neutre</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>Coéquipier d’Alexandre Lavoie</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>Lève la rondelle, pas tes patins.</t>
-        </is>
-      </c>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>Tente de sortir le Cadet de la rue</t>
-        </is>
-      </c>
-      <c r="G44" s="18" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>Aline Tremblay</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>Famille / Gratien</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>Mère de Gratien, clope au 3e</t>
-        </is>
-      </c>
-      <c r="E45" s="19" t="inlineStr">
-        <is>
-          <t>Mange donc, tu sens la fumée.</t>
-        </is>
-      </c>
-      <c r="F45" s="19" t="inlineStr">
-        <is>
-          <t>Coupe les vivres à son fils</t>
-        </is>
-      </c>
-      <c r="G45" s="19" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>Amina Traoré</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="n"/>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>Santé / Propre</t>
-        </is>
-      </c>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>Pharmacie du quartier, voit les ordonnances</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>Sans papier, j’vends rien, même à toi.</t>
-        </is>
-      </c>
-      <c r="F46" s="18" t="inlineStr">
-        <is>
-          <t>Repère les ordonnances détournées</t>
-        </is>
-      </c>
-      <c r="G46" s="18" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="19" t="inlineStr">
-        <is>
-          <t>Amélie Martel</t>
-        </is>
-      </c>
-      <c r="B47" s="19" t="n"/>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>Ville / Tourisme</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr">
-        <is>
-          <t>Vérifie les permis de location</t>
-        </is>
-      </c>
-      <c r="E47" s="19" t="inlineStr">
-        <is>
-          <t>L’image du fjord, c’est pas ça.</t>
-        </is>
-      </c>
-      <c r="F47" s="19" t="inlineStr">
-        <is>
-          <t>Ferme les locations illégales du bloc</t>
-        </is>
-      </c>
-      <c r="G47" s="19" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="18" t="inlineStr">
-        <is>
-          <t>Anne Girard</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="n"/>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>Santé / Propre</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>Soigne les dents du quartier</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>Qui s’est battu, cette fois ?</t>
-        </is>
-      </c>
-      <c r="F48" s="18" t="inlineStr">
-        <is>
-          <t>Constate les blessures de Lio</t>
-        </is>
-      </c>
-      <c r="G48" s="18" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>Armand Lacroix</t>
-        </is>
-      </c>
-      <c r="B49" s="19" t="n"/>
-      <c r="C49" s="19" t="inlineStr">
-        <is>
-          <t>Institutions</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>Neveu de Lucien, salon funéraire</t>
-        </is>
-      </c>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t>Une place, j’en garde toujours une.</t>
-        </is>
-      </c>
-      <c r="F49" s="19" t="inlineStr">
-        <is>
-          <t>Prépare la première chapelle ardente</t>
-        </is>
-      </c>
-      <c r="G49" s="19" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>Bernard Tremblay</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="inlineStr">
-        <is>
-          <t>Bunker</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle / Survivaliste</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>Vend des conserves à Dévon</t>
-        </is>
-      </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>Quand ça va péter, tu vas m’revoir.</t>
-        </is>
-      </c>
-      <c r="F50" s="18" t="inlineStr">
-        <is>
-          <t>Son abri sert de planque</t>
-        </is>
-      </c>
-      <c r="G50" s="18" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>Bertrand Gagnon</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="n"/>
-      <c r="C51" s="19" t="inlineStr">
-        <is>
-          <t>Argent</t>
-        </is>
-      </c>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>Ex-mari de Sylvie, connaît les baux</t>
-        </is>
-      </c>
-      <c r="E51" s="19" t="inlineStr">
-        <is>
-          <t>Le problème, c’est jamais la maison, c’est le monde.</t>
-        </is>
-      </c>
-      <c r="F51" s="19" t="inlineStr">
-        <is>
-          <t>Tente de racheter le bloc avec elle</t>
-        </is>
-      </c>
-      <c r="G51" s="19" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
-        <is>
-          <t>Big Jo Bérubé</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>Big Jo</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle d'en Face</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>Cousin de Kevin, travaille pour Dévon</t>
-        </is>
-      </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>Bouge pas. Bon chien.</t>
-        </is>
-      </c>
-      <c r="F52" s="18" t="inlineStr">
-        <is>
-          <t>Premier à frapper au Spot</t>
-        </is>
-      </c>
-      <c r="G52" s="18" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="19" t="inlineStr">
-        <is>
-          <t>Bobby Gagnon</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>La Pieuvre</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="inlineStr">
-        <is>
-          <t>Motards / Louche</t>
-        </is>
-      </c>
-      <c r="D53" s="19" t="inlineStr">
-        <is>
-          <t>Reçoit la marchandise volée</t>
-        </is>
-      </c>
-      <c r="E53" s="19" t="inlineStr">
-        <is>
-          <t>Ça tombe d'un camion, ça se ramasse.</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="inlineStr">
-        <is>
-          <t>Écoule le matériel piraté</t>
-        </is>
-      </c>
-      <c r="G53" s="19" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>Carl Dubé</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="n"/>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>Garage / Neutre</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>Frère de Mélo, tient le garage</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>Ton char est mort comme l'hiver.</t>
-        </is>
-      </c>
-      <c r="F54" s="18" t="inlineStr">
-        <is>
-          <t>Cache le véhicule volé du réseau</t>
-        </is>
-      </c>
-      <c r="G54" s="18" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>Chantal Gauthier</t>
-        </is>
-      </c>
-      <c r="B55" s="19" t="n"/>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>Commerce / Neutre</t>
-        </is>
-      </c>
-      <c r="D55" s="19" t="inlineStr">
-        <is>
-          <t>Voit tout le monde au Tim du coin</t>
-        </is>
-      </c>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t>Un double-double, pis tes histoires itou.</t>
-        </is>
-      </c>
-      <c r="F55" s="19" t="inlineStr">
-        <is>
-          <t>Refuse sa table à Dévon</t>
-        </is>
-      </c>
-      <c r="G55" s="19" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="18" t="inlineStr">
-        <is>
-          <t>Cindy Lavoie</t>
-        </is>
-      </c>
-      <c r="B56" s="18" t="inlineStr">
-        <is>
-          <t>Cin</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle</t>
-        </is>
-      </c>
-      <c r="D56" s="18" t="inlineStr">
-        <is>
-          <t>Estafette de Gratien, fille de Manon</t>
-        </is>
-      </c>
-      <c r="E56" s="18" t="inlineStr">
-        <is>
-          <t>J'livre, j'pose, j'me sauve.</t>
-        </is>
-      </c>
-      <c r="F56" s="18" t="inlineStr">
-        <is>
-          <t>Ouvre une liasse qui contient pas d’la dope</t>
-        </is>
-      </c>
-      <c r="G56" s="18" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="19" t="inlineStr">
-        <is>
-          <t>Claude Lavoie</t>
-        </is>
-      </c>
-      <c r="B57" s="19" t="n"/>
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>Média / Rang</t>
-        </is>
-      </c>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>Père de Michel, ex-animateur radio</t>
-        </is>
-      </c>
-      <c r="E57" s="19" t="inlineStr">
-        <is>
-          <t>En ondes, on dit la vraie vérité.</t>
-        </is>
-      </c>
-      <c r="F57" s="19" t="inlineStr">
-        <is>
-          <t>Reprend l’antenne avec Raymond</t>
-        </is>
-      </c>
-      <c r="G57" s="19" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="18" t="inlineStr">
-        <is>
-          <t>Corinne Noël</t>
-        </is>
-      </c>
-      <c r="B58" s="18" t="inlineStr">
-        <is>
-          <t>La Corneille</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle / Marge</t>
-        </is>
-      </c>
-      <c r="D58" s="18" t="inlineStr">
-        <is>
-          <t>Fournit Sam Aubin en motifs</t>
-        </is>
-      </c>
-      <c r="E58" s="18" t="inlineStr">
-        <is>
-          <t>La mort, ça se brosse, tu sais.</t>
-        </is>
-      </c>
-      <c r="F58" s="18" t="inlineStr">
-        <is>
-          <t>Fait disparaître un trophée gênant</t>
-        </is>
-      </c>
-      <c r="G58" s="18" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="19" t="inlineStr">
-        <is>
-          <t>Cécile Truchon</t>
-        </is>
-      </c>
-      <c r="B59" s="19" t="n"/>
-      <c r="C59" s="19" t="inlineStr">
-        <is>
-          <t>Famille / Truchon</t>
-        </is>
-      </c>
-      <c r="D59" s="19" t="inlineStr">
-        <is>
-          <t>Mère d’Yvan, garde la caisse</t>
-        </is>
-      </c>
-      <c r="E59" s="19" t="inlineStr">
-        <is>
-          <t>Mon fils est pas pire qu’un autre.</t>
-        </is>
-      </c>
-      <c r="F59" s="19" t="inlineStr">
-        <is>
-          <t>Décide de parler des cigarettes</t>
-        </is>
-      </c>
-      <c r="G59" s="19" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>Céline Pedneault</t>
-        </is>
-      </c>
-      <c r="B60" s="18" t="n"/>
-      <c r="C60" s="18" t="inlineStr">
-        <is>
-          <t>Port / Neutre</t>
-        </is>
-      </c>
-      <c r="D60" s="18" t="inlineStr">
-        <is>
-          <t>Répare les filets avec Réjean</t>
-        </is>
-      </c>
-      <c r="E60" s="18" t="inlineStr">
-        <is>
-          <t>Le fjord nous doit rien.</t>
-        </is>
-      </c>
-      <c r="F60" s="18" t="inlineStr">
-        <is>
-          <t>Trouve un ballot dans ses filets</t>
-        </is>
-      </c>
-      <c r="G60" s="18" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>Dominic Audet</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>Dom</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="inlineStr">
-        <is>
-          <t>Taxi / Neutre</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>Dépose tout le monde au Spot à 3 h</t>
-        </is>
-      </c>
-      <c r="E61" s="19" t="inlineStr">
-        <is>
-          <t>J’tourne pas la tête, j’tourne le coin.</t>
-        </is>
-      </c>
-      <c r="F61" s="19" t="inlineStr">
-        <is>
-          <t>Son carnet de courses accuse</t>
-        </is>
-      </c>
-      <c r="G61" s="19" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="18" t="inlineStr">
-        <is>
-          <t>Fernand Côté</t>
-        </is>
-      </c>
-      <c r="B62" s="18" t="inlineStr">
-        <is>
-          <t>Ti-Fern</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>Vieux bloc / Port</t>
-        </is>
-      </c>
-      <c r="D62" s="18" t="inlineStr">
-        <is>
-          <t>Voisin du Spot, ex-dockeur</t>
-        </is>
-      </c>
-      <c r="E62" s="18" t="inlineStr">
-        <is>
-          <t>Au quai, on parlait pas.</t>
-        </is>
-      </c>
-      <c r="F62" s="18" t="inlineStr">
-        <is>
-          <t>Reconnaît le conteneur de Sal</t>
-        </is>
-      </c>
-      <c r="G62" s="18" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="19" t="inlineStr">
-        <is>
-          <t>Fernande Boucher</t>
-        </is>
-      </c>
-      <c r="B63" s="19" t="inlineStr">
-        <is>
-          <t>Maman Snake</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="inlineStr">
-        <is>
-          <t>Ruelle d'en Face / Famille</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>Mère de Dévon et d’Éric</t>
-        </is>
-      </c>
-      <c r="E63" s="19" t="inlineStr">
-        <is>
-          <t>Mon gars est dur, mais c’t’un tendre.</t>
-        </is>
-      </c>
-      <c r="F63" s="19" t="inlineStr">
-        <is>
-          <t>Vient plaider pour son fils</t>
-        </is>
-      </c>
-      <c r="G63" s="19" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="18" t="inlineStr">
-        <is>
-          <t>France Boivin</t>
-        </is>
-      </c>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="18" t="inlineStr">
-        <is>
-          <t>Commerce / Neutre</t>
-        </is>
-      </c>
-      <c r="D64" s="18" t="inlineStr">
-        <is>
-          <t>Fleuriste, sœur de Maxime</t>
-        </is>
-      </c>
-      <c r="E64" s="18" t="inlineStr">
-        <is>
-          <t>Des fleurs, ça dit tout sans parler.</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>Prépare les couronnes anonymes</t>
-        </is>
-      </c>
-      <c r="G64" s="18" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="19" t="inlineStr">
-        <is>
-          <t>François Harvey</t>
-        </is>
-      </c>
-      <c r="B65" s="19" t="inlineStr">
-        <is>
-          <t>Ti-Hydro</t>
-        </is>
-      </c>
-      <c r="C65" s="19" t="inlineStr">
-        <is>
-          <t>Hydro / Syndicat</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>Oncle de Mélissa, monteur de ligne</t>
-        </is>
-      </c>
-      <c r="E65" s="19" t="inlineStr">
-        <is>
-          <t>L'hiver, la ligne décide.</t>
-        </is>
-      </c>
-      <c r="F65" s="19" t="inlineStr">
-        <is>
-          <t>Rétablit le courant après la descente</t>
-        </is>
-      </c>
-      <c r="G65" s="19" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="18" t="inlineStr">
-        <is>
-          <t>Frère Ézéchiel</t>
-        </is>
-      </c>
-      <c r="B66" s="18" t="inlineStr">
-        <is>
-          <t>Ézéchiel</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="inlineStr">
-        <is>
-          <t>Église / Marge</t>
-        </is>
-      </c>
-      <c r="D66" s="18" t="inlineStr">
-        <is>
-          <t>Harangue Lucien dans la rue</t>
-        </is>
-      </c>
-      <c r="E66" s="18" t="inlineStr">
-        <is>
-          <t>La fournaise vous attend, mes agnelets !</t>
-        </is>
-      </c>
-      <c r="F66" s="18" t="inlineStr">
-        <is>
-          <t>Prophétise l’incendie du bloc</t>
-        </is>
-      </c>
-      <c r="G66" s="18" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="19" t="inlineStr">
-        <is>
-          <t>Félix Otis</t>
-        </is>
-      </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>L’Homme-Fjord</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="inlineStr">
-        <is>
-          <t>Fjord / Neutre</t>
-        </is>
-      </c>
-      <c r="D67" s="19" t="inlineStr">
-        <is>
-          <t>Neveu de Jeanne Otis, nage en eau glacée</t>
-        </is>
-      </c>
-      <c r="E67" s="19" t="inlineStr">
-        <is>
-          <t>Quand l'eau m'ordonne, j'obéis.</t>
-        </is>
-      </c>
-      <c r="F67" s="19" t="inlineStr">
-        <is>
-          <t>Repêche une preuve dans la baie</t>
-        </is>
-      </c>
-      <c r="G67" s="19" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="18" t="inlineStr">
-        <is>
-          <t>Gaston Ha! Ha!</t>
-        </is>
-      </c>
-      <c r="B68" s="18" t="inlineStr">
-        <is>
-          <t>Cédez</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="inlineStr">
-        <is>
-          <t>Pyramide / Neutre</t>
-        </is>
-      </c>
-      <c r="D68" s="18" t="inlineStr">
-        <is>
-          <t>Vit pour la Pyramide des Ha! Ha!</t>
-        </is>
-      </c>
-      <c r="E68" s="18" t="inlineStr">
-        <is>
-          <t>Cédez ! Cédez ! Cédez !</t>
-        </is>
-      </c>
-      <c r="F68" s="18" t="inlineStr">
-        <is>
-          <t>Voit un échange nocturne au bord de l’eau</t>
-        </is>
-      </c>
-      <c r="G68" s="18" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="19" t="inlineStr">
-        <is>
-          <t>Gaston Pelletier</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>Ti-Gas</t>
-        </is>
-      </c>
-      <c r="C69" s="19" t="inlineStr">
-        <is>
-          <t>Bar du Coin / Famille</t>
-        </is>
-      </c>
-      <c r="D69" s="19" t="inlineStr">
-        <is>
-          <t>Père d’Hugo, grand-père de Léa</t>
-        </is>
-      </c>
-      <c r="E69" s="19" t="inlineStr">
-        <is>
-          <t>Mon bar, c’tait du monde, pas du bruit.</t>
-        </is>
-      </c>
-      <c r="F69" s="19" t="inlineStr">
-        <is>
-          <t>Raconte qui tenait le Coin avant</t>
-        </is>
-      </c>
-      <c r="G69" s="19" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="18" t="inlineStr">
-        <is>
-          <t>Gaétan Lavoie</t>
-        </is>
-      </c>
-      <c r="B70" s="18" t="inlineStr">
-        <is>
-          <t>Ti-Gaétan</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle / Lavoie</t>
-        </is>
-      </c>
-      <c r="D70" s="18" t="inlineStr">
-        <is>
-          <t>Père de Chantal, journalier</t>
-        </is>
-      </c>
-      <c r="E70" s="18" t="inlineStr">
-        <is>
-          <t>Une job, j'prends. Une fierté, j'ai.</t>
-        </is>
-      </c>
-      <c r="F70" s="18" t="inlineStr">
-        <is>
-          <t>Refuse que Chantal plonge avec Gratien</t>
-        </is>
-      </c>
-      <c r="G70" s="18" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>Gisèle Truchon</t>
-        </is>
-      </c>
-      <c r="B71" s="19" t="n"/>
-      <c r="C71" s="19" t="inlineStr">
-        <is>
-          <t>Famille / Truchon</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>Conjointe d’Yvan, caissière de route</t>
-        </is>
-      </c>
-      <c r="E71" s="19" t="inlineStr">
-        <is>
-          <t>La caisse, j’la compte deux fois.</t>
-        </is>
-      </c>
-      <c r="F71" s="19" t="inlineStr">
-        <is>
-          <t>Voit les paquets passer au dépanneur</t>
-        </is>
-      </c>
-      <c r="G71" s="19" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="18" t="inlineStr">
-        <is>
-          <t>Guy Tremblay</t>
-        </is>
-      </c>
-      <c r="B72" s="18" t="inlineStr">
-        <is>
-          <t>Ti-Guy Indienne</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle</t>
-        </is>
-      </c>
-      <c r="D72" s="18" t="inlineStr">
-        <is>
-          <t>Relais d’Yvan sur le Petit-Parc</t>
-        </is>
-      </c>
-      <c r="E72" s="18" t="inlineStr">
-        <is>
-          <t>Du Next, du vrai, pas d’la cendre.</t>
-        </is>
-      </c>
-      <c r="F72" s="18" t="inlineStr">
-        <is>
-          <t>Se fait pincer avec une cargaison</t>
-        </is>
-      </c>
-      <c r="G72" s="18" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="19" t="inlineStr">
-        <is>
-          <t>Hassan Benali</t>
-        </is>
-      </c>
-      <c r="B73" s="19" t="n"/>
-      <c r="C73" s="19" t="inlineStr">
-        <is>
-          <t>Dépanneur / Neutre</t>
-        </is>
-      </c>
-      <c r="D73" s="19" t="inlineStr">
-        <is>
-          <t>Fils d’Ahmed et Nadia</t>
-        </is>
-      </c>
-      <c r="E73" s="19" t="inlineStr">
-        <is>
-          <t>Crédit ? Mon père dit non en deux langues.</t>
-        </is>
-      </c>
-      <c r="F73" s="19" t="inlineStr">
-        <is>
-          <t>Reconnaît les clients de Gratien</t>
-        </is>
-      </c>
-      <c r="G73" s="19" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="18" t="inlineStr">
-        <is>
-          <t>Hugo Pelletier</t>
-        </is>
-      </c>
-      <c r="B74" s="18" t="inlineStr">
-        <is>
-          <t>Le Boss</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="inlineStr">
-        <is>
-          <t>Bar du Coin</t>
-        </is>
-      </c>
-      <c r="D74" s="18" t="inlineStr">
-        <is>
-          <t>Patron du Coin, époux de Sarah</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="inlineStr">
-        <is>
-          <t>Dehors, tu reviendras sobre.</t>
-        </is>
-      </c>
-      <c r="F74" s="18" t="inlineStr">
-        <is>
-          <t>Impose le Coin comme zone neutre</t>
-        </is>
-      </c>
-      <c r="G74" s="18" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="19" t="inlineStr">
-        <is>
-          <t>Hélène Blackburn</t>
-        </is>
-      </c>
-      <c r="B75" s="19" t="n"/>
-      <c r="C75" s="19" t="inlineStr">
-        <is>
-          <t>Hôpital / Aide</t>
-        </is>
-      </c>
-      <c r="D75" s="19" t="inlineStr">
-        <is>
-          <t>Directrice de l’Hôpital de La Baie</t>
-        </is>
-      </c>
-      <c r="E75" s="19" t="inlineStr">
-        <is>
-          <t>Un lit, ça se mérite pas, ça se donne.</t>
-        </is>
-      </c>
-      <c r="F75" s="19" t="inlineStr">
-        <is>
-          <t>Ouvre les dossiers de surdoses</t>
-        </is>
-      </c>
-      <c r="G75" s="19" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="18" t="inlineStr">
-        <is>
-          <t>Hélène Chicoine</t>
-        </is>
-      </c>
-      <c r="B76" s="18" t="n"/>
-      <c r="C76" s="18" t="inlineStr">
-        <is>
-          <t>Famille / Chicoine</t>
-        </is>
-      </c>
-      <c r="D76" s="18" t="inlineStr">
-        <is>
-          <t>Mère de Réal</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="inlineStr">
-        <is>
-          <t>Mon fils est doux, comprenez-vous.</t>
-        </is>
-      </c>
-      <c r="F76" s="18" t="inlineStr">
-        <is>
-          <t>Réclame Réal après sa disparition</t>
-        </is>
-      </c>
-      <c r="G76" s="18" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="19" t="inlineStr">
-        <is>
-          <t>Isabelle Bergeron</t>
-        </is>
-      </c>
-      <c r="B77" s="19" t="n"/>
-      <c r="C77" s="19" t="inlineStr">
-        <is>
-          <t>École / Aide</t>
-        </is>
-      </c>
-      <c r="D77" s="19" t="inlineStr">
-        <is>
-          <t>Institutrice primaire, fille de Gilles</t>
-        </is>
-      </c>
-      <c r="E77" s="19" t="inlineStr">
-        <is>
-          <t>Les enfants parlent, faut écouter.</t>
-        </is>
-      </c>
-      <c r="F77" s="19" t="inlineStr">
-        <is>
-          <t>Signale les bleus de Lio</t>
-        </is>
-      </c>
-      <c r="G77" s="19" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="18" t="inlineStr">
-        <is>
-          <t>Jacques Maltais</t>
-        </is>
-      </c>
-      <c r="B78" s="18" t="n"/>
-      <c r="C78" s="18" t="inlineStr">
-        <is>
-          <t>Ville / Argent</t>
-        </is>
-      </c>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>Conseiller d’arrondissement La Baie</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="inlineStr">
-        <is>
-          <t>La Baie, ça se gère comme un gros frigidaire.</t>
-        </is>
-      </c>
-      <c r="F78" s="18" t="inlineStr">
-        <is>
-          <t>Subit les pressions d’expulsion</t>
-        </is>
-      </c>
-      <c r="G78" s="18" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="19" t="inlineStr">
-        <is>
-          <t>Jeanne Gagnon</t>
-        </is>
-      </c>
-      <c r="B79" s="19" t="n"/>
-      <c r="C79" s="19" t="inlineStr">
-        <is>
-          <t>Argent / Famille</t>
-        </is>
-      </c>
-      <c r="D79" s="19" t="inlineStr">
-        <is>
-          <t>Mère de Sylvie, héritière</t>
-        </is>
-      </c>
-      <c r="E79" s="19" t="inlineStr">
-        <is>
-          <t>Les briques meurent pas, les familles oui.</t>
-        </is>
-      </c>
-      <c r="F79" s="19" t="inlineStr">
-        <is>
-          <t>Lègue le bloc à la surprise générale</t>
-        </is>
-      </c>
-      <c r="G79" s="19" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="18" t="inlineStr">
-        <is>
-          <t>Jeanne Otis</t>
-        </is>
-      </c>
-      <c r="B80" s="18" t="n"/>
-      <c r="C80" s="18" t="inlineStr">
-        <is>
-          <t>Bibliothèque / Neutre</t>
-        </is>
-      </c>
-      <c r="D80" s="18" t="inlineStr">
-        <is>
-          <t>Bibliothécaire, tante de Félix</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="inlineStr">
-        <is>
-          <t>Chut. Les livres écoutent tout.</t>
-        </is>
-      </c>
-      <c r="F80" s="18" t="inlineStr">
-        <is>
-          <t>Cache Ti-Coune en section jeunesse</t>
-        </is>
-      </c>
-      <c r="G80" s="18" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="19" t="inlineStr">
-        <is>
-          <t>Jessica Paradis</t>
-        </is>
-      </c>
-      <c r="B81" s="19" t="inlineStr">
-        <is>
-          <t>Jess</t>
-        </is>
-      </c>
-      <c r="C81" s="19" t="inlineStr">
-        <is>
-          <t>Locataires / Neutre</t>
-        </is>
-      </c>
-      <c r="D81" s="19" t="inlineStr">
-        <is>
-          <t>Locataire de Sylvie Gagnon</t>
-        </is>
-      </c>
-      <c r="E81" s="19" t="inlineStr">
-        <is>
-          <t>Mon loyer est payé. En tout cas, j’pense.</t>
-        </is>
-      </c>
-      <c r="F81" s="19" t="inlineStr">
-        <is>
-          <t>Témoin des visites d’expulsion</t>
-        </is>
-      </c>
-      <c r="G81" s="19" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="18" t="inlineStr">
-        <is>
-          <t>Jessy Bérubé</t>
-        </is>
-      </c>
-      <c r="B82" s="18" t="inlineStr">
-        <is>
-          <t>Ti-Jess</t>
-        </is>
-      </c>
-      <c r="C82" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle / Bérubé</t>
-        </is>
-      </c>
-      <c r="D82" s="18" t="inlineStr">
-        <is>
-          <t>Frère de Kevin, entrepôt</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="inlineStr">
-        <is>
-          <t>J'porte, j'pose, j'demande rien.</t>
-        </is>
-      </c>
-      <c r="F82" s="18" t="inlineStr">
-        <is>
-          <t>Remplace Big Jo quand ça tourne mal</t>
-        </is>
-      </c>
-      <c r="G82" s="18" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="19" t="inlineStr">
-        <is>
-          <t>Josée Langlois</t>
-        </is>
-      </c>
-      <c r="B83" s="19" t="n"/>
-      <c r="C83" s="19" t="inlineStr">
-        <is>
-          <t>1er étage</t>
-        </is>
-      </c>
-      <c r="D83" s="19" t="inlineStr">
-        <is>
-          <t>Femme du Plombier, secrétaire de chantier</t>
-        </is>
-      </c>
-      <c r="E83" s="19" t="inlineStr">
-        <is>
-          <t>La facture va suivre, comme toujours.</t>
-        </is>
-      </c>
-      <c r="F83" s="19" t="inlineStr">
-        <is>
-          <t>Photographie les dégâts à son tour</t>
-        </is>
-      </c>
-      <c r="G83" s="19" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="18" t="inlineStr">
-        <is>
-          <t>Julie Martel</t>
-        </is>
-      </c>
-      <c r="B84" s="18" t="n"/>
-      <c r="C84" s="18" t="inlineStr">
-        <is>
-          <t>Tourisme / Neutre</t>
-        </is>
-      </c>
-      <c r="D84" s="18" t="inlineStr">
-        <is>
-          <t>Guide des croisières, sœur d’Amélie</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="inlineStr">
-        <is>
-          <t>Sur le fjord, pas de Wi-Fi, juste des baleines.</t>
-        </is>
-      </c>
-      <c r="F84" s="18" t="inlineStr">
-        <is>
-          <t>Voit un transfert depuis le large</t>
-        </is>
-      </c>
-      <c r="G84" s="18" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="19" t="inlineStr">
-        <is>
-          <t>Justine Fortin</t>
-        </is>
-      </c>
-      <c r="B85" s="19" t="n"/>
-      <c r="C85" s="19" t="inlineStr">
-        <is>
-          <t>Bec-Scie / Neutre</t>
-        </is>
-      </c>
-      <c r="D85" s="19" t="inlineStr">
-        <is>
-          <t>Patrouilleuse, nièce d’Yves</t>
-        </is>
-      </c>
-      <c r="E85" s="19" t="inlineStr">
-        <is>
-          <t>La neige cache tout, sauf les traces.</t>
-        </is>
-      </c>
-      <c r="F85" s="19" t="inlineStr">
-        <is>
-          <t>Découvre la planque de Bernard</t>
-        </is>
-      </c>
-      <c r="G85" s="19" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="18" t="inlineStr">
-        <is>
-          <t>Karim Al-Hassan</t>
-        </is>
-      </c>
-      <c r="B86" s="18" t="n"/>
-      <c r="C86" s="18" t="inlineStr">
-        <is>
-          <t>Rue / Neutre</t>
-        </is>
-      </c>
-      <c r="D86" s="18" t="inlineStr">
-        <is>
-          <t>Cuisinier du camion, mari de Fatima</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="inlineStr">
-        <is>
-          <t>Sans piasse ? Une assiette quand même.</t>
-        </is>
-      </c>
-      <c r="F86" s="18" t="inlineStr">
-        <is>
-          <t>Le camion cantine devient QG neutre</t>
-        </is>
-      </c>
-      <c r="G86" s="18" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="19" t="inlineStr">
-        <is>
-          <t>Karine Desrosiers</t>
-        </is>
-      </c>
-      <c r="B87" s="19" t="inlineStr">
-        <is>
-          <t>Zoom</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>Bloc d'en Face</t>
-        </is>
-      </c>
-      <c r="D87" s="19" t="inlineStr">
-        <is>
-          <t>Cousine d’Anik, archiviste de plaques</t>
-        </is>
-      </c>
-      <c r="E87" s="19" t="inlineStr">
-        <is>
-          <t>Une plaque, c’est une confession en métal.</t>
-        </is>
-      </c>
-      <c r="F87" s="19" t="inlineStr">
-        <is>
-          <t>Retrace le VUS de la soirée Chen</t>
-        </is>
-      </c>
-      <c r="G87" s="19" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="18" t="inlineStr">
-        <is>
-          <t>Kim Boudreault</t>
-        </is>
-      </c>
-      <c r="B88" s="18" t="n"/>
-      <c r="C88" s="18" t="inlineStr">
-        <is>
-          <t>Urgences / Aide</t>
-        </is>
-      </c>
-      <c r="D88" s="18" t="inlineStr">
-        <is>
-          <t>Paramédic, tourne au Spot les nuits de bagarre</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="inlineStr">
-        <is>
-          <t>Respire. Reste avec moi.</t>
-        </is>
-      </c>
-      <c r="F88" s="18" t="inlineStr">
-        <is>
-          <t>Témoin des appels coupés au 427</t>
-        </is>
-      </c>
-      <c r="G88" s="18" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="19" t="inlineStr">
-        <is>
-          <t>Linda Tremblay</t>
-        </is>
-      </c>
-      <c r="B89" s="19" t="n"/>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t>Ruelle</t>
-        </is>
-      </c>
-      <c r="D89" s="19" t="inlineStr">
-        <is>
-          <t>Conjointe de Gratien, préposée d’entretien</t>
-        </is>
-      </c>
-      <c r="E89" s="19" t="inlineStr">
-        <is>
-          <t>J'récure, j'vois rien, c'est mon don.</t>
-        </is>
-      </c>
-      <c r="F89" s="19" t="inlineStr">
-        <is>
-          <t>Quitte Gratien et parle à Samson</t>
-        </is>
-      </c>
-      <c r="G89" s="19" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="18" t="inlineStr">
-        <is>
-          <t>Lise Blackburn</t>
-        </is>
-      </c>
-      <c r="B90" s="18" t="n"/>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>CLSC / Aide</t>
-        </is>
-      </c>
-      <c r="D90" s="18" t="inlineStr">
-        <is>
-          <t>Travailleuse sociale, collègue de Gigi</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="inlineStr">
-        <is>
-          <t>On peut pas sauver quelqu’un à sa place.</t>
-        </is>
-      </c>
-      <c r="F90" s="18" t="inlineStr">
-        <is>
-          <t>Ouvre un dossier sur les Cloutier</t>
-        </is>
-      </c>
-      <c r="G90" s="18" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="19" t="inlineStr">
-        <is>
-          <t>Louis Girard</t>
-        </is>
-      </c>
-      <c r="B91" s="19" t="n"/>
-      <c r="C91" s="19" t="inlineStr">
-        <is>
-          <t>Propre</t>
-        </is>
-      </c>
-      <c r="D91" s="19" t="inlineStr">
-        <is>
-          <t>Comptable, époux d’Anne</t>
-        </is>
-      </c>
-      <c r="E91" s="19" t="inlineStr">
-        <is>
-          <t>Les chiffres mentent pas, le monde oui.</t>
-        </is>
-      </c>
-      <c r="F91" s="19" t="inlineStr">
-        <is>
-          <t>Démêle les sociétés-écrans</t>
-        </is>
-      </c>
-      <c r="G91" s="19" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="18" t="inlineStr">
-        <is>
-          <t>Luc Villeneuve</t>
-        </is>
-      </c>
-      <c r="B92" s="18" t="inlineStr">
-        <is>
-          <t>OVNI-Luc</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>Bagotville / Marge</t>
-        </is>
-      </c>
-      <c r="D92" s="18" t="inlineStr">
-        <is>
-          <t>Guetteur, croise Will</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="inlineStr">
-        <is>
-          <t>Dans l'ciel, c'est pas juste des avions.</t>
-        </is>
-      </c>
-      <c r="F92" s="18" t="inlineStr">
-        <is>
-          <t>Confond un vol de contrebande avec un OVNI</t>
-        </is>
-      </c>
-      <c r="G92" s="18" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="19" t="inlineStr">
-        <is>
-          <t>Lucie Bérubé</t>
-        </is>
-      </c>
-      <c r="B93" s="19" t="n"/>
-      <c r="C93" s="19" t="inlineStr">
-        <is>
-          <t>Famille / Bérubé</t>
-        </is>
-      </c>
-      <c r="D93" s="19" t="inlineStr">
-        <is>
-          <t>Mère de Kevin et Jessy</t>
-        </is>
-      </c>
-      <c r="E93" s="19" t="inlineStr">
-        <is>
-          <t>Mes gars sont des porteurs, pas des frappeurs.</t>
-        </is>
-      </c>
-      <c r="F93" s="19" t="inlineStr">
-        <is>
-          <t>Cache les enfants du quartier</t>
-        </is>
-      </c>
-      <c r="G93" s="19" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="18" t="inlineStr">
-        <is>
-          <t>Lucie Côté</t>
-        </is>
-      </c>
-      <c r="B94" s="18" t="n"/>
-      <c r="C94" s="18" t="inlineStr">
-        <is>
-          <t>Vieux bloc</t>
-        </is>
-      </c>
-      <c r="D94" s="18" t="inlineStr">
-        <is>
-          <t>Voisine du 425 Victoria</t>
-        </is>
-      </c>
-      <c r="E94" s="18" t="inlineStr">
-        <is>
-          <t>Au tri, on jetait tout, même les patrons.</t>
-        </is>
-      </c>
-      <c r="F94" s="18" t="inlineStr">
-        <is>
-          <t>Colporte les nouvelles du palier</t>
-        </is>
-      </c>
-      <c r="G94" s="18" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="19" t="inlineStr">
-        <is>
-          <t>Léa Pelletier</t>
-        </is>
-      </c>
-      <c r="B95" s="19" t="n"/>
-      <c r="C95" s="19" t="inlineStr">
-        <is>
-          <t>Bar du Coin</t>
-        </is>
-      </c>
-      <c r="D95" s="19" t="inlineStr">
-        <is>
-          <t>Serveuse, fille d’Hugo et Sarah</t>
-        </is>
-      </c>
-      <c r="E95" s="19" t="inlineStr">
-        <is>
-          <t>Un café, pis oublie pas ton change.</t>
-        </is>
-      </c>
-      <c r="F95" s="19" t="inlineStr">
-        <is>
-          <t>Rapporte à Ginette ce qu’elle entend</t>
-        </is>
-      </c>
-      <c r="G95" s="19" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="18" t="inlineStr">
-        <is>
-          <t>Manon Cloutier</t>
-        </is>
-      </c>
-      <c r="B96" s="18" t="n"/>
-      <c r="C96" s="18" t="inlineStr">
-        <is>
-          <t>Station-service / Famille</t>
-        </is>
-      </c>
-      <c r="D96" s="18" t="inlineStr">
-        <is>
-          <t>Mère de Dave et Lio</t>
-        </is>
-      </c>
-      <c r="E96" s="18" t="inlineStr">
-        <is>
-          <t>Le gaz est cher, les erreurs itou.</t>
-        </is>
-      </c>
-      <c r="F96" s="18" t="inlineStr">
-        <is>
-          <t>Cache Dave et ment pour Lio</t>
-        </is>
-      </c>
-      <c r="G96" s="18" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="19" t="inlineStr">
-        <is>
-          <t>Manon Lavoie</t>
-        </is>
-      </c>
-      <c r="B97" s="19" t="n"/>
-      <c r="C97" s="19" t="inlineStr">
-        <is>
-          <t>Ruelle / Gratien</t>
-        </is>
-      </c>
-      <c r="D97" s="19" t="inlineStr">
-        <is>
-          <t>Mère de Cindy, 92 Prince-Albert</t>
-        </is>
-      </c>
-      <c r="E97" s="19" t="inlineStr">
-        <is>
-          <t>J'ai rien dit, j'ai rien vu, j'ai survécu.</t>
-        </is>
-      </c>
-      <c r="F97" s="19" t="inlineStr">
-        <is>
-          <t>Perd son logement de la rue</t>
-        </is>
-      </c>
-      <c r="G97" s="19" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="18" t="inlineStr">
-        <is>
-          <t>Manon Villeneuve</t>
-        </is>
-      </c>
-      <c r="B98" s="18" t="inlineStr">
-        <is>
-          <t>Manon-Louve</t>
-        </is>
-      </c>
-      <c r="C98" s="18" t="inlineStr">
-        <is>
-          <t>Motards / Louves</t>
-        </is>
-      </c>
-      <c r="D98" s="18" t="inlineStr">
-        <is>
-          <t>Bras droit de Karine Gagnon</t>
-        </is>
-      </c>
-      <c r="E98" s="18" t="inlineStr">
-        <is>
-          <t>Les Louves mordent en silence.</t>
-        </is>
-      </c>
-      <c r="F98" s="18" t="inlineStr">
-        <is>
-          <t>Prend la relève si Karine tombe</t>
-        </is>
-      </c>
-      <c r="G98" s="18" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="19" t="inlineStr">
-        <is>
-          <t>Marc-André Simard</t>
-        </is>
-      </c>
-      <c r="B99" s="19" t="inlineStr">
-        <is>
-          <t>Simard</t>
-        </is>
-      </c>
-      <c r="C99" s="19" t="inlineStr">
-        <is>
-          <t>Bloc d'en Face</t>
-        </is>
-      </c>
-      <c r="D99" s="19" t="inlineStr">
-        <is>
-          <t>Conjoint d’Anik, opérateur d’usine</t>
-        </is>
-      </c>
-      <c r="E99" s="19" t="inlineStr">
-        <is>
-          <t>J'vois rien la nuit, j'travaille.</t>
-        </is>
-      </c>
-      <c r="F99" s="19" t="inlineStr">
-        <is>
-          <t>Confirme l’alibi d’Anik</t>
-        </is>
-      </c>
-      <c r="G99" s="19" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="18" t="inlineStr">
-        <is>
-          <t>Marcel Bouchard</t>
-        </is>
-      </c>
-      <c r="B100" s="18" t="inlineStr">
-        <is>
-          <t>Le Prêteur</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="inlineStr">
-        <is>
-          <t>Argent / Ruelle</t>
-        </is>
-      </c>
-      <c r="D100" s="18" t="inlineStr">
-        <is>
-          <t>Prêteur, Dévon lui doit</t>
-        </is>
-      </c>
-      <c r="E100" s="18" t="inlineStr">
-        <is>
-          <t>J'prête pas de l'argent, j'prête du temps.</t>
-        </is>
-      </c>
-      <c r="F100" s="18" t="inlineStr">
-        <is>
-          <t>Rachète la dette du Spot</t>
-        </is>
-      </c>
-      <c r="G100" s="18" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="19" t="inlineStr">
-        <is>
-          <t>Marie-Claude Brassard</t>
-        </is>
-      </c>
-      <c r="B101" s="19" t="inlineStr">
-        <is>
-          <t>MC</t>
-        </is>
-      </c>
-      <c r="C101" s="19" t="inlineStr">
-        <is>
-          <t>Urgences / Aide</t>
-        </is>
-      </c>
-      <c r="D101" s="19" t="inlineStr">
-        <is>
-          <t>Ambulancière, épouse d’Émile</t>
-        </is>
-      </c>
-      <c r="E101" s="19" t="inlineStr">
-        <is>
-          <t>On roule même pour les pires.</t>
-        </is>
-      </c>
-      <c r="F101" s="19" t="inlineStr">
-        <is>
-          <t>Transporte Dave après la descente</t>
-        </is>
-      </c>
-      <c r="G101" s="19" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="18" t="inlineStr">
-        <is>
-          <t>Martine Lavoie</t>
-        </is>
-      </c>
-      <c r="B102" s="18" t="n"/>
-      <c r="C102" s="18" t="inlineStr">
-        <is>
-          <t>École</t>
-        </is>
-      </c>
-      <c r="D102" s="18" t="inlineStr">
-        <is>
-          <t>Directrice de l’école secondaire</t>
-        </is>
-      </c>
-      <c r="E102" s="18" t="inlineStr">
-        <is>
-          <t>Ton frère a manqué douze jours.</t>
-        </is>
-      </c>
-      <c r="F102" s="18" t="inlineStr">
-        <is>
-          <t>Convoque la famille Lavoie</t>
-        </is>
-      </c>
-      <c r="G102" s="18" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="19" t="inlineStr">
-        <is>
-          <t>Maxime Boivin</t>
-        </is>
-      </c>
-      <c r="B103" s="19" t="n"/>
-      <c r="C103" s="19" t="inlineStr">
-        <is>
-          <t>Santé / Propre</t>
-        </is>
-      </c>
-      <c r="D103" s="19" t="inlineStr">
-        <is>
-          <t>Vétérinaire du quartier</t>
-        </is>
-      </c>
-      <c r="E103" s="19" t="inlineStr">
-        <is>
-          <t>Même les chats ont des histoires.</t>
-        </is>
-      </c>
-      <c r="F103" s="19" t="inlineStr">
-        <is>
-          <t>Soigne Pisse-Feu et donne un indice</t>
-        </is>
-      </c>
-      <c r="G103" s="19" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="18" t="inlineStr">
-        <is>
-          <t>Nadia Benali</t>
-        </is>
-      </c>
-      <c r="B104" s="18" t="n"/>
-      <c r="C104" s="18" t="inlineStr">
-        <is>
-          <t>Dépanneur / Famille</t>
-        </is>
-      </c>
-      <c r="D104" s="18" t="inlineStr">
-        <is>
-          <t>Tient le cahier des dettes</t>
-        </is>
-      </c>
-      <c r="E104" s="18" t="inlineStr">
-        <is>
-          <t>Le cahier, c’est ma mémoire, et j’oublie rien.</t>
-        </is>
-      </c>
-      <c r="F104" s="18" t="inlineStr">
-        <is>
-          <t>Confie le cahier à Samson</t>
-        </is>
-      </c>
-      <c r="G104" s="18" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="19" t="inlineStr">
-        <is>
-          <t>Nancy Dubois</t>
-        </is>
-      </c>
-      <c r="B105" s="19" t="n"/>
-      <c r="C105" s="19" t="inlineStr">
-        <is>
-          <t>Bar du Coin</t>
-        </is>
-      </c>
-      <c r="D105" s="19" t="inlineStr">
-        <is>
-          <t>Serveuse, sœur de Patrice</t>
-        </is>
-      </c>
-      <c r="E105" s="19" t="inlineStr">
-        <is>
-          <t>Verre cassé, compte cassé.</t>
-        </is>
-      </c>
-      <c r="F105" s="19" t="inlineStr">
-        <is>
-          <t>Travaille la soirée de la descente</t>
-        </is>
-      </c>
-      <c r="G105" s="19" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="18" t="inlineStr">
-        <is>
-          <t>Natasha Vollant</t>
-        </is>
-      </c>
-      <c r="B106" s="18" t="n"/>
-      <c r="C106" s="18" t="inlineStr">
-        <is>
-          <t>Parc du Fjord</t>
-        </is>
-      </c>
-      <c r="D106" s="18" t="inlineStr">
-        <is>
-          <t>Guide innue, sentier Eucher</t>
-        </is>
-      </c>
-      <c r="E106" s="18" t="inlineStr">
-        <is>
-          <t>La forêt vous laisse passer, pas voler.</t>
-        </is>
-      </c>
-      <c r="F106" s="18" t="inlineStr">
-        <is>
-          <t>Guide les flics jusqu'à la planque</t>
-        </is>
-      </c>
-      <c r="G106" s="18" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="19" t="inlineStr">
-        <is>
-          <t>Nathalie Bouchard</t>
-        </is>
-      </c>
-      <c r="B107" s="19" t="n"/>
-      <c r="C107" s="19" t="inlineStr">
-        <is>
-          <t>Famille / Chloé</t>
-        </is>
-      </c>
-      <c r="D107" s="19" t="inlineStr">
-        <is>
-          <t>Préposée IGA, mère de Chloé</t>
-        </is>
-      </c>
-      <c r="E107" s="19" t="inlineStr">
-        <is>
-          <t>Ma fille streame ma vie, fine.</t>
-        </is>
-      </c>
-      <c r="F107" s="19" t="inlineStr">
-        <is>
-          <t>Héberge Chloé après la vidéo virale</t>
-        </is>
-      </c>
-      <c r="G107" s="19" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="18" t="inlineStr">
-        <is>
-          <t>Normand Boucher</t>
-        </is>
-      </c>
-      <c r="B108" s="18" t="inlineStr">
-        <is>
-          <t>Norm</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle d'en Face</t>
-        </is>
-      </c>
-      <c r="D108" s="18" t="inlineStr">
-        <is>
-          <t>Cousin de Dévon, casse illégale</t>
-        </is>
-      </c>
-      <c r="E108" s="18" t="inlineStr">
-        <is>
-          <t>Un char, ça meurt. Les preuves itou.</t>
-        </is>
-      </c>
-      <c r="F108" s="18" t="inlineStr">
-        <is>
-          <t>La casse avale la caméra volée</t>
-        </is>
-      </c>
-      <c r="G108" s="18" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="19" t="inlineStr">
-        <is>
-          <t>Paule Desbiens</t>
-        </is>
-      </c>
-      <c r="B109" s="19" t="n"/>
-      <c r="C109" s="19" t="inlineStr">
-        <is>
-          <t>Institutions</t>
-        </is>
-      </c>
-      <c r="D109" s="19" t="inlineStr">
-        <is>
-          <t>Notaire de La Baie</t>
-        </is>
-      </c>
-      <c r="E109" s="19" t="inlineStr">
-        <is>
-          <t>Signez ici, et priez un peu.</t>
-        </is>
-      </c>
-      <c r="F109" s="19" t="inlineStr">
-        <is>
-          <t>Trouve l’irrégularité dans le bail</t>
-        </is>
-      </c>
-      <c r="G109" s="19" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="18" t="inlineStr">
-        <is>
-          <t>Pauline Fortin</t>
-        </is>
-      </c>
-      <c r="B110" s="18" t="n"/>
-      <c r="C110" s="18" t="inlineStr">
-        <is>
-          <t>Campagne / Neutre</t>
-        </is>
-      </c>
-      <c r="D110" s="18" t="inlineStr">
-        <is>
-          <t>Maraîchère, épouse d’Yves</t>
-        </is>
-      </c>
-      <c r="E110" s="18" t="inlineStr">
-        <is>
-          <t>Des bleuets, du temps, c’est tout c’que j’vends.</t>
-        </is>
-      </c>
-      <c r="F110" s="18" t="inlineStr">
-        <is>
-          <t>Son kiosque voit les boîtes passer</t>
-        </is>
-      </c>
-      <c r="G110" s="18" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="19" t="inlineStr">
-        <is>
-          <t>Philippe Villeneuve</t>
-        </is>
-      </c>
-      <c r="B111" s="19" t="inlineStr">
-        <is>
-          <t>Dr Phil</t>
-        </is>
-      </c>
-      <c r="C111" s="19" t="inlineStr">
-        <is>
-          <t>Hôpital</t>
-        </is>
-      </c>
-      <c r="D111" s="19" t="inlineStr">
-        <is>
-          <t>Médecin à l’Hôpital de La Baie</t>
-        </is>
-      </c>
-      <c r="E111" s="19" t="inlineStr">
-        <is>
-          <t>J'suis médecin, pas juge.</t>
-        </is>
-      </c>
-      <c r="F111" s="19" t="inlineStr">
-        <is>
-          <t>Soigne un blessé non déclaré</t>
-        </is>
-      </c>
-      <c r="G111" s="19" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="18" t="inlineStr">
-        <is>
-          <t>Pierrette Simard</t>
-        </is>
-      </c>
-      <c r="B112" s="18" t="n"/>
-      <c r="C112" s="18" t="inlineStr">
-        <is>
-          <t>Bloc d'en Face / Famille</t>
-        </is>
-      </c>
-      <c r="D112" s="18" t="inlineStr">
-        <is>
-          <t>Mère de Marc-André, ex-caissière IGA</t>
-        </is>
-      </c>
-      <c r="E112" s="18" t="inlineStr">
-        <is>
-          <t>À la caisse, on sait tout l’monde.</t>
-        </is>
-      </c>
-      <c r="F112" s="18" t="inlineStr">
-        <is>
-          <t>Se souvient des achats suspects</t>
-        </is>
-      </c>
-      <c r="G112" s="18" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="19" t="inlineStr">
-        <is>
-          <t>Raymond Gagnon</t>
-        </is>
-      </c>
-      <c r="B113" s="19" t="inlineStr">
-        <is>
-          <t>Antenna</t>
-        </is>
-      </c>
-      <c r="C113" s="19" t="inlineStr">
-        <is>
-          <t>Radio pirate / Marge</t>
-        </is>
-      </c>
-      <c r="D113" s="19" t="inlineStr">
-        <is>
-          <t>Pirate radio, écoute Alex T.</t>
-        </is>
-      </c>
-      <c r="E113" s="19" t="inlineStr">
-        <is>
-          <t>Ils m’écoutent ? Parfait, j’ai des choses à dire.</t>
-        </is>
-      </c>
-      <c r="F113" s="19" t="inlineStr">
-        <is>
-          <t>Diffuse les bandes d’Alex en direct</t>
-        </is>
-      </c>
-      <c r="G113" s="19" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="18" t="inlineStr">
-        <is>
-          <t>Richard Villeneuve</t>
-        </is>
-      </c>
-      <c r="B114" s="18" t="inlineStr">
-        <is>
-          <t>Rich</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="inlineStr">
-        <is>
-          <t>STS / Neutre</t>
-        </is>
-      </c>
-      <c r="D114" s="18" t="inlineStr">
-        <is>
-          <t>Chauffeur d’autobus</t>
-        </is>
-      </c>
-      <c r="E114" s="18" t="inlineStr">
-        <is>
-          <t>Prochain arrêt : tes conséquences.</t>
-        </is>
-      </c>
-      <c r="F114" s="18" t="inlineStr">
-        <is>
-          <t>La caméra du bus filme la mauvaise course</t>
-        </is>
-      </c>
-      <c r="G114" s="18" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="19" t="inlineStr">
-        <is>
-          <t>Rico Leduc</t>
-        </is>
-      </c>
-      <c r="B115" s="19" t="inlineStr">
-        <is>
-          <t>Rico</t>
-        </is>
-      </c>
-      <c r="C115" s="19" t="inlineStr">
-        <is>
-          <t>Santini / Ruelle</t>
-        </is>
-      </c>
-      <c r="D115" s="19" t="inlineStr">
-        <is>
-          <t>Recouvre pour Tony à La Baie</t>
-        </is>
-      </c>
-      <c r="E115" s="19" t="inlineStr">
-        <is>
-          <t>Tu payes, ou tu comprends.</t>
-        </is>
-      </c>
-      <c r="F115" s="19" t="inlineStr">
-        <is>
-          <t>Envoyé appuyer Dévon au Spot</t>
-        </is>
-      </c>
-      <c r="G115" s="19" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="18" t="inlineStr">
-        <is>
-          <t>Rock Côté</t>
-        </is>
-      </c>
-      <c r="B116" s="18" t="inlineStr">
-        <is>
-          <t>Ti-Rock</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="D116" s="18" t="inlineStr">
-        <is>
-          <t>Débardeur, filleul de Fernand</t>
-        </is>
-      </c>
-      <c r="E116" s="18" t="inlineStr">
-        <is>
-          <t>Un conteneur, ça s’ouvre toujours.</t>
-        </is>
-      </c>
-      <c r="F116" s="18" t="inlineStr">
-        <is>
-          <t>Repère le conteneur de Sal</t>
-        </is>
-      </c>
-      <c r="G116" s="18" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="19" t="inlineStr">
-        <is>
-          <t>Rock Gagnon</t>
-        </is>
-      </c>
-      <c r="B117" s="19" t="inlineStr">
-        <is>
-          <t>Rocky</t>
-        </is>
-      </c>
-      <c r="C117" s="19" t="inlineStr">
-        <is>
-          <t>Motards</t>
-        </is>
-      </c>
-      <c r="D117" s="19" t="inlineStr">
-        <is>
-          <t>Mécano moto, frère de Karine</t>
-        </is>
-      </c>
-      <c r="E117" s="19" t="inlineStr">
-        <is>
-          <t>Une moto, ça ment jamais.</t>
-        </is>
-      </c>
-      <c r="F117" s="19" t="inlineStr">
-        <is>
-          <t>Prépare les bécanes de repli</t>
-        </is>
-      </c>
-      <c r="G117" s="19" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="18" t="inlineStr">
-        <is>
-          <t>Réjean Pedneault</t>
-        </is>
-      </c>
-      <c r="B118" s="18" t="inlineStr">
-        <is>
-          <t>Ti-Peche</t>
-        </is>
-      </c>
-      <c r="C118" s="18" t="inlineStr">
-        <is>
-          <t>Port / Neutre</t>
-        </is>
-      </c>
-      <c r="D118" s="18" t="inlineStr">
-        <is>
-          <t>Pêche la baie des Ha! Ha! avec Céline</t>
-        </is>
-      </c>
-      <c r="E118" s="18" t="inlineStr">
-        <is>
-          <t>Le fjord parle à qui sait r’garder.</t>
-        </is>
-      </c>
-      <c r="F118" s="18" t="inlineStr">
-        <is>
-          <t>Repêche le ballot tombé d’un conteneur</t>
-        </is>
-      </c>
-      <c r="G118" s="18" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="19" t="inlineStr">
-        <is>
-          <t>Réjean Roy</t>
-        </is>
-      </c>
-      <c r="B119" s="19" t="inlineStr">
-        <is>
-          <t>Ti-Jean</t>
-        </is>
-      </c>
-      <c r="C119" s="19" t="inlineStr">
-        <is>
-          <t>Aide / Famille</t>
-        </is>
-      </c>
-      <c r="D119" s="19" t="inlineStr">
-        <is>
-          <t>Mari de Gigi, ex-papetier</t>
-        </is>
-      </c>
-      <c r="E119" s="19" t="inlineStr">
-        <is>
-          <t>À l’usine, on s’occupait des nôtres.</t>
-        </is>
-      </c>
-      <c r="F119" s="19" t="inlineStr">
-        <is>
-          <t>Accompagne Ginette quand elle doit parler</t>
-        </is>
-      </c>
-      <c r="G119" s="19" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="18" t="inlineStr">
-        <is>
-          <t>Salvatore Martel</t>
-        </is>
-      </c>
-      <c r="B120" s="18" t="inlineStr">
-        <is>
-          <t>Sal</t>
-        </is>
-      </c>
-      <c r="C120" s="18" t="inlineStr">
-        <is>
-          <t>Santini / Port</t>
-        </is>
-      </c>
-      <c r="D120" s="18" t="inlineStr">
-        <is>
-          <t>Relais conteneurs, croise Yvan</t>
-        </is>
-      </c>
-      <c r="E120" s="18" t="inlineStr">
-        <is>
-          <t>Le quai dort jamais.</t>
-        </is>
-      </c>
-      <c r="F120" s="18" t="inlineStr">
-        <is>
-          <t>Reçoit le mauvais conteneur</t>
-        </is>
-      </c>
-      <c r="G120" s="18" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="19" t="inlineStr">
-        <is>
-          <t>Samuel Joseph</t>
-        </is>
-      </c>
-      <c r="B121" s="19" t="inlineStr">
-        <is>
-          <t>Samy</t>
-        </is>
-      </c>
-      <c r="C121" s="19" t="inlineStr">
-        <is>
-          <t>Aide / CHSLD</t>
-        </is>
-      </c>
-      <c r="D121" s="19" t="inlineStr">
-        <is>
-          <t>Préposé, fils de Mireille</t>
-        </is>
-      </c>
-      <c r="E121" s="19" t="inlineStr">
-        <is>
-          <t>Mamie, t’es où encore ?</t>
-        </is>
-      </c>
-      <c r="F121" s="19" t="inlineStr">
-        <is>
-          <t>Retrouve Mireille qui cache Ti-Coune</t>
-        </is>
-      </c>
-      <c r="G121" s="19" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="18" t="inlineStr">
-        <is>
-          <t>Sarah Pelletier</t>
-        </is>
-      </c>
-      <c r="B122" s="18" t="n"/>
-      <c r="C122" s="18" t="inlineStr">
-        <is>
-          <t>Bar du Coin</t>
-        </is>
-      </c>
-      <c r="D122" s="18" t="inlineStr">
-        <is>
-          <t>Barmaid, épouse d’Hugo</t>
-        </is>
-      </c>
-      <c r="E122" s="18" t="inlineStr">
-        <is>
-          <t>Pas de mains sur le comptoir, pas d’mains sur moi.</t>
-        </is>
-      </c>
-      <c r="F122" s="18" t="inlineStr">
-        <is>
-          <t>Tient la barre pendant la tempête</t>
-        </is>
-      </c>
-      <c r="G122" s="18" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="19" t="inlineStr">
-        <is>
-          <t>Serge Potvin</t>
-        </is>
-      </c>
-      <c r="B123" s="19" t="inlineStr">
-        <is>
-          <t>Pelle</t>
-        </is>
-      </c>
-      <c r="C123" s="19" t="inlineStr">
-        <is>
-          <t>Ville / Neutre</t>
-        </is>
-      </c>
-      <c r="D123" s="19" t="inlineStr">
-        <is>
-          <t>Opérateur de déneigement</t>
-        </is>
-      </c>
-      <c r="E123" s="19" t="inlineStr">
-        <is>
-          <t>La neige tombe pour tout le monde, sauf mon horaire.</t>
-        </is>
-      </c>
-      <c r="F123" s="19" t="inlineStr">
-        <is>
-          <t>Sa niveleuse ouvre la ruelle de la descente</t>
-        </is>
-      </c>
-      <c r="G123" s="19" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="18" t="inlineStr">
-        <is>
-          <t>Solange Bouchard</t>
-        </is>
-      </c>
-      <c r="B124" s="18" t="inlineStr">
-        <is>
-          <t>La Reine de Grande-Baie</t>
-        </is>
-      </c>
-      <c r="C124" s="18" t="inlineStr">
-        <is>
-          <t>Quartier / Marge</t>
-        </is>
-      </c>
-      <c r="D124" s="18" t="inlineStr">
-        <is>
-          <t>Souverainiste de Grande-Baie</t>
-        </is>
-      </c>
-      <c r="E124" s="18" t="inlineStr">
-        <is>
-          <t>La Grande-Baie est souveraine !</t>
-        </is>
-      </c>
-      <c r="F124" s="18" t="inlineStr">
-        <is>
-          <t>Mobilise le quartier contre l’expulsion</t>
-        </is>
-      </c>
-      <c r="G124" s="18" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="19" t="inlineStr">
-        <is>
-          <t>Sonia Tremblay</t>
-        </is>
-      </c>
-      <c r="B125" s="19" t="n"/>
-      <c r="C125" s="19" t="inlineStr">
-        <is>
-          <t>Famille / Alex</t>
-        </is>
-      </c>
-      <c r="D125" s="19" t="inlineStr">
-        <is>
-          <t>Mère d’Alex Tremblay, préposée aux bénéficiaires</t>
-        </is>
-      </c>
-      <c r="E125" s="19" t="inlineStr">
-        <is>
-          <t>Mon fils sortira de sa chambre, un jour.</t>
-        </is>
-      </c>
-      <c r="F125" s="19" t="inlineStr">
-        <is>
-          <t>Débranche l'ordinateur, trouve les preuves</t>
-        </is>
-      </c>
-      <c r="G125" s="19" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="18" t="inlineStr">
-        <is>
-          <t>Steve Gauthier</t>
-        </is>
-      </c>
-      <c r="B126" s="18" t="inlineStr">
-        <is>
-          <t>Stevie Chop</t>
-        </is>
-      </c>
-      <c r="C126" s="18" t="inlineStr">
-        <is>
-          <t>Casse</t>
-        </is>
-      </c>
-      <c r="D126" s="18" t="inlineStr">
-        <is>
-          <t>Dépeceur, fournit Bobby</t>
-        </is>
-      </c>
-      <c r="E126" s="18" t="inlineStr">
-        <is>
-          <t>J'enlève juste ce qui dérange.</t>
-        </is>
-      </c>
-      <c r="F126" s="18" t="inlineStr">
-        <is>
-          <t>Démontre la voiture d’Antoine</t>
-        </is>
-      </c>
-      <c r="G126" s="18" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="19" t="inlineStr">
-        <is>
-          <t>Sylvain Bouchard</t>
-        </is>
-      </c>
-      <c r="B127" s="19" t="inlineStr">
-        <is>
-          <t>Coach Bouche</t>
-        </is>
-      </c>
-      <c r="C127" s="19" t="inlineStr">
-        <is>
-          <t>Aréna</t>
-        </is>
-      </c>
-      <c r="D127" s="19" t="inlineStr">
-        <is>
-          <t>Entraîneur hockey junior</t>
-        </is>
-      </c>
-      <c r="E127" s="19" t="inlineStr">
-        <is>
-          <t>Sur glace, pas de gang, juste une équipe.</t>
-        </is>
-      </c>
-      <c r="F127" s="19" t="inlineStr">
-        <is>
-          <t>Sort les jeunes du recrutement de Dévon</t>
-        </is>
-      </c>
-      <c r="G127" s="19" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="18" t="inlineStr">
-        <is>
-          <t>Sylvain Gagné</t>
-        </is>
-      </c>
-      <c r="B128" s="18" t="n"/>
-      <c r="C128" s="18" t="inlineStr">
-        <is>
-          <t>Ruelle / Salon</t>
-        </is>
-      </c>
-      <c r="D128" s="18" t="inlineStr">
-        <is>
-          <t>Coiffeur à domicile, conjoint de Johanne</t>
-        </is>
-      </c>
-      <c r="E128" s="18" t="inlineStr">
-        <is>
-          <t>J’entends tout sous le casque-séchoir.</t>
-        </is>
-      </c>
-      <c r="F128" s="18" t="inlineStr">
-        <is>
-          <t>Coiffe les dames et capte les rumeurs</t>
-        </is>
-      </c>
-      <c r="G128" s="18" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="19" t="inlineStr">
-        <is>
-          <t>Thérèse Gagnon</t>
-        </is>
-      </c>
-      <c r="B129" s="19" t="inlineStr">
-        <is>
-          <t>Maman Louve</t>
-        </is>
-      </c>
-      <c r="C129" s="19" t="inlineStr">
-        <is>
-          <t>Motards / Aînée</t>
-        </is>
-      </c>
-      <c r="D129" s="19" t="inlineStr">
-        <is>
-          <t>Mère de Karine et Rock, ex-Louve</t>
-        </is>
-      </c>
-      <c r="E129" s="19" t="inlineStr">
-        <is>
-          <t>Les Louves, c’était moi la première.</t>
-        </is>
-      </c>
-      <c r="F129" s="19" t="inlineStr">
-        <is>
-          <t>Protège les gamins du quartier</t>
-        </is>
-      </c>
-      <c r="G129" s="19" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="18" t="inlineStr">
-        <is>
-          <t>Thérèse Lacroix</t>
-        </is>
-      </c>
-      <c r="B130" s="18" t="n"/>
-      <c r="C130" s="18" t="inlineStr">
-        <is>
-          <t>Église</t>
-        </is>
-      </c>
-      <c r="D130" s="18" t="inlineStr">
-        <is>
-          <t>Ex-sacristine, sœur de Lucien</t>
-        </is>
-      </c>
-      <c r="E130" s="18" t="inlineStr">
-        <is>
-          <t>Les cierges coûtent cher, les péchés itou.</t>
-        </is>
-      </c>
-      <c r="F130" s="18" t="inlineStr">
-        <is>
-          <t>Ouvre la sacristie aux sans-logis</t>
-        </is>
-      </c>
-      <c r="G130" s="18" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="19" t="inlineStr">
-        <is>
-          <t>Ti-Paul Côté</t>
-        </is>
-      </c>
-      <c r="B131" s="19" t="inlineStr">
-        <is>
-          <t>Le Panier</t>
-        </is>
-      </c>
-      <c r="C131" s="19" t="inlineStr">
-        <is>
-          <t>Ruelle</t>
-        </is>
-      </c>
-      <c r="D131" s="19" t="inlineStr">
-        <is>
-          <t>Chiffonnier, copain de Réal</t>
-        </is>
-      </c>
-      <c r="E131" s="19" t="inlineStr">
-        <is>
-          <t>Une canette, c’est cinq cennes. Un secret, c’est gratuit.</t>
-        </is>
-      </c>
-      <c r="F131" s="19" t="inlineStr">
-        <is>
-          <t>Récupère une preuve dans ses chariots</t>
-        </is>
-      </c>
-      <c r="G131" s="19" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="18" t="inlineStr">
-        <is>
-          <t>Tommy Fortin</t>
-        </is>
-      </c>
-      <c r="B132" s="18" t="n"/>
-      <c r="C132" s="18" t="inlineStr">
-        <is>
-          <t>Campagne</t>
-        </is>
-      </c>
-      <c r="D132" s="18" t="inlineStr">
-        <is>
-          <t>Journalier à la bleuetière, fils d’Yves</t>
-        </is>
-      </c>
-      <c r="E132" s="18" t="inlineStr">
-        <is>
-          <t>Aux bleuets, pas de Wi-Fi, pas d’mensonge.</t>
-        </is>
-      </c>
-      <c r="F132" s="18" t="inlineStr">
-        <is>
-          <t>Voit les boîtes de contrebande aux champs</t>
-        </is>
-      </c>
-      <c r="G132" s="18" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="19" t="inlineStr">
-        <is>
-          <t>Tony Santini</t>
-        </is>
-      </c>
-      <c r="B133" s="19" t="inlineStr">
-        <is>
-          <t>Tony Capo</t>
-        </is>
-      </c>
-      <c r="C133" s="19" t="inlineStr">
-        <is>
-          <t>Santini / Quai</t>
-        </is>
-      </c>
-      <c r="D133" s="19" t="inlineStr">
-        <is>
-          <t>Lieutenant, neveu de Vittorio</t>
-        </is>
-      </c>
-      <c r="E133" s="19" t="inlineStr">
-        <is>
-          <t>Le quai et la casse, même famille.</t>
-        </is>
-      </c>
-      <c r="F133" s="19" t="inlineStr">
-        <is>
-          <t>Ordonne la pression sur Dévon</t>
-        </is>
-      </c>
-      <c r="G133" s="19" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="18" t="inlineStr">
-        <is>
-          <t>Véronique Côté</t>
-        </is>
-      </c>
-      <c r="B134" s="18" t="inlineStr">
-        <is>
-          <t>Véro</t>
-        </is>
-      </c>
-      <c r="C134" s="18" t="inlineStr">
-        <is>
-          <t>CPE / Aide</t>
-        </is>
-      </c>
-      <c r="D134" s="18" t="inlineStr">
-        <is>
-          <t>Éducatrice, collègue de Mélo</t>
-        </is>
-      </c>
-      <c r="E134" s="18" t="inlineStr">
-        <is>
-          <t>Un coco, ça sent quand ça va mal chez nous.</t>
-        </is>
-      </c>
-      <c r="F134" s="18" t="inlineStr">
-        <is>
-          <t>Porte plainte après avoir vu Lio</t>
-        </is>
-      </c>
-      <c r="G134" s="18" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="19" t="inlineStr">
-        <is>
-          <t>William McKenzie</t>
-        </is>
-      </c>
-      <c r="B135" s="19" t="inlineStr">
-        <is>
-          <t>Will</t>
-        </is>
-      </c>
-      <c r="C135" s="19" t="inlineStr">
-        <is>
-          <t>Armée / Bagotville</t>
-        </is>
-      </c>
-      <c r="D135" s="19" t="inlineStr">
-        <is>
-          <t>Militaire de la 3e Escadre</t>
-        </is>
-      </c>
-      <c r="E135" s="19" t="inlineStr">
-        <is>
-          <t>Règlements, monsieur. Rien que les règlements.</t>
-        </is>
-      </c>
-      <c r="F135" s="19" t="inlineStr">
-        <is>
-          <t>Confond un vol de nuit avec un exercice</t>
-        </is>
-      </c>
-      <c r="G135" s="19" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="18" t="inlineStr">
-        <is>
-          <t>Yan Couture</t>
-        </is>
-      </c>
-      <c r="B136" s="18" t="n"/>
-      <c r="C136" s="18" t="inlineStr">
-        <is>
-          <t>Art / Musique</t>
-        </is>
-      </c>
-      <c r="D136" s="18" t="inlineStr">
-        <is>
-          <t>Guitariste de bar, joue au bingo</t>
-        </is>
-      </c>
-      <c r="E136" s="18" t="inlineStr">
-        <is>
-          <t>Une toune pour t’souler, une autre pour t’garder.</t>
-        </is>
-      </c>
-      <c r="F136" s="18" t="inlineStr">
-        <is>
-          <t>Sa chanson devient l’hymne du bloc</t>
-        </is>
-      </c>
-      <c r="G136" s="18" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="19" t="inlineStr">
-        <is>
-          <t>Yves Fortin</t>
-        </is>
-      </c>
-      <c r="B137" s="19" t="n"/>
-      <c r="C137" s="19" t="inlineStr">
-        <is>
-          <t>Campagne</t>
-        </is>
-      </c>
-      <c r="D137" s="19" t="inlineStr">
-        <is>
-          <t>Producteur de bleuets</t>
-        </is>
-      </c>
-      <c r="E137" s="19" t="inlineStr">
-        <is>
-          <t>Les bleuets poussent seuls, les hommes non.</t>
-        </is>
-      </c>
-      <c r="F137" s="19" t="inlineStr">
-        <is>
-          <t>Compte les passages sur son chemin</t>
-        </is>
-      </c>
-      <c r="G137" s="19" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="18" t="inlineStr">
-        <is>
-          <t>Élodie Martel</t>
-        </is>
-      </c>
-      <c r="B138" s="18" t="n"/>
-      <c r="C138" s="18" t="inlineStr">
-        <is>
-          <t>Culture / Neutre</t>
-        </is>
-      </c>
-      <c r="D138" s="18" t="inlineStr">
-        <is>
-          <t>Éducatrice au Musée du Fjord</t>
-        </is>
-      </c>
-      <c r="E138" s="18" t="inlineStr">
-        <is>
-          <t>Le fjord s’en fiche de nos chicanes.</t>
-        </is>
-      </c>
-      <c r="F138" s="18" t="inlineStr">
-        <is>
-          <t>Archive une photo qui gêne</t>
-        </is>
-      </c>
-      <c r="G138" s="18" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="19" t="inlineStr">
-        <is>
-          <t>Émile Brassard</t>
-        </is>
-      </c>
-      <c r="B139" s="19" t="n"/>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t>Caserne / Urgences</t>
-        </is>
-      </c>
-      <c r="D139" s="19" t="inlineStr">
-        <is>
-          <t>Pompier, époux de MC</t>
-        </is>
-      </c>
-      <c r="E139" s="19" t="inlineStr">
-        <is>
-          <t>On éteint tout, sauf les dettes.</t>
-        </is>
-      </c>
-      <c r="F139" s="19" t="inlineStr">
-        <is>
-          <t>Premier sur la fausse alerte du Spot</t>
-        </is>
-      </c>
-      <c r="G139" s="19" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="18" t="inlineStr">
-        <is>
-          <t>Émilie Gauthier</t>
-        </is>
-      </c>
-      <c r="B140" s="18" t="n"/>
-      <c r="C140" s="18" t="inlineStr">
-        <is>
-          <t>Commerce / Neutre</t>
-        </is>
-      </c>
-      <c r="D140" s="18" t="inlineStr">
-        <is>
-          <t>Gérante du Dollarama</t>
-        </is>
-      </c>
-      <c r="E140" s="18" t="inlineStr">
-        <is>
-          <t>Tout est à 1,25, la morale de même.</t>
-        </is>
-      </c>
-      <c r="F140" s="18" t="inlineStr">
-        <is>
-          <t>La couronne de Solange sort de son magasin</t>
-        </is>
-      </c>
-      <c r="G140" s="18" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="19" t="inlineStr">
-        <is>
-          <t>Éric Boucher</t>
-        </is>
-      </c>
-      <c r="B141" s="19" t="inlineStr">
-        <is>
-          <t>Boubou</t>
-        </is>
-      </c>
-      <c r="C141" s="19" t="inlineStr">
-        <is>
-          <t>Ruelle d'en Face</t>
-        </is>
-      </c>
-      <c r="D141" s="19" t="inlineStr">
-        <is>
-          <t>Frère de Dévon, ferrailleur</t>
-        </is>
-      </c>
-      <c r="E141" s="19" t="inlineStr">
-        <is>
-          <t>La ferraille pèse, les secrets itou.</t>
-        </is>
-      </c>
-      <c r="F141" s="19" t="inlineStr">
-        <is>
-          <t>Exécute la casse sans poser de question</t>
-        </is>
-      </c>
-      <c r="G141" s="19" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="18" t="inlineStr">
-        <is>
-          <t>Albert Dufour</t>
-        </is>
-      </c>
-      <c r="B142" s="18" t="n"/>
-      <c r="C142" s="18" t="inlineStr">
-        <is>
-          <t>Ville / Famille</t>
-        </is>
-      </c>
-      <c r="D142" s="18" t="inlineStr">
-        <is>
-          <t>Ex-conseiller, père du maire</t>
-        </is>
-      </c>
-      <c r="E142" s="18" t="inlineStr">
-        <is>
-          <t>Mon fils m’a dépassé, comme le progrès.</t>
-        </is>
-      </c>
-      <c r="F142" s="18" t="inlineStr">
-        <is>
-          <t>Lâche une vieille combine immobilière</t>
-        </is>
-      </c>
-      <c r="G142" s="18" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="19" t="inlineStr">
-        <is>
-          <t>André Simard</t>
-        </is>
-      </c>
-      <c r="B143" s="19" t="inlineStr">
-        <is>
-          <t>Le Chef</t>
-        </is>
-      </c>
-      <c r="C143" s="19" t="inlineStr">
-        <is>
-          <t>Loi / Direction</t>
-        </is>
-      </c>
-      <c r="D143" s="19" t="inlineStr">
-        <is>
-          <t>Directeur du Service de police</t>
-        </is>
-      </c>
-      <c r="E143" s="19" t="inlineStr">
-        <is>
-          <t>La loi, c’est un édredon : ça cache rien longtemps.</t>
-        </is>
-      </c>
-      <c r="F143" s="19" t="inlineStr">
-        <is>
-          <t>Retient Samson ou le lâche ?</t>
-        </is>
-      </c>
-      <c r="G143" s="19" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="18" t="inlineStr">
-        <is>
-          <t>Caroline Otis</t>
-        </is>
-      </c>
-      <c r="B144" s="18" t="n"/>
-      <c r="C144" s="18" t="inlineStr">
-        <is>
-          <t>Argent / Chambre</t>
-        </is>
-      </c>
-      <c r="D144" s="18" t="inlineStr">
-        <is>
-          <t>Présidente de la Chambre de commerce</t>
-        </is>
-      </c>
-      <c r="E144" s="18" t="inlineStr">
-        <is>
-          <t>Un commerce qui dérange, c’est un commerce.</t>
-        </is>
-      </c>
-      <c r="F144" s="18" t="inlineStr">
-        <is>
-          <t>Fait pression sur les permis du Néon</t>
-        </is>
-      </c>
-      <c r="G144" s="18" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="19" t="inlineStr">
-        <is>
-          <t>Catherine Samson</t>
-        </is>
-      </c>
-      <c r="B145" s="19" t="n"/>
-      <c r="C145" s="19" t="inlineStr">
-        <is>
-          <t>Loi / Famille</t>
-        </is>
-      </c>
-      <c r="D145" s="19" t="inlineStr">
-        <is>
-          <t>Adjointe au palais, épouse de Pierre</t>
-        </is>
-      </c>
-      <c r="E145" s="19" t="inlineStr">
-        <is>
-          <t>Au palais, les dossiers ont des yeux.</t>
-        </is>
-      </c>
-      <c r="F145" s="19" t="inlineStr">
-        <is>
-          <t>Trouve les sociétés-écrans au greffe</t>
-        </is>
-      </c>
-      <c r="G145" s="19" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="18" t="inlineStr">
-        <is>
-          <t>Danny Fortin</t>
-        </is>
-      </c>
-      <c r="B146" s="18" t="inlineStr">
-        <is>
-          <t>Néon</t>
-        </is>
-      </c>
-      <c r="C146" s="18" t="inlineStr">
-        <is>
-          <t>Santini / Façade</t>
-        </is>
-      </c>
-      <c r="D146" s="18" t="inlineStr">
-        <is>
-          <t>Gérant de façade du Néon</t>
-        </is>
-      </c>
-      <c r="E146" s="18" t="inlineStr">
-        <is>
-          <t>Bienvenue au Néon : lumière pis oubli.</t>
-        </is>
-      </c>
-      <c r="F146" s="18" t="inlineStr">
-        <is>
-          <t>Sa porte d’en arrière filtre les rencontres</t>
-        </is>
-      </c>
-      <c r="G146" s="18" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="19" t="inlineStr">
-        <is>
-          <t>Denis Pedneault</t>
-        </is>
-      </c>
-      <c r="B147" s="19" t="inlineStr">
-        <is>
-          <t>Den</t>
-        </is>
-      </c>
-      <c r="C147" s="19" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="D147" s="19" t="inlineStr">
-        <is>
-          <t>Propriétaire de CKRS, cousin de Réjean</t>
-        </is>
-      </c>
-      <c r="E147" s="19" t="inlineStr">
-        <is>
-          <t>En onde, tout le monde est innocent.</t>
-        </is>
-      </c>
-      <c r="F147" s="19" t="inlineStr">
-        <is>
-          <t>Vend du temps d’antenne au plus offrant</t>
-        </is>
-      </c>
-      <c r="G147" s="19" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="18" t="inlineStr">
-        <is>
-          <t>Enzo Bianchi</t>
-        </is>
-      </c>
-      <c r="B148" s="18" t="inlineStr">
-        <is>
-          <t>Le Conseiller</t>
-        </is>
-      </c>
-      <c r="C148" s="18" t="inlineStr">
-        <is>
-          <t>Santini / Conseiller</t>
-        </is>
-      </c>
-      <c r="D148" s="18" t="inlineStr">
-        <is>
-          <t>Conseiller de Vittorio</t>
-        </is>
-      </c>
-      <c r="E148" s="18" t="inlineStr">
-        <is>
-          <t>Je suggère, jamais j’ordonne.</t>
-        </is>
-      </c>
-      <c r="F148" s="18" t="inlineStr">
-        <is>
-          <t>Négocie la sortie de Vittorio</t>
-        </is>
-      </c>
-      <c r="G148" s="18" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="19" t="inlineStr">
-        <is>
-          <t>François Côté</t>
-        </is>
-      </c>
-      <c r="B149" s="19" t="n"/>
-      <c r="C149" s="19" t="inlineStr">
-        <is>
-          <t>Presse</t>
-        </is>
-      </c>
-      <c r="D149" s="19" t="inlineStr">
-        <is>
-          <t>Rédacteur en chef du Quotidien</t>
-        </is>
-      </c>
-      <c r="E149" s="19" t="inlineStr">
-        <is>
-          <t>Une nouvelle, ça se prouve. Une rumeur, ça se vend.</t>
-        </is>
-      </c>
-      <c r="F149" s="19" t="inlineStr">
-        <is>
-          <t>Enterre ou publie le dossier</t>
-        </is>
-      </c>
-      <c r="G149" s="19" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="18" t="inlineStr">
-        <is>
-          <t>Gilles Dufour</t>
-        </is>
-      </c>
-      <c r="B150" s="18" t="inlineStr">
-        <is>
-          <t>Monsieur le Maire</t>
-        </is>
-      </c>
-      <c r="C150" s="18" t="inlineStr">
-        <is>
-          <t>Ville</t>
-        </is>
-      </c>
-      <c r="D150" s="18" t="inlineStr">
-        <is>
-          <t>Maire de Saguenay, fils d’Albert</t>
-        </is>
-      </c>
-      <c r="E150" s="18" t="inlineStr">
-        <is>
-          <t>Saguenay regarde en avant, surtout en arrière.</t>
-        </is>
-      </c>
-      <c r="F150" s="18" t="inlineStr">
-        <is>
-          <t>Pris entre la police et la Chambre</t>
-        </is>
-      </c>
-      <c r="G150" s="18" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="19" t="inlineStr">
-        <is>
-          <t>Hélène Samson</t>
-        </is>
-      </c>
-      <c r="B151" s="19" t="n"/>
-      <c r="C151" s="19" t="inlineStr">
-        <is>
-          <t>Loi / Famille</t>
-        </is>
-      </c>
-      <c r="D151" s="19" t="inlineStr">
-        <is>
-          <t>Ex-secrétaire de palais, mère de Pierre</t>
-        </is>
-      </c>
-      <c r="E151" s="19" t="inlineStr">
-        <is>
-          <t>J'ai tapé les aveux de trois générations.</t>
-        </is>
-      </c>
-      <c r="F151" s="19" t="inlineStr">
-        <is>
-          <t>Ressort les vieux dossiers Santini</t>
-        </is>
-      </c>
-      <c r="G151" s="19" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="18" t="inlineStr">
-        <is>
-          <t>Isabelle Gagné</t>
-        </is>
-      </c>
-      <c r="B152" s="18" t="n"/>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>Politique</t>
-        </is>
-      </c>
-      <c r="D152" s="18" t="inlineStr">
-        <is>
-          <t>Députée à l’Assemblée nationale</t>
-        </is>
-      </c>
-      <c r="E152" s="18" t="inlineStr">
-        <is>
-          <t>À Québec, vos ruelles, c’est abstrait.</t>
-        </is>
-      </c>
-      <c r="F152" s="18" t="inlineStr">
-        <is>
-          <t>Promet des fonds puis disparaît</t>
-        </is>
-      </c>
-      <c r="G152" s="18" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="19" t="inlineStr">
-        <is>
-          <t>Jonathan Roy</t>
-        </is>
-      </c>
-      <c r="B153" s="19" t="inlineStr">
-        <is>
-          <t>Johnny Fake</t>
-        </is>
-      </c>
-      <c r="C153" s="19" t="inlineStr">
-        <is>
-          <t>Réseau / Louche</t>
-        </is>
-      </c>
-      <c r="D153" s="19" t="inlineStr">
-        <is>
-          <t>Fausses identités, boulevard Talbot</t>
-        </is>
-      </c>
-      <c r="E153" s="19" t="inlineStr">
-        <is>
-          <t>Qui tu veux être aujourd’hui ? J’ai le papier.</t>
-        </is>
-      </c>
-      <c r="F153" s="19" t="inlineStr">
-        <is>
-          <t>Fabrique l’identité du témoin</t>
-        </is>
-      </c>
-      <c r="G153" s="19" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="18" t="inlineStr">
-        <is>
-          <t>Julien Gagné</t>
-        </is>
-      </c>
-      <c r="B154" s="18" t="inlineStr">
-        <is>
-          <t>Le Volant</t>
-        </is>
-      </c>
-      <c r="C154" s="18" t="inlineStr">
-        <is>
-          <t>Santini</t>
-        </is>
-      </c>
-      <c r="D154" s="18" t="inlineStr">
-        <is>
-          <t>Chauffeur de Vittorio</t>
-        </is>
-      </c>
-      <c r="E154" s="18" t="inlineStr">
-        <is>
-          <t>J'demande pas où on va, c'est mieux.</t>
-        </is>
-      </c>
-      <c r="F154" s="18" t="inlineStr">
-        <is>
-          <t>Conduit la mauvaise nuit</t>
-        </is>
-      </c>
-      <c r="G154" s="18" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="19" t="inlineStr">
-        <is>
-          <t>Louise Villeneuve</t>
-        </is>
-      </c>
-      <c r="B155" s="19" t="n"/>
-      <c r="C155" s="19" t="inlineStr">
-        <is>
-          <t>Loi / Magistrature</t>
-        </is>
-      </c>
-      <c r="D155" s="19" t="inlineStr">
-        <is>
-          <t>Juge à la Cour du Québec</t>
-        </is>
-      </c>
-      <c r="E155" s="19" t="inlineStr">
-        <is>
-          <t>La balance penche du côté des preuves.</t>
-        </is>
-      </c>
-      <c r="F155" s="19" t="inlineStr">
-        <is>
-          <t>Signe les mandats du bloc</t>
-        </is>
-      </c>
-      <c r="G155" s="19" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="18" t="inlineStr">
-        <is>
-          <t>Maria Santini</t>
-        </is>
-      </c>
-      <c r="B156" s="18" t="inlineStr">
-        <is>
-          <t>Donna Maria</t>
-        </is>
-      </c>
-      <c r="C156" s="18" t="inlineStr">
-        <is>
-          <t>Santini / Famille</t>
-        </is>
-      </c>
-      <c r="D156" s="18" t="inlineStr">
-        <is>
-          <t>Matriarche, restaurant familial</t>
-        </is>
-      </c>
-      <c r="E156" s="18" t="inlineStr">
-        <is>
-          <t>Mange. Les affaires attendent, les pâtes non.</t>
-        </is>
-      </c>
-      <c r="F156" s="18" t="inlineStr">
-        <is>
-          <t>Négocie la clémence en cuisine</t>
-        </is>
-      </c>
-      <c r="G156" s="18" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="19" t="inlineStr">
-        <is>
-          <t>Mei Chen</t>
-        </is>
-      </c>
-      <c r="B157" s="19" t="n"/>
-      <c r="C157" s="19" t="inlineStr">
-        <is>
-          <t>Commerces / Famille</t>
-        </is>
-      </c>
-      <c r="D157" s="19" t="inlineStr">
-        <is>
-          <t>Préposée d’hôtel, mère de Justin</t>
-        </is>
-      </c>
-      <c r="E157" s="19" t="inlineStr">
-        <is>
-          <t>Mon fils se croit riche, il est juste jeune.</t>
-        </is>
-      </c>
-      <c r="F157" s="19" t="inlineStr">
-        <is>
-          <t>Héberge les témoins à l’hôtel</t>
-        </is>
-      </c>
-      <c r="G157" s="19" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="18" t="inlineStr">
-        <is>
-          <t>Mgr Paul Tremblay</t>
-        </is>
-      </c>
-      <c r="B158" s="18" t="inlineStr">
-        <is>
-          <t>Monseigneur</t>
-        </is>
-      </c>
-      <c r="C158" s="18" t="inlineStr">
-        <is>
-          <t>Église / Diocèse</t>
-        </is>
-      </c>
-      <c r="D158" s="18" t="inlineStr">
-        <is>
-          <t>Évêque, supérieur de Lucien</t>
-        </is>
-      </c>
-      <c r="E158" s="18" t="inlineStr">
-        <is>
-          <t>L'Église écoute. L'Église se tait. Parfois.</t>
-        </is>
-      </c>
-      <c r="F158" s="18" t="inlineStr">
-        <is>
-          <t>Doit muter Lucien au mauvais moment</t>
-        </is>
-      </c>
-      <c r="G158" s="18" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="19" t="inlineStr">
-        <is>
-          <t>Nico Santini</t>
-        </is>
-      </c>
-      <c r="B159" s="19" t="inlineStr">
-        <is>
-          <t>Nico</t>
-        </is>
-      </c>
-      <c r="C159" s="19" t="inlineStr">
-        <is>
-          <t>Santini / Relève</t>
-        </is>
-      </c>
-      <c r="D159" s="19" t="inlineStr">
-        <is>
-          <t>Fils de Vittorio et Maria</t>
-        </is>
-      </c>
-      <c r="E159" s="19" t="inlineStr">
-        <is>
-          <t>J'suis prêt, parrain. J'suis prêt.</t>
-        </is>
-      </c>
-      <c r="F159" s="19" t="inlineStr">
-        <is>
-          <t>Envoyé en premier, il flanche</t>
-        </is>
-      </c>
-      <c r="G159" s="19" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="18" t="inlineStr">
-        <is>
-          <t>Olivier Savard</t>
-        </is>
-      </c>
-      <c r="B160" s="18" t="n"/>
-      <c r="C160" s="18" t="inlineStr">
-        <is>
-          <t>Presse</t>
-        </is>
-      </c>
-      <c r="D160" s="18" t="inlineStr">
-        <is>
-          <t>Journaliste, ex-collègue de JP</t>
-        </is>
-      </c>
-      <c r="E160" s="18" t="inlineStr">
-        <is>
-          <t>Ta source, elle s’appelle comment déjà ?</t>
-        </is>
-      </c>
-      <c r="F160" s="18" t="inlineStr">
-        <is>
-          <t>Reçoit les bandes d’Alex</t>
-        </is>
-      </c>
-      <c r="G160" s="18" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="19" t="inlineStr">
-        <is>
-          <t>Paul-André Côté</t>
-        </is>
-      </c>
-      <c r="B161" s="19" t="inlineStr">
-        <is>
-          <t>Le Chiffre</t>
-        </is>
-      </c>
-      <c r="C161" s="19" t="inlineStr">
-        <is>
-          <t>Santini / Argent</t>
-        </is>
-      </c>
-      <c r="D161" s="19" t="inlineStr">
-        <is>
-          <t>Comptable des sociétés-écrans</t>
-        </is>
-      </c>
-      <c r="E161" s="19" t="inlineStr">
-        <is>
-          <t>Deux et deux font cinq si je signe.</t>
-        </is>
-      </c>
-      <c r="F161" s="19" t="inlineStr">
-        <is>
-          <t>Les livres basculent entre ses mains</t>
-        </is>
-      </c>
-      <c r="G161" s="19" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="18" t="inlineStr">
-        <is>
-          <t>Sophie Labbé</t>
-        </is>
-      </c>
-      <c r="B162" s="18" t="n"/>
-      <c r="C162" s="18" t="inlineStr">
-        <is>
-          <t>Aide / Université</t>
-        </is>
-      </c>
-      <c r="D162" s="18" t="inlineStr">
-        <is>
-          <t>Psychologue, collègue de Laurie</t>
-        </is>
-      </c>
-      <c r="E162" s="18" t="inlineStr">
-        <is>
-          <t>Assieds-toi. On a toute la séance.</t>
-        </is>
-      </c>
-      <c r="F162" s="18" t="inlineStr">
-        <is>
-          <t>Évalue les mineurs de l’affaire</t>
-        </is>
-      </c>
-      <c r="G162" s="18" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="19" t="inlineStr">
-        <is>
-          <t>Vittorio Santini</t>
-        </is>
-      </c>
-      <c r="B163" s="19" t="inlineStr">
-        <is>
-          <t>Don Vittorio</t>
-        </is>
-      </c>
-      <c r="C163" s="19" t="inlineStr">
-        <is>
-          <t>Santini / Sommet</t>
-        </is>
-      </c>
-      <c r="D163" s="19" t="inlineStr">
-        <is>
-          <t>Patriarche, restauration et bars</t>
-        </is>
-      </c>
-      <c r="E163" s="19" t="inlineStr">
-        <is>
-          <t>La famille, c’est une entreprise avec des tombes.</t>
-        </is>
-      </c>
-      <c r="F163" s="19" t="inlineStr">
-        <is>
-          <t>Propose un deal à Samson</t>
-        </is>
-      </c>
-      <c r="G163" s="19" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="18" t="inlineStr">
-        <is>
-          <t>Éric Simard</t>
-        </is>
-      </c>
-      <c r="B164" s="18" t="inlineStr">
-        <is>
-          <t>Ti-Eric</t>
-        </is>
-      </c>
-      <c r="C164" s="18" t="inlineStr">
-        <is>
-          <t>Cégep / Naïf</t>
-        </is>
-      </c>
-      <c r="D164" s="18" t="inlineStr">
-        <is>
-          <t>Coloc de Justin Chen</t>
-        </is>
-      </c>
-      <c r="E164" s="18" t="inlineStr">
-        <is>
-          <t>Wô, c’tait pas supposé aller loin, ça.</t>
-        </is>
-      </c>
-      <c r="F164" s="18" t="inlineStr">
-        <is>
-          <t>Témoin gênant de la soirée Chen</t>
-        </is>
-      </c>
-      <c r="G164" s="18" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="19" t="inlineStr">
-        <is>
-          <t>Benoit Larouche</t>
-        </is>
-      </c>
-      <c r="B165" s="19" t="n"/>
-      <c r="C165" s="19" t="inlineStr">
-        <is>
-          <t>ATM / École</t>
-        </is>
-      </c>
-      <c r="D165" s="19" t="inlineStr">
-        <is>
-          <t>Prof de cinéma d’Antoine</t>
-        </is>
-      </c>
-      <c r="E165" s="19" t="inlineStr">
-        <is>
-          <t>Le cinéma, c’est regarder deux fois.</t>
-        </is>
-      </c>
-      <c r="F165" s="19" t="inlineStr">
-        <is>
-          <t>Oblige Antoine à rendre les images</t>
-        </is>
-      </c>
-      <c r="G165" s="19" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="18" t="inlineStr">
-        <is>
-          <t>Camille Lefèvre</t>
-        </is>
-      </c>
-      <c r="B166" s="18" t="n"/>
-      <c r="C166" s="18" t="inlineStr">
-        <is>
-          <t>ATM / Art</t>
-        </is>
-      </c>
-      <c r="D166" s="18" t="inlineStr">
-        <is>
-          <t>Étudiante en comm, sœur d’Antoine</t>
-        </is>
-      </c>
-      <c r="E166" s="18" t="inlineStr">
-        <is>
-          <t>Une photo, ça trahit pas, ça révèle.</t>
-        </is>
-      </c>
-      <c r="F166" s="18" t="inlineStr">
-        <is>
-          <t>Tire les clichés qui manquent</t>
-        </is>
-      </c>
-      <c r="G166" s="18" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="19" t="inlineStr">
-        <is>
-          <t>Dany Aubin</t>
-        </is>
-      </c>
-      <c r="B167" s="19" t="n"/>
-      <c r="C167" s="19" t="inlineStr">
-        <is>
-          <t>Famille / Aubin</t>
-        </is>
-      </c>
-      <c r="D167" s="19" t="inlineStr">
-        <is>
-          <t>Soudeur, frère de Sam</t>
-        </is>
-      </c>
-      <c r="E167" s="19" t="inlineStr">
-        <is>
-          <t>La soudure ferme les trous, les familles non.</t>
-        </is>
-      </c>
-      <c r="F167" s="19" t="inlineStr">
-        <is>
-          <t>Descend à La Baie soutenir Sam</t>
-        </is>
-      </c>
-      <c r="G167" s="19" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="18" t="inlineStr">
-        <is>
-          <t>Gérald Tremblay</t>
-        </is>
-      </c>
-      <c r="B168" s="18" t="inlineStr">
-        <is>
-          <t>Le Syndic</t>
-        </is>
-      </c>
-      <c r="C168" s="18" t="inlineStr">
-        <is>
-          <t>Aluminerie / Syndicat</t>
-        </is>
-      </c>
-      <c r="D168" s="18" t="inlineStr">
-        <is>
-          <t>Délégué syndical, collègue de Mathieu</t>
-        </is>
-      </c>
-      <c r="E168" s="18" t="inlineStr">
-        <is>
-          <t>La convention dit ça, et elle a raison.</t>
-        </is>
-      </c>
-      <c r="F168" s="18" t="inlineStr">
-        <is>
-          <t>Son grief devient un levier</t>
-        </is>
-      </c>
-      <c r="G168" s="18" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="19" t="inlineStr">
-        <is>
-          <t>Jean-Marc Fortin</t>
-        </is>
-      </c>
-      <c r="B169" s="19" t="n"/>
-      <c r="C169" s="19" t="inlineStr">
-        <is>
-          <t>Aluminerie / Direction</t>
-        </is>
-      </c>
-      <c r="D169" s="19" t="inlineStr">
-        <is>
-          <t>Directeur d’usine à Arvida</t>
-        </is>
-      </c>
-      <c r="E169" s="19" t="inlineStr">
-        <is>
-          <t>Un four ne négocie pas.</t>
-        </is>
-      </c>
-      <c r="F169" s="19" t="inlineStr">
-        <is>
-          <t>Gère une saisie de conteneurs à l'usine</t>
-        </is>
-      </c>
-      <c r="G169" s="19" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="18" t="inlineStr">
-        <is>
-          <t>Mélissa Harvey</t>
-        </is>
-      </c>
-      <c r="B170" s="18" t="n"/>
-      <c r="C170" s="18" t="inlineStr">
-        <is>
-          <t>ATM / Art</t>
-        </is>
-      </c>
-      <c r="D170" s="18" t="inlineStr">
-        <is>
-          <t>Étudiante ATM, nièce de François</t>
-        </is>
-      </c>
-      <c r="E170" s="18" t="inlineStr">
-        <is>
-          <t>Je filme tout, même ce qui faut pas.</t>
-        </is>
-      </c>
-      <c r="F170" s="18" t="inlineStr">
-        <is>
-          <t>Sa perche capte une confession</t>
-        </is>
-      </c>
-      <c r="G170" s="18" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="19" t="inlineStr">
-        <is>
-          <t>Nicolas Gagné</t>
-        </is>
-      </c>
-      <c r="B171" s="19" t="n"/>
-      <c r="C171" s="19" t="inlineStr">
-        <is>
-          <t>Aluminerie / Syndiqué</t>
-        </is>
-      </c>
-      <c r="D171" s="19" t="inlineStr">
-        <is>
-          <t>Technicien, collègue de Mathieu</t>
-        </is>
-      </c>
-      <c r="E171" s="19" t="inlineStr">
-        <is>
-          <t>Le métal pardonne, le contremaître non.</t>
-        </is>
-      </c>
-      <c r="F171" s="19" t="inlineStr">
-        <is>
-          <t>Repère des cargaisons marquées</t>
-        </is>
-      </c>
-      <c r="G171" s="19" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="18" t="inlineStr">
-        <is>
-          <t>Léo Cloutier</t>
-        </is>
-      </c>
-      <c r="B172" s="18" t="inlineStr">
-        <is>
-          <t>Lio</t>
-        </is>
-      </c>
-      <c r="C172" s="18" t="inlineStr">
-        <is>
-          <t>Famille / Ruelle</t>
-        </is>
-      </c>
-      <c r="D172" s="18" t="inlineStr">
-        <is>
-          <t>P’tit frère de Ti-Coune</t>
-        </is>
-      </c>
-      <c r="E172" s="18" t="inlineStr">
-        <is>
-          <t>Mon grand frère, y’est connu, moé.</t>
-        </is>
-      </c>
-      <c r="F172" s="18" t="inlineStr">
-        <is>
-          <t>Voit Dave se faire pognner</t>
-        </is>
-      </c>
-      <c r="G172" s="18" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="19" t="inlineStr">
-        <is>
-          <t>Nour Benali</t>
-        </is>
-      </c>
-      <c r="B173" s="19" t="n"/>
-      <c r="C173" s="19" t="inlineStr">
-        <is>
-          <t>Dépanneur / Famille</t>
-        </is>
-      </c>
-      <c r="D173" s="19" t="inlineStr">
-        <is>
-          <t>Fait ses devoirs sur le comptoir</t>
-        </is>
-      </c>
-      <c r="E173" s="19" t="inlineStr">
-        <is>
-          <t>Maman, quelqu’un veut encore du crédit.</t>
-        </is>
-      </c>
-      <c r="F173" s="19" t="inlineStr">
-        <is>
-          <t>Tient le vrai registre des dettes</t>
-        </is>
-      </c>
-      <c r="G173" s="19" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="18" t="inlineStr">
-        <is>
-          <t>Alexandre Lavoie</t>
-        </is>
-      </c>
-      <c r="B174" s="18" t="inlineStr">
-        <is>
-          <t>Le Cadet</t>
-        </is>
-      </c>
-      <c r="C174" s="18" t="inlineStr">
-        <is>
-          <t>Famille JP / Aréna</t>
-        </is>
-      </c>
-      <c r="D174" s="18" t="inlineStr">
-        <is>
-          <t>Frère cadet de JP, hockey juvénile</t>
-        </is>
-      </c>
-      <c r="E174" s="18" t="inlineStr">
-        <is>
-          <t>J'vas m'rendre dans la Ligue un jour, moé.</t>
-        </is>
-      </c>
-      <c r="F174" s="18" t="inlineStr">
-        <is>
-          <t>Veut que JP revienne à la maison</t>
-        </is>
-      </c>
-      <c r="G174" s="18" t="n">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G174"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/base_personnages_fictifs.xlsx
+++ b/base_personnages_fictifs.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Lisez-moi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$P$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$P$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P174"/>
+  <dimension ref="A1:P184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6515,21 +6515,25 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Maxime Boivin</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="n"/>
+          <t>Mathis Truchon</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Ti-Pompe</t>
+        </is>
+      </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Vétérinaire</t>
+          <t>Pompiste — dépanneur de route</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -6539,56 +6543,56 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>180, Rue Cimon</t>
+          <t>1456, Route du Petit-Parc</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>48.3428</v>
+        <v>48.30545</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>-70.881</v>
+        <v>-70.90805</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Barbe, blouse</t>
+          <t>Moustache naissante, casquette camo</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Blouse véto</t>
+          <t>Manteau de travail à bandes</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Stéthoscope animal</t>
+          <t>Cigarette derrière l’oreille</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>portraits/90-maxime-boivin-web.webp</t>
+          <t>portraits/178-mathis-truchon-web.webp</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Boivin</t>
+          <t>Truchon</t>
         </is>
       </c>
       <c r="O84" s="2" t="n"/>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>Célibataire — véto du quartier</t>
+          <t>Fils d’Yvan Truchon et Gisèle</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Michel Lavoie</t>
+          <t>Maude Pedneault</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Lady Dynamite</t>
+          <t>La Zèbre</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -6597,11 +6601,11 @@
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Drag queen — animatrice de bingo</t>
+          <t>Arbitre — hockey mineur</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -6611,73 +6615,65 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>210, Rue Bagot</t>
+          <t>24, Avenue du Port</t>
         </is>
       </c>
       <c r="H85" s="7" t="n">
-        <v>48.337959</v>
+        <v>48.33045</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>-70.88593899999999</v>
+        <v>-70.89445000000001</v>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>Perruque blonde volumineuse, maquillage élégant</t>
+          <t>Queue de cheval, regard décidé</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>Veste paillettes</t>
+          <t>Chandail rayé d’arbitre</t>
         </is>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>Anime bingo</t>
+          <t>Sifflet au cou</t>
         </is>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>portraits/23-michel-lavoie-web.webp</t>
+          <t>portraits/174-maude-pedneault-web.webp</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr">
         <is>
-          <t>Lavoie</t>
-        </is>
-      </c>
-      <c r="O85" s="5" t="inlineStr">
-        <is>
-          <t>Michel</t>
-        </is>
-      </c>
+          <t>Pedneault</t>
+        </is>
+      </c>
+      <c r="O85" s="5" t="n"/>
       <c r="P85" s="5" t="inlineStr">
         <is>
-          <t>Fils de Claude</t>
+          <t>Petite-fille de Réjean et Céline Pedneault</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Mireille Joseph</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Mamie Mireille</t>
-        </is>
-      </c>
+          <t>Maxime Boivin</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n"/>
       <c r="C86" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Gardienne d'enfants — herboriste</t>
+          <t>Vétérinaire</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -6687,65 +6683,69 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>160, Rue des Lilas</t>
+          <t>180, Rue Cimon</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>48.341885</v>
+        <v>48.3428</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>-70.896035</v>
+        <v>-70.881</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Haïtienne, cheveux gris courts</t>
+          <t>Barbe, blouse</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Tablier cuisine</t>
+          <t>Blouse véto</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Thé plantes</t>
+          <t>Stéthoscope animal</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>portraits/27-mireille-joseph-web.webp</t>
+          <t>portraits/90-maxime-boivin-web.webp</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Boivin</t>
         </is>
       </c>
       <c r="O86" s="2" t="n"/>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>Mère de Samuel</t>
+          <t>Célibataire — véto du quartier</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Monique Bouchard</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="n"/>
+          <t>Michel Lavoie</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Lady Dynamite</t>
+        </is>
+      </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Retraitée — ex-couturière</t>
+          <t>Drag queen — animatrice de bingo</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -6755,60 +6755,60 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>700, Rue du Docteur-Tanguay</t>
+          <t>210, Rue Bagot</t>
         </is>
       </c>
       <c r="H87" s="7" t="n">
-        <v>48.339524</v>
+        <v>48.337959</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>-70.876985</v>
+        <v>-70.88593899999999</v>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>Bouclés roux</t>
+          <t>Perruque blonde volumineuse, maquillage élégant</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>Cardigan</t>
+          <t>Veste paillettes</t>
         </is>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>Confiture bleuets</t>
+          <t>Anime bingo</t>
         </is>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>portraits/38-monique-bouchard-web.webp</t>
+          <t>portraits/23-michel-lavoie-web.webp</t>
         </is>
       </c>
       <c r="N87" s="5" t="inlineStr">
         <is>
-          <t>Lapointe</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O87" s="5" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="P87" s="5" t="inlineStr">
         <is>
-          <t>Mère de Marco</t>
+          <t>Fils de Claude</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Mélanie Dubé</t>
+          <t>Mireille Joseph</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Mélo</t>
+          <t>Mamie Mireille</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -6817,11 +6817,11 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Éducatrice en CPE</t>
+          <t>Gardienne d'enfants — herboriste</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -6831,51 +6831,51 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>260, Rue de la Colline</t>
+          <t>160, Rue des Lilas</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>48.341675</v>
+        <v>48.341885</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>-70.88487000000001</v>
+        <v>-70.896035</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Claire, cheveux attachés</t>
+          <t>Haïtienne, cheveux gris courts</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Chandail CPE</t>
+          <t>Tablier cuisine</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Porte-clés kid</t>
+          <t>Thé plantes</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>portraits/15-melanie-dube-web.webp</t>
+          <t>portraits/27-mireille-joseph-web.webp</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Dubé</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O88" s="2" t="n"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>Sœur de Carl</t>
+          <t>Mère de Samuel</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Nadia Benali</t>
+          <t>Monique Bouchard</t>
         </is>
       </c>
       <c r="B89" s="5" t="n"/>
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Aide-caissière — dépanneur</t>
+          <t>Retraitée — ex-couturière</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -6899,65 +6899,73 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>1312, Rue Victoria</t>
+          <t>700, Rue du Docteur-Tanguay</t>
         </is>
       </c>
       <c r="H89" s="7" t="n">
-        <v>48.34541</v>
+        <v>48.339524</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>-70.8797</v>
+        <v>-70.876985</v>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>Hijab bleu marine, regard franc</t>
+          <t>Bouclés roux</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>Polo dépanneur</t>
+          <t>Cardigan</t>
         </is>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>Calepin dettes</t>
+          <t>Confiture bleuets</t>
         </is>
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>portraits/41-nadia-benali-web.webp</t>
+          <t>portraits/38-monique-bouchard-web.webp</t>
         </is>
       </c>
       <c r="N89" s="5" t="inlineStr">
         <is>
-          <t>Benali</t>
-        </is>
-      </c>
-      <c r="O89" s="5" t="n"/>
+          <t>Lapointe</t>
+        </is>
+      </c>
+      <c r="O89" s="5" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
       <c r="P89" s="5" t="inlineStr">
         <is>
-          <t>Épouse d’Ahmed Benali</t>
+          <t>Mère de Marco</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Nancy Dubois</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="n"/>
+          <t>Mélanie Dubé</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Mélo</t>
+        </is>
+      </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Serveuse de bar</t>
+          <t>Éducatrice en CPE</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -6967,51 +6975,51 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>90, Rue Saint-Denis</t>
+          <t>260, Rue de la Colline</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>48.3175</v>
+        <v>48.341675</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>-70.86132000000001</v>
+        <v>-70.88487000000001</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Petite, cheveux noirs</t>
+          <t>Claire, cheveux attachés</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>T-shirt du bar</t>
+          <t>Chandail CPE</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Plateau de verres</t>
+          <t>Porte-clés kid</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>portraits/58-nancy-dubois-web.webp</t>
+          <t>portraits/15-melanie-dube-web.webp</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Dubois</t>
+          <t>Dubé</t>
         </is>
       </c>
       <c r="O90" s="2" t="n"/>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>Sœur de Patrice Dubois</t>
+          <t>Sœur de Carl</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Natasha Vollant</t>
+          <t>Nadia Benali</t>
         </is>
       </c>
       <c r="B91" s="5" t="n"/>
@@ -7021,11 +7029,11 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Guide — parc du Fjord-du-Saguenay</t>
+          <t>Aide-caissière — dépanneur</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -7035,51 +7043,51 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Lieu-dit : sentier Eucher</t>
+          <t>1312, Rue Victoria</t>
         </is>
       </c>
       <c r="H91" s="7" t="n">
-        <v>48.356</v>
+        <v>48.34541</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>-70.83799999999999</v>
+        <v>-70.8797</v>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>Innue, tresses, calme</t>
+          <t>Hijab bleu marine, regard franc</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>Manteau outdoor</t>
+          <t>Polo dépanneur</t>
         </is>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>Jumelles</t>
+          <t>Calepin dettes</t>
         </is>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>portraits/98-natasha-vollant-web.webp</t>
+          <t>portraits/41-nadia-benali-web.webp</t>
         </is>
       </c>
       <c r="N91" s="5" t="inlineStr">
         <is>
-          <t>Vollant</t>
+          <t>Benali</t>
         </is>
       </c>
       <c r="O91" s="5" t="n"/>
       <c r="P91" s="5" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Épouse d’Ahmed Benali</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Nathalie Bouchard</t>
+          <t>Nancy Dubois</t>
         </is>
       </c>
       <c r="B92" s="2" t="n"/>
@@ -7089,11 +7097,11 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Préposée IGA</t>
+          <t>Serveuse de bar</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -7103,73 +7111,65 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>14, Rue des Mésanges</t>
+          <t>90, Rue Saint-Denis</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>48.31795</v>
+        <v>48.3175</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>-70.8981</v>
+        <v>-70.86132000000001</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Carré blond, lunettes</t>
+          <t>Petite, cheveux noirs</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Tablier IGA</t>
+          <t>T-shirt du bar</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Sacs réutilisables</t>
+          <t>Plateau de verres</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>portraits/45-nathalie-bouchard-web.webp</t>
+          <t>portraits/58-nancy-dubois-web.webp</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Bouchard</t>
-        </is>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>Chloé</t>
-        </is>
-      </c>
+          <t>Dubois</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="n"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>Mère de Chloé Bouchard</t>
+          <t>Sœur de Patrice Dubois</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Normand Boucher</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>Norm</t>
-        </is>
-      </c>
+          <t>Natasha Vollant</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n"/>
       <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Ferrailleur — casse illégale</t>
+          <t>Guide — parc du Fjord-du-Saguenay</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -7179,51 +7179,51 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2412, Chemin Saint-Anicet</t>
+          <t>Lieu-dit : sentier Eucher</t>
         </is>
       </c>
       <c r="H93" s="7" t="n">
-        <v>48.33025</v>
+        <v>48.356</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>-70.9328</v>
+        <v>-70.83799999999999</v>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>Cicatrice à la joue</t>
+          <t>Innue, tresses, calme</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>Manteau de travail</t>
+          <t>Manteau outdoor</t>
         </is>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>Chalumeau</t>
+          <t>Jumelles</t>
         </is>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>portraits/117-normand-boucher-web.webp</t>
+          <t>portraits/98-natasha-vollant-web.webp</t>
         </is>
       </c>
       <c r="N93" s="5" t="inlineStr">
         <is>
-          <t>Boucher</t>
+          <t>Vollant</t>
         </is>
       </c>
       <c r="O93" s="5" t="n"/>
       <c r="P93" s="5" t="inlineStr">
         <is>
-          <t>Cousin de Dévon et Éric Boucher</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Nour Benali</t>
+          <t>Nathalie Bouchard</t>
         </is>
       </c>
       <c r="B94" s="2" t="n"/>
@@ -7233,11 +7233,11 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Élève du secondaire — aide au dépanneur</t>
+          <t>Préposée IGA</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -7247,69 +7247,69 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1314, Rue Victoria</t>
+          <t>14, Rue des Mésanges</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>48.34545</v>
+        <v>48.31795</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>-70.87975</v>
+        <v>-70.8981</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Hijab beige, cahiers d’école empilés sous le comptoir</t>
+          <t>Carré blond, lunettes</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Fleece marine et jeans</t>
+          <t>Tablier IGA</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Manuels scolaires ouverts sur le comptoir-caisse</t>
+          <t>Sacs réutilisables</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>portraits/172-nour-benali-web.webp</t>
+          <t>portraits/45-nathalie-bouchard-web.webp</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Benali</t>
-        </is>
-      </c>
-      <c r="O94" s="2" t="n"/>
+          <t>Bouchard</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Chloé</t>
+        </is>
+      </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>Fille d’Ahmed et Nadia Benali — sœur d’Hassan</t>
+          <t>Mère de Chloé Bouchard</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Patrice Dubois</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>P'tit Pat</t>
-        </is>
-      </c>
+          <t>Noah Traoré</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n"/>
       <c r="C95" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Videur de bar</t>
+          <t>Élève du secondaire — planchiste</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -7319,65 +7319,69 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>88, Rue Saint-Denis</t>
+          <t>510, Rue Victoria</t>
         </is>
       </c>
       <c r="H95" s="7" t="n">
-        <v>48.317374</v>
+        <v>48.34315</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>-70.861193</v>
+        <v>-70.88015</v>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>Petite stature 4'6, massive</t>
+          <t>Grand, écouteurs au cou</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>Costume videur noir</t>
+          <t>Hoodie trop grand, tuque</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>Bras croisés</t>
+          <t>Planche à roulettes usée</t>
         </is>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>portraits/30-patrice-dubois-web.webp</t>
+          <t>portraits/180-noah-traore-web.webp</t>
         </is>
       </c>
       <c r="N95" s="5" t="inlineStr">
         <is>
-          <t>Dubois</t>
+          <t>Traoré</t>
         </is>
       </c>
       <c r="O95" s="5" t="n"/>
       <c r="P95" s="5" t="inlineStr">
         <is>
-          <t>Frère de Nancy</t>
+          <t>Neveu d’Amina Traoré</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Paule Desbiens</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="n"/>
+          <t>Normand Boucher</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Norm</t>
+        </is>
+      </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Notaire</t>
+          <t>Ferrailleur — casse illégale</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -7387,51 +7391,51 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>150, Rue Victoria</t>
+          <t>2412, Chemin Saint-Anicet</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>48.3412</v>
+        <v>48.33025</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>-70.879</v>
+        <v>-70.9328</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Cheveux châtains, lunettes</t>
+          <t>Cicatrice à la joue</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Tailleur gris</t>
+          <t>Manteau de travail</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Cachet de notaire</t>
+          <t>Chalumeau</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>portraits/81-paule-desbiens-web.webp</t>
+          <t>portraits/117-normand-boucher-web.webp</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Desbiens</t>
+          <t>Boucher</t>
         </is>
       </c>
       <c r="O96" s="2" t="n"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Cousin de Dévon et Éric Boucher</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Pauline Fortin</t>
+          <t>Nour Benali</t>
         </is>
       </c>
       <c r="B97" s="5" t="n"/>
@@ -7441,11 +7445,11 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Maraîchère — kiosque routier</t>
+          <t>Élève du secondaire — aide au dépanneur</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -7455,56 +7459,56 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2100, Chemin Saint-Anicet</t>
+          <t>1314, Rue Victoria</t>
         </is>
       </c>
       <c r="H97" s="7" t="n">
-        <v>48.3287</v>
+        <v>48.34545</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>-70.9277</v>
+        <v>-70.87975</v>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>Cheveux gris coupés court</t>
+          <t>Hijab beige, cahiers d’école empilés sous le comptoir</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
-          <t>Tablier de kiosque</t>
+          <t>Fleece marine et jeans</t>
         </is>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>Balance romaine</t>
+          <t>Manuels scolaires ouverts sur le comptoir-caisse</t>
         </is>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>portraits/71-pauline-fortin-web.webp</t>
+          <t>portraits/172-nour-benali-web.webp</t>
         </is>
       </c>
       <c r="N97" s="5" t="inlineStr">
         <is>
-          <t>Fortin</t>
+          <t>Benali</t>
         </is>
       </c>
       <c r="O97" s="5" t="n"/>
       <c r="P97" s="5" t="inlineStr">
         <is>
-          <t>Épouse d’Yves Fortin</t>
+          <t>Fille d’Ahmed et Nadia Benali — sœur d’Hassan</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Philippe Villeneuve</t>
+          <t>Océane Lapointe</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Dr Phil</t>
+          <t>Zamboni</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -7513,11 +7517,11 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Médecin — Hôpital de La Baie</t>
+          <t>Préposée à l’aréna — resurfaceuse</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -7527,69 +7531,73 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>74, Rue du Docteur-Desgagné</t>
+          <t>720, Rue du Docteur-Tanguay</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>48.3441</v>
+        <v>48.33955</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>-70.8839</v>
+        <v>-70.87654999999999</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Cheveux gris, blouse</t>
+          <t>Cheveux courts teints, l’air fière</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Blouse d’hôpital</t>
+          <t>Manteau de la Ville</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Stylo poche</t>
+          <t>Thermos cabossé</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>portraits/95-philippe-villeneuve-web.webp</t>
+          <t>portraits/179-oceane-lapointe-web.webp</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Villeneuve</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>hôpital</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Fille de Patrick Lapointe — nièce de Marco</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Pierrette Simard</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="n"/>
+          <t>Patrice Dubois</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>P'tit Pat</t>
+        </is>
+      </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Retraitée — ex-caissière IGA</t>
+          <t>Videur de bar</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -7599,65 +7607,65 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>430, Rue Victoria</t>
+          <t>88, Rue Saint-Denis</t>
         </is>
       </c>
       <c r="H99" s="7" t="n">
-        <v>48.3429</v>
+        <v>48.317374</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>-70.88079999999999</v>
+        <v>-70.861193</v>
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>Permanente, bijoux</t>
+          <t>Petite stature 4'6, massive</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t>Cardigan rose</t>
+          <t>Costume videur noir</t>
         </is>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>Sac à provisions</t>
+          <t>Bras croisés</t>
         </is>
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>portraits/92-pierrette-simard-web.webp</t>
+          <t>portraits/30-patrice-dubois-web.webp</t>
         </is>
       </c>
       <c r="N99" s="5" t="inlineStr">
         <is>
-          <t>Desrosiers-Simard</t>
+          <t>Dubois</t>
         </is>
       </c>
       <c r="O99" s="5" t="n"/>
       <c r="P99" s="5" t="inlineStr">
         <is>
-          <t>Mère de Marc-André Simard</t>
+          <t>Frère de Nancy</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Pisse-Feu</t>
+          <t>Paule Desbiens</t>
         </is>
       </c>
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Humain</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Chat domestique</t>
+          <t>Notaire</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -7667,73 +7675,65 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>427, Rue Victoria</t>
+          <t>150, Rue Victoria</t>
         </is>
       </c>
       <c r="H100" s="4" t="n">
-        <v>48.342429</v>
+        <v>48.3412</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>-70.87999000000001</v>
+        <v>-70.879</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Roux sale, dreads</t>
+          <t>Cheveux châtains, lunettes</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>s.o.</t>
+          <t>Tailleur gris</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Dort sur frigo</t>
+          <t>Cachet de notaire</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>portraits/12-pisse-feu-web.webp</t>
+          <t>portraits/81-paule-desbiens-web.webp</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Lapointe</t>
-        </is>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
+          <t>Desbiens</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="n"/>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>Chat du 427 Victoria</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Raymond Gagnon</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>Antenna</t>
-        </is>
-      </c>
+          <t>Pauline Fortin</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n"/>
       <c r="C101" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Pirate radio — théories du complot</t>
+          <t>Maraîchère — kiosque routier</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -7743,60 +7743,56 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>12, Chemin Saint-Anicet</t>
+          <t>2100, Chemin Saint-Anicet</t>
         </is>
       </c>
       <c r="H101" s="7" t="n">
-        <v>48.329</v>
+        <v>48.3287</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>-70.93000000000001</v>
+        <v>-70.9277</v>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Cheveux gras, visière aluminium</t>
+          <t>Cheveux gris coupés court</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>Parka et sac-antenne</t>
+          <t>Tablier de kiosque</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>Radio pirate 87.9</t>
+          <t>Balance romaine</t>
         </is>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>portraits/141-raymond-gagnon-web.webp</t>
+          <t>portraits/71-pauline-fortin-web.webp</t>
         </is>
       </c>
       <c r="N101" s="5" t="inlineStr">
         <is>
-          <t>Gagnon</t>
-        </is>
-      </c>
-      <c r="O101" s="5" t="inlineStr">
-        <is>
-          <t>complot</t>
-        </is>
-      </c>
+          <t>Fortin</t>
+        </is>
+      </c>
+      <c r="O101" s="5" t="n"/>
       <c r="P101" s="5" t="inlineStr">
         <is>
-          <t>Célibataire — écoute Alex Tremblay</t>
+          <t>Épouse d’Yves Fortin</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Richard Villeneuve</t>
+          <t>Philippe Villeneuve</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Rich</t>
+          <t>Dr Phil</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -7805,11 +7801,11 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Chauffeur d’autobus — STS</t>
+          <t>Médecin — Hôpital de La Baie</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -7819,33 +7815,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>10, Rue des Iris</t>
+          <t>74, Rue du Docteur-Desgagné</t>
         </is>
       </c>
       <c r="H102" s="4" t="n">
-        <v>48.3502</v>
+        <v>48.3441</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>-70.8824</v>
+        <v>-70.8839</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Bedaine, casquette STS</t>
+          <t>Cheveux gris, blouse</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Uniforme STS</t>
+          <t>Blouse d’hôpital</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Thermos de café</t>
+          <t>Stylo poche</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>portraits/82-richard-villeneuve-web.webp</t>
+          <t>portraits/95-philippe-villeneuve-web.webp</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7855,7 +7851,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>hôpital</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -7867,25 +7863,21 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Rico Leduc</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>Rico</t>
-        </is>
-      </c>
+          <t>Pierrette Simard</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n"/>
       <c r="C103" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Homme de main — recouvrement de dettes</t>
+          <t>Retraitée — ex-caissière IGA</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -7895,69 +7887,65 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>88, Rue Saint-Denis</t>
+          <t>430, Rue Victoria</t>
         </is>
       </c>
       <c r="H103" s="7" t="n">
-        <v>48.3173</v>
+        <v>48.3429</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>-70.86109999999999</v>
+        <v>-70.88079999999999</v>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Crâne rasé, jointures marquées</t>
+          <t>Permanente, bijoux</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>Chemise noire</t>
+          <t>Cardigan rose</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>Poings croisés</t>
+          <t>Sac à provisions</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>portraits/155-rico-leduc-web.webp</t>
+          <t>portraits/92-pierrette-simard-web.webp</t>
         </is>
       </c>
       <c r="N103" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Desrosiers-Simard</t>
         </is>
       </c>
       <c r="O103" s="5" t="n"/>
       <c r="P103" s="5" t="inlineStr">
         <is>
-          <t>Travaille pour Tony — croise Big Jo</t>
+          <t>Mère de Marc-André Simard</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Robert Lavoie</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
-      </c>
+          <t>Pisse-Feu</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n"/>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Humain</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Camionneur retraité</t>
+          <t>Chat domestique</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -7967,60 +7955,60 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>145, Avenue Lavoie</t>
+          <t>427, Rue Victoria</t>
         </is>
       </c>
       <c r="H104" s="4" t="n">
-        <v>48.325104</v>
+        <v>48.342429</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>-70.877376</v>
+        <v>-70.87999000000001</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Buriné, barbe grisonnante</t>
+          <t>Roux sale, dreads</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Chemise carreaux, casquette</t>
+          <t>s.o.</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Tasse café sale</t>
+          <t>Dort sur frigo</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>portraits/33-robert-lavoie-web.webp</t>
+          <t>portraits/12-pisse-feu-web.webp</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Lavoie</t>
+          <t>Lapointe</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>Père de JP</t>
+          <t>Chat du 427 Victoria</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Rock Côté</t>
+          <t>Raymond Gagnon</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Ti-Rock</t>
+          <t>Antenna</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -8029,11 +8017,11 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Débardeur — Port de La Baie</t>
+          <t>Pirate radio — théories du complot</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -8043,60 +8031,60 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>650, Avenue du Port</t>
+          <t>12, Chemin Saint-Anicet</t>
         </is>
       </c>
       <c r="H105" s="7" t="n">
-        <v>48.3309</v>
+        <v>48.329</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>-70.8952</v>
+        <v>-70.93000000000001</v>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Veste orange, casque</t>
+          <t>Cheveux gras, visière aluminium</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>Veste de sécurité</t>
+          <t>Parka et sac-antenne</t>
         </is>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>Casque de quai</t>
+          <t>Radio pirate 87.9</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>portraits/136-rock-cote-web.webp</t>
+          <t>portraits/141-raymond-gagnon-web.webp</t>
         </is>
       </c>
       <c r="N105" s="5" t="inlineStr">
         <is>
-          <t>Côté</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O105" s="5" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>complot</t>
         </is>
       </c>
       <c r="P105" s="5" t="inlineStr">
         <is>
-          <t>Filleul de Fernand Côté</t>
+          <t>Célibataire — écoute Alex Tremblay</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Rock Gagnon</t>
+          <t>Richard Villeneuve</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Rich</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -8105,11 +8093,11 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Mécanicien moto</t>
+          <t>Chauffeur d’autobus — STS</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -8119,69 +8107,73 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>3904, Route de L'Anse-à-Benjamin</t>
+          <t>10, Rue des Iris</t>
         </is>
       </c>
       <c r="H106" s="4" t="n">
-        <v>48.3803</v>
+        <v>48.3502</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>-70.8819</v>
+        <v>-70.8824</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Barbe grise, bedaine</t>
+          <t>Bedaine, casquette STS</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Veste cuir Les Loups</t>
+          <t>Uniforme STS</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Clé à molette</t>
+          <t>Thermos de café</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>portraits/52-rock-gagnon-web.webp</t>
+          <t>portraits/82-richard-villeneuve-web.webp</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Villeneuve</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>motards</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>Fils de Thérèse Gagnon — frère de Karine</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Roger Bontemps</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="n"/>
+          <t>Rico Leduc</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Rico</t>
+        </is>
+      </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Retraité — ex-fonctionnaire municipal</t>
+          <t>Homme de main — recouvrement de dettes</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -8191,56 +8183,56 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>902, Boulevard de la Grande-Baie Sud</t>
+          <t>88, Rue Saint-Denis</t>
         </is>
       </c>
       <c r="H107" s="7" t="n">
-        <v>48.333718</v>
+        <v>48.3173</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>-70.881891</v>
+        <v>-70.86109999999999</v>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Mince, lunettes double foyer</t>
+          <t>Crâne rasé, jointures marquées</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr">
         <is>
-          <t>Veston laine</t>
+          <t>Chemise noire</t>
         </is>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>Carnet noir</t>
+          <t>Poings croisés</t>
         </is>
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
-          <t>portraits/05-roger-bontemps-web.webp</t>
+          <t>portraits/155-rico-leduc-web.webp</t>
         </is>
       </c>
       <c r="N107" s="5" t="inlineStr">
         <is>
-          <t>Bontemps</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O107" s="5" t="n"/>
       <c r="P107" s="5" t="inlineStr">
         <is>
-          <t>Époux de Valette</t>
+          <t>Travaille pour Tony — croise Big Jo</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Réal Chicoine</t>
+          <t>Robert Lavoie</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Chicoine</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -8249,11 +8241,11 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Sans emploi fixe — récupérateur</t>
+          <t>Camionneur retraité</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -8263,56 +8255,60 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>118, Rue de la Fabrique</t>
+          <t>145, Avenue Lavoie</t>
         </is>
       </c>
       <c r="H108" s="4" t="n">
-        <v>48.342587</v>
+        <v>48.325104</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>-70.878451</v>
+        <v>-70.877376</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Maigre, visage creusé</t>
+          <t>Buriné, barbe grisonnante</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Manteau hiver trop grand</t>
+          <t>Chemise carreaux, casquette</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Dort assis</t>
+          <t>Tasse café sale</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>portraits/03-real-chicoine-web.webp</t>
+          <t>portraits/33-robert-lavoie-web.webp</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Chicoine</t>
-        </is>
-      </c>
-      <c r="O108" s="2" t="n"/>
+          <t>Lavoie</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>Fils d’Hélène</t>
+          <t>Père de JP</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Réjean Pedneault</t>
+          <t>Rock Côté</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Ti-Peche</t>
+          <t>Ti-Rock</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -8321,11 +8317,11 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Pêcheur — baie des Ha! Ha!</t>
+          <t>Débardeur — Port de La Baie</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -8335,56 +8331,60 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>20, Avenue du Port</t>
+          <t>650, Avenue du Port</t>
         </is>
       </c>
       <c r="H109" s="7" t="n">
-        <v>48.3302</v>
+        <v>48.3309</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>-70.8948</v>
+        <v>-70.8952</v>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Barbe sel et poivre, tuque</t>
+          <t>Veste orange, casque</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
-          <t>Ciré jaune</t>
+          <t>Veste de sécurité</t>
         </is>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>Couteau à poisson</t>
+          <t>Casque de quai</t>
         </is>
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>portraits/105-rejean-pedneault-web.webp</t>
+          <t>portraits/136-rock-cote-web.webp</t>
         </is>
       </c>
       <c r="N109" s="5" t="inlineStr">
         <is>
-          <t>Pedneault</t>
-        </is>
-      </c>
-      <c r="O109" s="5" t="n"/>
+          <t>Côté</t>
+        </is>
+      </c>
+      <c r="O109" s="5" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
       <c r="P109" s="5" t="inlineStr">
         <is>
-          <t>Époux de Céline Pedneault</t>
+          <t>Filleul de Fernand Côté</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Réjean Roy</t>
+          <t>Rock Gagnon</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Ti-Jean</t>
+          <t>Rocky</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -8393,11 +8393,11 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Retraité — ex-papetier</t>
+          <t>Mécanicien moto</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -8407,69 +8407,69 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>76, Rue du Docteur-Desgagné</t>
+          <t>3904, Route de L'Anse-à-Benjamin</t>
         </is>
       </c>
       <c r="H110" s="4" t="n">
-        <v>48.34355</v>
+        <v>48.3803</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>-70.88318</v>
+        <v>-70.8819</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>Ventre, lunettes</t>
+          <t>Barbe grise, bedaine</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Chemise à carreaux</t>
+          <t>Veste cuir Les Loups</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Canne et journal</t>
+          <t>Clé à molette</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>portraits/50-rejean-roy-web.webp</t>
+          <t>portraits/52-rock-gagnon-web.webp</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>Roy</t>
-        </is>
-      </c>
-      <c r="O110" s="2" t="n"/>
+          <t>Gagnon</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>motards</t>
+        </is>
+      </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>Mari de Ginette Roy</t>
+          <t>Fils de Thérèse Gagnon — frère de Karine</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Salvatore Martel</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>Sal</t>
-        </is>
-      </c>
+          <t>Roger Bontemps</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n"/>
       <c r="C111" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Import-export — conteneurs du port</t>
+          <t>Retraité — ex-fonctionnaire municipal</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -8479,69 +8479,65 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>700, Avenue du Port</t>
+          <t>902, Boulevard de la Grande-Baie Sud</t>
         </is>
       </c>
       <c r="H111" s="7" t="n">
-        <v>48.3307</v>
+        <v>48.333718</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>-70.8954</v>
+        <v>-70.881891</v>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Manteau camel, quai</t>
+          <t>Mince, lunettes double foyer</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>Manteau camel</t>
+          <t>Veston laine</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>Manifestes de cargo</t>
+          <t>Carnet noir</t>
         </is>
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>portraits/159-salvatore-martel-web.webp</t>
+          <t>portraits/05-roger-bontemps-web.webp</t>
         </is>
       </c>
       <c r="N111" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Bontemps</t>
         </is>
       </c>
       <c r="O111" s="5" t="n"/>
       <c r="P111" s="5" t="inlineStr">
         <is>
-          <t>Relais portuaire — croise Yvan Truchon</t>
+          <t>Époux de Valette</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Samuel Joseph</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Samy</t>
-        </is>
-      </c>
+          <t>Rosalie Girard</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n"/>
       <c r="C112" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Préposé aux bénéficiaires</t>
+          <t>Étudiante en soins infirmiers (Cégep de Chicoutimi)</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -8551,54 +8547,58 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>162, Rue des Lilas</t>
+          <t>202, Rue Bagot</t>
         </is>
       </c>
       <c r="H112" s="4" t="n">
-        <v>48.342</v>
+        <v>48.33835</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>-70.89615999999999</v>
+        <v>-70.88535</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Haïtien, dreadlocks courtes</t>
+          <t>Chignon brun, sourire fatigué</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>Uniforme CHSLD</t>
+          <t>Uniforme marine d’étudiante</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Thermos café fort</t>
+          <t>Calepin de stage</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>portraits/56-samuel-joseph-web.webp</t>
+          <t>portraits/181-rosalie-girard-web.webp</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Girard</t>
         </is>
       </c>
       <c r="O112" s="2" t="n"/>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>Fils de Mireille Joseph</t>
+          <t>Fille d’Anne et Louis Girard</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Sarah Pelletier</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="n"/>
+          <t>Réal Chicoine</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Chicoine</t>
+        </is>
+      </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Barmaid — Le Coin</t>
+          <t>Sans emploi fixe — récupérateur</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -8619,60 +8619,56 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>86, Rue Saint-Denis</t>
+          <t>118, Rue de la Fabrique</t>
         </is>
       </c>
       <c r="H113" s="7" t="n">
-        <v>48.3175</v>
+        <v>48.342587</v>
       </c>
       <c r="I113" s="7" t="n">
-        <v>-70.8608</v>
+        <v>-70.878451</v>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Cheveux roux, piercing</t>
+          <t>Maigre, visage creusé</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>T-shirt du bar</t>
+          <t>Manteau hiver trop grand</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>Shaker</t>
+          <t>Dort assis</t>
         </is>
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>portraits/73-sarah-pelletier-web.webp</t>
+          <t>portraits/03-real-chicoine-web.webp</t>
         </is>
       </c>
       <c r="N113" s="5" t="inlineStr">
         <is>
-          <t>Pelletier</t>
-        </is>
-      </c>
-      <c r="O113" s="5" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
+          <t>Chicoine</t>
+        </is>
+      </c>
+      <c r="O113" s="5" t="n"/>
       <c r="P113" s="5" t="inlineStr">
         <is>
-          <t>Épouse d’Hugo Pelletier</t>
+          <t>Fils d’Hélène</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Serge Potvin</t>
+          <t>Réjean Pedneault</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Pelle</t>
+          <t>Ti-Peche</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -8681,11 +8677,11 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Opérateur — déneigement municipal</t>
+          <t>Pêcheur — baie des Ha! Ha!</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -8695,56 +8691,56 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>800, Avenue du Port</t>
+          <t>20, Avenue du Port</t>
         </is>
       </c>
       <c r="H114" s="4" t="n">
-        <v>48.331</v>
+        <v>48.3302</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>-70.89400000000001</v>
+        <v>-70.8948</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Moustache, tuque</t>
+          <t>Barbe sel et poivre, tuque</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>Parka orange</t>
+          <t>Ciré jaune</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Clés de niveleuse</t>
+          <t>Couteau à poisson</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>portraits/88-serge-potvin-web.webp</t>
+          <t>portraits/105-rejean-pedneault-web.webp</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Potvin</t>
+          <t>Pedneault</t>
         </is>
       </c>
       <c r="O114" s="2" t="n"/>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Époux de Céline Pedneault</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Solange Bouchard</t>
+          <t>Réjean Roy</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>La Reine de Grande-Baie</t>
+          <t>Ti-Jean</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -8753,11 +8749,11 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Souverainiste autodéclarée du quartier</t>
+          <t>Retraité — ex-papetier</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -8767,69 +8763,69 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>10, Rue Prince-Albert</t>
+          <t>76, Rue du Docteur-Desgagné</t>
         </is>
       </c>
       <c r="H115" s="7" t="n">
-        <v>48.314</v>
+        <v>48.34355</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>-70.8608</v>
+        <v>-70.88318</v>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Maquillage chargé, couronne plastique</t>
+          <t>Ventre, lunettes</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t>Fausse fourrure</t>
+          <t>Chemise à carreaux</t>
         </is>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>Couronne Dollarama</t>
+          <t>Canne et journal</t>
         </is>
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>portraits/142-solange-bouchard-web.webp</t>
+          <t>portraits/50-rejean-roy-web.webp</t>
         </is>
       </c>
       <c r="N115" s="5" t="inlineStr">
         <is>
-          <t>Bouchard</t>
-        </is>
-      </c>
-      <c r="O115" s="5" t="inlineStr">
-        <is>
-          <t>couronne</t>
-        </is>
-      </c>
+          <t>Roy</t>
+        </is>
+      </c>
+      <c r="O115" s="5" t="n"/>
       <c r="P115" s="5" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Mari de Ginette Roy</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Sonia Tremblay</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="n"/>
+          <t>Salvatore Martel</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Préposée aux bénéficiaires</t>
+          <t>Import-export — conteneurs du port</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -8839,60 +8835,56 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>338, Boulevard de la Grande-Baie Nord</t>
+          <t>700, Avenue du Port</t>
         </is>
       </c>
       <c r="H116" s="4" t="n">
-        <v>48.33996</v>
+        <v>48.3307</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>-70.8809</v>
+        <v>-70.8954</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Cheveux châtains teints, fatigue</t>
+          <t>Manteau camel, quai</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Uniforme CHSLD</t>
+          <t>Manteau camel</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Lunch Tupperware</t>
+          <t>Manifestes de cargo</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>portraits/42-sonia-tremblay-web.webp</t>
+          <t>portraits/159-salvatore-martel-web.webp</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Tremblay</t>
-        </is>
-      </c>
-      <c r="O116" s="2" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="n"/>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>Mère d’Alex Tremblay</t>
+          <t>Relais portuaire — croise Yvan Truchon</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Steve Gauthier</t>
+          <t>Samuel Joseph</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Stevie Chop</t>
+          <t>Samy</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -8905,7 +8897,7 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>Dépeceur de voitures</t>
+          <t>Préposé aux bénéficiaires</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -8915,62 +8907,54 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>320, Chemin des Chutes</t>
+          <t>162, Rue des Lilas</t>
         </is>
       </c>
       <c r="H117" s="7" t="n">
-        <v>48.3263</v>
+        <v>48.342</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>-70.9238</v>
+        <v>-70.89615999999999</v>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Graisse, tuque</t>
+          <t>Haïtien, dreadlocks courtes</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>Salopette de garage</t>
+          <t>Uniforme CHSLD</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>Clé à chocs</t>
+          <t>Thermos café fort</t>
         </is>
       </c>
       <c r="M117" s="5" t="inlineStr">
         <is>
-          <t>portraits/118-steve-gauthier-web.webp</t>
+          <t>portraits/56-samuel-joseph-web.webp</t>
         </is>
       </c>
       <c r="N117" s="5" t="inlineStr">
         <is>
-          <t>Gauthier</t>
-        </is>
-      </c>
-      <c r="O117" s="5" t="inlineStr">
-        <is>
-          <t>casse</t>
-        </is>
-      </c>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O117" s="5" t="n"/>
       <c r="P117" s="5" t="inlineStr">
         <is>
-          <t>Célibataire — fournit Bobby</t>
+          <t>Fils de Mireille Joseph</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Steve Langlois</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Le Plombier</t>
-        </is>
-      </c>
+          <t>Sarah Pelletier</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n"/>
       <c r="C118" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
@@ -8981,7 +8965,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Plombier</t>
+          <t>Barmaid — Le Coin</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -8991,56 +8975,60 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>156, Rue Cimon</t>
+          <t>86, Rue Saint-Denis</t>
         </is>
       </c>
       <c r="H118" s="4" t="n">
-        <v>48.342509</v>
+        <v>48.3175</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>-70.88030000000001</v>
+        <v>-70.8608</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Gros bras, moustache</t>
+          <t>Cheveux roux, piercing</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Salopette</t>
+          <t>T-shirt du bar</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Coffre rouillé</t>
+          <t>Shaker</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>portraits/18-steve-langlois-web.webp</t>
+          <t>portraits/73-sarah-pelletier-web.webp</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Langlois</t>
-        </is>
-      </c>
-      <c r="O118" s="2" t="n"/>
+          <t>Pelletier</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>Époux de Josée</t>
+          <t>Épouse d’Hugo Pelletier</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Stéphanie Lapointe</t>
+          <t>Serge Potvin</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Steph</t>
+          <t>Pelle</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -9049,11 +9037,11 @@
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Commis chez Dollarama</t>
+          <t>Opérateur — déneigement municipal</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -9063,60 +9051,56 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>45, Rue des Iris</t>
+          <t>800, Avenue du Port</t>
         </is>
       </c>
       <c r="H119" s="7" t="n">
-        <v>48.350754</v>
+        <v>48.331</v>
       </c>
       <c r="I119" s="7" t="n">
-        <v>-70.88294999999999</v>
+        <v>-70.89400000000001</v>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Cheveux attachés</t>
+          <t>Moustache, tuque</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
-          <t>Polo Dollarama</t>
+          <t>Parka orange</t>
         </is>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>Jouets</t>
+          <t>Clés de niveleuse</t>
         </is>
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
-          <t>portraits/40-stephanie-lapointe-web.webp</t>
+          <t>portraits/88-serge-potvin-web.webp</t>
         </is>
       </c>
       <c r="N119" s="5" t="inlineStr">
         <is>
-          <t>Lapointe</t>
-        </is>
-      </c>
-      <c r="O119" s="5" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
+          <t>Potvin</t>
+        </is>
+      </c>
+      <c r="O119" s="5" t="n"/>
       <c r="P119" s="5" t="inlineStr">
         <is>
-          <t>Sœur de Marco</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Sylvain Bouchard</t>
+          <t>Solange Bouchard</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Coach Bouche</t>
+          <t>La Reine de Grande-Baie</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -9125,11 +9109,11 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Entraîneur — hockey junior La Baie</t>
+          <t>Souverainiste autodéclarée du quartier</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -9139,33 +9123,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>300, Avenue du Port</t>
+          <t>10, Rue Prince-Albert</t>
         </is>
       </c>
       <c r="H120" s="4" t="n">
-        <v>48.3312</v>
+        <v>48.314</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>-70.8935</v>
+        <v>-70.8608</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>Veste d’équipe, sifflet</t>
+          <t>Maquillage chargé, couronne plastique</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>Manteau hockey</t>
+          <t>Fausse fourrure</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Sifflet au cou</t>
+          <t>Couronne Dollarama</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>portraits/131-sylvain-bouchard-web.webp</t>
+          <t>portraits/142-solange-bouchard-web.webp</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9175,7 +9159,7 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>couronne</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
@@ -9187,7 +9171,7 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Sylvain Gagné</t>
+          <t>Sonia Tremblay</t>
         </is>
       </c>
       <c r="B121" s="5" t="n"/>
@@ -9197,11 +9181,11 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>Coiffeur — salon à domicile</t>
+          <t>Préposée aux bénéficiaires</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -9211,33 +9195,33 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>94, Rue Prince-Albert</t>
+          <t>338, Boulevard de la Grande-Baie Nord</t>
         </is>
       </c>
       <c r="H121" s="7" t="n">
-        <v>48.31214</v>
+        <v>48.33996</v>
       </c>
       <c r="I121" s="7" t="n">
-        <v>-70.86060000000001</v>
+        <v>-70.8809</v>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Barbe dessinée, bagues</t>
+          <t>Cheveux châtains teints, fatigue</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
         <is>
-          <t>Tablier de coiffeur</t>
+          <t>Uniforme CHSLD</t>
         </is>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>Ciseaux japonais</t>
+          <t>Lunch Tupperware</t>
         </is>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>portraits/67-sylvain-gagne-web.webp</t>
+          <t>portraits/42-sonia-tremblay-web.webp</t>
         </is>
       </c>
       <c r="N121" s="5" t="inlineStr">
@@ -9247,24 +9231,24 @@
       </c>
       <c r="O121" s="5" t="inlineStr">
         <is>
-          <t>Johanne</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="P121" s="5" t="inlineStr">
         <is>
-          <t>Conjoint de Johanne Tremblay</t>
+          <t>Mère d’Alex Tremblay</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Sylvie Gagnon</t>
+          <t>Steve Gauthier</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>La Proprio</t>
+          <t>Stevie Chop</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -9273,11 +9257,11 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Propriétaire immobilière</t>
+          <t>Dépeceur de voitures</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -9287,60 +9271,60 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>45, Rue de la Terrasse-Bellevue</t>
+          <t>320, Chemin des Chutes</t>
         </is>
       </c>
       <c r="H122" s="4" t="n">
-        <v>48.328952</v>
+        <v>48.3263</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>-70.893638</v>
+        <v>-70.9238</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>Bronzée Boucherville</t>
+          <t>Graisse, tuque</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>Salopette de garage</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Mercedes GLK, bail</t>
+          <t>Clé à chocs</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>portraits/13-sylvie-gagnon-web.webp</t>
+          <t>portraits/118-steve-gauthier-web.webp</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>immobilier</t>
+          <t>casse</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>Fille de Jeanne Gagnon — ex-épouse de Bertrand</t>
+          <t>Célibataire — fournit Bobby</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Thérèse Gagnon</t>
+          <t>Steve Langlois</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Maman Louve</t>
+          <t>Le Plombier</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -9349,11 +9333,11 @@
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>Retraitée — ex-motarde</t>
+          <t>Plombier</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -9363,69 +9347,69 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>3900, Route de L'Anse-à-Benjamin</t>
+          <t>156, Rue Cimon</t>
         </is>
       </c>
       <c r="H123" s="7" t="n">
-        <v>48.3801</v>
+        <v>48.342509</v>
       </c>
       <c r="I123" s="7" t="n">
-        <v>-70.8817</v>
+        <v>-70.88030000000001</v>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Queue de cheval grise, veste cuir</t>
+          <t>Gros bras, moustache</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>Veste cuir sur cardigan</t>
+          <t>Salopette</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>Harley parkée</t>
+          <t>Coffre rouillé</t>
         </is>
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
-          <t>portraits/164-therese-gagnon-web.webp</t>
+          <t>portraits/18-steve-langlois-web.webp</t>
         </is>
       </c>
       <c r="N123" s="5" t="inlineStr">
         <is>
-          <t>Gagnon</t>
-        </is>
-      </c>
-      <c r="O123" s="5" t="inlineStr">
-        <is>
-          <t>motards</t>
-        </is>
-      </c>
+          <t>Langlois</t>
+        </is>
+      </c>
+      <c r="O123" s="5" t="n"/>
       <c r="P123" s="5" t="inlineStr">
         <is>
-          <t>Mère de Karine et Rock Gagnon</t>
+          <t>Époux de Josée</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Thérèse Lacroix</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="n"/>
+          <t>Stéphanie Lapointe</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Steph</t>
+        </is>
+      </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Retraitée — ex-sacristine</t>
+          <t>Commis chez Dollarama</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -9435,56 +9419,60 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>23, Rue des Vingt-et-un</t>
+          <t>45, Rue des Iris</t>
         </is>
       </c>
       <c r="H124" s="4" t="n">
-        <v>48.31348</v>
+        <v>48.350754</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>-70.85599999999999</v>
+        <v>-70.88294999999999</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Cheveux blancs, petit cadre</t>
+          <t>Cheveux attachés</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>Manteau de messe</t>
+          <t>Polo Dollarama</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Chapelet</t>
+          <t>Jouets</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>portraits/54-therese-lacroix-web.webp</t>
+          <t>portraits/40-stephanie-lapointe-web.webp</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>Lacroix</t>
-        </is>
-      </c>
-      <c r="O124" s="2" t="n"/>
+          <t>Lapointe</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>Sœur de Lucien Lacroix</t>
+          <t>Sœur de Marco</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Ti-Paul Côté</t>
+          <t>Sylvain Bouchard</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Le Panier</t>
+          <t>Coach Bouche</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -9493,11 +9481,11 @@
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>Chiffonnier — chariots d’épicerie</t>
+          <t>Entraîneur — hockey junior La Baie</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -9507,55 +9495,55 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>118, Rue de la Fabrique</t>
+          <t>300, Avenue du Port</t>
         </is>
       </c>
       <c r="H125" s="7" t="n">
-        <v>48.34265</v>
+        <v>48.3312</v>
       </c>
       <c r="I125" s="7" t="n">
-        <v>-70.8784</v>
+        <v>-70.8935</v>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Peignoir taché, bottes d’hiver</t>
+          <t>Veste d’équipe, sifflet</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>Peignoir et manteau</t>
+          <t>Manteau hockey</t>
         </is>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>Chariot IGA</t>
+          <t>Sifflet au cou</t>
         </is>
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>portraits/144-ti-paul-cote-web.webp</t>
+          <t>portraits/131-sylvain-bouchard-web.webp</t>
         </is>
       </c>
       <c r="N125" s="5" t="inlineStr">
         <is>
-          <t>Côté</t>
+          <t>Bouchard</t>
         </is>
       </c>
       <c r="O125" s="5" t="inlineStr">
         <is>
-          <t>ruelle</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="P125" s="5" t="inlineStr">
         <is>
-          <t>Célibataire — copain de Réal Chicoine</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Tommy Fortin</t>
+          <t>Sylvain Gagné</t>
         </is>
       </c>
       <c r="B126" s="2" t="n"/>
@@ -9565,11 +9553,11 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Journalier — bleuetière</t>
+          <t>Coiffeur — salon à domicile</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -9579,56 +9567,60 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>2102, Chemin Saint-Anicet</t>
+          <t>94, Rue Prince-Albert</t>
         </is>
       </c>
       <c r="H126" s="4" t="n">
-        <v>48.32855</v>
+        <v>48.31214</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>-70.92785000000001</v>
+        <v>-70.86060000000001</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Bronzé, casquette John Deere</t>
+          <t>Barbe dessinée, bagues</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Chemise à carreaux</t>
+          <t>Tablier de coiffeur</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Bottes crottées</t>
+          <t>Ciseaux japonais</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>portraits/101-tommy-fortin-web.webp</t>
+          <t>portraits/67-sylvain-gagne-web.webp</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>Fortin</t>
-        </is>
-      </c>
-      <c r="O126" s="2" t="n"/>
+          <t>Tremblay</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Johanne</t>
+        </is>
+      </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>Fils d’Yves et Pauline Fortin</t>
+          <t>Conjoint de Johanne Tremblay</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Tony Santini</t>
+          <t>Sylvie Gagnon</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Tony Capo</t>
+          <t>La Proprio</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -9637,11 +9629,11 @@
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>Lieutenant — quai et casse</t>
+          <t>Propriétaire immobilière</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -9651,65 +9643,73 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>620, Avenue du Port</t>
+          <t>45, Rue de la Terrasse-Bellevue</t>
         </is>
       </c>
       <c r="H127" s="7" t="n">
-        <v>48.33085</v>
+        <v>48.328952</v>
       </c>
       <c r="I127" s="7" t="n">
-        <v>-70.8951</v>
+        <v>-70.893638</v>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Cou épais, veste de cuir</t>
+          <t>Bronzée Boucherville</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t>Veste de cuir</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>Cigarette au bec</t>
+          <t>Mercedes GLK, bail</t>
         </is>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
-          <t>portraits/154-tony-santini-web.webp</t>
+          <t>portraits/13-sylvie-gagnon-web.webp</t>
         </is>
       </c>
       <c r="N127" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
-        </is>
-      </c>
-      <c r="O127" s="5" t="n"/>
+          <t>Gagnon</t>
+        </is>
+      </c>
+      <c r="O127" s="5" t="inlineStr">
+        <is>
+          <t>immobilier</t>
+        </is>
+      </c>
       <c r="P127" s="5" t="inlineStr">
         <is>
-          <t>Neveu de Vittorio — parle à Bobby Gagnon</t>
+          <t>Fille de Jeanne Gagnon — ex-épouse de Bertrand</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Valette Bontemps</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="n"/>
+          <t>Thomas Bergeron</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Tom-Tom</t>
+        </is>
+      </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Retraitée — ex-caissière</t>
+          <t>Élève du secondaire — gardien de but</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -9719,56 +9719,56 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>902, Boulevard de la Grande-Baie Sud</t>
+          <t>604, Avenue du Port</t>
         </is>
       </c>
       <c r="H128" s="4" t="n">
-        <v>48.335632</v>
+        <v>48.33088</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>-70.88019199999999</v>
+        <v>-70.89545</v>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Permanente mauve-gris</t>
+          <t>Taches de rousseur, blond ébouriffé</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Cardigan, bijoux bruyants</t>
+          <t>Jambières de gardien</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Chasse odeur</t>
+          <t>Masque relevé</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>portraits/06-valette-bontemps-web.webp</t>
+          <t>portraits/176-thomas-bergeron-web.webp</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>Bontemps</t>
+          <t>Bergeron</t>
         </is>
       </c>
       <c r="O128" s="2" t="n"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>Épouse de Roger</t>
+          <t>Fils d’Isabelle Bergeron — petit-fils de Gilles</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Véronique Côté</t>
+          <t>Thérèse Gagnon</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Véro</t>
+          <t>Maman Louve</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -9777,11 +9777,11 @@
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>Éducatrice en CPE</t>
+          <t>Retraitée — ex-motarde</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
@@ -9791,73 +9791,69 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>264, Rue de la Colline</t>
+          <t>3900, Route de L'Anse-à-Benjamin</t>
         </is>
       </c>
       <c r="H129" s="7" t="n">
-        <v>48.3419</v>
+        <v>48.3801</v>
       </c>
       <c r="I129" s="7" t="n">
-        <v>-70.8852</v>
+        <v>-70.8817</v>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Frange, couleurs vives</t>
+          <t>Queue de cheval grise, veste cuir</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t>Chandail CPE</t>
+          <t>Veste cuir sur cardigan</t>
         </is>
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>Autocollants</t>
+          <t>Harley parkée</t>
         </is>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
-          <t>portraits/85-veronique-cote-web.webp</t>
+          <t>portraits/164-therese-gagnon-web.webp</t>
         </is>
       </c>
       <c r="N129" s="5" t="inlineStr">
         <is>
-          <t>Côté</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="O129" s="5" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>motards</t>
         </is>
       </c>
       <c r="P129" s="5" t="inlineStr">
         <is>
-          <t>Collègue de Mélanie Dubé</t>
+          <t>Mère de Karine et Rock Gagnon</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>William McKenzie</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Will</t>
-        </is>
-      </c>
+          <t>Thérèse Lacroix</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n"/>
       <c r="C130" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Militaires — 3e Escadre Bagotville</t>
+          <t>Retraitée — ex-sacristine</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -9867,65 +9863,69 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Lieu-dit : Base de Bagotville (3e Escadre)</t>
+          <t>23, Rue des Vingt-et-un</t>
         </is>
       </c>
       <c r="H130" s="4" t="n">
-        <v>48.3305</v>
+        <v>48.31348</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>-70.996</v>
+        <v>-70.85599999999999</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Coupe militaire, anglophone</t>
+          <t>Cheveux blancs, petit cadre</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Uniforme CADPAT</t>
+          <t>Manteau de messe</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Dog tags</t>
+          <t>Chapelet</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>portraits/97-william-mckenzie-web.webp</t>
+          <t>portraits/54-therese-lacroix-web.webp</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>McKenzie</t>
+          <t>Lacroix</t>
         </is>
       </c>
       <c r="O130" s="2" t="n"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Sœur de Lucien Lacroix</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Yan Couture</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="n"/>
+          <t>Ti-Paul Côté</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Le Panier</t>
+        </is>
+      </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>Musicien — guitariste de bar</t>
+          <t>Chiffonnier — chariots d’épicerie</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -9935,69 +9935,69 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>210, Rue Bagot</t>
+          <t>118, Rue de la Fabrique</t>
         </is>
       </c>
       <c r="H131" s="7" t="n">
-        <v>48.3377</v>
+        <v>48.34265</v>
       </c>
       <c r="I131" s="7" t="n">
-        <v>-70.8861</v>
+        <v>-70.8784</v>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Longs cheveux, boucle d’oreille</t>
+          <t>Peignoir taché, bottes d’hiver</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>Chemise à fleurs</t>
+          <t>Peignoir et manteau</t>
         </is>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>Guitare Folkway</t>
+          <t>Chariot IGA</t>
         </is>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>portraits/91-yan-couture-web.webp</t>
+          <t>portraits/144-ti-paul-cote-web.webp</t>
         </is>
       </c>
       <c r="N131" s="5" t="inlineStr">
         <is>
-          <t>Couture</t>
-        </is>
-      </c>
-      <c r="O131" s="5" t="n"/>
+          <t>Côté</t>
+        </is>
+      </c>
+      <c r="O131" s="5" t="inlineStr">
+        <is>
+          <t>ruelle</t>
+        </is>
+      </c>
       <c r="P131" s="5" t="inlineStr">
         <is>
-          <t>Célibataire — joue au bingo de Michel</t>
+          <t>Célibataire — copain de Réal Chicoine</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Yvan Truchon</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Cartoune</t>
-        </is>
-      </c>
+          <t>Tommy Fortin</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n"/>
       <c r="C132" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Contrebandier de cigarettes</t>
+          <t>Journalier — bleuetière</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -10007,65 +10007,69 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1450, Route du Petit-Parc</t>
+          <t>2102, Chemin Saint-Anicet</t>
         </is>
       </c>
       <c r="H132" s="4" t="n">
-        <v>48.305136</v>
+        <v>48.32855</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>-70.907684</v>
+        <v>-70.92785000000001</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Moustache</t>
+          <t>Bronzé, casquette John Deere</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>Casquette trucker</t>
+          <t>Chemise à carreaux</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Pontiac Grand Prix</t>
+          <t>Bottes crottées</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>portraits/11-yvan-truchon-web.webp</t>
+          <t>portraits/101-tommy-fortin-web.webp</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Truchon</t>
+          <t>Fortin</t>
         </is>
       </c>
       <c r="O132" s="2" t="n"/>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>Fils de Cécile Truchon — conjoint de Gisèle</t>
+          <t>Fils d’Yves et Pauline Fortin</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Yves Fortin</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="n"/>
+          <t>Tony Santini</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Tony Capo</t>
+        </is>
+      </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>Producteur de bleuets</t>
+          <t>Lieutenant — quai et casse</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -10075,51 +10079,51 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2100, Chemin Saint-Anicet</t>
+          <t>620, Avenue du Port</t>
         </is>
       </c>
       <c r="H133" s="7" t="n">
-        <v>48.3285</v>
+        <v>48.33085</v>
       </c>
       <c r="I133" s="7" t="n">
-        <v>-70.928</v>
+        <v>-70.8951</v>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Bronzé, casquette John Deere</t>
+          <t>Cou épais, veste de cuir</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
         <is>
-          <t>Chemise à carreaux</t>
+          <t>Veste de cuir</t>
         </is>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>Seau de bleuets</t>
+          <t>Cigarette au bec</t>
         </is>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
-          <t>portraits/70-yves-fortin-web.webp</t>
+          <t>portraits/154-tony-santini-web.webp</t>
         </is>
       </c>
       <c r="N133" s="5" t="inlineStr">
         <is>
-          <t>Fortin</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O133" s="5" t="n"/>
       <c r="P133" s="5" t="inlineStr">
         <is>
-          <t>Époux de Pauline Fortin</t>
+          <t>Neveu de Vittorio — parle à Bobby Gagnon</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Élodie Martel</t>
+          <t>Valette Bontemps</t>
         </is>
       </c>
       <c r="B134" s="2" t="n"/>
@@ -10129,11 +10133,11 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Éducatrice — Musée du Fjord</t>
+          <t>Retraitée — ex-caissière</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -10143,65 +10147,69 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>3346, Boulevard de la Grande-Baie Sud</t>
+          <t>902, Boulevard de la Grande-Baie Sud</t>
         </is>
       </c>
       <c r="H134" s="4" t="n">
-        <v>48.3178</v>
+        <v>48.335632</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>-70.854</v>
+        <v>-70.88019199999999</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Lanière, chandail</t>
+          <t>Permanente mauve-gris</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>Chandail musée</t>
+          <t>Cardigan, bijoux bruyants</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Dépliant d’expo</t>
+          <t>Chasse odeur</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>portraits/140-elodie-martel-web.webp</t>
+          <t>portraits/06-valette-bontemps-web.webp</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>Martel</t>
+          <t>Bontemps</t>
         </is>
       </c>
       <c r="O134" s="2" t="n"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>Cousine de Julie et Amélie Martel</t>
+          <t>Épouse de Roger</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Émile Brassard</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="n"/>
+          <t>Véronique Côté</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Véro</t>
+        </is>
+      </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>Pompier — caserne de La Baie</t>
+          <t>Éducatrice en CPE</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
@@ -10211,65 +10219,73 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>50, Rue des Pompiers</t>
+          <t>264, Rue de la Colline</t>
         </is>
       </c>
       <c r="H135" s="7" t="n">
-        <v>48.336</v>
+        <v>48.3419</v>
       </c>
       <c r="I135" s="7" t="n">
-        <v>-70.88200000000001</v>
+        <v>-70.8852</v>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Carrure, barbe courte</t>
+          <t>Frange, couleurs vives</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
         <is>
-          <t>T-shirt caserne</t>
+          <t>Chandail CPE</t>
         </is>
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>Radio portative</t>
+          <t>Autocollants</t>
         </is>
       </c>
       <c r="M135" s="5" t="inlineStr">
         <is>
-          <t>portraits/76-emile-brassard-web.webp</t>
+          <t>portraits/85-veronique-cote-web.webp</t>
         </is>
       </c>
       <c r="N135" s="5" t="inlineStr">
         <is>
-          <t>Brassard</t>
-        </is>
-      </c>
-      <c r="O135" s="5" t="n"/>
+          <t>Côté</t>
+        </is>
+      </c>
+      <c r="O135" s="5" t="inlineStr">
+        <is>
+          <t>CPE</t>
+        </is>
+      </c>
       <c r="P135" s="5" t="inlineStr">
         <is>
-          <t>Époux de Marie-Claude Brassard</t>
+          <t>Collègue de Mélanie Dubé</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Émilie Gauthier</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="n"/>
+          <t>William McKenzie</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Will</t>
+        </is>
+      </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Gérante Dollarama</t>
+          <t>Militaires — 3e Escadre Bagotville</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -10279,69 +10295,65 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>47, Rue des Iris</t>
+          <t>Lieu-dit : Base de Bagotville (3e Escadre)</t>
         </is>
       </c>
       <c r="H136" s="4" t="n">
-        <v>48.3509</v>
+        <v>48.3305</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>-70.8831</v>
+        <v>-70.996</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Cheveux attachés, badge</t>
+          <t>Coupe militaire, anglophone</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Polo Dollarama</t>
+          <t>Uniforme CADPAT</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Talkie-walkie</t>
+          <t>Dog tags</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>portraits/87-emilie-gauthier-web.webp</t>
+          <t>portraits/97-william-mckenzie-web.webp</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>McKenzie</t>
         </is>
       </c>
       <c r="O136" s="2" t="n"/>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>Supérieure de Stéphanie Lapointe</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Éric Boucher</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>Boubou</t>
-        </is>
-      </c>
+          <t>Yan Couture</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n"/>
       <c r="C137" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>Ferrailleur</t>
+          <t>Musicien — guitariste de bar</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
@@ -10351,130 +10363,126 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>2408, Chemin Saint-Anicet</t>
+          <t>210, Rue Bagot</t>
         </is>
       </c>
       <c r="H137" s="7" t="n">
-        <v>48.3302</v>
+        <v>48.3377</v>
       </c>
       <c r="I137" s="7" t="n">
-        <v>-70.93245</v>
+        <v>-70.8861</v>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>Barbe, casque de chantier</t>
+          <t>Longs cheveux, boucle d’oreille</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>Salopette tachée</t>
+          <t>Chemise à fleurs</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>Aimant à ferraille</t>
+          <t>Guitare Folkway</t>
         </is>
       </c>
       <c r="M137" s="5" t="inlineStr">
         <is>
-          <t>portraits/47-eric-boucher-web.webp</t>
+          <t>portraits/91-yan-couture-web.webp</t>
         </is>
       </c>
       <c r="N137" s="5" t="inlineStr">
         <is>
-          <t>Boucher</t>
+          <t>Couture</t>
         </is>
       </c>
       <c r="O137" s="5" t="n"/>
       <c r="P137" s="5" t="inlineStr">
         <is>
-          <t>Fils de Fernande — frère de Dévon</t>
+          <t>Célibataire — joue au bingo de Michel</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Albert Dufour</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="n"/>
+          <t>Yvan Truchon</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Cartoune</t>
+        </is>
+      </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Retraité — ex-conseiller</t>
+          <t>Contrebandier de cigarettes</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Chicoutimi</t>
+          <t>La Baie</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>205, Rue Racine Est</t>
+          <t>1450, Route du Petit-Parc</t>
         </is>
       </c>
       <c r="H138" s="4" t="n">
-        <v>48.4283</v>
+        <v>48.305136</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>-71.0535</v>
+        <v>-70.907684</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Cheveux blancs clairsemés, canne</t>
+          <t>Moustache</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>Veston</t>
+          <t>Casquette trucker</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Canne au parc</t>
+          <t>Pontiac Grand Prix</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>portraits/169-albert-dufour-web.webp</t>
+          <t>portraits/11-yvan-truchon-web.webp</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>Dufour</t>
-        </is>
-      </c>
-      <c r="O138" s="2" t="inlineStr">
-        <is>
-          <t>hôtel de ville</t>
-        </is>
-      </c>
+          <t>Truchon</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="n"/>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>Père du maire Gilles Dufour</t>
+          <t>Fils de Cécile Truchon — conjoint de Gisèle</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>André Simard</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>Le Chef</t>
-        </is>
-      </c>
+          <t>Yves Fortin</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n"/>
       <c r="C139" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
@@ -10485,133 +10493,133 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>Directeur du Service de police de Saguenay</t>
+          <t>Producteur de bleuets</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Chicoutimi</t>
+          <t>La Baie</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>155, Rue Bégin</t>
+          <t>2100, Chemin Saint-Anicet</t>
         </is>
       </c>
       <c r="H139" s="7" t="n">
-        <v>48.4214</v>
+        <v>48.3285</v>
       </c>
       <c r="I139" s="7" t="n">
-        <v>-71.05719999999999</v>
+        <v>-70.928</v>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Moustache grise, uniforme</t>
+          <t>Bronzé, casquette John Deere</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
         <is>
-          <t>Uniforme SPS</t>
+          <t>Chemise à carreaux</t>
         </is>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>Insigne de poitrine</t>
+          <t>Seau de bleuets</t>
         </is>
       </c>
       <c r="M139" s="5" t="inlineStr">
         <is>
-          <t>portraits/123-andre-simard-web.webp</t>
+          <t>portraits/70-yves-fortin-web.webp</t>
         </is>
       </c>
       <c r="N139" s="5" t="inlineStr">
         <is>
-          <t>Simard</t>
-        </is>
-      </c>
-      <c r="O139" s="5" t="inlineStr">
-        <is>
-          <t>police</t>
-        </is>
-      </c>
+          <t>Fortin</t>
+        </is>
+      </c>
+      <c r="O139" s="5" t="n"/>
       <c r="P139" s="5" t="inlineStr">
         <is>
-          <t>Supérieur de Pierre Samson</t>
+          <t>Époux de Pauline Fortin</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Caroline Otis</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="n"/>
+          <t>Zack Bérubé</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Ti-Zack</t>
+        </is>
+      </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Présidente — Chambre de commerce du Saguenay</t>
+          <t>Commis de nuit — beignerie</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Chicoutimi</t>
+          <t>La Baie</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>197, Rue Racine Est</t>
+          <t>314, Chemin des Chutes</t>
         </is>
       </c>
       <c r="H140" s="4" t="n">
-        <v>48.428</v>
+        <v>48.32615</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>-71.054</v>
+        <v>-70.92345</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Collier de perles, manteau</t>
+          <t>Cernes, casquette brune</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Manteau tailleur</t>
+          <t>Tablier sur hoodie</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Cartes de visite</t>
+          <t>Café en carton</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>portraits/128-caroline-otis-web.webp</t>
+          <t>portraits/175-zack-berube-web.webp</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>Otis</t>
+          <t>Bérubé</t>
         </is>
       </c>
       <c r="O140" s="2" t="n"/>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>Nièce de Jeanne Otis</t>
+          <t>Fils de Lucie Bérubé — cadet de Kevin et Jessy</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Catherine Samson</t>
+          <t>Élodie Martel</t>
         </is>
       </c>
       <c r="B141" s="5" t="n"/>
@@ -10621,214 +10629,206 @@
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>Adjointe administrative — palais de justice</t>
+          <t>Éducatrice — Musée du Fjord</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>Chicoutimi</t>
+          <t>La Baie</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>147, Rue Bégin</t>
+          <t>3346, Boulevard de la Grande-Baie Sud</t>
         </is>
       </c>
       <c r="H141" s="7" t="n">
-        <v>48.42133</v>
+        <v>48.3178</v>
       </c>
       <c r="I141" s="7" t="n">
-        <v>-71.05748</v>
+        <v>-70.854</v>
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Carré brun, sérieuse</t>
+          <t>Lanière, chandail</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
         <is>
-          <t>Manteau tailleur</t>
+          <t>Chandail musée</t>
         </is>
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>Agenda noir</t>
+          <t>Dépliant d’expo</t>
         </is>
       </c>
       <c r="M141" s="5" t="inlineStr">
         <is>
-          <t>portraits/64-catherine-samson-web.webp</t>
+          <t>portraits/140-elodie-martel-web.webp</t>
         </is>
       </c>
       <c r="N141" s="5" t="inlineStr">
         <is>
-          <t>Samson</t>
+          <t>Martel</t>
         </is>
       </c>
       <c r="O141" s="5" t="n"/>
       <c r="P141" s="5" t="inlineStr">
         <is>
-          <t>Épouse de Pierre Samson</t>
+          <t>Cousine de Julie et Amélie Martel</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Danny Fortin</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Néon</t>
-        </is>
-      </c>
+          <t>Émile Brassard</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n"/>
       <c r="C142" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Propriétaire — club Le Néon</t>
+          <t>Pompier — caserne de La Baie</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Chicoutimi</t>
+          <t>La Baie</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>590, Rue Racine Est</t>
+          <t>50, Rue des Pompiers</t>
         </is>
       </c>
       <c r="H142" s="4" t="n">
-        <v>48.4269</v>
+        <v>48.336</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>-71.0535</v>
+        <v>-70.88200000000001</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Chemise soie, chaîne</t>
+          <t>Carrure, barbe courte</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>Chemise de soie</t>
+          <t>T-shirt caserne</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>Néons du bar</t>
+          <t>Radio portative</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>portraits/158-danny-fortin-web.webp</t>
+          <t>portraits/76-emile-brassard-web.webp</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Brassard</t>
         </is>
       </c>
       <c r="O142" s="2" t="n"/>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>Façade du clan — croise Lady Dynamite</t>
+          <t>Époux de Marie-Claude Brassard</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Denis Pedneault</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>Den</t>
-        </is>
-      </c>
+          <t>Émilie Gauthier</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n"/>
       <c r="C143" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>Propriétaire — radio CKRS</t>
+          <t>Gérante Dollarama</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Chicoutimi</t>
+          <t>La Baie</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>121, Rue Racine Est</t>
+          <t>47, Rue des Iris</t>
         </is>
       </c>
       <c r="H143" s="7" t="n">
-        <v>48.4284</v>
+        <v>48.3509</v>
       </c>
       <c r="I143" s="7" t="n">
-        <v>-71.05249999999999</v>
+        <v>-70.8831</v>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Casque autour du cou, chemise voyante</t>
+          <t>Cheveux attachés, badge</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr">
         <is>
-          <t>Chemise radio</t>
+          <t>Polo Dollarama</t>
         </is>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>Casque-micro</t>
+          <t>Talkie-walkie</t>
         </is>
       </c>
       <c r="M143" s="5" t="inlineStr">
         <is>
-          <t>portraits/129-denis-pedneault-web.webp</t>
+          <t>portraits/87-emilie-gauthier-web.webp</t>
         </is>
       </c>
       <c r="N143" s="5" t="inlineStr">
         <is>
-          <t>Pedneault</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="O143" s="5" t="n"/>
       <c r="P143" s="5" t="inlineStr">
         <is>
-          <t>Cousin de Réjean Pedneault</t>
+          <t>Supérieure de Stéphanie Lapointe</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Enzo Bianchi</t>
+          <t>Éric Boucher</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Le Conseiller</t>
+          <t>Boubou</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -10837,65 +10837,65 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Conseiller en gestion d’entreprise</t>
+          <t>Ferrailleur</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Chicoutimi</t>
+          <t>La Baie</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>198, Rue Racine Est</t>
+          <t>2408, Chemin Saint-Anicet</t>
         </is>
       </c>
       <c r="H144" s="4" t="n">
-        <v>48.428</v>
+        <v>48.3302</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>-71.05419999999999</v>
+        <v>-70.93245</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Lunettes, complet gris</t>
+          <t>Barbe, casque de chantier</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Complet gris</t>
+          <t>Salopette tachée</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Carnet de cuir</t>
+          <t>Aimant à ferraille</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>portraits/153-enzo-bianchi-web.webp</t>
+          <t>portraits/47-eric-boucher-web.webp</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Boucher</t>
         </is>
       </c>
       <c r="O144" s="2" t="n"/>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>Conseiller de Vittorio</t>
+          <t>Fils de Fernande — frère de Dévon</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>François Côté</t>
+          <t>Albert Dufour</t>
         </is>
       </c>
       <c r="B145" s="5" t="n"/>
@@ -10905,11 +10905,11 @@
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>Rédacteur en chef — Le Quotidien</t>
+          <t>Retraité — ex-conseiller</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
@@ -10919,60 +10919,60 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>100, Rue Racine Est</t>
+          <t>205, Rue Racine Est</t>
         </is>
       </c>
       <c r="H145" s="7" t="n">
-        <v>48.4277</v>
+        <v>48.4283</v>
       </c>
       <c r="I145" s="7" t="n">
-        <v>-71.053</v>
+        <v>-71.0535</v>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Manches relevées, stylo rouge</t>
+          <t>Cheveux blancs clairsemés, canne</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr">
         <is>
-          <t>Chemise de rédaction</t>
+          <t>Veston</t>
         </is>
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>Stylo rouge</t>
+          <t>Canne au parc</t>
         </is>
       </c>
       <c r="M145" s="5" t="inlineStr">
         <is>
-          <t>portraits/134-francois-cote-web.webp</t>
+          <t>portraits/169-albert-dufour-web.webp</t>
         </is>
       </c>
       <c r="N145" s="5" t="inlineStr">
         <is>
-          <t>Côté</t>
+          <t>Dufour</t>
         </is>
       </c>
       <c r="O145" s="5" t="inlineStr">
         <is>
-          <t>presse</t>
+          <t>hôtel de ville</t>
         </is>
       </c>
       <c r="P145" s="5" t="inlineStr">
         <is>
-          <t>Patron d’Olivier Savard — ex-patron de JP</t>
+          <t>Père du maire Gilles Dufour</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Gilles Dufour</t>
+          <t>André Simard</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Monsieur le Maire</t>
+          <t>Le Chef</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -10981,11 +10981,11 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Maire de Saguenay</t>
+          <t>Directeur du Service de police de Saguenay</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -10995,55 +10995,55 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>201, Rue Racine Est</t>
+          <t>155, Rue Bégin</t>
         </is>
       </c>
       <c r="H146" s="4" t="n">
-        <v>48.4282</v>
+        <v>48.4214</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>-71.0534</v>
+        <v>-71.05719999999999</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Cheveux gris, veston marine</t>
+          <t>Moustache grise, uniforme</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Complet, épinglette de ville</t>
+          <t>Uniforme SPS</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>Poignée de main</t>
+          <t>Insigne de poitrine</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>portraits/121-gilles-dufour-web.webp</t>
+          <t>portraits/123-andre-simard-web.webp</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>Dufour</t>
+          <t>Simard</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>hôtel de ville</t>
+          <t>police</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>Fils d’Albert Dufour — maire de Saguenay</t>
+          <t>Supérieur de Pierre Samson</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Hélène Samson</t>
+          <t>Caroline Otis</t>
         </is>
       </c>
       <c r="B147" s="5" t="n"/>
@@ -11053,11 +11053,11 @@
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>Retraitée — ex-secrétaire de palais</t>
+          <t>Présidente — Chambre de commerce du Saguenay</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
@@ -11067,51 +11067,51 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>149, Rue Bégin</t>
+          <t>197, Rue Racine Est</t>
         </is>
       </c>
       <c r="H147" s="7" t="n">
-        <v>48.4213</v>
+        <v>48.428</v>
       </c>
       <c r="I147" s="7" t="n">
-        <v>-71.0574</v>
+        <v>-71.054</v>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Cheveux soignés, manteau beige</t>
+          <t>Collier de perles, manteau</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>Manteau beige</t>
+          <t>Manteau tailleur</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>Sac à main</t>
+          <t>Cartes de visite</t>
         </is>
       </c>
       <c r="M147" s="5" t="inlineStr">
         <is>
-          <t>portraits/168-helene-samson-web.webp</t>
+          <t>portraits/128-caroline-otis-web.webp</t>
         </is>
       </c>
       <c r="N147" s="5" t="inlineStr">
         <is>
-          <t>Samson</t>
+          <t>Otis</t>
         </is>
       </c>
       <c r="O147" s="5" t="n"/>
       <c r="P147" s="5" t="inlineStr">
         <is>
-          <t>Mère de Pierre Samson</t>
+          <t>Nièce de Jeanne Otis</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Isabelle Gagné</t>
+          <t>Catherine Samson</t>
         </is>
       </c>
       <c r="B148" s="2" t="n"/>
@@ -11121,11 +11121,11 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Députée — Assemblée nationale</t>
+          <t>Adjointe administrative — palais de justice</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -11135,60 +11135,56 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>145, Rue Racine Est</t>
+          <t>147, Rue Bégin</t>
         </is>
       </c>
       <c r="H148" s="4" t="n">
-        <v>48.4279</v>
+        <v>48.42133</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>-71.0531</v>
+        <v>-71.05748</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Carré blond, blazer rouge</t>
+          <t>Carré brun, sérieuse</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>Blazer rouge</t>
+          <t>Manteau tailleur</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Épinglette fleurdelisé</t>
+          <t>Agenda noir</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>portraits/122-isabelle-gagne-web.webp</t>
+          <t>portraits/64-catherine-samson-web.webp</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Gagné</t>
-        </is>
-      </c>
-      <c r="O148" s="2" t="inlineStr">
-        <is>
-          <t>politique</t>
-        </is>
-      </c>
+          <t>Samson</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="n"/>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Épouse de Pierre Samson</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Roy</t>
+          <t>Danny Fortin</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Johnny Fake</t>
+          <t>Néon</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -11197,11 +11193,11 @@
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>Arnaqueur — fausses identités</t>
+          <t>Propriétaire — club Le Néon</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
@@ -11211,60 +11207,56 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>1186, Boulevard Talbot</t>
+          <t>590, Rue Racine Est</t>
         </is>
       </c>
       <c r="H149" s="7" t="n">
-        <v>48.3986</v>
+        <v>48.4269</v>
       </c>
       <c r="I149" s="7" t="n">
-        <v>-71.0675</v>
+        <v>-71.0535</v>
       </c>
       <c r="J149" s="5" t="inlineStr">
         <is>
-          <t>Cheveux gominés, sourire</t>
+          <t>Chemise soie, chaîne</t>
         </is>
       </c>
       <c r="K149" s="5" t="inlineStr">
         <is>
-          <t>Complet cheap</t>
+          <t>Chemise de soie</t>
         </is>
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>Trois cellulaires</t>
+          <t>Néons du bar</t>
         </is>
       </c>
       <c r="M149" s="5" t="inlineStr">
         <is>
-          <t>portraits/119-jonathan-roy-web.webp</t>
+          <t>portraits/158-danny-fortin-web.webp</t>
         </is>
       </c>
       <c r="N149" s="5" t="inlineStr">
         <is>
-          <t>Roy</t>
-        </is>
-      </c>
-      <c r="O149" s="5" t="inlineStr">
-        <is>
-          <t>arnaque</t>
-        </is>
-      </c>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="O149" s="5" t="n"/>
       <c r="P149" s="5" t="inlineStr">
         <is>
-          <t>Célibataire — croise Alex Tremblay</t>
+          <t>Façade du clan — croise Lady Dynamite</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Julien Gagné</t>
+          <t>Denis Pedneault</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Le Volant</t>
+          <t>Den</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -11273,11 +11265,11 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Chauffeur de voiture de ville</t>
+          <t>Propriétaire — radio CKRS</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -11287,56 +11279,56 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>1188, Boulevard Talbot</t>
+          <t>121, Rue Racine Est</t>
         </is>
       </c>
       <c r="H150" s="4" t="n">
-        <v>48.3983</v>
+        <v>48.4284</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>-71.06780000000001</v>
+        <v>-71.05249999999999</v>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>Complet noir, oreillette</t>
+          <t>Casque autour du cou, chemise voyante</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>Complet noir</t>
+          <t>Chemise radio</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>VUS noir</t>
+          <t>Casque-micro</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>portraits/157-julien-gagne-web.webp</t>
+          <t>portraits/129-denis-pedneault-web.webp</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Pedneault</t>
         </is>
       </c>
       <c r="O150" s="2" t="n"/>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>Chauffeur de Vittorio</t>
+          <t>Cousin de Réjean Pedneault</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Justin Chen</t>
+          <t>Enzo Bianchi</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Junior Talbot</t>
+          <t>Le Conseiller</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -11345,11 +11337,11 @@
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>Étudiant en administration (Cégep de Chicoutimi)</t>
+          <t>Conseiller en gestion d’entreprise</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
@@ -11359,51 +11351,51 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>1180, Boulevard Talbot</t>
+          <t>198, Rue Racine Est</t>
         </is>
       </c>
       <c r="H151" s="7" t="n">
-        <v>48.398223</v>
+        <v>48.428</v>
       </c>
       <c r="I151" s="7" t="n">
-        <v>-71.06763599999999</v>
+        <v>-71.05419999999999</v>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Métis, Moncler propre</t>
+          <t>Lunettes, complet gris</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr">
         <is>
-          <t>Moncler noir</t>
+          <t>Complet gris</t>
         </is>
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>Paye trop cher</t>
+          <t>Carnet de cuir</t>
         </is>
       </c>
       <c r="M151" s="5" t="inlineStr">
         <is>
-          <t>portraits/26-justin-chen-web.webp</t>
+          <t>portraits/153-enzo-bianchi-web.webp</t>
         </is>
       </c>
       <c r="N151" s="5" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O151" s="5" t="n"/>
       <c r="P151" s="5" t="inlineStr">
         <is>
-          <t>Fils de Mei</t>
+          <t>Conseiller de Vittorio</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Laurie Lavoie</t>
+          <t>François Côté</t>
         </is>
       </c>
       <c r="B152" s="2" t="n"/>
@@ -11413,11 +11405,11 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Étudiante en psychologie (UQAC)</t>
+          <t>Rédacteur en chef — Le Quotidien</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -11427,69 +11419,73 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>555, Boulevard de l'Université</t>
+          <t>100, Rue Racine Est</t>
         </is>
       </c>
       <c r="H152" s="4" t="n">
-        <v>48.421623</v>
+        <v>48.4277</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>-71.07566199999999</v>
+        <v>-71.053</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Cheveux longs châtains, hoodie UQAC</t>
+          <t>Manches relevées, stylo rouge</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Hoodie UQAC</t>
+          <t>Chemise de rédaction</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Livre psycho</t>
+          <t>Stylo rouge</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>portraits/36-laurie-lavoie-web.webp</t>
+          <t>portraits/134-francois-cote-web.webp</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>Lavoie</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>presse</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>Sœur de JP</t>
+          <t>Patron d’Olivier Savard — ex-patron de JP</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Louise Villeneuve</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="n"/>
+          <t>Gilles Dufour</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Monsieur le Maire</t>
+        </is>
+      </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>Juge — Cour du Québec</t>
+          <t>Maire de Saguenay</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
@@ -11499,73 +11495,69 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>227, Rue Racine Est</t>
+          <t>201, Rue Racine Est</t>
         </is>
       </c>
       <c r="H153" s="7" t="n">
-        <v>48.4275</v>
+        <v>48.4282</v>
       </c>
       <c r="I153" s="7" t="n">
-        <v>-71.05419999999999</v>
+        <v>-71.0534</v>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Regard sévère, toge</t>
+          <t>Cheveux gris, veston marine</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
-          <t>Toge</t>
+          <t>Complet, épinglette de ville</t>
         </is>
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>Marteau de bois</t>
+          <t>Poignée de main</t>
         </is>
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
-          <t>portraits/127-louise-villeneuve-web.webp</t>
+          <t>portraits/121-gilles-dufour-web.webp</t>
         </is>
       </c>
       <c r="N153" s="5" t="inlineStr">
         <is>
-          <t>Villeneuve</t>
+          <t>Dufour</t>
         </is>
       </c>
       <c r="O153" s="5" t="inlineStr">
         <is>
-          <t>palais</t>
+          <t>hôtel de ville</t>
         </is>
       </c>
       <c r="P153" s="5" t="inlineStr">
         <is>
-          <t>Collègue de Catherine Samson</t>
+          <t>Fils d’Albert Dufour — maire de Saguenay</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Maria Santini</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>Donna Maria</t>
-        </is>
-      </c>
+          <t>Hélène Samson</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="n"/>
       <c r="C154" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Matriarche — restaurant familial</t>
+          <t>Retraitée — ex-secrétaire de palais</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -11575,51 +11567,51 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>200, Rue Racine Est</t>
+          <t>149, Rue Bégin</t>
         </is>
       </c>
       <c r="H154" s="4" t="n">
-        <v>48.42815</v>
+        <v>48.4213</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>-71.0543</v>
+        <v>-71.0574</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>Cheveux sombres, perles</t>
+          <t>Cheveux soignés, manteau beige</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Robe noire</t>
+          <t>Manteau beige</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Rosaire au poignet</t>
+          <t>Sac à main</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>portraits/152-maria-santini-web.webp</t>
+          <t>portraits/168-helene-samson-web.webp</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Samson</t>
         </is>
       </c>
       <c r="O154" s="2" t="n"/>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>Épouse de Vittorio</t>
+          <t>Mère de Pierre Samson</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Mei Chen</t>
+          <t>Isabelle Gagné</t>
         </is>
       </c>
       <c r="B155" s="5" t="n"/>
@@ -11629,11 +11621,11 @@
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>Préposée d’hôtel</t>
+          <t>Députée — Assemblée nationale</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
@@ -11643,56 +11635,60 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>1182, Boulevard Talbot</t>
+          <t>145, Rue Racine Est</t>
         </is>
       </c>
       <c r="H155" s="7" t="n">
-        <v>48.39835</v>
+        <v>48.4279</v>
       </c>
       <c r="I155" s="7" t="n">
-        <v>-71.06775</v>
+        <v>-71.0531</v>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Chinoise, chignon, calme</t>
+          <t>Carré blond, blazer rouge</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr">
         <is>
-          <t>Uniforme hôtel</t>
+          <t>Blazer rouge</t>
         </is>
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>Badges de chambre</t>
+          <t>Épinglette fleurdelisé</t>
         </is>
       </c>
       <c r="M155" s="5" t="inlineStr">
         <is>
-          <t>portraits/63-mei-chen-web.webp</t>
+          <t>portraits/122-isabelle-gagne-web.webp</t>
         </is>
       </c>
       <c r="N155" s="5" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="O155" s="5" t="n"/>
+          <t>Gagné</t>
+        </is>
+      </c>
+      <c r="O155" s="5" t="inlineStr">
+        <is>
+          <t>politique</t>
+        </is>
+      </c>
       <c r="P155" s="5" t="inlineStr">
         <is>
-          <t>Mère de Justin Chen</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Mgr Paul Tremblay</t>
+          <t>Jonathan Roy</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Monseigneur</t>
+          <t>Johnny Fake</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -11701,11 +11697,11 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Évêque — diocèse de Chicoutimi</t>
+          <t>Arnaqueur — fausses identités</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -11715,60 +11711,60 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>602, Rue Racine Est</t>
+          <t>1186, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H156" s="4" t="n">
-        <v>48.4268</v>
+        <v>48.3986</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>-71.0538</v>
+        <v>-71.0675</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>Cheveux blancs, col romain</t>
+          <t>Cheveux gominés, sourire</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>Soutane, rabat violet</t>
+          <t>Complet cheap</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Anneau pastoral</t>
+          <t>Trois cellulaires</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>portraits/126-mgr-paul-tremblay-web.webp</t>
+          <t>portraits/119-jonathan-roy-web.webp</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Tremblay</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>Église</t>
+          <t>arnaque</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>Supérieur de Lucien Lacroix</t>
+          <t>Célibataire — croise Alex Tremblay</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Nico Santini</t>
+          <t>Julien Gagné</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Nico</t>
+          <t>Le Volant</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -11777,11 +11773,11 @@
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>Préposé à la sécurité — restaurant</t>
+          <t>Chauffeur de voiture de ville</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
@@ -11791,33 +11787,33 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>202, Rue Racine Est</t>
+          <t>1188, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H157" s="7" t="n">
-        <v>48.4282</v>
+        <v>48.3983</v>
       </c>
       <c r="I157" s="7" t="n">
-        <v>-71.05459999999999</v>
+        <v>-71.06780000000001</v>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Cheveux gominés, veste cuir</t>
+          <t>Complet noir, oreillette</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr">
         <is>
-          <t>Veste de cuir</t>
+          <t>Complet noir</t>
         </is>
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>Sourire de défi</t>
+          <t>VUS noir</t>
         </is>
       </c>
       <c r="M157" s="5" t="inlineStr">
         <is>
-          <t>portraits/160-nico-santini-web.webp</t>
+          <t>portraits/157-julien-gagne-web.webp</t>
         </is>
       </c>
       <c r="N157" s="5" t="inlineStr">
@@ -11828,28 +11824,32 @@
       <c r="O157" s="5" t="n"/>
       <c r="P157" s="5" t="inlineStr">
         <is>
-          <t>Fils de Vittorio et Maria</t>
+          <t>Chauffeur de Vittorio</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Olivier Savard</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="n"/>
+          <t>Justin Chen</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Junior Talbot</t>
+        </is>
+      </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Journaliste — Le Quotidien</t>
+          <t>Étudiant en administration (Cégep de Chicoutimi)</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -11859,69 +11859,65 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>100, Rue Racine Est</t>
+          <t>1180, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H158" s="4" t="n">
-        <v>48.4278</v>
+        <v>48.398223</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>-71.05289999999999</v>
+        <v>-71.06763599999999</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Barbe, sacoche</t>
+          <t>Métis, Moncler propre</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>Manteau de ville</t>
+          <t>Moncler noir</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Carnet spiralé</t>
+          <t>Paye trop cher</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>portraits/78-olivier-savard-web.webp</t>
+          <t>portraits/26-justin-chen-web.webp</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Savard</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="O158" s="2" t="n"/>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>Célibataire — ex-collègue de JP</t>
+          <t>Fils de Mei</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Patrick Lapointe</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
-        <is>
-          <t>Pat</t>
-        </is>
-      </c>
+          <t>Laurie Lavoie</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="n"/>
       <c r="C159" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>Entrepreneur en construction</t>
+          <t>Étudiante en psychologie (UQAC)</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
@@ -11931,73 +11927,69 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>1250, Boulevard Talbot</t>
+          <t>555, Boulevard de l'Université</t>
         </is>
       </c>
       <c r="H159" s="7" t="n">
-        <v>48.3985</v>
+        <v>48.421623</v>
       </c>
       <c r="I159" s="7" t="n">
-        <v>-71.06276</v>
+        <v>-71.07566199999999</v>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>Polo construction</t>
+          <t>Cheveux longs châtains, hoodie UQAC</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>Polo construction</t>
+          <t>Hoodie UQAC</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>Devis 400k</t>
+          <t>Livre psycho</t>
         </is>
       </c>
       <c r="M159" s="5" t="inlineStr">
         <is>
-          <t>portraits/39-patrick-lapointe-web.webp</t>
+          <t>portraits/36-laurie-lavoie-web.webp</t>
         </is>
       </c>
       <c r="N159" s="5" t="inlineStr">
         <is>
-          <t>Lapointe</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O159" s="5" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="P159" s="5" t="inlineStr">
         <is>
-          <t>Frère de Marco</t>
+          <t>Sœur de JP</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Paul-André Côté</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>Le Chiffre</t>
-        </is>
-      </c>
+          <t>Louise Villeneuve</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="n"/>
       <c r="C160" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Comptable — sociétés-écrans</t>
+          <t>Juge — Cour du Québec</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -12007,56 +11999,60 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>1252, Boulevard Talbot</t>
+          <t>227, Rue Racine Est</t>
         </is>
       </c>
       <c r="H160" s="4" t="n">
-        <v>48.39855</v>
+        <v>48.4275</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-71.0629</v>
+        <v>-71.05419999999999</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Maigre, lunettes cheap</t>
+          <t>Regard sévère, toge</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>Chemise et classeur</t>
+          <t>Toge</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Tableurs</t>
+          <t>Marteau de bois</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>portraits/156-paul-andre-cote-web.webp</t>
+          <t>portraits/127-louise-villeneuve-web.webp</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Santini</t>
-        </is>
-      </c>
-      <c r="O160" s="2" t="n"/>
+          <t>Villeneuve</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>palais</t>
+        </is>
+      </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>Comptable du clan — croise Bertrand Gagnon</t>
+          <t>Collègue de Catherine Samson</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Pierre Samson</t>
+          <t>Maria Santini</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>L'Enquêteur</t>
+          <t>Donna Maria</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -12065,11 +12061,11 @@
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>Policier — Service de police de Saguenay, stupéfiants</t>
+          <t>Matriarche — restaurant familial</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
@@ -12079,51 +12075,51 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>145, Rue Bégin</t>
+          <t>200, Rue Racine Est</t>
         </is>
       </c>
       <c r="H161" s="7" t="n">
-        <v>48.421205</v>
+        <v>48.42815</v>
       </c>
       <c r="I161" s="7" t="n">
-        <v>-71.057355</v>
+        <v>-71.0543</v>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Cernes violacés</t>
+          <t>Cheveux sombres, perles</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr">
         <is>
-          <t>Pardessus brun-beige</t>
+          <t>Robe noire</t>
         </is>
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>Clique Bic bleu</t>
+          <t>Rosaire au poignet</t>
         </is>
       </c>
       <c r="M161" s="5" t="inlineStr">
         <is>
-          <t>portraits/07-pierre-samson-web.webp</t>
+          <t>portraits/152-maria-santini-web.webp</t>
         </is>
       </c>
       <c r="N161" s="5" t="inlineStr">
         <is>
-          <t>Samson</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O161" s="5" t="n"/>
       <c r="P161" s="5" t="inlineStr">
         <is>
-          <t>Fils d’Hélène Samson — époux de Catherine</t>
+          <t>Épouse de Vittorio</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Sophie Labbé</t>
+          <t>Mei Chen</t>
         </is>
       </c>
       <c r="B162" s="2" t="n"/>
@@ -12133,11 +12129,11 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Psychologue — clinique UQAC</t>
+          <t>Préposée d’hôtel</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -12147,56 +12143,56 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>555, Boulevard de l'Université</t>
+          <t>1182, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H162" s="4" t="n">
-        <v>48.4215</v>
+        <v>48.39835</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>-71.07550000000001</v>
+        <v>-71.06775</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>Chignon, lunettes</t>
+          <t>Chinoise, chignon, calme</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Cardigan</t>
+          <t>Uniforme hôtel</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Carnet de notes</t>
+          <t>Badges de chambre</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>portraits/104-sophie-labbe-web.webp</t>
+          <t>portraits/63-mei-chen-web.webp</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Labbé</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="O162" s="2" t="n"/>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>Célibataire — collègue de Laurie Lavoie</t>
+          <t>Mère de Justin Chen</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Vittorio Santini</t>
+          <t>Mgr Paul Tremblay</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Don Vittorio</t>
+          <t>Monseigneur</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
@@ -12205,11 +12201,11 @@
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Homme d’affaires — restauration et bars</t>
+          <t>Évêque — diocèse de Chicoutimi</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
@@ -12219,56 +12215,60 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>200, Rue Racine Est</t>
+          <t>602, Rue Racine Est</t>
         </is>
       </c>
       <c r="H163" s="7" t="n">
-        <v>48.4281</v>
+        <v>48.4268</v>
       </c>
       <c r="I163" s="7" t="n">
-        <v>-71.0545</v>
+        <v>-71.0538</v>
       </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
-          <t>Cheveux argentés gominés, chevalière</t>
+          <t>Cheveux blancs, col romain</t>
         </is>
       </c>
       <c r="K163" s="5" t="inlineStr">
         <is>
-          <t>Manteau noir</t>
+          <t>Soutane, rabat violet</t>
         </is>
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>Chevalière en or</t>
+          <t>Anneau pastoral</t>
         </is>
       </c>
       <c r="M163" s="5" t="inlineStr">
         <is>
-          <t>portraits/151-vittorio-santini-web.webp</t>
+          <t>portraits/126-mgr-paul-tremblay-web.webp</t>
         </is>
       </c>
       <c r="N163" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
-        </is>
-      </c>
-      <c r="O163" s="5" t="n"/>
+          <t>Tremblay</t>
+        </is>
+      </c>
+      <c r="O163" s="5" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
       <c r="P163" s="5" t="inlineStr">
         <is>
-          <t>Époux de Maria — tient Dévon à distance</t>
+          <t>Supérieur de Lucien Lacroix</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Éric Simard</t>
+          <t>Nico Santini</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Ti-Eric</t>
+          <t>Nico</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -12277,11 +12277,11 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Étudiant — Cégep de Chicoutimi</t>
+          <t>Préposé à la sécurité — restaurant</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -12291,332 +12291,344 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>1184, Boulevard Talbot</t>
+          <t>202, Rue Racine Est</t>
         </is>
       </c>
       <c r="H164" s="4" t="n">
-        <v>48.3984</v>
+        <v>48.4282</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-71.06740000000001</v>
+        <v>-71.05459999999999</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>Casquette, jeans</t>
+          <t>Cheveux gominés, veste cuir</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Hoodie cégep</t>
+          <t>Veste de cuir</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Skateboard</t>
+          <t>Sourire de défi</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>portraits/100-eric-simard-web.webp</t>
+          <t>portraits/160-nico-santini-web.webp</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O164" s="2" t="n"/>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>Colocataire de Justin Chen</t>
+          <t>Fils de Vittorio et Maria</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Antoine Lefèvre</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="inlineStr">
-        <is>
-          <t>Le Français</t>
-        </is>
-      </c>
+          <t>Olivier Savard</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="n"/>
       <c r="C165" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+          <t>Journaliste — Le Quotidien</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>1125, Rue Saint-Dominique</t>
+          <t>100, Rue Racine Est</t>
         </is>
       </c>
       <c r="H165" s="7" t="n">
-        <v>48.421279</v>
+        <v>48.4278</v>
       </c>
       <c r="I165" s="7" t="n">
-        <v>-71.244586</v>
+        <v>-71.05289999999999</v>
       </c>
       <c r="J165" s="5" t="inlineStr">
         <is>
-          <t>Barbe hipster</t>
+          <t>Barbe, sacoche</t>
         </is>
       </c>
       <c r="K165" s="5" t="inlineStr">
         <is>
-          <t>Friperie, caméra Sony</t>
+          <t>Manteau de ville</t>
         </is>
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>Veut docu raw</t>
+          <t>Carnet spiralé</t>
         </is>
       </c>
       <c r="M165" s="5" t="inlineStr">
         <is>
-          <t>portraits/20-antoine-lefevre-web.webp</t>
+          <t>portraits/78-olivier-savard-web.webp</t>
         </is>
       </c>
       <c r="N165" s="5" t="inlineStr">
         <is>
-          <t>Lefèvre</t>
+          <t>Savard</t>
         </is>
       </c>
       <c r="O165" s="5" t="n"/>
       <c r="P165" s="5" t="inlineStr">
         <is>
-          <t>Frère de Camille</t>
+          <t>Célibataire — ex-collègue de JP</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Benoit Larouche</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="n"/>
+          <t>Patrick Lapointe</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Enseignant — Cégep de Jonquière (ATM)</t>
+          <t>Entrepreneur en construction</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>2505, Rue Saint-Hubert</t>
+          <t>1250, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H166" s="4" t="n">
-        <v>48.416</v>
+        <v>48.3985</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>-71.253</v>
+        <v>-71.06276</v>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>Lunettes, barbe grise</t>
+          <t>Polo construction</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Chemise et cardigan</t>
+          <t>Polo construction</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Clap de cinéma</t>
+          <t>Devis 400k</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>portraits/86-benoit-larouche-web.webp</t>
+          <t>portraits/39-patrick-lapointe-web.webp</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>Larouche</t>
-        </is>
-      </c>
-      <c r="O166" s="2" t="n"/>
+          <t>Lapointe</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>Prof d’Antoine Lefèvre</t>
+          <t>Frère de Marco</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Camille Lefèvre</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="n"/>
+          <t>Paul-André Côté</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Le Chiffre</t>
+        </is>
+      </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>Étudiante en communications (UQAC)</t>
+          <t>Comptable — sociétés-écrans</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>1127, Rue Saint-Dominique</t>
+          <t>1252, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H167" s="7" t="n">
-        <v>48.4214</v>
+        <v>48.39855</v>
       </c>
       <c r="I167" s="7" t="n">
-        <v>-71.24469999999999</v>
+        <v>-71.0629</v>
       </c>
       <c r="J167" s="5" t="inlineStr">
         <is>
-          <t>Carré brun, appareil photo</t>
+          <t>Maigre, lunettes cheap</t>
         </is>
       </c>
       <c r="K167" s="5" t="inlineStr">
         <is>
-          <t>Manteau friperie</t>
+          <t>Chemise et classeur</t>
         </is>
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>Pentax vintage</t>
+          <t>Tableurs</t>
         </is>
       </c>
       <c r="M167" s="5" t="inlineStr">
         <is>
-          <t>portraits/65-camille-lefevre-web.webp</t>
+          <t>portraits/156-paul-andre-cote-web.webp</t>
         </is>
       </c>
       <c r="N167" s="5" t="inlineStr">
         <is>
-          <t>Lefèvre</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O167" s="5" t="n"/>
       <c r="P167" s="5" t="inlineStr">
         <is>
-          <t>Sœur d’Antoine Lefèvre</t>
+          <t>Comptable du clan — croise Bertrand Gagnon</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Dany Aubin</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="n"/>
+          <t>Pierre Samson</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>L'Enquêteur</t>
+        </is>
+      </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Soudeur</t>
+          <t>Policier — Service de police de Saguenay, stupéfiants</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2147, Boulevard Harvey</t>
+          <t>145, Rue Bégin</t>
         </is>
       </c>
       <c r="H168" s="4" t="n">
-        <v>48.41282</v>
+        <v>48.421205</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>-71.24145</v>
+        <v>-71.057355</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>Brûlé de soudeur, casque relevé</t>
+          <t>Cernes violacés</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>Manteau de soudeur</t>
+          <t>Pardessus brun-beige</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Masque de soudure</t>
+          <t>Clique Bic bleu</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>portraits/66-dany-aubin-web.webp</t>
+          <t>portraits/07-pierre-samson-web.webp</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t>Aubin</t>
+          <t>Samson</t>
         </is>
       </c>
       <c r="O168" s="2" t="n"/>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>Frère de Sam Aubin</t>
+          <t>Fils d’Hélène Samson — époux de Catherine</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Gérald Tremblay</t>
+          <t>Sofia Santini</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Le Syndic</t>
+          <t>Sofi</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -12625,69 +12637,65 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Délégué syndical — aluminerie</t>
+          <t>Élève du secondaire — aide au restaurant familial</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>3324, Rue Price</t>
+          <t>204, Rue Racine Est</t>
         </is>
       </c>
       <c r="H169" s="7" t="n">
-        <v>48.4258</v>
+        <v>48.42825</v>
       </c>
       <c r="I169" s="7" t="n">
-        <v>-71.24039999999999</v>
+        <v>-71.05475</v>
       </c>
       <c r="J169" s="5" t="inlineStr">
         <is>
-          <t>Manteau de travail, épinglette</t>
+          <t>Cheveux noirs ondulés, sourire en coin</t>
         </is>
       </c>
       <c r="K169" s="5" t="inlineStr">
         <is>
-          <t>Manteau d’usine</t>
+          <t>Tablier noir de service</t>
         </is>
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>Cartable de griefs</t>
+          <t>Cabaret à deux mains</t>
         </is>
       </c>
       <c r="M169" s="5" t="inlineStr">
         <is>
-          <t>portraits/137-gerald-tremblay-web.webp</t>
+          <t>portraits/177-sofia-santini-web.webp</t>
         </is>
       </c>
       <c r="N169" s="5" t="inlineStr">
         <is>
-          <t>Tremblay</t>
-        </is>
-      </c>
-      <c r="O169" s="5" t="inlineStr">
-        <is>
-          <t>syndicat</t>
-        </is>
-      </c>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="O169" s="5" t="n"/>
       <c r="P169" s="5" t="inlineStr">
         <is>
-          <t>Collègue de Mathieu Lavoie</t>
+          <t>Fille de Nico Santini — petite-fille de Vittorio et Maria</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Jean-Marc Fortin</t>
+          <t>Sophie Labbé</t>
         </is>
       </c>
       <c r="B170" s="2" t="n"/>
@@ -12697,74 +12705,70 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Directeur d’usine — Rio Tinto Arvida</t>
+          <t>Psychologue — clinique UQAC</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>1, Rue des Alumineries</t>
+          <t>555, Boulevard de l'Université</t>
         </is>
       </c>
       <c r="H170" s="4" t="n">
-        <v>48.4265</v>
+        <v>48.4215</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>-71.182</v>
+        <v>-71.07550000000001</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Cheveux argentés, manteau</t>
+          <t>Chignon, lunettes</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Manteau et casque blanc</t>
+          <t>Cardigan</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>Casque sous le bras</t>
+          <t>Carnet de notes</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>portraits/125-jean-marc-fortin-web.webp</t>
+          <t>portraits/104-sophie-labbe-web.webp</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>Fortin</t>
-        </is>
-      </c>
-      <c r="O170" s="2" t="inlineStr">
-        <is>
-          <t>industrie</t>
-        </is>
-      </c>
+          <t>Labbé</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="n"/>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
+          <t>Célibataire — collègue de Laurie Lavoie</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Mathieu Lavoie</t>
+          <t>Vittorio Santini</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Don Vittorio</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
@@ -12773,151 +12777,155 @@
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Technicien à l'aluminerie Rio Tinto — Arvida</t>
+          <t>Homme d’affaires — restauration et bars</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>3320, Rue Price</t>
+          <t>200, Rue Racine Est</t>
         </is>
       </c>
       <c r="H171" s="7" t="n">
-        <v>48.425907</v>
+        <v>48.4281</v>
       </c>
       <c r="I171" s="7" t="n">
-        <v>-71.240752</v>
+        <v>-71.0545</v>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>Propre, polo Rio Tinto</t>
+          <t>Cheveux argentés gominés, chevalière</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>Polo Rio Tinto</t>
+          <t>Manteau noir</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>Boîte à lunch</t>
+          <t>Chevalière en or</t>
         </is>
       </c>
       <c r="M171" s="5" t="inlineStr">
         <is>
-          <t>portraits/35-mathieu-lavoie-web.webp</t>
+          <t>portraits/151-vittorio-santini-web.webp</t>
         </is>
       </c>
       <c r="N171" s="5" t="inlineStr">
         <is>
-          <t>Lavoie</t>
-        </is>
-      </c>
-      <c r="O171" s="5" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="O171" s="5" t="n"/>
       <c r="P171" s="5" t="inlineStr">
         <is>
-          <t>Frère aîné de JP</t>
+          <t>Époux de Maria — tient Dévon à distance</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Mélissa Harvey</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="n"/>
+          <t>Éric Simard</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Ti-Eric</t>
+        </is>
+      </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Étudiante en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+          <t>Étudiant — Cégep de Chicoutimi</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>1129, Rue Saint-Dominique</t>
+          <t>1184, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H172" s="4" t="n">
-        <v>48.42135</v>
+        <v>48.3984</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-71.24464999999999</v>
+        <v>-71.06740000000001</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Chignon brouillon, manteau friperie</t>
+          <t>Casquette, jeans</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Manteau friperie</t>
+          <t>Hoodie cégep</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>Perche micro</t>
+          <t>Skateboard</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>portraits/110-melissa-harvey-web.webp</t>
+          <t>portraits/100-eric-simard-web.webp</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="O172" s="2" t="n"/>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>Nièce de François Harvey</t>
+          <t>Colocataire de Justin Chen</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>Nicolas Gagné</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="n"/>
+          <t>Antoine Lefèvre</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Le Français</t>
+        </is>
+      </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D173" s="6" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Technicien — aluminerie Rio Tinto Arvida</t>
+          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
@@ -12927,73 +12935,65 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>3322, Rue Price</t>
+          <t>1125, Rue Saint-Dominique</t>
         </is>
       </c>
       <c r="H173" s="7" t="n">
-        <v>48.426</v>
+        <v>48.421279</v>
       </c>
       <c r="I173" s="7" t="n">
-        <v>-71.2405</v>
+        <v>-71.244586</v>
       </c>
       <c r="J173" s="5" t="inlineStr">
         <is>
-          <t>Propre, lunettes de sécurité</t>
+          <t>Barbe hipster</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
         <is>
-          <t>Polo Rio Tinto</t>
+          <t>Friperie, caméra Sony</t>
         </is>
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>Casque blanc</t>
+          <t>Veut docu raw</t>
         </is>
       </c>
       <c r="M173" s="5" t="inlineStr">
         <is>
-          <t>portraits/94-nicolas-gagne-web.webp</t>
+          <t>portraits/20-antoine-lefevre-web.webp</t>
         </is>
       </c>
       <c r="N173" s="5" t="inlineStr">
         <is>
-          <t>Gagné</t>
-        </is>
-      </c>
-      <c r="O173" s="5" t="inlineStr">
-        <is>
-          <t>Arvida</t>
-        </is>
-      </c>
+          <t>Lefèvre</t>
+        </is>
+      </c>
+      <c r="O173" s="5" t="n"/>
       <c r="P173" s="5" t="inlineStr">
         <is>
-          <t>Collègue de Mathieu Lavoie</t>
+          <t>Frère de Camille</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Sam Aubin</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>Ink</t>
-        </is>
-      </c>
+          <t>Benoit Larouche</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n"/>
       <c r="C174" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Tatoueur</t>
+          <t>Enseignant — Cégep de Jonquière (ATM)</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -13003,49 +13003,761 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2145, Boulevard Harvey</t>
+          <t>2505, Rue Saint-Hubert</t>
         </is>
       </c>
       <c r="H174" s="4" t="n">
-        <v>48.412694</v>
+        <v>48.416</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-71.241325</v>
+        <v>-71.253</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>Cheveux bleus, full tattoos</t>
+          <t>Lunettes, barbe grise</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Tablier noir</t>
+          <t>Chemise et cardigan</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Efface tattoos gang</t>
+          <t>Clap de cinéma</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>portraits/24-sam-aubin-web.webp</t>
+          <t>portraits/86-benoit-larouche-web.webp</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>Aubin</t>
+          <t>Larouche</t>
         </is>
       </c>
       <c r="O174" s="2" t="n"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
+          <t>Prof d’Antoine Lefèvre</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>Camille Lefèvre</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="n"/>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>Étudiante en communications (UQAC)</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>1127, Rue Saint-Dominique</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="n">
+        <v>48.4214</v>
+      </c>
+      <c r="I175" s="7" t="n">
+        <v>-71.24469999999999</v>
+      </c>
+      <c r="J175" s="5" t="inlineStr">
+        <is>
+          <t>Carré brun, appareil photo</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="inlineStr">
+        <is>
+          <t>Manteau friperie</t>
+        </is>
+      </c>
+      <c r="L175" s="5" t="inlineStr">
+        <is>
+          <t>Pentax vintage</t>
+        </is>
+      </c>
+      <c r="M175" s="5" t="inlineStr">
+        <is>
+          <t>portraits/65-camille-lefevre-web.webp</t>
+        </is>
+      </c>
+      <c r="N175" s="5" t="inlineStr">
+        <is>
+          <t>Lefèvre</t>
+        </is>
+      </c>
+      <c r="O175" s="5" t="n"/>
+      <c r="P175" s="5" t="inlineStr">
+        <is>
+          <t>Sœur d’Antoine Lefèvre</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Dany Aubin</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Soudeur</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>2147, Boulevard Harvey</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="n">
+        <v>48.41282</v>
+      </c>
+      <c r="I176" s="4" t="n">
+        <v>-71.24145</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>Brûlé de soudeur, casque relevé</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>Manteau de soudeur</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>Masque de soudure</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>portraits/66-dany-aubin-web.webp</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Aubin</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="n"/>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>Frère de Sam Aubin</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Gérald Tremblay</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Le Syndic</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>Délégué syndical — aluminerie</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>3324, Rue Price</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="n">
+        <v>48.4258</v>
+      </c>
+      <c r="I177" s="7" t="n">
+        <v>-71.24039999999999</v>
+      </c>
+      <c r="J177" s="5" t="inlineStr">
+        <is>
+          <t>Manteau de travail, épinglette</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="inlineStr">
+        <is>
+          <t>Manteau d’usine</t>
+        </is>
+      </c>
+      <c r="L177" s="5" t="inlineStr">
+        <is>
+          <t>Cartable de griefs</t>
+        </is>
+      </c>
+      <c r="M177" s="5" t="inlineStr">
+        <is>
+          <t>portraits/137-gerald-tremblay-web.webp</t>
+        </is>
+      </c>
+      <c r="N177" s="5" t="inlineStr">
+        <is>
+          <t>Tremblay</t>
+        </is>
+      </c>
+      <c r="O177" s="5" t="inlineStr">
+        <is>
+          <t>syndicat</t>
+        </is>
+      </c>
+      <c r="P177" s="5" t="inlineStr">
+        <is>
+          <t>Collègue de Mathieu Lavoie</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Jade Boivin</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Élève du primaire — patineuse artistique</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>2350, Rue Sainte-Famille</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="n">
+        <v>48.4293</v>
+      </c>
+      <c r="I178" s="4" t="n">
+        <v>-71.23480000000001</v>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>Chignon serré, sourire édenté</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Veston d’entraînement mauve</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>Protège-lames</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>portraits/183-jade-boivin-web.webp</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Boivin</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="n"/>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>Nièce de France et Maxime Boivin</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Marc Fortin</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>Directeur d’usine — Rio Tinto Arvida</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>1, Rue des Alumineries</t>
+        </is>
+      </c>
+      <c r="H179" s="7" t="n">
+        <v>48.4265</v>
+      </c>
+      <c r="I179" s="7" t="n">
+        <v>-71.182</v>
+      </c>
+      <c r="J179" s="5" t="inlineStr">
+        <is>
+          <t>Cheveux argentés, manteau</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="inlineStr">
+        <is>
+          <t>Manteau et casque blanc</t>
+        </is>
+      </c>
+      <c r="L179" s="5" t="inlineStr">
+        <is>
+          <t>Casque sous le bras</t>
+        </is>
+      </c>
+      <c r="M179" s="5" t="inlineStr">
+        <is>
+          <t>portraits/125-jean-marc-fortin-web.webp</t>
+        </is>
+      </c>
+      <c r="N179" s="5" t="inlineStr">
+        <is>
+          <t>Fortin</t>
+        </is>
+      </c>
+      <c r="O179" s="5" t="inlineStr">
+        <is>
+          <t>industrie</t>
+        </is>
+      </c>
+      <c r="P179" s="5" t="inlineStr">
+        <is>
+          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Ludovic Larouche</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Ludo</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>2507, Rue Saint-Hubert</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="n">
+        <v>48.41615</v>
+      </c>
+      <c r="I180" s="4" t="n">
+        <v>-71.25285</v>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>Boucles, lunettes rondes</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Veste en velours côtelé</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>Caméscope à l’épaule</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>portraits/182-ludovic-larouche-web.webp</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Larouche</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="n"/>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>Fils de Benoit Larouche</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>Mathieu Lavoie</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>Mat</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>Technicien à l'aluminerie Rio Tinto — Arvida</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>3320, Rue Price</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="n">
+        <v>48.425907</v>
+      </c>
+      <c r="I181" s="7" t="n">
+        <v>-71.240752</v>
+      </c>
+      <c r="J181" s="5" t="inlineStr">
+        <is>
+          <t>Propre, polo Rio Tinto</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="inlineStr">
+        <is>
+          <t>Polo Rio Tinto</t>
+        </is>
+      </c>
+      <c r="L181" s="5" t="inlineStr">
+        <is>
+          <t>Boîte à lunch</t>
+        </is>
+      </c>
+      <c r="M181" s="5" t="inlineStr">
+        <is>
+          <t>portraits/35-mathieu-lavoie-web.webp</t>
+        </is>
+      </c>
+      <c r="N181" s="5" t="inlineStr">
+        <is>
+          <t>Lavoie</t>
+        </is>
+      </c>
+      <c r="O181" s="5" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="P181" s="5" t="inlineStr">
+        <is>
+          <t>Frère aîné de JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Mélissa Harvey</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Étudiante en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>1129, Rue Saint-Dominique</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="n">
+        <v>48.42135</v>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>-71.24464999999999</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>Chignon brouillon, manteau friperie</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>Manteau friperie</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>Perche micro</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>portraits/110-melissa-harvey-web.webp</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="n"/>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>Nièce de François Harvey</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Nicolas Gagné</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>Technicien — aluminerie Rio Tinto Arvida</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>3322, Rue Price</t>
+        </is>
+      </c>
+      <c r="H183" s="7" t="n">
+        <v>48.426</v>
+      </c>
+      <c r="I183" s="7" t="n">
+        <v>-71.2405</v>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>Propre, lunettes de sécurité</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="inlineStr">
+        <is>
+          <t>Polo Rio Tinto</t>
+        </is>
+      </c>
+      <c r="L183" s="5" t="inlineStr">
+        <is>
+          <t>Casque blanc</t>
+        </is>
+      </c>
+      <c r="M183" s="5" t="inlineStr">
+        <is>
+          <t>portraits/94-nicolas-gagne-web.webp</t>
+        </is>
+      </c>
+      <c r="N183" s="5" t="inlineStr">
+        <is>
+          <t>Gagné</t>
+        </is>
+      </c>
+      <c r="O183" s="5" t="inlineStr">
+        <is>
+          <t>Arvida</t>
+        </is>
+      </c>
+      <c r="P183" s="5" t="inlineStr">
+        <is>
+          <t>Collègue de Mathieu Lavoie</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Sam Aubin</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Ink</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Tatoueur</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>2145, Boulevard Harvey</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="n">
+        <v>48.412694</v>
+      </c>
+      <c r="I184" s="4" t="n">
+        <v>-71.241325</v>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Cheveux bleus, full tattoos</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Tablier noir</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>Efface tattoos gang</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>portraits/24-sam-aubin-web.webp</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>Aubin</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="n"/>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
           <t>Frère de Dany</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P174"/>
+  <autoFilter ref="A1:P184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13081,7 +13793,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>173 entrées · 16 colonnes · région du Saguenay (Québec)</t>
+          <t>183 entrées · 16 colonnes · région du Saguenay (Québec)</t>
         </is>
       </c>
     </row>

--- a/base_personnages_fictifs.xlsx
+++ b/base_personnages_fictifs.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Lisez-moi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$P$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$P$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P184"/>
+  <dimension ref="A1:P194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11467,12 +11467,12 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Gilles Dufour</t>
+          <t>Gaétan Bossé</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Monsieur le Maire</t>
+          <t>Le Bouquiniste</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -11481,11 +11481,11 @@
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>Maire de Saguenay</t>
+          <t>Bouquiniste — livres usagés</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
@@ -11495,69 +11495,69 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>201, Rue Racine Est</t>
+          <t>312, Rue Bossé</t>
         </is>
       </c>
       <c r="H153" s="7" t="n">
-        <v>48.4282</v>
+        <v>48.42445</v>
       </c>
       <c r="I153" s="7" t="n">
-        <v>-71.0534</v>
+        <v>-71.07605</v>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Cheveux gris, veston marine</t>
+          <t>Barbe grise, lunettes sur le front</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
-          <t>Complet, épinglette de ville</t>
+          <t>Veste de laine sur chemise à carreaux</t>
         </is>
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>Poignée de main</t>
+          <t>Livre relié sous le bras</t>
         </is>
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
-          <t>portraits/121-gilles-dufour-web.webp</t>
+          <t>portraits/184-gaetan-bosse-web.webp</t>
         </is>
       </c>
       <c r="N153" s="5" t="inlineStr">
         <is>
-          <t>Dufour</t>
-        </is>
-      </c>
-      <c r="O153" s="5" t="inlineStr">
-        <is>
-          <t>hôtel de ville</t>
-        </is>
-      </c>
+          <t>Bossé</t>
+        </is>
+      </c>
+      <c r="O153" s="5" t="n"/>
       <c r="P153" s="5" t="inlineStr">
         <is>
-          <t>Fils d’Albert Dufour — maire de Saguenay</t>
+          <t>Frère de Stéphane Bossé</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Hélène Samson</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="n"/>
+          <t>Gilles Dufour</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Monsieur le Maire</t>
+        </is>
+      </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Retraitée — ex-secrétaire de palais</t>
+          <t>Maire de Saguenay</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -11567,51 +11567,55 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>149, Rue Bégin</t>
+          <t>201, Rue Racine Est</t>
         </is>
       </c>
       <c r="H154" s="4" t="n">
-        <v>48.4213</v>
+        <v>48.4282</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>-71.0574</v>
+        <v>-71.0534</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>Cheveux soignés, manteau beige</t>
+          <t>Cheveux gris, veston marine</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Manteau beige</t>
+          <t>Complet, épinglette de ville</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Sac à main</t>
+          <t>Poignée de main</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>portraits/168-helene-samson-web.webp</t>
+          <t>portraits/121-gilles-dufour-web.webp</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>Samson</t>
-        </is>
-      </c>
-      <c r="O154" s="2" t="n"/>
+          <t>Dufour</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>hôtel de ville</t>
+        </is>
+      </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>Mère de Pierre Samson</t>
+          <t>Fils d’Albert Dufour — maire de Saguenay</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Isabelle Gagné</t>
+          <t>Hélène Samson</t>
         </is>
       </c>
       <c r="B155" s="5" t="n"/>
@@ -11621,11 +11625,11 @@
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>Députée — Assemblée nationale</t>
+          <t>Retraitée — ex-secrétaire de palais</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
@@ -11635,73 +11639,65 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>145, Rue Racine Est</t>
+          <t>149, Rue Bégin</t>
         </is>
       </c>
       <c r="H155" s="7" t="n">
-        <v>48.4279</v>
+        <v>48.4213</v>
       </c>
       <c r="I155" s="7" t="n">
-        <v>-71.0531</v>
+        <v>-71.0574</v>
       </c>
       <c r="J155" s="5" t="inlineStr">
         <is>
-          <t>Carré blond, blazer rouge</t>
+          <t>Cheveux soignés, manteau beige</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr">
         <is>
-          <t>Blazer rouge</t>
+          <t>Manteau beige</t>
         </is>
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>Épinglette fleurdelisé</t>
+          <t>Sac à main</t>
         </is>
       </c>
       <c r="M155" s="5" t="inlineStr">
         <is>
-          <t>portraits/122-isabelle-gagne-web.webp</t>
+          <t>portraits/168-helene-samson-web.webp</t>
         </is>
       </c>
       <c r="N155" s="5" t="inlineStr">
         <is>
-          <t>Gagné</t>
-        </is>
-      </c>
-      <c r="O155" s="5" t="inlineStr">
-        <is>
-          <t>politique</t>
-        </is>
-      </c>
+          <t>Samson</t>
+        </is>
+      </c>
+      <c r="O155" s="5" t="n"/>
       <c r="P155" s="5" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Mère de Pierre Samson</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Jonathan Roy</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>Johnny Fake</t>
-        </is>
-      </c>
+          <t>Isabelle Gagné</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="n"/>
       <c r="C156" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Arnaqueur — fausses identités</t>
+          <t>Députée — Assemblée nationale</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -11711,60 +11707,60 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>1186, Boulevard Talbot</t>
+          <t>145, Rue Racine Est</t>
         </is>
       </c>
       <c r="H156" s="4" t="n">
-        <v>48.3986</v>
+        <v>48.4279</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>-71.0675</v>
+        <v>-71.0531</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>Cheveux gominés, sourire</t>
+          <t>Carré blond, blazer rouge</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>Complet cheap</t>
+          <t>Blazer rouge</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Trois cellulaires</t>
+          <t>Épinglette fleurdelisé</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>portraits/119-jonathan-roy-web.webp</t>
+          <t>portraits/122-isabelle-gagne-web.webp</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Gagné</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>arnaque</t>
+          <t>politique</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>Célibataire — croise Alex Tremblay</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Julien Gagné</t>
+          <t>Jonathan Roy</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Le Volant</t>
+          <t>Johnny Fake</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -11773,11 +11769,11 @@
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>Chauffeur de voiture de ville</t>
+          <t>Arnaqueur — fausses identités</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
@@ -11787,56 +11783,60 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>1188, Boulevard Talbot</t>
+          <t>1186, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H157" s="7" t="n">
-        <v>48.3983</v>
+        <v>48.3986</v>
       </c>
       <c r="I157" s="7" t="n">
-        <v>-71.06780000000001</v>
+        <v>-71.0675</v>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Complet noir, oreillette</t>
+          <t>Cheveux gominés, sourire</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr">
         <is>
-          <t>Complet noir</t>
+          <t>Complet cheap</t>
         </is>
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>VUS noir</t>
+          <t>Trois cellulaires</t>
         </is>
       </c>
       <c r="M157" s="5" t="inlineStr">
         <is>
-          <t>portraits/157-julien-gagne-web.webp</t>
+          <t>portraits/119-jonathan-roy-web.webp</t>
         </is>
       </c>
       <c r="N157" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
-        </is>
-      </c>
-      <c r="O157" s="5" t="n"/>
+          <t>Roy</t>
+        </is>
+      </c>
+      <c r="O157" s="5" t="inlineStr">
+        <is>
+          <t>arnaque</t>
+        </is>
+      </c>
       <c r="P157" s="5" t="inlineStr">
         <is>
-          <t>Chauffeur de Vittorio</t>
+          <t>Célibataire — croise Alex Tremblay</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Justin Chen</t>
+          <t>Julien Gagné</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Junior Talbot</t>
+          <t>Le Volant</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -11845,11 +11845,11 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Étudiant en administration (Cégep de Chicoutimi)</t>
+          <t>Chauffeur de voiture de ville</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -11859,65 +11859,69 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>1180, Boulevard Talbot</t>
+          <t>1188, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H158" s="4" t="n">
-        <v>48.398223</v>
+        <v>48.3983</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>-71.06763599999999</v>
+        <v>-71.06780000000001</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Métis, Moncler propre</t>
+          <t>Complet noir, oreillette</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>Moncler noir</t>
+          <t>Complet noir</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Paye trop cher</t>
+          <t>VUS noir</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>portraits/26-justin-chen-web.webp</t>
+          <t>portraits/157-julien-gagne-web.webp</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O158" s="2" t="n"/>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>Fils de Mei</t>
+          <t>Chauffeur de Vittorio</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Laurie Lavoie</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="n"/>
+          <t>Justin Chen</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Junior Talbot</t>
+        </is>
+      </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>Étudiante en psychologie (UQAC)</t>
+          <t>Étudiant en administration (Cégep de Chicoutimi)</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
@@ -11927,69 +11931,69 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>555, Boulevard de l'Université</t>
+          <t>1180, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H159" s="7" t="n">
-        <v>48.421623</v>
+        <v>48.398223</v>
       </c>
       <c r="I159" s="7" t="n">
-        <v>-71.07566199999999</v>
+        <v>-71.06763599999999</v>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>Cheveux longs châtains, hoodie UQAC</t>
+          <t>Métis, Moncler propre</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>Hoodie UQAC</t>
+          <t>Moncler noir</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>Livre psycho</t>
+          <t>Paye trop cher</t>
         </is>
       </c>
       <c r="M159" s="5" t="inlineStr">
         <is>
-          <t>portraits/36-laurie-lavoie-web.webp</t>
+          <t>portraits/26-justin-chen-web.webp</t>
         </is>
       </c>
       <c r="N159" s="5" t="inlineStr">
         <is>
-          <t>Lavoie</t>
-        </is>
-      </c>
-      <c r="O159" s="5" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="O159" s="5" t="n"/>
       <c r="P159" s="5" t="inlineStr">
         <is>
-          <t>Sœur de JP</t>
+          <t>Fils de Mei</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Louise Villeneuve</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="n"/>
+          <t>Jérémie Côté</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Ti-Poste</t>
+        </is>
+      </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Juge — Cour du Québec</t>
+          <t>Facteur — Postes Canada</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -11999,73 +12003,69 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>227, Rue Racine Est</t>
+          <t>145, Rue Sainte-Anne</t>
         </is>
       </c>
       <c r="H160" s="4" t="n">
-        <v>48.4275</v>
+        <v>48.42915</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>-71.05419999999999</v>
+        <v>-71.06835</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Regard sévère, toge</t>
+          <t>Barbe taillée, joues rouges</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>Toge</t>
+          <t>Parka de facteur à bandes</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Marteau de bois</t>
+          <t>Sacoche de courrier</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>portraits/127-louise-villeneuve-web.webp</t>
+          <t>portraits/187-jeremie-cote-web.webp</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Villeneuve</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>palais</t>
+          <t>poste</t>
         </is>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>Collègue de Catherine Samson</t>
+          <t>Neveu d’Alain Côté</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Maria Santini</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
-        <is>
-          <t>Donna Maria</t>
-        </is>
-      </c>
+          <t>Laurie Lavoie</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="n"/>
       <c r="C161" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>Matriarche — restaurant familial</t>
+          <t>Étudiante en psychologie (UQAC)</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
@@ -12075,51 +12075,55 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>200, Rue Racine Est</t>
+          <t>555, Boulevard de l'Université</t>
         </is>
       </c>
       <c r="H161" s="7" t="n">
-        <v>48.42815</v>
+        <v>48.421623</v>
       </c>
       <c r="I161" s="7" t="n">
-        <v>-71.0543</v>
+        <v>-71.07566199999999</v>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Cheveux sombres, perles</t>
+          <t>Cheveux longs châtains, hoodie UQAC</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr">
         <is>
-          <t>Robe noire</t>
+          <t>Hoodie UQAC</t>
         </is>
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>Rosaire au poignet</t>
+          <t>Livre psycho</t>
         </is>
       </c>
       <c r="M161" s="5" t="inlineStr">
         <is>
-          <t>portraits/152-maria-santini-web.webp</t>
+          <t>portraits/36-laurie-lavoie-web.webp</t>
         </is>
       </c>
       <c r="N161" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
-        </is>
-      </c>
-      <c r="O161" s="5" t="n"/>
+          <t>Lavoie</t>
+        </is>
+      </c>
+      <c r="O161" s="5" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
       <c r="P161" s="5" t="inlineStr">
         <is>
-          <t>Épouse de Vittorio</t>
+          <t>Sœur de JP</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Mei Chen</t>
+          <t>Lise Gauthier</t>
         </is>
       </c>
       <c r="B162" s="2" t="n"/>
@@ -12129,11 +12133,11 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Préposée d’hôtel</t>
+          <t>Infirmière clinicienne — CLSC</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -12143,69 +12147,65 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>1182, Boulevard Talbot</t>
+          <t>222, Rue du Havre</t>
         </is>
       </c>
       <c r="H162" s="4" t="n">
-        <v>48.39835</v>
+        <v>48.4293</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>-71.06775</v>
+        <v>-71.05445</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>Chinoise, chignon, calme</t>
+          <t>Cheveux blancs courts, lunettes à chaînette</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Uniforme hôtel</t>
+          <t>Cardigan bourgogne sur uniforme</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Badges de chambre</t>
+          <t>Tensiomètre</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>portraits/63-mei-chen-web.webp</t>
+          <t>portraits/188-lise-gauthier-web.webp</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="O162" s="2" t="n"/>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>Mère de Justin Chen</t>
+          <t>Tante de Steve et Chantal Gauthier</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Mgr Paul Tremblay</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>Monseigneur</t>
-        </is>
-      </c>
+          <t>Louise Villeneuve</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="n"/>
       <c r="C163" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Évêque — diocèse de Chicoutimi</t>
+          <t>Juge — Cour du Québec</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
@@ -12215,60 +12215,60 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>602, Rue Racine Est</t>
+          <t>227, Rue Racine Est</t>
         </is>
       </c>
       <c r="H163" s="7" t="n">
-        <v>48.4268</v>
+        <v>48.4275</v>
       </c>
       <c r="I163" s="7" t="n">
-        <v>-71.0538</v>
+        <v>-71.05419999999999</v>
       </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
-          <t>Cheveux blancs, col romain</t>
+          <t>Regard sévère, toge</t>
         </is>
       </c>
       <c r="K163" s="5" t="inlineStr">
         <is>
-          <t>Soutane, rabat violet</t>
+          <t>Toge</t>
         </is>
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>Anneau pastoral</t>
+          <t>Marteau de bois</t>
         </is>
       </c>
       <c r="M163" s="5" t="inlineStr">
         <is>
-          <t>portraits/126-mgr-paul-tremblay-web.webp</t>
+          <t>portraits/127-louise-villeneuve-web.webp</t>
         </is>
       </c>
       <c r="N163" s="5" t="inlineStr">
         <is>
-          <t>Tremblay</t>
+          <t>Villeneuve</t>
         </is>
       </c>
       <c r="O163" s="5" t="inlineStr">
         <is>
-          <t>Église</t>
+          <t>palais</t>
         </is>
       </c>
       <c r="P163" s="5" t="inlineStr">
         <is>
-          <t>Supérieur de Lucien Lacroix</t>
+          <t>Collègue de Catherine Samson</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Nico Santini</t>
+          <t>Maria Santini</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Nico</t>
+          <t>Donna Maria</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -12277,11 +12277,11 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Préposé à la sécurité — restaurant</t>
+          <t>Matriarche — restaurant familial</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -12291,33 +12291,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>202, Rue Racine Est</t>
+          <t>200, Rue Racine Est</t>
         </is>
       </c>
       <c r="H164" s="4" t="n">
-        <v>48.4282</v>
+        <v>48.42815</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-71.05459999999999</v>
+        <v>-71.0543</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>Cheveux gominés, veste cuir</t>
+          <t>Cheveux sombres, perles</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Veste de cuir</t>
+          <t>Robe noire</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Sourire de défi</t>
+          <t>Rosaire au poignet</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>portraits/160-nico-santini-web.webp</t>
+          <t>portraits/152-maria-santini-web.webp</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12328,17 +12328,21 @@
       <c r="O164" s="2" t="n"/>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>Fils de Vittorio et Maria</t>
+          <t>Épouse de Vittorio</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Olivier Savard</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="n"/>
+          <t>Marie-Ève Boucher</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>La Plume</t>
+        </is>
+      </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
@@ -12349,7 +12353,7 @@
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Journaliste — Le Quotidien</t>
+          <t>Journaliste — quotidien régional</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
@@ -12359,69 +12363,65 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>100, Rue Racine Est</t>
+          <t>412, Rue Jacques-Cartier Ouest</t>
         </is>
       </c>
       <c r="H165" s="7" t="n">
-        <v>48.4278</v>
+        <v>48.4268</v>
       </c>
       <c r="I165" s="7" t="n">
-        <v>-71.05289999999999</v>
+        <v>-71.0699</v>
       </c>
       <c r="J165" s="5" t="inlineStr">
         <is>
-          <t>Barbe, sacoche</t>
+          <t>Cheveux courts noirs, regard vif</t>
         </is>
       </c>
       <c r="K165" s="5" t="inlineStr">
         <is>
-          <t>Manteau de ville</t>
+          <t>Trench, cordon de presse</t>
         </is>
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>Carnet spiralé</t>
+          <t>Calepin et téléphone</t>
         </is>
       </c>
       <c r="M165" s="5" t="inlineStr">
         <is>
-          <t>portraits/78-olivier-savard-web.webp</t>
+          <t>portraits/185-marie-eve-boucher-web.webp</t>
         </is>
       </c>
       <c r="N165" s="5" t="inlineStr">
         <is>
-          <t>Savard</t>
+          <t>Bossé</t>
         </is>
       </c>
       <c r="O165" s="5" t="n"/>
       <c r="P165" s="5" t="inlineStr">
         <is>
-          <t>Célibataire — ex-collègue de JP</t>
+          <t>Conjointe de Stéphane Bossé — cousine de Normand Boucher</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Patrick Lapointe</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>Pat</t>
-        </is>
-      </c>
+          <t>Mei Chen</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="n"/>
       <c r="C166" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneur en construction</t>
+          <t>Préposée d’hôtel</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -12431,60 +12431,56 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>1250, Boulevard Talbot</t>
+          <t>1182, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H166" s="4" t="n">
-        <v>48.3985</v>
+        <v>48.39835</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>-71.06276</v>
+        <v>-71.06775</v>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>Polo construction</t>
+          <t>Chinoise, chignon, calme</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Polo construction</t>
+          <t>Uniforme hôtel</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Devis 400k</t>
+          <t>Badges de chambre</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>portraits/39-patrick-lapointe-web.webp</t>
+          <t>portraits/63-mei-chen-web.webp</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>Lapointe</t>
-        </is>
-      </c>
-      <c r="O166" s="2" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="n"/>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>Frère de Marco</t>
+          <t>Mère de Justin Chen</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Paul-André Côté</t>
+          <t>Mgr Paul Tremblay</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Le Chiffre</t>
+          <t>Monseigneur</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
@@ -12493,11 +12489,11 @@
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>Comptable — sociétés-écrans</t>
+          <t>Évêque — diocèse de Chicoutimi</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
@@ -12507,56 +12503,60 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>1252, Boulevard Talbot</t>
+          <t>602, Rue Racine Est</t>
         </is>
       </c>
       <c r="H167" s="7" t="n">
-        <v>48.39855</v>
+        <v>48.4268</v>
       </c>
       <c r="I167" s="7" t="n">
-        <v>-71.0629</v>
+        <v>-71.0538</v>
       </c>
       <c r="J167" s="5" t="inlineStr">
         <is>
-          <t>Maigre, lunettes cheap</t>
+          <t>Cheveux blancs, col romain</t>
         </is>
       </c>
       <c r="K167" s="5" t="inlineStr">
         <is>
-          <t>Chemise et classeur</t>
+          <t>Soutane, rabat violet</t>
         </is>
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>Tableurs</t>
+          <t>Anneau pastoral</t>
         </is>
       </c>
       <c r="M167" s="5" t="inlineStr">
         <is>
-          <t>portraits/156-paul-andre-cote-web.webp</t>
+          <t>portraits/126-mgr-paul-tremblay-web.webp</t>
         </is>
       </c>
       <c r="N167" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
-        </is>
-      </c>
-      <c r="O167" s="5" t="n"/>
+          <t>Tremblay</t>
+        </is>
+      </c>
+      <c r="O167" s="5" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
       <c r="P167" s="5" t="inlineStr">
         <is>
-          <t>Comptable du clan — croise Bertrand Gagnon</t>
+          <t>Supérieur de Lucien Lacroix</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Pierre Samson</t>
+          <t>Nico Santini</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>L'Enquêteur</t>
+          <t>Nico</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -12565,11 +12565,11 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Policier — Service de police de Saguenay, stupéfiants</t>
+          <t>Préposé à la sécurité — restaurant</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -12579,69 +12579,65 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>145, Rue Bégin</t>
+          <t>202, Rue Racine Est</t>
         </is>
       </c>
       <c r="H168" s="4" t="n">
-        <v>48.421205</v>
+        <v>48.4282</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>-71.057355</v>
+        <v>-71.05459999999999</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>Cernes violacés</t>
+          <t>Cheveux gominés, veste cuir</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>Pardessus brun-beige</t>
+          <t>Veste de cuir</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Clique Bic bleu</t>
+          <t>Sourire de défi</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>portraits/07-pierre-samson-web.webp</t>
+          <t>portraits/160-nico-santini-web.webp</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t>Samson</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O168" s="2" t="n"/>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>Fils d’Hélène Samson — époux de Catherine</t>
+          <t>Fils de Vittorio et Maria</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Sofia Santini</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
-        <is>
-          <t>Sofi</t>
-        </is>
-      </c>
+          <t>Olivier Savard</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="n"/>
       <c r="C169" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Élève du secondaire — aide au restaurant familial</t>
+          <t>Journaliste — Le Quotidien</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
@@ -12651,65 +12647,69 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>204, Rue Racine Est</t>
+          <t>100, Rue Racine Est</t>
         </is>
       </c>
       <c r="H169" s="7" t="n">
-        <v>48.42825</v>
+        <v>48.4278</v>
       </c>
       <c r="I169" s="7" t="n">
-        <v>-71.05475</v>
+        <v>-71.05289999999999</v>
       </c>
       <c r="J169" s="5" t="inlineStr">
         <is>
-          <t>Cheveux noirs ondulés, sourire en coin</t>
+          <t>Barbe, sacoche</t>
         </is>
       </c>
       <c r="K169" s="5" t="inlineStr">
         <is>
-          <t>Tablier noir de service</t>
+          <t>Manteau de ville</t>
         </is>
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>Cabaret à deux mains</t>
+          <t>Carnet spiralé</t>
         </is>
       </c>
       <c r="M169" s="5" t="inlineStr">
         <is>
-          <t>portraits/177-sofia-santini-web.webp</t>
+          <t>portraits/78-olivier-savard-web.webp</t>
         </is>
       </c>
       <c r="N169" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Savard</t>
         </is>
       </c>
       <c r="O169" s="5" t="n"/>
       <c r="P169" s="5" t="inlineStr">
         <is>
-          <t>Fille de Nico Santini — petite-fille de Vittorio et Maria</t>
+          <t>Célibataire — ex-collègue de JP</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Sophie Labbé</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="n"/>
+          <t>Patrick Lapointe</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Psychologue — clinique UQAC</t>
+          <t>Entrepreneur en construction</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -12719,56 +12719,60 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>555, Boulevard de l'Université</t>
+          <t>1250, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H170" s="4" t="n">
-        <v>48.4215</v>
+        <v>48.3985</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>-71.07550000000001</v>
+        <v>-71.06276</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Chignon, lunettes</t>
+          <t>Polo construction</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Cardigan</t>
+          <t>Polo construction</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>Carnet de notes</t>
+          <t>Devis 400k</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>portraits/104-sophie-labbe-web.webp</t>
+          <t>portraits/39-patrick-lapointe-web.webp</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>Labbé</t>
-        </is>
-      </c>
-      <c r="O170" s="2" t="n"/>
+          <t>Lapointe</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>Célibataire — collègue de Laurie Lavoie</t>
+          <t>Frère de Marco</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Vittorio Santini</t>
+          <t>Paul-André Côté</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Don Vittorio</t>
+          <t>Le Chiffre</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
@@ -12777,11 +12781,11 @@
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Homme d’affaires — restauration et bars</t>
+          <t>Comptable — sociétés-écrans</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
@@ -12791,33 +12795,33 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>200, Rue Racine Est</t>
+          <t>1252, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H171" s="7" t="n">
-        <v>48.4281</v>
+        <v>48.39855</v>
       </c>
       <c r="I171" s="7" t="n">
-        <v>-71.0545</v>
+        <v>-71.0629</v>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>Cheveux argentés gominés, chevalière</t>
+          <t>Maigre, lunettes cheap</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>Manteau noir</t>
+          <t>Chemise et classeur</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>Chevalière en or</t>
+          <t>Tableurs</t>
         </is>
       </c>
       <c r="M171" s="5" t="inlineStr">
         <is>
-          <t>portraits/151-vittorio-santini-web.webp</t>
+          <t>portraits/156-paul-andre-cote-web.webp</t>
         </is>
       </c>
       <c r="N171" s="5" t="inlineStr">
@@ -12828,19 +12832,19 @@
       <c r="O171" s="5" t="n"/>
       <c r="P171" s="5" t="inlineStr">
         <is>
-          <t>Époux de Maria — tient Dévon à distance</t>
+          <t>Comptable du clan — croise Bertrand Gagnon</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Éric Simard</t>
+          <t>Pierre Samson</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Ti-Eric</t>
+          <t>L'Enquêteur</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -12849,11 +12853,11 @@
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Étudiant — Cégep de Chicoutimi</t>
+          <t>Policier — Service de police de Saguenay, stupéfiants</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -12863,56 +12867,56 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>1184, Boulevard Talbot</t>
+          <t>145, Rue Bégin</t>
         </is>
       </c>
       <c r="H172" s="4" t="n">
-        <v>48.3984</v>
+        <v>48.421205</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-71.06740000000001</v>
+        <v>-71.057355</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Casquette, jeans</t>
+          <t>Cernes violacés</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Hoodie cégep</t>
+          <t>Pardessus brun-beige</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>Skateboard</t>
+          <t>Clique Bic bleu</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>portraits/100-eric-simard-web.webp</t>
+          <t>portraits/07-pierre-samson-web.webp</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Samson</t>
         </is>
       </c>
       <c r="O172" s="2" t="n"/>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>Colocataire de Justin Chen</t>
+          <t>Fils d’Hélène Samson — époux de Catherine</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>Antoine Lefèvre</t>
+          <t>Sofia Santini</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Le Français</t>
+          <t>Sofi</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
@@ -12921,65 +12925,65 @@
         </is>
       </c>
       <c r="D173" s="6" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+          <t>Élève du secondaire — aide au restaurant familial</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>1125, Rue Saint-Dominique</t>
+          <t>204, Rue Racine Est</t>
         </is>
       </c>
       <c r="H173" s="7" t="n">
-        <v>48.421279</v>
+        <v>48.42825</v>
       </c>
       <c r="I173" s="7" t="n">
-        <v>-71.244586</v>
+        <v>-71.05475</v>
       </c>
       <c r="J173" s="5" t="inlineStr">
         <is>
-          <t>Barbe hipster</t>
+          <t>Cheveux noirs ondulés, sourire en coin</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
         <is>
-          <t>Friperie, caméra Sony</t>
+          <t>Tablier noir de service</t>
         </is>
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>Veut docu raw</t>
+          <t>Cabaret à deux mains</t>
         </is>
       </c>
       <c r="M173" s="5" t="inlineStr">
         <is>
-          <t>portraits/20-antoine-lefevre-web.webp</t>
+          <t>portraits/177-sofia-santini-web.webp</t>
         </is>
       </c>
       <c r="N173" s="5" t="inlineStr">
         <is>
-          <t>Lefèvre</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O173" s="5" t="n"/>
       <c r="P173" s="5" t="inlineStr">
         <is>
-          <t>Frère de Camille</t>
+          <t>Fille de Nico Santini — petite-fille de Vittorio et Maria</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Benoit Larouche</t>
+          <t>Sophie Labbé</t>
         </is>
       </c>
       <c r="B174" s="2" t="n"/>
@@ -12989,133 +12993,137 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Enseignant — Cégep de Jonquière (ATM)</t>
+          <t>Psychologue — clinique UQAC</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2505, Rue Saint-Hubert</t>
+          <t>555, Boulevard de l'Université</t>
         </is>
       </c>
       <c r="H174" s="4" t="n">
-        <v>48.416</v>
+        <v>48.4215</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-71.253</v>
+        <v>-71.07550000000001</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>Lunettes, barbe grise</t>
+          <t>Chignon, lunettes</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Chemise et cardigan</t>
+          <t>Cardigan</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Clap de cinéma</t>
+          <t>Carnet de notes</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>portraits/86-benoit-larouche-web.webp</t>
+          <t>portraits/104-sophie-labbe-web.webp</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>Larouche</t>
+          <t>Labbé</t>
         </is>
       </c>
       <c r="O174" s="2" t="n"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>Prof d’Antoine Lefèvre</t>
+          <t>Célibataire — collègue de Laurie Lavoie</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>Camille Lefèvre</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="n"/>
+          <t>Stéphane Bossé</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Steph Patate</t>
+        </is>
+      </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D175" s="6" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Étudiante en communications (UQAC)</t>
+          <t>Cuisinier — casse-croûte</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>1127, Rue Saint-Dominique</t>
+          <t>410, Rue Jacques-Cartier Ouest</t>
         </is>
       </c>
       <c r="H175" s="7" t="n">
-        <v>48.4214</v>
+        <v>48.42675</v>
       </c>
       <c r="I175" s="7" t="n">
-        <v>-71.24469999999999</v>
+        <v>-71.07004999999999</v>
       </c>
       <c r="J175" s="5" t="inlineStr">
         <is>
-          <t>Carré brun, appareil photo</t>
+          <t>Cheveux ras, avant-bras tatoués</t>
         </is>
       </c>
       <c r="K175" s="5" t="inlineStr">
         <is>
-          <t>Manteau friperie</t>
+          <t>Tablier blanc taché</t>
         </is>
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>Pentax vintage</t>
+          <t>Spatule à la main</t>
         </is>
       </c>
       <c r="M175" s="5" t="inlineStr">
         <is>
-          <t>portraits/65-camille-lefevre-web.webp</t>
+          <t>portraits/186-stephane-bosse-web.webp</t>
         </is>
       </c>
       <c r="N175" s="5" t="inlineStr">
         <is>
-          <t>Lefèvre</t>
+          <t>Bossé</t>
         </is>
       </c>
       <c r="O175" s="5" t="n"/>
       <c r="P175" s="5" t="inlineStr">
         <is>
-          <t>Sœur d’Antoine Lefèvre</t>
+          <t>Frère de Gaétan Bossé — conjoint de Marie-Ève Boucher</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Dany Aubin</t>
+          <t>Valentina Rojas</t>
         </is>
       </c>
       <c r="B176" s="2" t="n"/>
@@ -13125,70 +13133,70 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Soudeur</t>
+          <t>Épicière — produits latino-américains</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2147, Boulevard Harvey</t>
+          <t>318, Rue Bossé</t>
         </is>
       </c>
       <c r="H176" s="4" t="n">
-        <v>48.41282</v>
+        <v>48.4245</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>-71.24145</v>
+        <v>-71.07585</v>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>Brûlé de soudeur, casque relevé</t>
+          <t>Longs cheveux noirs, anneaux dorés</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Manteau de soudeur</t>
+          <t>Tablier vert sur chandail</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>Masque de soudure</t>
+          <t>Caisse de plantains</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>portraits/66-dany-aubin-web.webp</t>
+          <t>portraits/189-valentina-rojas-web.webp</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>Aubin</t>
+          <t>Rojas</t>
         </is>
       </c>
       <c r="O176" s="2" t="n"/>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>Frère de Sam Aubin</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Gérald Tremblay</t>
+          <t>Vittorio Santini</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Le Syndic</t>
+          <t>Don Vittorio</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -13197,151 +13205,155 @@
         </is>
       </c>
       <c r="D177" s="6" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Délégué syndical — aluminerie</t>
+          <t>Homme d’affaires — restauration et bars</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>3324, Rue Price</t>
+          <t>200, Rue Racine Est</t>
         </is>
       </c>
       <c r="H177" s="7" t="n">
-        <v>48.4258</v>
+        <v>48.4281</v>
       </c>
       <c r="I177" s="7" t="n">
-        <v>-71.24039999999999</v>
+        <v>-71.0545</v>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>Manteau de travail, épinglette</t>
+          <t>Cheveux argentés gominés, chevalière</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>Manteau d’usine</t>
+          <t>Manteau noir</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>Cartable de griefs</t>
+          <t>Chevalière en or</t>
         </is>
       </c>
       <c r="M177" s="5" t="inlineStr">
         <is>
-          <t>portraits/137-gerald-tremblay-web.webp</t>
+          <t>portraits/151-vittorio-santini-web.webp</t>
         </is>
       </c>
       <c r="N177" s="5" t="inlineStr">
         <is>
-          <t>Tremblay</t>
-        </is>
-      </c>
-      <c r="O177" s="5" t="inlineStr">
-        <is>
-          <t>syndicat</t>
-        </is>
-      </c>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="O177" s="5" t="n"/>
       <c r="P177" s="5" t="inlineStr">
         <is>
-          <t>Collègue de Mathieu Lavoie</t>
+          <t>Époux de Maria — tient Dévon à distance</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Jade Boivin</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="n"/>
+          <t>Éric Simard</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Ti-Eric</t>
+        </is>
+      </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Élève du primaire — patineuse artistique</t>
+          <t>Étudiant — Cégep de Chicoutimi</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2350, Rue Sainte-Famille</t>
+          <t>1184, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H178" s="4" t="n">
-        <v>48.4293</v>
+        <v>48.3984</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>-71.23480000000001</v>
+        <v>-71.06740000000001</v>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Chignon serré, sourire édenté</t>
+          <t>Casquette, jeans</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>Veston d’entraînement mauve</t>
+          <t>Hoodie cégep</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>Protège-lames</t>
+          <t>Skateboard</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>portraits/183-jade-boivin-web.webp</t>
+          <t>portraits/100-eric-simard-web.webp</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>Boivin</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="O178" s="2" t="n"/>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>Nièce de France et Maxime Boivin</t>
+          <t>Colocataire de Justin Chen</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Jean-Marc Fortin</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="n"/>
+          <t>Antoine Lefèvre</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Le Français</t>
+        </is>
+      </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D179" s="6" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>Directeur d’usine — Rio Tinto Arvida</t>
+          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
@@ -13351,73 +13363,65 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>1, Rue des Alumineries</t>
+          <t>1125, Rue Saint-Dominique</t>
         </is>
       </c>
       <c r="H179" s="7" t="n">
-        <v>48.4265</v>
+        <v>48.421279</v>
       </c>
       <c r="I179" s="7" t="n">
-        <v>-71.182</v>
+        <v>-71.244586</v>
       </c>
       <c r="J179" s="5" t="inlineStr">
         <is>
-          <t>Cheveux argentés, manteau</t>
+          <t>Barbe hipster</t>
         </is>
       </c>
       <c r="K179" s="5" t="inlineStr">
         <is>
-          <t>Manteau et casque blanc</t>
+          <t>Friperie, caméra Sony</t>
         </is>
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>Casque sous le bras</t>
+          <t>Veut docu raw</t>
         </is>
       </c>
       <c r="M179" s="5" t="inlineStr">
         <is>
-          <t>portraits/125-jean-marc-fortin-web.webp</t>
+          <t>portraits/20-antoine-lefevre-web.webp</t>
         </is>
       </c>
       <c r="N179" s="5" t="inlineStr">
         <is>
-          <t>Fortin</t>
-        </is>
-      </c>
-      <c r="O179" s="5" t="inlineStr">
-        <is>
-          <t>industrie</t>
-        </is>
-      </c>
+          <t>Lefèvre</t>
+        </is>
+      </c>
+      <c r="O179" s="5" t="n"/>
       <c r="P179" s="5" t="inlineStr">
         <is>
-          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
+          <t>Frère de Camille</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Ludovic Larouche</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>Ludo</t>
-        </is>
-      </c>
+          <t>Audrey Lavoie</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n"/>
       <c r="C180" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+          <t>Apprentie électricienne — aluminerie Rio Tinto Arvida</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -13427,69 +13431,69 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2507, Rue Saint-Hubert</t>
+          <t>2135, Rue Davis</t>
         </is>
       </c>
       <c r="H180" s="4" t="n">
-        <v>48.41615</v>
+        <v>48.42455</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>-71.25285</v>
+        <v>-71.18219999999999</v>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Boucles, lunettes rondes</t>
+          <t>Tresse blonde, lunettes de sécurité</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>Veste en velours côtelé</t>
+          <t>Manteau orange haute visibilité</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>Caméscope à l’épaule</t>
+          <t>Glacière à lunch</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>portraits/182-ludovic-larouche-web.webp</t>
+          <t>portraits/191-audrey-lavoie-web.webp</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>Larouche</t>
-        </is>
-      </c>
-      <c r="O180" s="2" t="n"/>
+          <t>Lavoie</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Arvida</t>
+        </is>
+      </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>Fils de Benoit Larouche</t>
+          <t>Fille de Fernand Lavoie — collègue de Nicolas Gagné</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Mathieu Lavoie</t>
-        </is>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
-        <is>
-          <t>Mat</t>
-        </is>
-      </c>
+          <t>Benoit Larouche</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="n"/>
       <c r="C181" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D181" s="6" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Technicien à l'aluminerie Rio Tinto — Arvida</t>
+          <t>Enseignant — Cégep de Jonquière (ATM)</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
@@ -13499,55 +13503,51 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>3320, Rue Price</t>
+          <t>2505, Rue Saint-Hubert</t>
         </is>
       </c>
       <c r="H181" s="7" t="n">
-        <v>48.425907</v>
+        <v>48.416</v>
       </c>
       <c r="I181" s="7" t="n">
-        <v>-71.240752</v>
+        <v>-71.253</v>
       </c>
       <c r="J181" s="5" t="inlineStr">
         <is>
-          <t>Propre, polo Rio Tinto</t>
+          <t>Lunettes, barbe grise</t>
         </is>
       </c>
       <c r="K181" s="5" t="inlineStr">
         <is>
-          <t>Polo Rio Tinto</t>
+          <t>Chemise et cardigan</t>
         </is>
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>Boîte à lunch</t>
+          <t>Clap de cinéma</t>
         </is>
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>portraits/35-mathieu-lavoie-web.webp</t>
+          <t>portraits/86-benoit-larouche-web.webp</t>
         </is>
       </c>
       <c r="N181" s="5" t="inlineStr">
         <is>
-          <t>Lavoie</t>
-        </is>
-      </c>
-      <c r="O181" s="5" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+          <t>Larouche</t>
+        </is>
+      </c>
+      <c r="O181" s="5" t="n"/>
       <c r="P181" s="5" t="inlineStr">
         <is>
-          <t>Frère aîné de JP</t>
+          <t>Prof d’Antoine Lefèvre</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Mélissa Harvey</t>
+          <t>Camille Lefèvre</t>
         </is>
       </c>
       <c r="B182" s="2" t="n"/>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Étudiante en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+          <t>Étudiante en communications (UQAC)</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -13571,18 +13571,18 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>1129, Rue Saint-Dominique</t>
+          <t>1127, Rue Saint-Dominique</t>
         </is>
       </c>
       <c r="H182" s="4" t="n">
-        <v>48.42135</v>
+        <v>48.4214</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>-71.24464999999999</v>
+        <v>-71.24469999999999</v>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Chignon brouillon, manteau friperie</t>
+          <t>Carré brun, appareil photo</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -13592,30 +13592,30 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>Perche micro</t>
+          <t>Pentax vintage</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>portraits/110-melissa-harvey-web.webp</t>
+          <t>portraits/65-camille-lefevre-web.webp</t>
         </is>
       </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Lefèvre</t>
         </is>
       </c>
       <c r="O182" s="2" t="n"/>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>Nièce de François Harvey</t>
+          <t>Sœur d’Antoine Lefèvre</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Nicolas Gagné</t>
+          <t>Dany Aubin</t>
         </is>
       </c>
       <c r="B183" s="5" t="n"/>
@@ -13625,11 +13625,11 @@
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Technicien — aluminerie Rio Tinto Arvida</t>
+          <t>Soudeur</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
@@ -13639,125 +13639,849 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>3322, Rue Price</t>
+          <t>2147, Boulevard Harvey</t>
         </is>
       </c>
       <c r="H183" s="7" t="n">
-        <v>48.426</v>
+        <v>48.41282</v>
       </c>
       <c r="I183" s="7" t="n">
-        <v>-71.2405</v>
+        <v>-71.24145</v>
       </c>
       <c r="J183" s="5" t="inlineStr">
         <is>
-          <t>Propre, lunettes de sécurité</t>
+          <t>Brûlé de soudeur, casque relevé</t>
         </is>
       </c>
       <c r="K183" s="5" t="inlineStr">
         <is>
-          <t>Polo Rio Tinto</t>
+          <t>Manteau de soudeur</t>
         </is>
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>Casque blanc</t>
+          <t>Masque de soudure</t>
         </is>
       </c>
       <c r="M183" s="5" t="inlineStr">
         <is>
-          <t>portraits/94-nicolas-gagne-web.webp</t>
+          <t>portraits/66-dany-aubin-web.webp</t>
         </is>
       </c>
       <c r="N183" s="5" t="inlineStr">
         <is>
-          <t>Gagné</t>
-        </is>
-      </c>
-      <c r="O183" s="5" t="inlineStr">
-        <is>
-          <t>Arvida</t>
-        </is>
-      </c>
+          <t>Aubin</t>
+        </is>
+      </c>
+      <c r="O183" s="5" t="n"/>
       <c r="P183" s="5" t="inlineStr">
         <is>
-          <t>Collègue de Mathieu Lavoie</t>
+          <t>Frère de Sam Aubin</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
+          <t>Fernand Lavoie</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Ti-Fer</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Retraité — ex-opérateur de cuves à l’aluminerie</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>2131, Rue Davis</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="n">
+        <v>48.4244</v>
+      </c>
+      <c r="I184" s="4" t="n">
+        <v>-71.18225</v>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Casquette plate, mains larges</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Veste de laine à carreaux</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>Pipe éteinte</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>portraits/190-fernand-lavoie-web.webp</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>Lavoie</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>Arvida</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>Père d’Audrey Lavoie — cousin éloigné de Mathieu Lavoie</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Gérald Tremblay</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Le Syndic</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>Délégué syndical — aluminerie</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>3324, Rue Price</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="n">
+        <v>48.4258</v>
+      </c>
+      <c r="I185" s="7" t="n">
+        <v>-71.24039999999999</v>
+      </c>
+      <c r="J185" s="5" t="inlineStr">
+        <is>
+          <t>Manteau de travail, épinglette</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="inlineStr">
+        <is>
+          <t>Manteau d’usine</t>
+        </is>
+      </c>
+      <c r="L185" s="5" t="inlineStr">
+        <is>
+          <t>Cartable de griefs</t>
+        </is>
+      </c>
+      <c r="M185" s="5" t="inlineStr">
+        <is>
+          <t>portraits/137-gerald-tremblay-web.webp</t>
+        </is>
+      </c>
+      <c r="N185" s="5" t="inlineStr">
+        <is>
+          <t>Tremblay</t>
+        </is>
+      </c>
+      <c r="O185" s="5" t="inlineStr">
+        <is>
+          <t>syndicat</t>
+        </is>
+      </c>
+      <c r="P185" s="5" t="inlineStr">
+        <is>
+          <t>Collègue de Mathieu Lavoie</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Jade Boivin</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Élève du primaire — patineuse artistique</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>2350, Rue Sainte-Famille</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="n">
+        <v>48.4293</v>
+      </c>
+      <c r="I186" s="4" t="n">
+        <v>-71.23480000000001</v>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>Chignon serré, sourire édenté</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>Veston d’entraînement mauve</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>Protège-lames</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>portraits/183-jade-boivin-web.webp</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>Boivin</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="n"/>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>Nièce de France et Maxime Boivin</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Marc Fortin</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>Directeur d’usine — Rio Tinto Arvida</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>1, Rue des Alumineries</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="n">
+        <v>48.4265</v>
+      </c>
+      <c r="I187" s="7" t="n">
+        <v>-71.182</v>
+      </c>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>Cheveux argentés, manteau</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="inlineStr">
+        <is>
+          <t>Manteau et casque blanc</t>
+        </is>
+      </c>
+      <c r="L187" s="5" t="inlineStr">
+        <is>
+          <t>Casque sous le bras</t>
+        </is>
+      </c>
+      <c r="M187" s="5" t="inlineStr">
+        <is>
+          <t>portraits/125-jean-marc-fortin-web.webp</t>
+        </is>
+      </c>
+      <c r="N187" s="5" t="inlineStr">
+        <is>
+          <t>Fortin</t>
+        </is>
+      </c>
+      <c r="O187" s="5" t="inlineStr">
+        <is>
+          <t>industrie</t>
+        </is>
+      </c>
+      <c r="P187" s="5" t="inlineStr">
+        <is>
+          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Ludovic Larouche</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Ludo</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>2507, Rue Saint-Hubert</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="n">
+        <v>48.41615</v>
+      </c>
+      <c r="I188" s="4" t="n">
+        <v>-71.25285</v>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>Boucles, lunettes rondes</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>Veste en velours côtelé</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>Caméscope à l’épaule</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>portraits/182-ludovic-larouche-web.webp</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>Larouche</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="n"/>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>Fils de Benoit Larouche</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Marc Picard</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>L’Arpenteur</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>Arpenteur-géomètre</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>1220, Rue du Vieux-Pont</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="n">
+        <v>48.4113</v>
+      </c>
+      <c r="I189" s="7" t="n">
+        <v>-71.2679</v>
+      </c>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>Innu de Mashteuiatsh, cheveux longs attachés</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="inlineStr">
+        <is>
+          <t>Dossard orange sur polar</t>
+        </is>
+      </c>
+      <c r="L189" s="5" t="inlineStr">
+        <is>
+          <t>Station totale sur trépied</t>
+        </is>
+      </c>
+      <c r="M189" s="5" t="inlineStr">
+        <is>
+          <t>portraits/193-marc-picard-web.webp</t>
+        </is>
+      </c>
+      <c r="N189" s="5" t="inlineStr">
+        <is>
+          <t>Picard</t>
+        </is>
+      </c>
+      <c r="O189" s="5" t="n"/>
+      <c r="P189" s="5" t="inlineStr">
+        <is>
+          <t>Célibataire — croise William McKenzie</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Mathieu Lavoie</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Mat</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Technicien à l'aluminerie Rio Tinto — Arvida</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>3320, Rue Price</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="n">
+        <v>48.425907</v>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>-71.240752</v>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>Propre, polo Rio Tinto</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Polo Rio Tinto</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>Boîte à lunch</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>portraits/35-mathieu-lavoie-web.webp</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>Lavoie</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>Frère aîné de JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>Mélissa Harvey</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>Étudiante en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>1129, Rue Saint-Dominique</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="n">
+        <v>48.42135</v>
+      </c>
+      <c r="I191" s="7" t="n">
+        <v>-71.24464999999999</v>
+      </c>
+      <c r="J191" s="5" t="inlineStr">
+        <is>
+          <t>Chignon brouillon, manteau friperie</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="inlineStr">
+        <is>
+          <t>Manteau friperie</t>
+        </is>
+      </c>
+      <c r="L191" s="5" t="inlineStr">
+        <is>
+          <t>Perche micro</t>
+        </is>
+      </c>
+      <c r="M191" s="5" t="inlineStr">
+        <is>
+          <t>portraits/110-melissa-harvey-web.webp</t>
+        </is>
+      </c>
+      <c r="N191" s="5" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="O191" s="5" t="n"/>
+      <c r="P191" s="5" t="inlineStr">
+        <is>
+          <t>Nièce de François Harvey</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Nancy Simard</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Nancy Ciseaux</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Coiffeuse — propriétaire de salon</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>3812, Rue Saint-Hubert</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="n">
+        <v>48.41605</v>
+      </c>
+      <c r="I192" s="4" t="n">
+        <v>-71.2453</v>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>Blond platine, grosses boucles d’oreilles</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>Sarrau noir de coiffeuse</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>Ciseaux et peigne</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>portraits/192-nancy-simard-web.webp</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>Simard</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>salon</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>Célibataire — voisine de Benoit Larouche</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>Nicolas Gagné</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>Technicien — aluminerie Rio Tinto Arvida</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>3322, Rue Price</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="n">
+        <v>48.426</v>
+      </c>
+      <c r="I193" s="7" t="n">
+        <v>-71.2405</v>
+      </c>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>Propre, lunettes de sécurité</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="inlineStr">
+        <is>
+          <t>Polo Rio Tinto</t>
+        </is>
+      </c>
+      <c r="L193" s="5" t="inlineStr">
+        <is>
+          <t>Casque blanc</t>
+        </is>
+      </c>
+      <c r="M193" s="5" t="inlineStr">
+        <is>
+          <t>portraits/94-nicolas-gagne-web.webp</t>
+        </is>
+      </c>
+      <c r="N193" s="5" t="inlineStr">
+        <is>
+          <t>Gagné</t>
+        </is>
+      </c>
+      <c r="O193" s="5" t="inlineStr">
+        <is>
+          <t>Arvida</t>
+        </is>
+      </c>
+      <c r="P193" s="5" t="inlineStr">
+        <is>
+          <t>Collègue de Mathieu Lavoie</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
           <t>Sam Aubin</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>Ink</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr">
-        <is>
-          <t>Humain</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="n">
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Tatoueur</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Jonquière</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>2145, Boulevard Harvey</t>
         </is>
       </c>
-      <c r="H184" s="4" t="n">
+      <c r="H194" s="4" t="n">
         <v>48.412694</v>
       </c>
-      <c r="I184" s="4" t="n">
+      <c r="I194" s="4" t="n">
         <v>-71.241325</v>
       </c>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>Cheveux bleus, full tattoos</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr">
+      <c r="K194" s="2" t="inlineStr">
         <is>
           <t>Tablier noir</t>
         </is>
       </c>
-      <c r="L184" s="2" t="inlineStr">
+      <c r="L194" s="2" t="inlineStr">
         <is>
           <t>Efface tattoos gang</t>
         </is>
       </c>
-      <c r="M184" s="2" t="inlineStr">
+      <c r="M194" s="2" t="inlineStr">
         <is>
           <t>portraits/24-sam-aubin-web.webp</t>
         </is>
       </c>
-      <c r="N184" s="2" t="inlineStr">
+      <c r="N194" s="2" t="inlineStr">
         <is>
           <t>Aubin</t>
         </is>
       </c>
-      <c r="O184" s="2" t="n"/>
-      <c r="P184" s="2" t="inlineStr">
+      <c r="O194" s="2" t="n"/>
+      <c r="P194" s="2" t="inlineStr">
         <is>
           <t>Frère de Dany</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P184"/>
+  <autoFilter ref="A1:P194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13793,7 +14517,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>183 entrées · 16 colonnes · région du Saguenay (Québec)</t>
+          <t>193 entrées · 16 colonnes · région du Saguenay (Québec)</t>
         </is>
       </c>
     </row>

--- a/base_personnages_fictifs.xlsx
+++ b/base_personnages_fictifs.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Lisez-moi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$P$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$P$214</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P204"/>
+  <dimension ref="A1:P214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12055,12 +12055,12 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Enzo Bianchi</t>
+          <t>Diane Perron</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Le Conseiller</t>
+          <t>La Prof</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -12069,11 +12069,11 @@
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>Conseiller en gestion d’entreprise</t>
+          <t>Professeure de sociologie (UQAC)</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
@@ -12083,65 +12083,69 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>198, Rue Racine Est</t>
+          <t>126, Rue Dréan</t>
         </is>
       </c>
       <c r="H161" s="7" t="n">
-        <v>48.428</v>
+        <v>48.42605</v>
       </c>
       <c r="I161" s="7" t="n">
-        <v>-71.05419999999999</v>
+        <v>-71.0804</v>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Lunettes, complet gris</t>
+          <t>Longs cheveux gris, boucles d’oreilles en argent</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr">
         <is>
-          <t>Complet gris</t>
+          <t>Blazer de lin sur col roulé</t>
         </is>
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>Carnet de cuir</t>
+          <t>Pile de copies</t>
         </is>
       </c>
       <c r="M161" s="5" t="inlineStr">
         <is>
-          <t>portraits/153-enzo-bianchi-web.webp</t>
+          <t>portraits/209-diane-perron-web.webp</t>
         </is>
       </c>
       <c r="N161" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Perron</t>
         </is>
       </c>
       <c r="O161" s="5" t="n"/>
       <c r="P161" s="5" t="inlineStr">
         <is>
-          <t>Conseiller de Vittorio</t>
+          <t>Célibataire — directrice de recherche de Laurie Lavoie</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>François Côté</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="n"/>
+          <t>Emma Boucher</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Rédacteur en chef — Le Quotidien</t>
+          <t>Étudiante en sciences humaines (Cégep de Chicoutimi)</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -12151,60 +12155,60 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>100, Rue Racine Est</t>
+          <t>318, Rue Saint-Vallier</t>
         </is>
       </c>
       <c r="H162" s="4" t="n">
-        <v>48.4277</v>
+        <v>48.42635</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>-71.053</v>
+        <v>-71.05029999999999</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>Manches relevées, stylo rouge</t>
+          <t>Cheveux mauves, lunettes</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Chemise de rédaction</t>
+          <t>Gros tricot</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Stylo rouge</t>
+          <t>Portable couvert d’autocollants</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>portraits/134-francois-cote-web.webp</t>
+          <t>portraits/204-emma-boucher-web.webp</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Côté</t>
+          <t>Boucher</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>presse</t>
+          <t>coloc</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>Patron d’Olivier Savard — ex-patron de JP</t>
+          <t>Nièce de Fernande Boucher — cousine de Dévon — colocataire de Moussa et William</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Gaétan Bossé</t>
+          <t>Enzo Bianchi</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Le Bouquiniste</t>
+          <t>Le Conseiller</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
@@ -12213,11 +12217,11 @@
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Bouquiniste — livres usagés</t>
+          <t>Conseiller en gestion d’entreprise</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
@@ -12227,69 +12231,65 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>312, Rue Bossé</t>
+          <t>198, Rue Racine Est</t>
         </is>
       </c>
       <c r="H163" s="7" t="n">
-        <v>48.42445</v>
+        <v>48.428</v>
       </c>
       <c r="I163" s="7" t="n">
-        <v>-71.07605</v>
+        <v>-71.05419999999999</v>
       </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
-          <t>Barbe grise, lunettes sur le front</t>
+          <t>Lunettes, complet gris</t>
         </is>
       </c>
       <c r="K163" s="5" t="inlineStr">
         <is>
-          <t>Veste de laine sur chemise à carreaux</t>
+          <t>Complet gris</t>
         </is>
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>Livre relié sous le bras</t>
+          <t>Carnet de cuir</t>
         </is>
       </c>
       <c r="M163" s="5" t="inlineStr">
         <is>
-          <t>portraits/184-gaetan-bosse-web.webp</t>
+          <t>portraits/153-enzo-bianchi-web.webp</t>
         </is>
       </c>
       <c r="N163" s="5" t="inlineStr">
         <is>
-          <t>Bossé</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O163" s="5" t="n"/>
       <c r="P163" s="5" t="inlineStr">
         <is>
-          <t>Frère de Stéphane Bossé</t>
+          <t>Conseiller de Vittorio</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Gilles Dufour</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>Monsieur le Maire</t>
-        </is>
-      </c>
+          <t>François Côté</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="n"/>
       <c r="C164" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Maire de Saguenay</t>
+          <t>Rédacteur en chef — Le Quotidien</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -12299,69 +12299,73 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>201, Rue Racine Est</t>
+          <t>100, Rue Racine Est</t>
         </is>
       </c>
       <c r="H164" s="4" t="n">
-        <v>48.4282</v>
+        <v>48.4277</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>-71.0534</v>
+        <v>-71.053</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>Cheveux gris, veston marine</t>
+          <t>Manches relevées, stylo rouge</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Complet, épinglette de ville</t>
+          <t>Chemise de rédaction</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Poignée de main</t>
+          <t>Stylo rouge</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>portraits/121-gilles-dufour-web.webp</t>
+          <t>portraits/134-francois-cote-web.webp</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>Dufour</t>
+          <t>Côté</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>hôtel de ville</t>
+          <t>presse</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>Fils d’Albert Dufour — maire de Saguenay</t>
+          <t>Patron d’Olivier Savard — ex-patron de JP</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Hélène Samson</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="n"/>
+          <t>Gaétan Bossé</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>Le Bouquiniste</t>
+        </is>
+      </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Retraitée — ex-secrétaire de palais</t>
+          <t>Bouquiniste — livres usagés</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
@@ -12371,65 +12375,69 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>149, Rue Bégin</t>
+          <t>312, Rue Bossé</t>
         </is>
       </c>
       <c r="H165" s="7" t="n">
-        <v>48.4213</v>
+        <v>48.42445</v>
       </c>
       <c r="I165" s="7" t="n">
-        <v>-71.0574</v>
+        <v>-71.07605</v>
       </c>
       <c r="J165" s="5" t="inlineStr">
         <is>
-          <t>Cheveux soignés, manteau beige</t>
+          <t>Barbe grise, lunettes sur le front</t>
         </is>
       </c>
       <c r="K165" s="5" t="inlineStr">
         <is>
-          <t>Manteau beige</t>
+          <t>Veste de laine sur chemise à carreaux</t>
         </is>
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>Sac à main</t>
+          <t>Livre relié sous le bras</t>
         </is>
       </c>
       <c r="M165" s="5" t="inlineStr">
         <is>
-          <t>portraits/168-helene-samson-web.webp</t>
+          <t>portraits/184-gaetan-bosse-web.webp</t>
         </is>
       </c>
       <c r="N165" s="5" t="inlineStr">
         <is>
-          <t>Samson</t>
+          <t>Bossé</t>
         </is>
       </c>
       <c r="O165" s="5" t="n"/>
       <c r="P165" s="5" t="inlineStr">
         <is>
-          <t>Mère de Pierre Samson</t>
+          <t>Frère de Stéphane Bossé</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Isabelle Gagné</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="n"/>
+          <t>Gilles Dufour</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Monsieur le Maire</t>
+        </is>
+      </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Députée — Assemblée nationale</t>
+          <t>Maire de Saguenay</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -12439,73 +12447,69 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>145, Rue Racine Est</t>
+          <t>201, Rue Racine Est</t>
         </is>
       </c>
       <c r="H166" s="4" t="n">
-        <v>48.4279</v>
+        <v>48.4282</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>-71.0531</v>
+        <v>-71.0534</v>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>Carré blond, blazer rouge</t>
+          <t>Cheveux gris, veston marine</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Blazer rouge</t>
+          <t>Complet, épinglette de ville</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Épinglette fleurdelisé</t>
+          <t>Poignée de main</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>portraits/122-isabelle-gagne-web.webp</t>
+          <t>portraits/121-gilles-dufour-web.webp</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>Gagné</t>
+          <t>Dufour</t>
         </is>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>politique</t>
+          <t>hôtel de ville</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Fils d’Albert Dufour — maire de Saguenay</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Roy</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
-        <is>
-          <t>Johnny Fake</t>
-        </is>
-      </c>
+          <t>Hélène Samson</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="n"/>
       <c r="C167" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>Arnaqueur — fausses identités</t>
+          <t>Retraitée — ex-secrétaire de palais</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
@@ -12515,73 +12519,65 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>1186, Boulevard Talbot</t>
+          <t>149, Rue Bégin</t>
         </is>
       </c>
       <c r="H167" s="7" t="n">
-        <v>48.3986</v>
+        <v>48.4213</v>
       </c>
       <c r="I167" s="7" t="n">
-        <v>-71.0675</v>
+        <v>-71.0574</v>
       </c>
       <c r="J167" s="5" t="inlineStr">
         <is>
-          <t>Cheveux gominés, sourire</t>
+          <t>Cheveux soignés, manteau beige</t>
         </is>
       </c>
       <c r="K167" s="5" t="inlineStr">
         <is>
-          <t>Complet cheap</t>
+          <t>Manteau beige</t>
         </is>
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>Trois cellulaires</t>
+          <t>Sac à main</t>
         </is>
       </c>
       <c r="M167" s="5" t="inlineStr">
         <is>
-          <t>portraits/119-jonathan-roy-web.webp</t>
+          <t>portraits/168-helene-samson-web.webp</t>
         </is>
       </c>
       <c r="N167" s="5" t="inlineStr">
         <is>
-          <t>Roy</t>
-        </is>
-      </c>
-      <c r="O167" s="5" t="inlineStr">
-        <is>
-          <t>arnaque</t>
-        </is>
-      </c>
+          <t>Samson</t>
+        </is>
+      </c>
+      <c r="O167" s="5" t="n"/>
       <c r="P167" s="5" t="inlineStr">
         <is>
-          <t>Célibataire — croise Alex Tremblay</t>
+          <t>Mère de Pierre Samson</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Julien Gagné</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>Le Volant</t>
-        </is>
-      </c>
+          <t>Isabelle Gagné</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="n"/>
       <c r="C168" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Chauffeur de voiture de ville</t>
+          <t>Députée — Assemblée nationale</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -12591,56 +12587,60 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>1188, Boulevard Talbot</t>
+          <t>145, Rue Racine Est</t>
         </is>
       </c>
       <c r="H168" s="4" t="n">
-        <v>48.3983</v>
+        <v>48.4279</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>-71.06780000000001</v>
+        <v>-71.0531</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>Complet noir, oreillette</t>
+          <t>Carré blond, blazer rouge</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>Complet noir</t>
+          <t>Blazer rouge</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>VUS noir</t>
+          <t>Épinglette fleurdelisé</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>portraits/157-julien-gagne-web.webp</t>
+          <t>portraits/122-isabelle-gagne-web.webp</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t>Santini</t>
-        </is>
-      </c>
-      <c r="O168" s="2" t="n"/>
+          <t>Gagné</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>politique</t>
+        </is>
+      </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>Chauffeur de Vittorio</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Justin Chen</t>
+          <t>Jonathan Roy</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Junior Talbot</t>
+          <t>Johnny Fake</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -12649,11 +12649,11 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Étudiant en administration (Cégep de Chicoutimi)</t>
+          <t>Arnaqueur — fausses identités</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
@@ -12663,56 +12663,60 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>1180, Boulevard Talbot</t>
+          <t>1186, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H169" s="7" t="n">
-        <v>48.398223</v>
+        <v>48.3986</v>
       </c>
       <c r="I169" s="7" t="n">
-        <v>-71.06763599999999</v>
+        <v>-71.0675</v>
       </c>
       <c r="J169" s="5" t="inlineStr">
         <is>
-          <t>Métis, Moncler propre</t>
+          <t>Cheveux gominés, sourire</t>
         </is>
       </c>
       <c r="K169" s="5" t="inlineStr">
         <is>
-          <t>Moncler noir</t>
+          <t>Complet cheap</t>
         </is>
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>Paye trop cher</t>
+          <t>Trois cellulaires</t>
         </is>
       </c>
       <c r="M169" s="5" t="inlineStr">
         <is>
-          <t>portraits/26-justin-chen-web.webp</t>
+          <t>portraits/119-jonathan-roy-web.webp</t>
         </is>
       </c>
       <c r="N169" s="5" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="O169" s="5" t="n"/>
+          <t>Roy</t>
+        </is>
+      </c>
+      <c r="O169" s="5" t="inlineStr">
+        <is>
+          <t>arnaque</t>
+        </is>
+      </c>
       <c r="P169" s="5" t="inlineStr">
         <is>
-          <t>Fils de Mei</t>
+          <t>Célibataire — croise Alex Tremblay</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Jérémie Côté</t>
+          <t>Julien Gagné</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Ti-Poste</t>
+          <t>Le Volant</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -12721,11 +12725,11 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Facteur — Postes Canada</t>
+          <t>Chauffeur de voiture de ville</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -12735,69 +12739,69 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>145, Rue Sainte-Anne</t>
+          <t>1188, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H170" s="4" t="n">
-        <v>48.42915</v>
+        <v>48.3983</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>-71.06835</v>
+        <v>-71.06780000000001</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Barbe taillée, joues rouges</t>
+          <t>Complet noir, oreillette</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Parka de facteur à bandes</t>
+          <t>Complet noir</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>Sacoche de courrier</t>
+          <t>VUS noir</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>portraits/187-jeremie-cote-web.webp</t>
+          <t>portraits/157-julien-gagne-web.webp</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>Côté</t>
-        </is>
-      </c>
-      <c r="O170" s="2" t="inlineStr">
-        <is>
-          <t>poste</t>
-        </is>
-      </c>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="n"/>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>Neveu d’Alain Côté</t>
+          <t>Chauffeur de Vittorio</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Laurie Lavoie</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="n"/>
+          <t>Justin Chen</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Junior Talbot</t>
+        </is>
+      </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Étudiante en psychologie (UQAC)</t>
+          <t>Étudiant en administration (Cégep de Chicoutimi)</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
@@ -12807,69 +12811,69 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>555, Boulevard de l'Université</t>
+          <t>1180, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H171" s="7" t="n">
-        <v>48.421623</v>
+        <v>48.398223</v>
       </c>
       <c r="I171" s="7" t="n">
-        <v>-71.07566199999999</v>
+        <v>-71.06763599999999</v>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>Cheveux longs châtains, hoodie UQAC</t>
+          <t>Métis, Moncler propre</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>Hoodie UQAC</t>
+          <t>Moncler noir</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>Livre psycho</t>
+          <t>Paye trop cher</t>
         </is>
       </c>
       <c r="M171" s="5" t="inlineStr">
         <is>
-          <t>portraits/36-laurie-lavoie-web.webp</t>
+          <t>portraits/26-justin-chen-web.webp</t>
         </is>
       </c>
       <c r="N171" s="5" t="inlineStr">
         <is>
-          <t>Lavoie</t>
-        </is>
-      </c>
-      <c r="O171" s="5" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="O171" s="5" t="n"/>
       <c r="P171" s="5" t="inlineStr">
         <is>
-          <t>Sœur de JP</t>
+          <t>Fils de Mei</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Lise Gauthier</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="n"/>
+          <t>Jérémie Côté</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Ti-Poste</t>
+        </is>
+      </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Infirmière clinicienne — CLSC</t>
+          <t>Facteur — Postes Canada</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -12879,51 +12883,55 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>222, Rue du Havre</t>
+          <t>145, Rue Sainte-Anne</t>
         </is>
       </c>
       <c r="H172" s="4" t="n">
-        <v>48.4293</v>
+        <v>48.42915</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>-71.05445</v>
+        <v>-71.06835</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Cheveux blancs courts, lunettes à chaînette</t>
+          <t>Barbe taillée, joues rouges</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Cardigan bourgogne sur uniforme</t>
+          <t>Parka de facteur à bandes</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>Tensiomètre</t>
+          <t>Sacoche de courrier</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>portraits/188-lise-gauthier-web.webp</t>
+          <t>portraits/187-jeremie-cote-web.webp</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>Gauthier</t>
-        </is>
-      </c>
-      <c r="O172" s="2" t="n"/>
+          <t>Côté</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>Tante de Steve et Chantal Gauthier</t>
+          <t>Neveu d’Alain Côté</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>Louise Villeneuve</t>
+          <t>Laurie Lavoie</t>
         </is>
       </c>
       <c r="B173" s="5" t="n"/>
@@ -12933,11 +12941,11 @@
         </is>
       </c>
       <c r="D173" s="6" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Juge — Cour du Québec</t>
+          <t>Étudiante en psychologie (UQAC)</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
@@ -12947,73 +12955,69 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>227, Rue Racine Est</t>
+          <t>555, Boulevard de l'Université</t>
         </is>
       </c>
       <c r="H173" s="7" t="n">
-        <v>48.4275</v>
+        <v>48.421623</v>
       </c>
       <c r="I173" s="7" t="n">
-        <v>-71.05419999999999</v>
+        <v>-71.07566199999999</v>
       </c>
       <c r="J173" s="5" t="inlineStr">
         <is>
-          <t>Regard sévère, toge</t>
+          <t>Cheveux longs châtains, hoodie UQAC</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
         <is>
-          <t>Toge</t>
+          <t>Hoodie UQAC</t>
         </is>
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>Marteau de bois</t>
+          <t>Livre psycho</t>
         </is>
       </c>
       <c r="M173" s="5" t="inlineStr">
         <is>
-          <t>portraits/127-louise-villeneuve-web.webp</t>
+          <t>portraits/36-laurie-lavoie-web.webp</t>
         </is>
       </c>
       <c r="N173" s="5" t="inlineStr">
         <is>
-          <t>Villeneuve</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O173" s="5" t="inlineStr">
         <is>
-          <t>palais</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="P173" s="5" t="inlineStr">
         <is>
-          <t>Collègue de Catherine Samson</t>
+          <t>Sœur de JP</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Maria Santini</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>Donna Maria</t>
-        </is>
-      </c>
+          <t>Lise Gauthier</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="n"/>
       <c r="C174" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Matriarche — restaurant familial</t>
+          <t>Infirmière clinicienne — CLSC</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -13023,69 +13027,65 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>200, Rue Racine Est</t>
+          <t>222, Rue du Havre</t>
         </is>
       </c>
       <c r="H174" s="4" t="n">
-        <v>48.42815</v>
+        <v>48.4293</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>-71.0543</v>
+        <v>-71.05445</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>Cheveux sombres, perles</t>
+          <t>Cheveux blancs courts, lunettes à chaînette</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Robe noire</t>
+          <t>Cardigan bourgogne sur uniforme</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Rosaire au poignet</t>
+          <t>Tensiomètre</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>portraits/152-maria-santini-web.webp</t>
+          <t>portraits/188-lise-gauthier-web.webp</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="O174" s="2" t="n"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>Épouse de Vittorio</t>
+          <t>Tante de Steve et Chantal Gauthier</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>Marie-Ève Boucher</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>La Plume</t>
-        </is>
-      </c>
+          <t>Louise Villeneuve</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="n"/>
       <c r="C175" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D175" s="6" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Journaliste — quotidien régional</t>
+          <t>Juge — Cour du Québec</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
@@ -13095,65 +13095,73 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>412, Rue Jacques-Cartier Ouest</t>
+          <t>227, Rue Racine Est</t>
         </is>
       </c>
       <c r="H175" s="7" t="n">
-        <v>48.4268</v>
+        <v>48.4275</v>
       </c>
       <c r="I175" s="7" t="n">
-        <v>-71.0699</v>
+        <v>-71.05419999999999</v>
       </c>
       <c r="J175" s="5" t="inlineStr">
         <is>
-          <t>Cheveux courts noirs, regard vif</t>
+          <t>Regard sévère, toge</t>
         </is>
       </c>
       <c r="K175" s="5" t="inlineStr">
         <is>
-          <t>Trench, cordon de presse</t>
+          <t>Toge</t>
         </is>
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>Calepin et téléphone</t>
+          <t>Marteau de bois</t>
         </is>
       </c>
       <c r="M175" s="5" t="inlineStr">
         <is>
-          <t>portraits/185-marie-eve-boucher-web.webp</t>
+          <t>portraits/127-louise-villeneuve-web.webp</t>
         </is>
       </c>
       <c r="N175" s="5" t="inlineStr">
         <is>
-          <t>Bossé</t>
-        </is>
-      </c>
-      <c r="O175" s="5" t="n"/>
+          <t>Villeneuve</t>
+        </is>
+      </c>
+      <c r="O175" s="5" t="inlineStr">
+        <is>
+          <t>palais</t>
+        </is>
+      </c>
       <c r="P175" s="5" t="inlineStr">
         <is>
-          <t>Conjointe de Stéphane Bossé — cousine de Normand Boucher</t>
+          <t>Collègue de Catherine Samson</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Mei Chen</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="n"/>
+          <t>Lucien Gagné</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Le Proprio des étudiants</t>
+        </is>
+      </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Préposée d’hôtel</t>
+          <t>Propriétaire — logements étudiants</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -13163,56 +13171,60 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>1182, Boulevard Talbot</t>
+          <t>320, Rue Saint-Vallier</t>
         </is>
       </c>
       <c r="H176" s="4" t="n">
-        <v>48.39835</v>
+        <v>48.42645</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>-71.06775</v>
+        <v>-71.0502</v>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>Chinoise, chignon, calme</t>
+          <t>Chauve, lunettes sur le nez</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Uniforme hôtel</t>
+          <t>Veste matelassée sur chemise à carreaux</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>Badges de chambre</t>
+          <t>Trousseau de clés</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>portraits/63-mei-chen-web.webp</t>
+          <t>portraits/210-lucien-gagne-web.webp</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="O176" s="2" t="n"/>
+          <t>Gagné</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>logements</t>
+        </is>
+      </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>Mère de Justin Chen</t>
+          <t>Oncle d’Isabelle Gagné — propriétaire d’Emma, Moussa et William</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Mgr Paul Tremblay</t>
+          <t>Maria Santini</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Monseigneur</t>
+          <t>Donna Maria</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -13221,11 +13233,11 @@
         </is>
       </c>
       <c r="D177" s="6" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Évêque — diocèse de Chicoutimi</t>
+          <t>Matriarche — restaurant familial</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
@@ -13235,60 +13247,56 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>602, Rue Racine Est</t>
+          <t>200, Rue Racine Est</t>
         </is>
       </c>
       <c r="H177" s="7" t="n">
-        <v>48.4268</v>
+        <v>48.42815</v>
       </c>
       <c r="I177" s="7" t="n">
-        <v>-71.0538</v>
+        <v>-71.0543</v>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>Cheveux blancs, col romain</t>
+          <t>Cheveux sombres, perles</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>Soutane, rabat violet</t>
+          <t>Robe noire</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>Anneau pastoral</t>
+          <t>Rosaire au poignet</t>
         </is>
       </c>
       <c r="M177" s="5" t="inlineStr">
         <is>
-          <t>portraits/126-mgr-paul-tremblay-web.webp</t>
+          <t>portraits/152-maria-santini-web.webp</t>
         </is>
       </c>
       <c r="N177" s="5" t="inlineStr">
         <is>
-          <t>Tremblay</t>
-        </is>
-      </c>
-      <c r="O177" s="5" t="inlineStr">
-        <is>
-          <t>Église</t>
-        </is>
-      </c>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="O177" s="5" t="n"/>
       <c r="P177" s="5" t="inlineStr">
         <is>
-          <t>Supérieur de Lucien Lacroix</t>
+          <t>Épouse de Vittorio</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Nico Santini</t>
+          <t>Marie-Ève Boucher</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Nico</t>
+          <t>La Plume</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -13297,11 +13305,11 @@
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Préposé à la sécurité — restaurant</t>
+          <t>Journaliste — quotidien régional</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -13311,51 +13319,51 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>202, Rue Racine Est</t>
+          <t>412, Rue Jacques-Cartier Ouest</t>
         </is>
       </c>
       <c r="H178" s="4" t="n">
-        <v>48.4282</v>
+        <v>48.4268</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>-71.05459999999999</v>
+        <v>-71.0699</v>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Cheveux gominés, veste cuir</t>
+          <t>Cheveux courts noirs, regard vif</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>Veste de cuir</t>
+          <t>Trench, cordon de presse</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>Sourire de défi</t>
+          <t>Calepin et téléphone</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>portraits/160-nico-santini-web.webp</t>
+          <t>portraits/185-marie-eve-boucher-web.webp</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>Santini</t>
+          <t>Bossé</t>
         </is>
       </c>
       <c r="O178" s="2" t="n"/>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>Fils de Vittorio et Maria</t>
+          <t>Conjointe de Stéphane Bossé — cousine de Normand Boucher</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Olivier Savard</t>
+          <t>Maïka Gauthier</t>
         </is>
       </c>
       <c r="B179" s="5" t="n"/>
@@ -13365,11 +13373,11 @@
         </is>
       </c>
       <c r="D179" s="6" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>Journaliste — Le Quotidien</t>
+          <t>Étudiante en soins infirmiers (Cégep de Chicoutimi) — caissière de pharmacie</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
@@ -13379,69 +13387,65 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>100, Rue Racine Est</t>
+          <t>152, Rue LaFontaine</t>
         </is>
       </c>
       <c r="H179" s="7" t="n">
-        <v>48.4278</v>
+        <v>48.4205</v>
       </c>
       <c r="I179" s="7" t="n">
-        <v>-71.05289999999999</v>
+        <v>-71.06075</v>
       </c>
       <c r="J179" s="5" t="inlineStr">
         <is>
-          <t>Barbe, sacoche</t>
+          <t>Queue de cheval châtaine, sourire poli</t>
         </is>
       </c>
       <c r="K179" s="5" t="inlineStr">
         <is>
-          <t>Manteau de ville</t>
+          <t>Sarrau blanc de pharmacie</t>
         </is>
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>Carnet spiralé</t>
+          <t>Étiquette de nom</t>
         </is>
       </c>
       <c r="M179" s="5" t="inlineStr">
         <is>
-          <t>portraits/78-olivier-savard-web.webp</t>
+          <t>portraits/207-maika-gauthier-web.webp</t>
         </is>
       </c>
       <c r="N179" s="5" t="inlineStr">
         <is>
-          <t>Savard</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="O179" s="5" t="n"/>
       <c r="P179" s="5" t="inlineStr">
         <is>
-          <t>Célibataire — ex-collègue de JP</t>
+          <t>Nièce de Lise Gauthier — cousine de Steve et Chantal</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Patrick Lapointe</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>Pat</t>
-        </is>
-      </c>
+          <t>Mei Chen</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n"/>
       <c r="C180" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneur en construction</t>
+          <t>Préposée d’hôtel</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -13451,60 +13455,56 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>1250, Boulevard Talbot</t>
+          <t>1182, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H180" s="4" t="n">
-        <v>48.3985</v>
+        <v>48.39835</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>-71.06276</v>
+        <v>-71.06775</v>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Polo construction</t>
+          <t>Chinoise, chignon, calme</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>Polo construction</t>
+          <t>Uniforme hôtel</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>Devis 400k</t>
+          <t>Badges de chambre</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>portraits/39-patrick-lapointe-web.webp</t>
+          <t>portraits/63-mei-chen-web.webp</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>Lapointe</t>
-        </is>
-      </c>
-      <c r="O180" s="2" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="n"/>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>Frère de Marco</t>
+          <t>Mère de Justin Chen</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Paul-André Côté</t>
+          <t>Mgr Paul Tremblay</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Le Chiffre</t>
+          <t>Monseigneur</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -13513,11 +13513,11 @@
         </is>
       </c>
       <c r="D181" s="6" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Comptable — sociétés-écrans</t>
+          <t>Évêque — diocèse de Chicoutimi</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
@@ -13527,69 +13527,69 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>1252, Boulevard Talbot</t>
+          <t>602, Rue Racine Est</t>
         </is>
       </c>
       <c r="H181" s="7" t="n">
-        <v>48.39855</v>
+        <v>48.4268</v>
       </c>
       <c r="I181" s="7" t="n">
-        <v>-71.0629</v>
+        <v>-71.0538</v>
       </c>
       <c r="J181" s="5" t="inlineStr">
         <is>
-          <t>Maigre, lunettes cheap</t>
+          <t>Cheveux blancs, col romain</t>
         </is>
       </c>
       <c r="K181" s="5" t="inlineStr">
         <is>
-          <t>Chemise et classeur</t>
+          <t>Soutane, rabat violet</t>
         </is>
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>Tableurs</t>
+          <t>Anneau pastoral</t>
         </is>
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>portraits/156-paul-andre-cote-web.webp</t>
+          <t>portraits/126-mgr-paul-tremblay-web.webp</t>
         </is>
       </c>
       <c r="N181" s="5" t="inlineStr">
         <is>
-          <t>Santini</t>
-        </is>
-      </c>
-      <c r="O181" s="5" t="n"/>
+          <t>Tremblay</t>
+        </is>
+      </c>
+      <c r="O181" s="5" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
       <c r="P181" s="5" t="inlineStr">
         <is>
-          <t>Comptable du clan — croise Bertrand Gagnon</t>
+          <t>Supérieur de Lucien Lacroix</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Pierre Samson</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>L'Enquêteur</t>
-        </is>
-      </c>
+          <t>Moussa Diallo</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="n"/>
       <c r="C182" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Policier — Service de police de Saguenay, stupéfiants</t>
+          <t>Étudiant en informatique (UQAC)</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -13599,56 +13599,56 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>145, Rue Bégin</t>
+          <t>318, Rue Saint-Vallier</t>
         </is>
       </c>
       <c r="H182" s="4" t="n">
-        <v>48.421205</v>
+        <v>48.4264</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>-71.057355</v>
+        <v>-71.05025000000001</v>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Cernes violacés</t>
+          <t>Grand, sourire large</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>Pardessus brun-beige</t>
+          <t>Doudoune sur hoodie</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>Clique Bic bleu</t>
+          <t>Écouteurs autour du cou</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>portraits/07-pierre-samson-web.webp</t>
+          <t>portraits/205-moussa-diallo-web.webp</t>
         </is>
       </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
-          <t>Samson</t>
+          <t>Diallo</t>
         </is>
       </c>
       <c r="O182" s="2" t="n"/>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>Fils d’Hélène Samson — époux de Catherine</t>
+          <t>Célibataire — colocataire d’Emma Boucher et William Lavoie</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Sofia Santini</t>
+          <t>Nico Santini</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Sofi</t>
+          <t>Nico</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -13657,11 +13657,11 @@
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Élève du secondaire — aide au restaurant familial</t>
+          <t>Préposé à la sécurité — restaurant</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
@@ -13671,33 +13671,33 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>204, Rue Racine Est</t>
+          <t>202, Rue Racine Est</t>
         </is>
       </c>
       <c r="H183" s="7" t="n">
-        <v>48.42825</v>
+        <v>48.4282</v>
       </c>
       <c r="I183" s="7" t="n">
-        <v>-71.05475</v>
+        <v>-71.05459999999999</v>
       </c>
       <c r="J183" s="5" t="inlineStr">
         <is>
-          <t>Cheveux noirs ondulés, sourire en coin</t>
+          <t>Cheveux gominés, veste cuir</t>
         </is>
       </c>
       <c r="K183" s="5" t="inlineStr">
         <is>
-          <t>Tablier noir de service</t>
+          <t>Veste de cuir</t>
         </is>
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>Cabaret à deux mains</t>
+          <t>Sourire de défi</t>
         </is>
       </c>
       <c r="M183" s="5" t="inlineStr">
         <is>
-          <t>portraits/177-sofia-santini-web.webp</t>
+          <t>portraits/160-nico-santini-web.webp</t>
         </is>
       </c>
       <c r="N183" s="5" t="inlineStr">
@@ -13708,28 +13708,32 @@
       <c r="O183" s="5" t="n"/>
       <c r="P183" s="5" t="inlineStr">
         <is>
-          <t>Fille de Nico Santini — petite-fille de Vittorio et Maria</t>
+          <t>Fils de Vittorio et Maria</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Sophie Labbé</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="n"/>
+          <t>Olivier Brassard</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Oli</t>
+        </is>
+      </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Psychologue — clinique UQAC</t>
+          <t>Coursier à vélo — musicien</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -13739,69 +13743,65 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>555, Boulevard de l'Université</t>
+          <t>122, Rue Dréan</t>
         </is>
       </c>
       <c r="H184" s="4" t="n">
-        <v>48.4215</v>
+        <v>48.42615</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>-71.07550000000001</v>
+        <v>-71.08029999999999</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Chignon, lunettes</t>
+          <t>Moustache, casquette à l’envers</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>Cardigan</t>
+          <t>Veste en denim à écussons</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>Carnet de notes</t>
+          <t>Ukulélé sur le sac</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>portraits/104-sophie-labbe-web.webp</t>
+          <t>portraits/208-olivier-brassard-web.webp</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
-          <t>Labbé</t>
+          <t>Brassard</t>
         </is>
       </c>
       <c r="O184" s="2" t="n"/>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>Célibataire — collègue de Laurie Lavoie</t>
+          <t>Neveu d’Émile Brassard</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>Stéphane Bossé</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
-        <is>
-          <t>Steph Patate</t>
-        </is>
-      </c>
+          <t>Olivier Savard</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="n"/>
       <c r="C185" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Cuisinier — casse-croûte</t>
+          <t>Journaliste — Le Quotidien</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
@@ -13811,65 +13811,69 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>410, Rue Jacques-Cartier Ouest</t>
+          <t>100, Rue Racine Est</t>
         </is>
       </c>
       <c r="H185" s="7" t="n">
-        <v>48.42675</v>
+        <v>48.4278</v>
       </c>
       <c r="I185" s="7" t="n">
-        <v>-71.07004999999999</v>
+        <v>-71.05289999999999</v>
       </c>
       <c r="J185" s="5" t="inlineStr">
         <is>
-          <t>Cheveux ras, avant-bras tatoués</t>
+          <t>Barbe, sacoche</t>
         </is>
       </c>
       <c r="K185" s="5" t="inlineStr">
         <is>
-          <t>Tablier blanc taché</t>
+          <t>Manteau de ville</t>
         </is>
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>Spatule à la main</t>
+          <t>Carnet spiralé</t>
         </is>
       </c>
       <c r="M185" s="5" t="inlineStr">
         <is>
-          <t>portraits/186-stephane-bosse-web.webp</t>
+          <t>portraits/78-olivier-savard-web.webp</t>
         </is>
       </c>
       <c r="N185" s="5" t="inlineStr">
         <is>
-          <t>Bossé</t>
+          <t>Savard</t>
         </is>
       </c>
       <c r="O185" s="5" t="n"/>
       <c r="P185" s="5" t="inlineStr">
         <is>
-          <t>Frère de Gaétan Bossé — conjoint de Marie-Ève Boucher</t>
+          <t>Célibataire — ex-collègue de JP</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Valentina Rojas</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="n"/>
+          <t>Patrick Lapointe</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Épicière — produits latino-américains</t>
+          <t>Entrepreneur en construction</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -13879,56 +13883,60 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>318, Rue Bossé</t>
+          <t>1250, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H186" s="4" t="n">
-        <v>48.4245</v>
+        <v>48.3985</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>-71.07585</v>
+        <v>-71.06276</v>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Longs cheveux noirs, anneaux dorés</t>
+          <t>Polo construction</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Tablier vert sur chandail</t>
+          <t>Polo construction</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>Caisse de plantains</t>
+          <t>Devis 400k</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>portraits/189-valentina-rojas-web.webp</t>
+          <t>portraits/39-patrick-lapointe-web.webp</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>Rojas</t>
-        </is>
-      </c>
-      <c r="O186" s="2" t="n"/>
+          <t>Lapointe</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Frère de Marco</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>Vittorio Santini</t>
+          <t>Paul-André Côté</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>Don Vittorio</t>
+          <t>Le Chiffre</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
@@ -13937,11 +13945,11 @@
         </is>
       </c>
       <c r="D187" s="6" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Homme d’affaires — restauration et bars</t>
+          <t>Comptable — sociétés-écrans</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
@@ -13951,33 +13959,33 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>200, Rue Racine Est</t>
+          <t>1252, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H187" s="7" t="n">
-        <v>48.4281</v>
+        <v>48.39855</v>
       </c>
       <c r="I187" s="7" t="n">
-        <v>-71.0545</v>
+        <v>-71.0629</v>
       </c>
       <c r="J187" s="5" t="inlineStr">
         <is>
-          <t>Cheveux argentés gominés, chevalière</t>
+          <t>Maigre, lunettes cheap</t>
         </is>
       </c>
       <c r="K187" s="5" t="inlineStr">
         <is>
-          <t>Manteau noir</t>
+          <t>Chemise et classeur</t>
         </is>
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>Chevalière en or</t>
+          <t>Tableurs</t>
         </is>
       </c>
       <c r="M187" s="5" t="inlineStr">
         <is>
-          <t>portraits/151-vittorio-santini-web.webp</t>
+          <t>portraits/156-paul-andre-cote-web.webp</t>
         </is>
       </c>
       <c r="N187" s="5" t="inlineStr">
@@ -13988,19 +13996,19 @@
       <c r="O187" s="5" t="n"/>
       <c r="P187" s="5" t="inlineStr">
         <is>
-          <t>Époux de Maria — tient Dévon à distance</t>
+          <t>Comptable du clan — croise Bertrand Gagnon</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Éric Simard</t>
+          <t>Pierre Samson</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Ti-Eric</t>
+          <t>L'Enquêteur</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -14009,11 +14017,11 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Étudiant — Cégep de Chicoutimi</t>
+          <t>Policier — Service de police de Saguenay, stupéfiants</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -14023,56 +14031,56 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>1184, Boulevard Talbot</t>
+          <t>145, Rue Bégin</t>
         </is>
       </c>
       <c r="H188" s="4" t="n">
-        <v>48.3984</v>
+        <v>48.421205</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>-71.06740000000001</v>
+        <v>-71.057355</v>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Casquette, jeans</t>
+          <t>Cernes violacés</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Hoodie cégep</t>
+          <t>Pardessus brun-beige</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>Skateboard</t>
+          <t>Clique Bic bleu</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>portraits/100-eric-simard-web.webp</t>
+          <t>portraits/07-pierre-samson-web.webp</t>
         </is>
       </c>
       <c r="N188" s="2" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Samson</t>
         </is>
       </c>
       <c r="O188" s="2" t="n"/>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>Colocataire de Justin Chen</t>
+          <t>Fils d’Hélène Samson — époux de Catherine</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>Antoine Lefèvre</t>
+          <t>Sofia Santini</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>Le Français</t>
+          <t>Sofi</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
@@ -14081,65 +14089,65 @@
         </is>
       </c>
       <c r="D189" s="6" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+          <t>Élève du secondaire — aide au restaurant familial</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>1125, Rue Saint-Dominique</t>
+          <t>204, Rue Racine Est</t>
         </is>
       </c>
       <c r="H189" s="7" t="n">
-        <v>48.421279</v>
+        <v>48.42825</v>
       </c>
       <c r="I189" s="7" t="n">
-        <v>-71.244586</v>
+        <v>-71.05475</v>
       </c>
       <c r="J189" s="5" t="inlineStr">
         <is>
-          <t>Barbe hipster</t>
+          <t>Cheveux noirs ondulés, sourire en coin</t>
         </is>
       </c>
       <c r="K189" s="5" t="inlineStr">
         <is>
-          <t>Friperie, caméra Sony</t>
+          <t>Tablier noir de service</t>
         </is>
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>Veut docu raw</t>
+          <t>Cabaret à deux mains</t>
         </is>
       </c>
       <c r="M189" s="5" t="inlineStr">
         <is>
-          <t>portraits/20-antoine-lefevre-web.webp</t>
+          <t>portraits/177-sofia-santini-web.webp</t>
         </is>
       </c>
       <c r="N189" s="5" t="inlineStr">
         <is>
-          <t>Lefèvre</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O189" s="5" t="n"/>
       <c r="P189" s="5" t="inlineStr">
         <is>
-          <t>Frère de Camille</t>
+          <t>Fille de Nico Santini — petite-fille de Vittorio et Maria</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Audrey Lavoie</t>
+          <t>Sophie Labbé</t>
         </is>
       </c>
       <c r="B190" s="2" t="n"/>
@@ -14149,137 +14157,137 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Apprentie électricienne — aluminerie Rio Tinto Arvida</t>
+          <t>Psychologue — clinique UQAC</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>2135, Rue Davis</t>
+          <t>555, Boulevard de l'Université</t>
         </is>
       </c>
       <c r="H190" s="4" t="n">
-        <v>48.42455</v>
+        <v>48.4215</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>-71.18219999999999</v>
+        <v>-71.07550000000001</v>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Tresse blonde, lunettes de sécurité</t>
+          <t>Chignon, lunettes</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>Manteau orange haute visibilité</t>
+          <t>Cardigan</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>Glacière à lunch</t>
+          <t>Carnet de notes</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>portraits/191-audrey-lavoie-web.webp</t>
+          <t>portraits/104-sophie-labbe-web.webp</t>
         </is>
       </c>
       <c r="N190" s="2" t="inlineStr">
         <is>
-          <t>Lavoie</t>
-        </is>
-      </c>
-      <c r="O190" s="2" t="inlineStr">
-        <is>
-          <t>Arvida</t>
-        </is>
-      </c>
+          <t>Labbé</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="n"/>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>Fille de Fernand Lavoie — collègue de Nicolas Gagné</t>
+          <t>Célibataire — collègue de Laurie Lavoie</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>Benoit Larouche</t>
-        </is>
-      </c>
-      <c r="B191" s="5" t="n"/>
+          <t>Stéphane Bossé</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>Steph Patate</t>
+        </is>
+      </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D191" s="6" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>Enseignant — Cégep de Jonquière (ATM)</t>
+          <t>Cuisinier — casse-croûte</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>2505, Rue Saint-Hubert</t>
+          <t>410, Rue Jacques-Cartier Ouest</t>
         </is>
       </c>
       <c r="H191" s="7" t="n">
-        <v>48.416</v>
+        <v>48.42675</v>
       </c>
       <c r="I191" s="7" t="n">
-        <v>-71.253</v>
+        <v>-71.07004999999999</v>
       </c>
       <c r="J191" s="5" t="inlineStr">
         <is>
-          <t>Lunettes, barbe grise</t>
+          <t>Cheveux ras, avant-bras tatoués</t>
         </is>
       </c>
       <c r="K191" s="5" t="inlineStr">
         <is>
-          <t>Chemise et cardigan</t>
+          <t>Tablier blanc taché</t>
         </is>
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>Clap de cinéma</t>
+          <t>Spatule à la main</t>
         </is>
       </c>
       <c r="M191" s="5" t="inlineStr">
         <is>
-          <t>portraits/86-benoit-larouche-web.webp</t>
+          <t>portraits/186-stephane-bosse-web.webp</t>
         </is>
       </c>
       <c r="N191" s="5" t="inlineStr">
         <is>
-          <t>Larouche</t>
+          <t>Bossé</t>
         </is>
       </c>
       <c r="O191" s="5" t="n"/>
       <c r="P191" s="5" t="inlineStr">
         <is>
-          <t>Prof d’Antoine Lefèvre</t>
+          <t>Frère de Gaétan Bossé — conjoint de Marie-Ève Boucher</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Camille Lefèvre</t>
+          <t>Valentina Rojas</t>
         </is>
       </c>
       <c r="B192" s="2" t="n"/>
@@ -14289,138 +14297,142 @@
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Étudiante en communications (UQAC)</t>
+          <t>Épicière — produits latino-américains</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>1127, Rue Saint-Dominique</t>
+          <t>318, Rue Bossé</t>
         </is>
       </c>
       <c r="H192" s="4" t="n">
-        <v>48.4214</v>
+        <v>48.4245</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>-71.24469999999999</v>
+        <v>-71.07585</v>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Carré brun, appareil photo</t>
+          <t>Longs cheveux noirs, anneaux dorés</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Manteau friperie</t>
+          <t>Tablier vert sur chandail</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>Pentax vintage</t>
+          <t>Caisse de plantains</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>portraits/65-camille-lefevre-web.webp</t>
+          <t>portraits/189-valentina-rojas-web.webp</t>
         </is>
       </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t>Lefèvre</t>
+          <t>Rojas</t>
         </is>
       </c>
       <c r="O192" s="2" t="n"/>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>Sœur d’Antoine Lefèvre</t>
+          <t>Célibataire</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>Dany Aubin</t>
-        </is>
-      </c>
-      <c r="B193" s="5" t="n"/>
+          <t>Vittorio Santini</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>Don Vittorio</t>
+        </is>
+      </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D193" s="6" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>Soudeur</t>
+          <t>Homme d’affaires — restauration et bars</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>2147, Boulevard Harvey</t>
+          <t>200, Rue Racine Est</t>
         </is>
       </c>
       <c r="H193" s="7" t="n">
-        <v>48.41282</v>
+        <v>48.4281</v>
       </c>
       <c r="I193" s="7" t="n">
-        <v>-71.24145</v>
+        <v>-71.0545</v>
       </c>
       <c r="J193" s="5" t="inlineStr">
         <is>
-          <t>Brûlé de soudeur, casque relevé</t>
+          <t>Cheveux argentés gominés, chevalière</t>
         </is>
       </c>
       <c r="K193" s="5" t="inlineStr">
         <is>
-          <t>Manteau de soudeur</t>
+          <t>Manteau noir</t>
         </is>
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>Masque de soudure</t>
+          <t>Chevalière en or</t>
         </is>
       </c>
       <c r="M193" s="5" t="inlineStr">
         <is>
-          <t>portraits/66-dany-aubin-web.webp</t>
+          <t>portraits/151-vittorio-santini-web.webp</t>
         </is>
       </c>
       <c r="N193" s="5" t="inlineStr">
         <is>
-          <t>Aubin</t>
+          <t>Santini</t>
         </is>
       </c>
       <c r="O193" s="5" t="n"/>
       <c r="P193" s="5" t="inlineStr">
         <is>
-          <t>Frère de Sam Aubin</t>
+          <t>Époux de Maria — tient Dévon à distance</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Fernand Lavoie</t>
+          <t>William Lavoie</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Ti-Fer</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -14429,47 +14441,47 @@
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Retraité — ex-opérateur de cuves à l’aluminerie</t>
+          <t>Cuisinier — bistro du centre-ville</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>2131, Rue Davis</t>
+          <t>318, Rue Saint-Vallier</t>
         </is>
       </c>
       <c r="H194" s="4" t="n">
-        <v>48.4244</v>
+        <v>48.4263</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>-71.18225</v>
+        <v>-71.05034999999999</v>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Casquette plate, mains larges</t>
+          <t>Bandana, bras tatoué</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>Veste de laine à carreaux</t>
+          <t>Veste de cuisine ouverte</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>Pipe éteinte</t>
+          <t>Vapoteuse</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>portraits/190-fernand-lavoie-web.webp</t>
+          <t>portraits/206-william-lavoie-web.webp</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
@@ -14479,24 +14491,24 @@
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>Arvida</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>Père d’Audrey Lavoie — cousin éloigné de Mathieu Lavoie</t>
+          <t>Cousin de JP — colocataire d’Emma Boucher et Moussa Diallo</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>Gérald Tremblay</t>
+          <t>Éric Simard</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Le Syndic</t>
+          <t>Ti-Eric</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -14505,83 +14517,83 @@
         </is>
       </c>
       <c r="D195" s="6" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>Délégué syndical — aluminerie</t>
+          <t>Étudiant — Cégep de Chicoutimi</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>Jonquière</t>
+          <t>Chicoutimi</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>3324, Rue Price</t>
+          <t>1184, Boulevard Talbot</t>
         </is>
       </c>
       <c r="H195" s="7" t="n">
-        <v>48.4258</v>
+        <v>48.3984</v>
       </c>
       <c r="I195" s="7" t="n">
-        <v>-71.24039999999999</v>
+        <v>-71.06740000000001</v>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>Manteau de travail, épinglette</t>
+          <t>Casquette, jeans</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>Manteau d’usine</t>
+          <t>Hoodie cégep</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>Cartable de griefs</t>
+          <t>Skateboard</t>
         </is>
       </c>
       <c r="M195" s="5" t="inlineStr">
         <is>
-          <t>portraits/137-gerald-tremblay-web.webp</t>
+          <t>portraits/100-eric-simard-web.webp</t>
         </is>
       </c>
       <c r="N195" s="5" t="inlineStr">
         <is>
-          <t>Tremblay</t>
-        </is>
-      </c>
-      <c r="O195" s="5" t="inlineStr">
-        <is>
-          <t>syndicat</t>
-        </is>
-      </c>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="O195" s="5" t="n"/>
       <c r="P195" s="5" t="inlineStr">
         <is>
-          <t>Collègue de Mathieu Lavoie</t>
+          <t>Colocataire de Justin Chen</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Jade Boivin</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="n"/>
+          <t>Anthony Simard</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Tony Steak</t>
+        </is>
+      </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Élève du primaire — patineuse artistique</t>
+          <t>Apprenti boucher — boucherie familiale</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -14591,65 +14603,73 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2350, Rue Sainte-Famille</t>
+          <t>2216, Rue Saint-Joseph</t>
         </is>
       </c>
       <c r="H196" s="4" t="n">
-        <v>48.4293</v>
+        <v>48.42405</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>-71.23480000000001</v>
+        <v>-71.2316</v>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Chignon serré, sourire édenté</t>
+          <t>Cheveux ras, pansement au doigt</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>Veston d’entraînement mauve</t>
+          <t>Sarrau blanc, tablier rayé</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>Protège-lames</t>
+          <t>Couteau à désosser</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>portraits/183-jade-boivin-web.webp</t>
+          <t>portraits/212-anthony-simard-web.webp</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>Boivin</t>
-        </is>
-      </c>
-      <c r="O196" s="2" t="n"/>
+          <t>Simard</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>Kénogami</t>
+        </is>
+      </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>Nièce de France et Maxime Boivin</t>
+          <t>Fils de Karine Simard — frère de Léa — neveu de Nancy Simard</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Jean-Marc Fortin</t>
-        </is>
-      </c>
-      <c r="B197" s="5" t="n"/>
+          <t>Antoine Lefèvre</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>Le Français</t>
+        </is>
+      </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D197" s="6" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>Directeur d’usine — Rio Tinto Arvida</t>
+          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
@@ -14659,73 +14679,65 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>1, Rue des Alumineries</t>
+          <t>1125, Rue Saint-Dominique</t>
         </is>
       </c>
       <c r="H197" s="7" t="n">
-        <v>48.4265</v>
+        <v>48.421279</v>
       </c>
       <c r="I197" s="7" t="n">
-        <v>-71.182</v>
+        <v>-71.244586</v>
       </c>
       <c r="J197" s="5" t="inlineStr">
         <is>
-          <t>Cheveux argentés, manteau</t>
+          <t>Barbe hipster</t>
         </is>
       </c>
       <c r="K197" s="5" t="inlineStr">
         <is>
-          <t>Manteau et casque blanc</t>
+          <t>Friperie, caméra Sony</t>
         </is>
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>Casque sous le bras</t>
+          <t>Veut docu raw</t>
         </is>
       </c>
       <c r="M197" s="5" t="inlineStr">
         <is>
-          <t>portraits/125-jean-marc-fortin-web.webp</t>
+          <t>portraits/20-antoine-lefevre-web.webp</t>
         </is>
       </c>
       <c r="N197" s="5" t="inlineStr">
         <is>
-          <t>Fortin</t>
-        </is>
-      </c>
-      <c r="O197" s="5" t="inlineStr">
-        <is>
-          <t>industrie</t>
-        </is>
-      </c>
+          <t>Lefèvre</t>
+        </is>
+      </c>
+      <c r="O197" s="5" t="n"/>
       <c r="P197" s="5" t="inlineStr">
         <is>
-          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
+          <t>Frère de Camille</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Ludovic Larouche</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>Ludo</t>
-        </is>
-      </c>
+          <t>Audrey Lavoie</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="n"/>
       <c r="C198" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+          <t>Apprentie électricienne — aluminerie Rio Tinto Arvida</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -14735,69 +14747,69 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2507, Rue Saint-Hubert</t>
+          <t>2135, Rue Davis</t>
         </is>
       </c>
       <c r="H198" s="4" t="n">
-        <v>48.41615</v>
+        <v>48.42455</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>-71.25285</v>
+        <v>-71.18219999999999</v>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Boucles, lunettes rondes</t>
+          <t>Tresse blonde, lunettes de sécurité</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>Veste en velours côtelé</t>
+          <t>Manteau orange haute visibilité</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>Caméscope à l’épaule</t>
+          <t>Glacière à lunch</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>portraits/182-ludovic-larouche-web.webp</t>
+          <t>portraits/191-audrey-lavoie-web.webp</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>Larouche</t>
-        </is>
-      </c>
-      <c r="O198" s="2" t="n"/>
+          <t>Lavoie</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>Arvida</t>
+        </is>
+      </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>Fils de Benoit Larouche</t>
+          <t>Fille de Fernand Lavoie — collègue de Nicolas Gagné</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>Marc Picard</t>
-        </is>
-      </c>
-      <c r="B199" s="5" t="inlineStr">
-        <is>
-          <t>L’Arpenteur</t>
-        </is>
-      </c>
+          <t>Benoit Larouche</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="n"/>
       <c r="C199" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D199" s="6" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>Arpenteur-géomètre</t>
+          <t>Enseignant — Cégep de Jonquière (ATM)</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
@@ -14807,69 +14819,65 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>1220, Rue du Vieux-Pont</t>
+          <t>2505, Rue Saint-Hubert</t>
         </is>
       </c>
       <c r="H199" s="7" t="n">
-        <v>48.4113</v>
+        <v>48.416</v>
       </c>
       <c r="I199" s="7" t="n">
-        <v>-71.2679</v>
+        <v>-71.253</v>
       </c>
       <c r="J199" s="5" t="inlineStr">
         <is>
-          <t>Innu de Mashteuiatsh, cheveux longs attachés</t>
+          <t>Lunettes, barbe grise</t>
         </is>
       </c>
       <c r="K199" s="5" t="inlineStr">
         <is>
-          <t>Dossard orange sur polar</t>
+          <t>Chemise et cardigan</t>
         </is>
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>Station totale sur trépied</t>
+          <t>Clap de cinéma</t>
         </is>
       </c>
       <c r="M199" s="5" t="inlineStr">
         <is>
-          <t>portraits/193-marc-picard-web.webp</t>
+          <t>portraits/86-benoit-larouche-web.webp</t>
         </is>
       </c>
       <c r="N199" s="5" t="inlineStr">
         <is>
-          <t>Picard</t>
+          <t>Larouche</t>
         </is>
       </c>
       <c r="O199" s="5" t="n"/>
       <c r="P199" s="5" t="inlineStr">
         <is>
-          <t>Célibataire — croise William McKenzie</t>
+          <t>Prof d’Antoine Lefèvre</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Mathieu Lavoie</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>Mat</t>
-        </is>
-      </c>
+          <t>Camille Lefèvre</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="n"/>
       <c r="C200" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Technicien à l'aluminerie Rio Tinto — Arvida</t>
+          <t>Étudiante en communications (UQAC)</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -14879,55 +14887,51 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>3320, Rue Price</t>
+          <t>1127, Rue Saint-Dominique</t>
         </is>
       </c>
       <c r="H200" s="4" t="n">
-        <v>48.425907</v>
+        <v>48.4214</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>-71.240752</v>
+        <v>-71.24469999999999</v>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Propre, polo Rio Tinto</t>
+          <t>Carré brun, appareil photo</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>Polo Rio Tinto</t>
+          <t>Manteau friperie</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>Boîte à lunch</t>
+          <t>Pentax vintage</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>portraits/35-mathieu-lavoie-web.webp</t>
+          <t>portraits/65-camille-lefevre-web.webp</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t>Lavoie</t>
-        </is>
-      </c>
-      <c r="O200" s="2" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
+          <t>Lefèvre</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="n"/>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>Frère aîné de JP</t>
+          <t>Sœur d’Antoine Lefèvre</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>Mélissa Harvey</t>
+          <t>Dany Aubin</t>
         </is>
       </c>
       <c r="B201" s="5" t="n"/>
@@ -14937,11 +14941,11 @@
         </is>
       </c>
       <c r="D201" s="6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>Étudiante en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+          <t>Soudeur</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
@@ -14951,56 +14955,56 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>1129, Rue Saint-Dominique</t>
+          <t>2147, Boulevard Harvey</t>
         </is>
       </c>
       <c r="H201" s="7" t="n">
-        <v>48.42135</v>
+        <v>48.41282</v>
       </c>
       <c r="I201" s="7" t="n">
-        <v>-71.24464999999999</v>
+        <v>-71.24145</v>
       </c>
       <c r="J201" s="5" t="inlineStr">
         <is>
-          <t>Chignon brouillon, manteau friperie</t>
+          <t>Brûlé de soudeur, casque relevé</t>
         </is>
       </c>
       <c r="K201" s="5" t="inlineStr">
         <is>
-          <t>Manteau friperie</t>
+          <t>Manteau de soudeur</t>
         </is>
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>Perche micro</t>
+          <t>Masque de soudure</t>
         </is>
       </c>
       <c r="M201" s="5" t="inlineStr">
         <is>
-          <t>portraits/110-melissa-harvey-web.webp</t>
+          <t>portraits/66-dany-aubin-web.webp</t>
         </is>
       </c>
       <c r="N201" s="5" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Aubin</t>
         </is>
       </c>
       <c r="O201" s="5" t="n"/>
       <c r="P201" s="5" t="inlineStr">
         <is>
-          <t>Nièce de François Harvey</t>
+          <t>Frère de Sam Aubin</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Nancy Simard</t>
+          <t>Fernand Lavoie</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Nancy Ciseaux</t>
+          <t>Ti-Fer</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -15009,11 +15013,11 @@
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Coiffeuse — propriétaire de salon</t>
+          <t>Retraité — ex-opérateur de cuves à l’aluminerie</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -15023,69 +15027,73 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>3812, Rue Saint-Hubert</t>
+          <t>2131, Rue Davis</t>
         </is>
       </c>
       <c r="H202" s="4" t="n">
-        <v>48.41605</v>
+        <v>48.4244</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>-71.2453</v>
+        <v>-71.18225</v>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>Blond platine, grosses boucles d’oreilles</t>
+          <t>Casquette plate, mains larges</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>Sarrau noir de coiffeuse</t>
+          <t>Veste de laine à carreaux</t>
         </is>
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>Ciseaux et peigne</t>
+          <t>Pipe éteinte</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>portraits/192-nancy-simard-web.webp</t>
+          <t>portraits/190-fernand-lavoie-web.webp</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>Simard</t>
+          <t>Lavoie</t>
         </is>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>Arvida</t>
         </is>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>Célibataire — voisine de Benoit Larouche</t>
+          <t>Père d’Audrey Lavoie — cousin éloigné de Mathieu Lavoie</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>Nicolas Gagné</t>
-        </is>
-      </c>
-      <c r="B203" s="5" t="n"/>
+          <t>Gérald Tremblay</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>Le Syndic</t>
+        </is>
+      </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D203" s="6" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>Technicien — aluminerie Rio Tinto Arvida</t>
+          <t>Délégué syndical — aluminerie</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
@@ -15095,43 +15103,43 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>3322, Rue Price</t>
+          <t>3324, Rue Price</t>
         </is>
       </c>
       <c r="H203" s="7" t="n">
-        <v>48.426</v>
+        <v>48.4258</v>
       </c>
       <c r="I203" s="7" t="n">
-        <v>-71.2405</v>
+        <v>-71.24039999999999</v>
       </c>
       <c r="J203" s="5" t="inlineStr">
         <is>
-          <t>Propre, lunettes de sécurité</t>
+          <t>Manteau de travail, épinglette</t>
         </is>
       </c>
       <c r="K203" s="5" t="inlineStr">
         <is>
-          <t>Polo Rio Tinto</t>
+          <t>Manteau d’usine</t>
         </is>
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>Casque blanc</t>
+          <t>Cartable de griefs</t>
         </is>
       </c>
       <c r="M203" s="5" t="inlineStr">
         <is>
-          <t>portraits/94-nicolas-gagne-web.webp</t>
+          <t>portraits/137-gerald-tremblay-web.webp</t>
         </is>
       </c>
       <c r="N203" s="5" t="inlineStr">
         <is>
-          <t>Gagné</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="O203" s="5" t="inlineStr">
         <is>
-          <t>Arvida</t>
+          <t>syndicat</t>
         </is>
       </c>
       <c r="P203" s="5" t="inlineStr">
@@ -15143,25 +15151,21 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Sam Aubin</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>Ink</t>
-        </is>
-      </c>
+          <t>Jade Boivin</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n"/>
       <c r="C204" s="3" t="inlineStr">
         <is>
           <t>Humain</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Tatoueur</t>
+          <t>Élève du primaire — patineuse artistique</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -15171,49 +15175,777 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2145, Boulevard Harvey</t>
+          <t>2350, Rue Sainte-Famille</t>
         </is>
       </c>
       <c r="H204" s="4" t="n">
-        <v>48.412694</v>
+        <v>48.4293</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>-71.241325</v>
+        <v>-71.23480000000001</v>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>Cheveux bleus, full tattoos</t>
+          <t>Chignon serré, sourire édenté</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>Tablier noir</t>
+          <t>Veston d’entraînement mauve</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>Efface tattoos gang</t>
+          <t>Protège-lames</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>portraits/24-sam-aubin-web.webp</t>
+          <t>portraits/183-jade-boivin-web.webp</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>Aubin</t>
+          <t>Boivin</t>
         </is>
       </c>
       <c r="O204" s="2" t="n"/>
       <c r="P204" s="2" t="inlineStr">
         <is>
+          <t>Nièce de France et Maxime Boivin</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Marc Fortin</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>Directeur d’usine — Rio Tinto Arvida</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>1, Rue des Alumineries</t>
+        </is>
+      </c>
+      <c r="H205" s="7" t="n">
+        <v>48.4265</v>
+      </c>
+      <c r="I205" s="7" t="n">
+        <v>-71.182</v>
+      </c>
+      <c r="J205" s="5" t="inlineStr">
+        <is>
+          <t>Cheveux argentés, manteau</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="inlineStr">
+        <is>
+          <t>Manteau et casque blanc</t>
+        </is>
+      </c>
+      <c r="L205" s="5" t="inlineStr">
+        <is>
+          <t>Casque sous le bras</t>
+        </is>
+      </c>
+      <c r="M205" s="5" t="inlineStr">
+        <is>
+          <t>portraits/125-jean-marc-fortin-web.webp</t>
+        </is>
+      </c>
+      <c r="N205" s="5" t="inlineStr">
+        <is>
+          <t>Fortin</t>
+        </is>
+      </c>
+      <c r="O205" s="5" t="inlineStr">
+        <is>
+          <t>industrie</t>
+        </is>
+      </c>
+      <c r="P205" s="5" t="inlineStr">
+        <is>
+          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Karine Simard</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Coach K</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Enseignante d’éducation physique — entraîneuse de natation</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>2216, Rue Saint-Joseph</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="n">
+        <v>48.42395</v>
+      </c>
+      <c r="I206" s="4" t="n">
+        <v>-71.23180000000001</v>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>Athlétique, queue de cheval blonde</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>Veste de survêtement marine</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>Chronomètre</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>portraits/213-karine-simard-web.webp</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>Simard</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>Kénogami</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>Mère de Léa et Anthony — sœur de Nancy Simard</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>Ludovic Larouche</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>Ludo</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>Étudiant en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>2507, Rue Saint-Hubert</t>
+        </is>
+      </c>
+      <c r="H207" s="7" t="n">
+        <v>48.41615</v>
+      </c>
+      <c r="I207" s="7" t="n">
+        <v>-71.25285</v>
+      </c>
+      <c r="J207" s="5" t="inlineStr">
+        <is>
+          <t>Boucles, lunettes rondes</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="inlineStr">
+        <is>
+          <t>Veste en velours côtelé</t>
+        </is>
+      </c>
+      <c r="L207" s="5" t="inlineStr">
+        <is>
+          <t>Caméscope à l’épaule</t>
+        </is>
+      </c>
+      <c r="M207" s="5" t="inlineStr">
+        <is>
+          <t>portraits/182-ludovic-larouche-web.webp</t>
+        </is>
+      </c>
+      <c r="N207" s="5" t="inlineStr">
+        <is>
+          <t>Larouche</t>
+        </is>
+      </c>
+      <c r="O207" s="5" t="n"/>
+      <c r="P207" s="5" t="inlineStr">
+        <is>
+          <t>Fils de Benoit Larouche</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Léa Simard</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n"/>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Élève du secondaire — nageuse de compétition</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>2216, Rue Saint-Joseph</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="n">
+        <v>48.424</v>
+      </c>
+      <c r="I208" s="4" t="n">
+        <v>-71.2317</v>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>Cheveux mouillés, l’air déterminé</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>Serviette sur les épaules</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>Lunettes de piscine sur le front</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>portraits/211-lea-simard-web.webp</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>Simard</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>Kénogami</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>Fille de Karine Simard — sœur d’Anthony</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>Marc Picard</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>L’Arpenteur</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>Arpenteur-géomètre</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>1220, Rue du Vieux-Pont</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="n">
+        <v>48.4113</v>
+      </c>
+      <c r="I209" s="7" t="n">
+        <v>-71.2679</v>
+      </c>
+      <c r="J209" s="5" t="inlineStr">
+        <is>
+          <t>Innu de Mashteuiatsh, cheveux longs attachés</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="inlineStr">
+        <is>
+          <t>Dossard orange sur polar</t>
+        </is>
+      </c>
+      <c r="L209" s="5" t="inlineStr">
+        <is>
+          <t>Station totale sur trépied</t>
+        </is>
+      </c>
+      <c r="M209" s="5" t="inlineStr">
+        <is>
+          <t>portraits/193-marc-picard-web.webp</t>
+        </is>
+      </c>
+      <c r="N209" s="5" t="inlineStr">
+        <is>
+          <t>Picard</t>
+        </is>
+      </c>
+      <c r="O209" s="5" t="n"/>
+      <c r="P209" s="5" t="inlineStr">
+        <is>
+          <t>Célibataire — croise William McKenzie</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Mathieu Lavoie</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Mat</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Technicien à l'aluminerie Rio Tinto — Arvida</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>3320, Rue Price</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="n">
+        <v>48.425907</v>
+      </c>
+      <c r="I210" s="4" t="n">
+        <v>-71.240752</v>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>Propre, polo Rio Tinto</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>Polo Rio Tinto</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>Boîte à lunch</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>portraits/35-mathieu-lavoie-web.webp</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>Lavoie</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>Frère aîné de JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>Mélissa Harvey</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>Étudiante en cinéma et télévision (Cégep de Jonquière — ATM)</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>1129, Rue Saint-Dominique</t>
+        </is>
+      </c>
+      <c r="H211" s="7" t="n">
+        <v>48.42135</v>
+      </c>
+      <c r="I211" s="7" t="n">
+        <v>-71.24464999999999</v>
+      </c>
+      <c r="J211" s="5" t="inlineStr">
+        <is>
+          <t>Chignon brouillon, manteau friperie</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="inlineStr">
+        <is>
+          <t>Manteau friperie</t>
+        </is>
+      </c>
+      <c r="L211" s="5" t="inlineStr">
+        <is>
+          <t>Perche micro</t>
+        </is>
+      </c>
+      <c r="M211" s="5" t="inlineStr">
+        <is>
+          <t>portraits/110-melissa-harvey-web.webp</t>
+        </is>
+      </c>
+      <c r="N211" s="5" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="O211" s="5" t="n"/>
+      <c r="P211" s="5" t="inlineStr">
+        <is>
+          <t>Nièce de François Harvey</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Nancy Simard</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Nancy Ciseaux</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Coiffeuse — propriétaire de salon</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>3812, Rue Saint-Hubert</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="n">
+        <v>48.41605</v>
+      </c>
+      <c r="I212" s="4" t="n">
+        <v>-71.2453</v>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>Blond platine, grosses boucles d’oreilles</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>Sarrau noir de coiffeuse</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>Ciseaux et peigne</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>portraits/192-nancy-simard-web.webp</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>Simard</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>salon</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>Célibataire — voisine de Benoit Larouche</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>Nicolas Gagné</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>Technicien — aluminerie Rio Tinto Arvida</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>3322, Rue Price</t>
+        </is>
+      </c>
+      <c r="H213" s="7" t="n">
+        <v>48.426</v>
+      </c>
+      <c r="I213" s="7" t="n">
+        <v>-71.2405</v>
+      </c>
+      <c r="J213" s="5" t="inlineStr">
+        <is>
+          <t>Propre, lunettes de sécurité</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="inlineStr">
+        <is>
+          <t>Polo Rio Tinto</t>
+        </is>
+      </c>
+      <c r="L213" s="5" t="inlineStr">
+        <is>
+          <t>Casque blanc</t>
+        </is>
+      </c>
+      <c r="M213" s="5" t="inlineStr">
+        <is>
+          <t>portraits/94-nicolas-gagne-web.webp</t>
+        </is>
+      </c>
+      <c r="N213" s="5" t="inlineStr">
+        <is>
+          <t>Gagné</t>
+        </is>
+      </c>
+      <c r="O213" s="5" t="inlineStr">
+        <is>
+          <t>Arvida</t>
+        </is>
+      </c>
+      <c r="P213" s="5" t="inlineStr">
+        <is>
+          <t>Collègue de Mathieu Lavoie</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Sam Aubin</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Ink</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Humain</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Tatoueur</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Jonquière</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>2145, Boulevard Harvey</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="n">
+        <v>48.412694</v>
+      </c>
+      <c r="I214" s="4" t="n">
+        <v>-71.241325</v>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>Cheveux bleus, full tattoos</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Tablier noir</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>Efface tattoos gang</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>portraits/24-sam-aubin-web.webp</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>Aubin</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="n"/>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
           <t>Frère de Dany</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P204"/>
+  <autoFilter ref="A1:P214"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15249,7 +15981,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>203 entrées · 16 colonnes · région du Saguenay (Québec)</t>
+          <t>213 entrées · 16 colonnes · région du Saguenay (Québec)</t>
         </is>
       </c>
     </row>

--- a/base_personnages_fictifs.xlsx
+++ b/base_personnages_fictifs.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet name="Personnages" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Lisez-moi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Narration" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$P$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Narration'!$A$1:$H$214</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -105,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -148,6 +150,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16347,14 +16355,14 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>• Statut          : source PRIVÉE (data/narration.csv, non versionnée).</t>
+          <t>• Statut          : source publique (data/narration.csv, versionnée dans le dépôt).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>• Ce classeur     : la narration est VOLONTAIREMENT ABSENTE — diffusion publique.</t>
+          <t>• Ce classeur     : la narration est présente (feuille « Narration »).</t>
         </is>
       </c>
     </row>
@@ -16368,7 +16376,7 @@
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>• Jamais exportée : ni dans le CSV / JSON / GeoJSON publics, ni dans la carte.</t>
+          <t>• Périmètre       : la narration reste hors des exports csv / json / geojson et de la carte (choix de périmètre, voir README).</t>
         </is>
       </c>
     </row>
@@ -16417,4 +16425,8243 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H214"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Surnom</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Faction</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Faction (détail)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Lien Spot</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Quote joual</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Arc S1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Age apparent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Ahmed Benali</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>Le Dépanneur</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>Dépanneur / Famille</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>Voit tout le quartier défiler au comptoir du dépanneur</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>Non. Ça, c’est le crédit dans les deux langues.</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>Découvre le registre que Nour tient en cachette</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>Alain Côté</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="n"/>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>Poste / Neutre</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>Passe au 427 chaque midi</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>J'livre le courrier, pas les secrets.</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>Voit Roger fouiller les boîtes</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Alex Tremblay</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Le Fantôme</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Sous-sol</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Sous-sol / Louche numérique</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Branché sur le Wi-Fi du 427, jamais croisé en personne</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Un mot de passe, c’est juste une porte polie.</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Laisse des bandes qui gênent tout le monde</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Alexandre Lavoie</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Le Cadet</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Famille JP / Aréna</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Frère cadet de JP, hockey juvénile</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>J'vas m'rendre dans la Ligue un jour, moé.</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>Veut que JP revienne à la maison</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Alexis Côté</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Ficelle</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>Fait les rez-de-chaussée du bloc</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Une porte barrée, c’est juste une opinion.</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>Se fait acheter par Dévon puis dérape</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Alexis Gagnon</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Lex</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Aréna / Neutre</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Coéquipier d’Alexandre Lavoie</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Lève la rondelle, pas tes patins.</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>Tente de sortir le Cadet de la rue</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Aline Tremblay</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Famille / Gratien</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Mère de Gratien, clope au 3e</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Mange donc, tu sens la fumée.</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>Coupe les vivres à son fils</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Amina Traoré</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Propre</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Propre</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Pharmacie du quartier, voit les ordonnances</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Sans papier, j’vends rien, même à toi.</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>Repère les ordonnances détournées</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Amélie Martel</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Ville / Tourisme</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Vérifie les permis de location</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>L’image du fjord, c’est pas ça.</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Ferme les locations illégales du bloc</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Anik Desrosiers</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>La Veilleuse</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Urgences / Nuit</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Rentre de nuit au 431, veille sur le bloc</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>La nuit, le quartier se confie plus facilement.</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>Note les mêmes blessures à trois adresses</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Anne Girard</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Propre</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Propre</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>Soigne les dents du quartier</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>Qui s’est battu, cette fois ?</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>Constate les blessures de Lio</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Armand Lacroix</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Neveu de Lucien, salon funéraire</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>Une place, j’en garde toujours une.</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>Prépare la première chapelle ardente</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Bernard Tremblay</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Bunker</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle / Survivaliste</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Vend des conserves à Dévon</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Quand ça va péter, tu vas m’revoir.</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Son abri sert de planque</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Bertrand Gagnon</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Argent</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Ex-mari de Sylvie, connaît les baux</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>Le problème, c’est jamais la maison, c’est le monde.</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>Tente de racheter le bloc avec elle</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Big Jo Bérubé</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Big Jo</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle d'en Face</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>Cousin de Kevin, travaille pour Dévon</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Bouge pas. Bon chien.</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>Premier à frapper au Spot</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Bobby Gagnon</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>La Pieuvre</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Motards</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Motards / Louche</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Reçoit la marchandise volée</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>Ça tombe d'un camion, ça se ramasse.</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>Écoule le matériel piraté</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Camille Desgagné</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Cam</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Caserne / Urgences</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>Répond des appels du Spot en binôme avec Émile</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Le feu, c’est simple. Le monde, non.</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>Sauvetage au quai la nuit du ballot</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Carl Dubé</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Garage / Neutre</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Frère de Mélo, tient le garage</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>Ton char est mort comme l'hiver.</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>Cache le véhicule volé du réseau</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Chantal Gauthier</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>Commerce / Neutre</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>Voit tout le monde au Tim du coin</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Un double-double, pis tes histoires itou.</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>Refuse sa table à Dévon</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Chantal Lavoie</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>La Biche</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle / Lavoie</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Traîne au Spot pour échapper à la maison</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>J’ai pas d’job, j’ai du temps. C’est pire.</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>Plonge avec Gratien malgré son père</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>Chloé Bouchard</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Chlo</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Média / Créatrice</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>Filme le Spot en direct, abonnés en hausse à chaque chicane</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Vous êtes en direct, soyez pas fiers.</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>Sa live du 427 capte plus que prévu</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Cindy Lavoie</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Cin</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Estafette de Gratien, fille de Manon</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>J'livre, j'pose, j'me sauve.</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>Ouvre une liasse qui contient pas d’la dope</t>
+        </is>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Claude Lavoie</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Média / Rang</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>Père de Michel, ex-animateur radio</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>En ondes, on dit la vraie vérité.</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>Reprend l’antenne avec Raymond</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Corinne Noël</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>La Corneille</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle / Marge</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Fournit Sam Aubin en motifs</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>La mort, ça se brosse, tu sais.</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>Fait disparaître un trophée gênant</t>
+        </is>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Cécile Truchon</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Famille / Truchon</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>Mère d’Yvan, garde la caisse</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Mon fils est pas pire qu’un autre.</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>Décide de parler des cigarettes</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Céline Pedneault</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Port / Neutre</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Répare les filets avec Réjean</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>Le fjord nous doit rien.</t>
+        </is>
+      </c>
+      <c r="G27" s="19" t="inlineStr">
+        <is>
+          <t>Trouve un ballot dans ses filets</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Dave Cloutier</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Coune</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle / Jeune</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>Livre au 427, dort où on veut bien de lui</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Moé j’pédale, j’demande pas où.</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Se cache à la bibliothèque après la descente</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Denis Desgagné</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Le Capitaine</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Caserne / Capitaine</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Sa caserne couvre le Spot, il connaît l’adresse par cœur</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>Ma caserne mange ensemble. Le reste se règle.</t>
+        </is>
+      </c>
+      <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>Signe le rapport de la fausse alerte et doute</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Diane Tremblay</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>Famille JP</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>Sa cuisine du 145 Lavoie alimente le Spot en muffins</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Mange. Après, on va ça.</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>Ravale sa peur quand JP reprend l’enquête</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Dominic Audet</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Dom</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Taxi / Neutre</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Dépose tout le monde au Spot à 3 h</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>J’tourne pas la tête, j’tourne le coin.</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>Son carnet de courses accuse</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>Dévon Boucher</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Le Snake</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle d'en Face / Chef</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>Sa casse de Saint-Anicet finance la pression sur le Spot</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Le quartier, c’est une cour de récré. Moé j’ai le ballon.</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>Pousse le Spot trop loin et s’y casse</t>
+        </is>
+      </c>
+      <c r="H32" s="18" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>Fatima Al-Hassan</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>Fatima Poutine</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>Rue / Cuisine</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>Camion garé face au Spot, midi et soir</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>Une poutine, ça console mieux qu’un avocat.</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
+        <is>
+          <t>Le camion devient le parloir du quartier</t>
+        </is>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Fernand Côté</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Fern</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Vieux bloc / Port</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>Voisin du Spot, ex-dockeur</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Au quai, on parlait pas.</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>Reconnaît le conteneur de Sal</t>
+        </is>
+      </c>
+      <c r="H34" s="18" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>Fernande Boucher</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Maman Snake</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle d'en Face / Famille</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Mère de Dévon et d’Éric</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>Mon gars est dur, mais c’t’un tendre.</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>Vient plaider pour son fils</t>
+        </is>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>France Boivin</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>Commerce / Neutre</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>Fleuriste, sœur de Maxime</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Des fleurs, ça dit tout sans parler.</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>Prépare les couronnes anonymes</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>François Harvey</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Ti-Hydro</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>Industrie</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Hydro / Syndicat</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>Oncle de Mélissa, monteur de ligne</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="inlineStr">
+        <is>
+          <t>L'hiver, la ligne décide.</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
+        <is>
+          <t>Rétablit le courant après la descente</t>
+        </is>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Frère Ézéchiel</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Ézéchiel</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>Église / Marge</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>Harangue Lucien dans la rue</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>La fournaise vous attend, mes agnelets !</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>Prophétise l’incendie du bloc</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Félix Otis</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>L’Homme-Fjord</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Fjord / Neutre</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>Neveu de Jeanne Otis, nage en eau glacée</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>Quand l'eau m'ordonne, j'obéis.</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>Repêche une preuve dans la baie</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>Gaston Ha! Ha!</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Cédez</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>Pyramide / Neutre</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>Vit pour la Pyramide des Ha! Ha!</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Cédez ! Cédez ! Cédez !</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>Voit un échange nocturne au bord de l’eau</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Gaston Pelletier</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Ti-Gas</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin / Famille</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>Père d’Hugo, grand-père de Léa</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>Mon bar, c’tait du monde, pas du bruit.</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>Raconte qui tenait le Coin avant</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>Gaétan Lavoie</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Gaétan</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle / Lavoie</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>Père de Chantal, journalier</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>Une job, j'prends. Une fierté, j'ai.</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>Refuse que Chantal plonge avec Gratien</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>Geneviève Bouchard</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="n"/>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>Loi / Sécurité</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Loi / Aide</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Consultations gratuites pour les locataires du 427</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>La loi protège ceux qui la paient. Changons ça.</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>Monte le recours contre l’expulsion</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>Gilles Bergeron</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>La Fouine</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Loi / Sécurité</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>Nuit / Ex-police</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Sa ronde de nuit longe le 427 deux fois</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Trente ans de police, ça vous suit comme un chien.</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>Reconnaît la silhouette d’un homme du réseau</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>Ginette Roy</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>Gigi</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>CLSC / Aide</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Connaît chaque jeune du Spot par son prénom</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
+          <t>Viens t’asseoir, on va ça ensemble.</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>Monte le dossier que la ville ne peut plus ignorer</t>
+        </is>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>Gisèle Truchon</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>Famille / Truchon</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>Conjointe d’Yvan, caissière de route</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>La caisse, j’la compte deux fois.</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>Voit les paquets passer au dépanneur</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>Gratien Tremblay</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>Crackhouse</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle / Chef</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>Sa porte de Prince-Albert alimente le Spot</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>J’vends pas d’la dope, j’vends du réconfort.</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>Voit son réseau se déliter et devient imprévisible</t>
+        </is>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>Guy Tremblay</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Guy Indienne</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>Relais d’Yvan sur le Petit-Parc</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>Du Next, du vrai, pas d’la cendre.</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>Se fait pincer avec une cargaison</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>Gérard Lapointe</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>Gerry</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Conciergerie / Retraite</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>A passé les clés du 427 à Marco, pas les secrets</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>Un plancher brillant, c’est une paix intérieure.</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>Se souvient d’un locataire de 1998</t>
+        </is>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>Hassan Benali</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>Dépanneur / Neutre</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>Fils d’Ahmed et Nadia</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Crédit ? Mon père dit non en deux langues.</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>Reconnaît les clients de Gratien</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>Hugo Pelletier</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>Le Boss</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>Patron du Coin, époux de Sarah</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>Dehors, tu reviendras sobre.</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>Impose le Coin comme zone neutre</t>
+        </is>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>Hélène Blackburn</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>Hôpital / Aide</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>Directrice de l’Hôpital de La Baie</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Un lit, ça se mérite pas, ça se donne.</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Ouvre les dossiers de surdoses</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>Hélène Chicoine</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="n"/>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Famille / Chicoine</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>Mère de Réal</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>Mon fils est doux, comprenez-vous.</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>Réclame Réal après sa disparition</t>
+        </is>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>Isabelle Bergeron</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>École / Aide</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>Institutrice primaire, fille de Gilles</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>Les enfants parlent, faut écouter.</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>Signale les bleus de Lio</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>Jacques Maltais</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="n"/>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>Ville / Argent</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>Conseiller d’arrondissement La Baie</t>
+        </is>
+      </c>
+      <c r="F55" s="19" t="inlineStr">
+        <is>
+          <t>La Baie, ça se gère comme un gros frigidaire.</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>Subit les pressions d’expulsion</t>
+        </is>
+      </c>
+      <c r="H55" s="19" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>Jean-Philippe Lavoie</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>427 / Ex-journaliste</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>Son 4e du 427 voit toute la ruelle</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>J’ai lâché le Quotidien, pas les questions.</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>Rassemble les bandes d’Alex et reprend la plume</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>Jeanne Gagnon</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="n"/>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>Argent / Famille</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>Mère de Sylvie, héritière</t>
+        </is>
+      </c>
+      <c r="F57" s="19" t="inlineStr">
+        <is>
+          <t>Les briques meurent pas, les familles oui.</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>Lègue le bloc à la surprise générale</t>
+        </is>
+      </c>
+      <c r="H57" s="19" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>Jeanne Otis</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="n"/>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>Bibliothèque / Neutre</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>Bibliothécaire, tante de Félix</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Chut. Les livres écoutent tout.</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="inlineStr">
+        <is>
+          <t>Cache Ti-Coune en section jeunesse</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>Jessica Paradis</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>Jess</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>Locataires / Neutre</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>Locataire de Sylvie Gagnon</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t>Mon loyer est payé. En tout cas, j’pense.</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>Témoin des visites d’expulsion</t>
+        </is>
+      </c>
+      <c r="H59" s="19" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>Jessy Bérubé</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Jess</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle / Bérubé</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>Frère de Kevin, entrepôt</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>J'porte, j'pose, j'demande rien.</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>Remplace Big Jo quand ça tourne mal</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>Johanne Gravel</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>Ville / Foncier</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>Sa base du rôle foncier voit la valeur de chaque secret</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
+        <is>
+          <t>Les maisons cachent jamais leurs dettes.</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>Repère une évaluation corrigée à la main</t>
+        </is>
+      </c>
+      <c r="H61" s="19" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>Johanne Tremblay</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>Jo</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle / Salon</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>Coupe les cheveux du Spot à prix ami</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>Sous le casque, j’entends tout pis j’répète rien.</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>Sait la bagarre avant qu’elle arrive</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>Josée Langlois</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="n"/>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>1er étage</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>Femme du Plombier, secrétaire de chantier</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="inlineStr">
+        <is>
+          <t>La facture va suivre, comme toujours.</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>Photographie les dégâts à son tour</t>
+        </is>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>Julie Martel</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>Tourisme / Neutre</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>Guide des croisières, sœur d’Amélie</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>Sur le fjord, pas de Wi-Fi, juste des baleines.</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>Voit un transfert depuis le large</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>Julien Desgagné</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>L’Abbé</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>Église / Paroisse</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>Sa paroisse de Grande-Baie jouxte les terrains Desgagné</t>
+        </is>
+      </c>
+      <c r="F65" s="19" t="inlineStr">
+        <is>
+          <t>J’porte le col, pas le jugement.</t>
+        </is>
+      </c>
+      <c r="G65" s="19" t="inlineStr">
+        <is>
+          <t>Refuse de bénir un chantier de Dévon</t>
+        </is>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>Justine Fortin</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="n"/>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>Bec-Scie / Neutre</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>Patrouilleuse, nièce d’Yves</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>La neige cache tout, sauf les traces.</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>Découvre la planque de Bernard</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>Karim Al-Hassan</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="n"/>
+      <c r="C67" s="19" t="inlineStr">
+        <is>
+          <t>Neutre</t>
+        </is>
+      </c>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>Rue / Neutre</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>Cuisinier du camion, mari de Fatima</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t>Sans piasse ? Une assiette quand même.</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr">
+        <is>
+          <t>Le camion cantine devient QG neutre</t>
+        </is>
+      </c>
+      <c r="H67" s="19" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>Karine Desrosiers</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>Zoom</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>Bloc d'en Face</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>Cousine d’Anik, archiviste de plaques</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>Une plaque, c’est une confession en métal.</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>Retrace le VUS de la soirée Chen</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>Karine Gagnon</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>K-Town</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>Motards</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>Motards / Chef</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>Son club de l’Anse-à-Benjamin veille sans conclure</t>
+        </is>
+      </c>
+      <c r="F69" s="19" t="inlineStr">
+        <is>
+          <t>On loue nos murs, pas nos opinions.</t>
+        </is>
+      </c>
+      <c r="G69" s="19" t="inlineStr">
+        <is>
+          <t>Vend sa neutralité au plus offrant, ou pas</t>
+        </is>
+      </c>
+      <c r="H69" s="19" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>Kevin Bérubé</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Boeuf</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle / Bérubé</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>Fait le videur au Néon, rentre par le chemin des Chutes</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>Dehors, c’est pas personnel. Presque.</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>Refuse de frapper au Spot, en paye le prix</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>Kim Boudreault</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="n"/>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>Urgences / Aide</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>Paramédic, tourne au Spot les nuits de bagarre</t>
+        </is>
+      </c>
+      <c r="F71" s="19" t="inlineStr">
+        <is>
+          <t>Respire. Reste avec moi.</t>
+        </is>
+      </c>
+      <c r="G71" s="19" t="inlineStr">
+        <is>
+          <t>Témoin des appels coupés au 427</t>
+        </is>
+      </c>
+      <c r="H71" s="19" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>Linda Tremblay</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="n"/>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>Conjointe de Gratien, préposée d’entretien</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>J'récure, j'vois rien, c'est mon don.</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>Quitte Gratien et parle à Samson</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>Lise Blackburn</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>CLSC / Aide</t>
+        </is>
+      </c>
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>Travailleuse sociale, collègue de Gigi</t>
+        </is>
+      </c>
+      <c r="F73" s="19" t="inlineStr">
+        <is>
+          <t>On peut pas sauver quelqu’un à sa place.</t>
+        </is>
+      </c>
+      <c r="G73" s="19" t="inlineStr">
+        <is>
+          <t>Ouvre un dossier sur les Cloutier</t>
+        </is>
+      </c>
+      <c r="H73" s="19" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>Louis Girard</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="n"/>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>Propre</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>Propre</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>Comptable, époux d’Anne</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>Les chiffres mentent pas, le monde oui.</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>Démêle les sociétés-écrans</t>
+        </is>
+      </c>
+      <c r="H74" s="18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>Luc Villeneuve</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>OVNI-Luc</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>Bagotville / Marge</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>Guetteur, croise Will</t>
+        </is>
+      </c>
+      <c r="F75" s="19" t="inlineStr">
+        <is>
+          <t>Dans l'ciel, c'est pas juste des avions.</t>
+        </is>
+      </c>
+      <c r="G75" s="19" t="inlineStr">
+        <is>
+          <t>Confond un vol de contrebande avec un OVNI</t>
+        </is>
+      </c>
+      <c r="H75" s="19" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>Lucie Bérubé</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="n"/>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>Famille / Bérubé</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>Mère de Kevin et Jessy</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>Mes gars sont des porteurs, pas des frappeurs.</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>Cache les enfants du quartier</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>Lucie Côté</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="n"/>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>Vieux bloc</t>
+        </is>
+      </c>
+      <c r="E77" s="19" t="inlineStr">
+        <is>
+          <t>Voisine du 425 Victoria</t>
+        </is>
+      </c>
+      <c r="F77" s="19" t="inlineStr">
+        <is>
+          <t>Au tri, on jetait tout, même les patrons.</t>
+        </is>
+      </c>
+      <c r="G77" s="19" t="inlineStr">
+        <is>
+          <t>Colporte les nouvelles du palier</t>
+        </is>
+      </c>
+      <c r="H77" s="19" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>Lucien Lacroix</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>Abbé Lacroix / Le Curé</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>Église / Paroisse</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>Garde les clés de l’église fermée du quartier</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>L’église est barrée, la porte non.</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>Choisit le quartier contre la mutation</t>
+        </is>
+      </c>
+      <c r="H78" s="18" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>Léa Pelletier</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="n"/>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="E79" s="19" t="inlineStr">
+        <is>
+          <t>Serveuse, fille d’Hugo et Sarah</t>
+        </is>
+      </c>
+      <c r="F79" s="19" t="inlineStr">
+        <is>
+          <t>Un café, pis oublie pas ton change.</t>
+        </is>
+      </c>
+      <c r="G79" s="19" t="inlineStr">
+        <is>
+          <t>Rapporte à Ginette ce qu’elle entend</t>
+        </is>
+      </c>
+      <c r="H79" s="19" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>Léo Cloutier</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>Lio</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>Famille / Ruelle</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>P’tit frère de Ti-Coune</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>Mon grand frère, y’est connu, moé.</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>Voit Dave se faire pognner</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>Manon Cloutier</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="n"/>
+      <c r="C81" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>Station-service / Famille</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>Mère de Dave et Lio</t>
+        </is>
+      </c>
+      <c r="F81" s="19" t="inlineStr">
+        <is>
+          <t>Le gaz est cher, les erreurs itou.</t>
+        </is>
+      </c>
+      <c r="G81" s="19" t="inlineStr">
+        <is>
+          <t>Cache Dave et ment pour Lio</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>Manon Lavoie</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="n"/>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle / Gratien</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>Mère de Cindy, 92 Prince-Albert</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>J'ai rien dit, j'ai rien vu, j'ai survécu.</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>Perd son logement de la rue</t>
+        </is>
+      </c>
+      <c r="H82" s="18" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>Manon Villeneuve</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>Manon-Louve</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
+        <is>
+          <t>Motards</t>
+        </is>
+      </c>
+      <c r="D83" s="19" t="inlineStr">
+        <is>
+          <t>Motards / Louves</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>Bras droit de Karine Gagnon</t>
+        </is>
+      </c>
+      <c r="F83" s="19" t="inlineStr">
+        <is>
+          <t>Les Louves mordent en silence.</t>
+        </is>
+      </c>
+      <c r="G83" s="19" t="inlineStr">
+        <is>
+          <t>Prend la relève si Karine tombe</t>
+        </is>
+      </c>
+      <c r="H83" s="19" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>Marc-André Simard</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>Simard</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>Bloc d'en Face</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>Conjoint d’Anik, opérateur d’usine</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>J'vois rien la nuit, j'travaille.</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>Confirme l’alibi d’Anik</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>Marcel Bouchard</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>Le Prêteur</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>Argent / Ruelle</t>
+        </is>
+      </c>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
+          <t>Prêteur, Dévon lui doit</t>
+        </is>
+      </c>
+      <c r="F85" s="19" t="inlineStr">
+        <is>
+          <t>J'prête pas de l'argent, j'prête du temps.</t>
+        </is>
+      </c>
+      <c r="G85" s="19" t="inlineStr">
+        <is>
+          <t>Rachète la dette du Spot</t>
+        </is>
+      </c>
+      <c r="H85" s="19" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>Marco Lapointe</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>Le Concierge</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>427 / Concierge</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>Le seul maître après Dieu au 427, chat compris</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>Moé, j’décide de quelle porte grince.</t>
+        </is>
+      </c>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>Garde la liste de qui entre au Spot</t>
+        </is>
+      </c>
+      <c r="H86" s="18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>Marie-Claude Brassard</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>Urgences / Aide</t>
+        </is>
+      </c>
+      <c r="E87" s="19" t="inlineStr">
+        <is>
+          <t>Deux nuits sur trois, c’est elle qui ramasse le Spot</t>
+        </is>
+      </c>
+      <c r="F87" s="19" t="inlineStr">
+        <is>
+          <t>Monte, ça va aller. Descends pas seule.</t>
+        </is>
+      </c>
+      <c r="G87" s="19" t="inlineStr">
+        <is>
+          <t>Devine la vraie urgence derrière la fausse alerte</t>
+        </is>
+      </c>
+      <c r="H87" s="19" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>Martine Lavoie</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="n"/>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>École</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>Directrice de l’école secondaire</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Ton frère a manqué douze jours.</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>Convoque la famille Lavoie</t>
+        </is>
+      </c>
+      <c r="H88" s="18" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>Mathieu Fortin</t>
+        </is>
+      </c>
+      <c r="B89" s="19" t="inlineStr">
+        <is>
+          <t>Ti-Police</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>Loi / Sécurité</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>Loi / Patrouille</t>
+        </is>
+      </c>
+      <c r="E89" s="19" t="inlineStr">
+        <is>
+          <t>Fait le pied de paix autour du Spot</t>
+        </is>
+      </c>
+      <c r="F89" s="19" t="inlineStr">
+        <is>
+          <t>Moé, ma juridiction, ce sont les prénoms.</t>
+        </is>
+      </c>
+      <c r="G89" s="19" t="inlineStr">
+        <is>
+          <t>Gagne la confiance que Pierre ne peut plus avoir</t>
+        </is>
+      </c>
+      <c r="H89" s="19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>Mathis Truchon</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Pompe</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>Station-service / Famille</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>Sa pompe de route sert les pleins suspects</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Plein, vidange, pis on parle pas.</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>Compte les camions qui ne dorment jamais</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>Maude Pedneault</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>La Zèbre</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t>Aréna</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>Siffle les matchs où les parents perdent la tête</t>
+        </is>
+      </c>
+      <c r="F91" s="19" t="inlineStr">
+        <is>
+          <t>Deux minutes. Moé aussi j’ai des yeux.</t>
+        </is>
+      </c>
+      <c r="G91" s="19" t="inlineStr">
+        <is>
+          <t>Siffle la punition qui fâche la mauvaise famille</t>
+        </is>
+      </c>
+      <c r="H91" s="19" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>Maxime Boivin</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="n"/>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>Propre</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Propre</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>Vétérinaire du quartier</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>Même les chats ont des histoires.</t>
+        </is>
+      </c>
+      <c r="G92" s="18" t="inlineStr">
+        <is>
+          <t>Soigne Pisse-Feu et donne un indice</t>
+        </is>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>Michel Lavoie</t>
+        </is>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>Lady Dynamite</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin / Scène</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>Son bingo du Coin est le parlement du quartier</t>
+        </is>
+      </c>
+      <c r="F93" s="19" t="inlineStr">
+        <is>
+          <t>Lady Dynamite oublie jamais une face, ni une dette.</t>
+        </is>
+      </c>
+      <c r="G93" s="19" t="inlineStr">
+        <is>
+          <t>Une joke de trop au Néon, pis c’est la guerre froide</t>
+        </is>
+      </c>
+      <c r="H93" s="19" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t>Mireille Joseph</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="inlineStr">
+        <is>
+          <t>Mamie Mireille</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D94" s="18" t="inlineStr">
+        <is>
+          <t>Gardienne / Marge</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="inlineStr">
+        <is>
+          <t>Garde les petits du Spot et soigne tout le monde en tisane</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>Une camomille, pis on reparle de ça.</t>
+        </is>
+      </c>
+      <c r="G94" s="18" t="inlineStr">
+        <is>
+          <t>Cache Ti-Coune sous son lit d’enfant</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>Monique Bouchard</t>
+        </is>
+      </c>
+      <c r="B95" s="19" t="n"/>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="inlineStr">
+        <is>
+          <t>Famille Marco</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>Recoud les manteaux du 427 sans poser de question</t>
+        </is>
+      </c>
+      <c r="F95" s="19" t="inlineStr">
+        <is>
+          <t>Une couture tient mieux qu’un secret.</t>
+        </is>
+      </c>
+      <c r="G95" s="19" t="inlineStr">
+        <is>
+          <t>Reconnaît un manteau qu’elle avait recousu</t>
+        </is>
+      </c>
+      <c r="H95" s="19" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>Mélanie Dubé</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>Mélo</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>CPE / Aide</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>Le CPE voit les parents du Spot avant tout le monde</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>Un dodo manqué, ça se voit au dessin.</t>
+        </is>
+      </c>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t>Sait pour Lio avant les autres et le dit enfin</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>Nadia Benali</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="n"/>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>Dépanneur / Famille</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>Tient le cahier des dettes</t>
+        </is>
+      </c>
+      <c r="F97" s="19" t="inlineStr">
+        <is>
+          <t>Le cahier, c’est ma mémoire, et j’oublie rien.</t>
+        </is>
+      </c>
+      <c r="G97" s="19" t="inlineStr">
+        <is>
+          <t>Confie le cahier à Samson</t>
+        </is>
+      </c>
+      <c r="H97" s="19" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>Nancy Dubois</t>
+        </is>
+      </c>
+      <c r="B98" s="18" t="n"/>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>Serveuse, sœur de Patrice</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>Verre cassé, compte cassé.</t>
+        </is>
+      </c>
+      <c r="G98" s="18" t="inlineStr">
+        <is>
+          <t>Travaille la soirée de la descente</t>
+        </is>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>Natasha Vollant</t>
+        </is>
+      </c>
+      <c r="B99" s="19" t="n"/>
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>Parc du Fjord</t>
+        </is>
+      </c>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>Guide innue, sentier Eucher</t>
+        </is>
+      </c>
+      <c r="F99" s="19" t="inlineStr">
+        <is>
+          <t>La forêt vous laisse passer, pas voler.</t>
+        </is>
+      </c>
+      <c r="G99" s="19" t="inlineStr">
+        <is>
+          <t>Guide les flics jusqu'à la planque</t>
+        </is>
+      </c>
+      <c r="H99" s="19" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>Nathalie Bouchard</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="n"/>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>Famille / Chloé</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>Préposée IGA, mère de Chloé</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>Ma fille streame ma vie, fine.</t>
+        </is>
+      </c>
+      <c r="G100" s="18" t="inlineStr">
+        <is>
+          <t>Héberge Chloé après la vidéo virale</t>
+        </is>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>Nathalie Tremblay</t>
+        </is>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>La Directrice</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>Ville</t>
+        </is>
+      </c>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>Son bureau d’Aimé-Gravel signe les permis du quartier</t>
+        </is>
+      </c>
+      <c r="F101" s="19" t="inlineStr">
+        <is>
+          <t>Un arrondissement, ça se planifie, ça s’improvise pas.</t>
+        </is>
+      </c>
+      <c r="G101" s="19" t="inlineStr">
+        <is>
+          <t>Freine des pressions venues de trop haut</t>
+        </is>
+      </c>
+      <c r="H101" s="19" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>Noah Traoré</t>
+        </is>
+      </c>
+      <c r="B102" s="18" t="n"/>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>Neutre</t>
+        </is>
+      </c>
+      <c r="D102" s="18" t="inlineStr">
+        <is>
+          <t>Rue / Planche</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>Sa planche roule du 427 au skatepark</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>Tombé sept fois, levé huit.</t>
+        </is>
+      </c>
+      <c r="G102" s="18" t="inlineStr">
+        <is>
+          <t>Filme la descente sans le savoir</t>
+        </is>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>Normand Boucher</t>
+        </is>
+      </c>
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>Norm</t>
+        </is>
+      </c>
+      <c r="C103" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle d'en Face</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="inlineStr">
+        <is>
+          <t>Cousin de Dévon, casse illégale</t>
+        </is>
+      </c>
+      <c r="F103" s="19" t="inlineStr">
+        <is>
+          <t>Un char, ça meurt. Les preuves itou.</t>
+        </is>
+      </c>
+      <c r="G103" s="19" t="inlineStr">
+        <is>
+          <t>La casse avale la caméra volée</t>
+        </is>
+      </c>
+      <c r="H103" s="19" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>Nour Benali</t>
+        </is>
+      </c>
+      <c r="B104" s="18" t="n"/>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr">
+        <is>
+          <t>Dépanneur / Famille</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>Fait ses devoirs sur le comptoir</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="inlineStr">
+        <is>
+          <t>Maman, quelqu’un veut encore du crédit.</t>
+        </is>
+      </c>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t>Tient le vrai registre des dettes</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>Océane Lapointe</t>
+        </is>
+      </c>
+      <c r="B105" s="19" t="inlineStr">
+        <is>
+          <t>Zamboni</t>
+        </is>
+      </c>
+      <c r="C105" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t>Aréna</t>
+        </is>
+      </c>
+      <c r="E105" s="19" t="inlineStr">
+        <is>
+          <t>Sa Zamboni lisse la glace où le quartier s’oublie</t>
+        </is>
+      </c>
+      <c r="F105" s="19" t="inlineStr">
+        <is>
+          <t>La glace, c’est plat. Le reste, non.</t>
+        </is>
+      </c>
+      <c r="G105" s="19" t="inlineStr">
+        <is>
+          <t>Voit l’aréna servir d’entrepôt une nuit</t>
+        </is>
+      </c>
+      <c r="H105" s="19" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>Patrice Dubois</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>P'tit Pat</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="D106" s="18" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>La porte du Coin, c’est lui</t>
+        </is>
+      </c>
+      <c r="F106" s="18" t="inlineStr">
+        <is>
+          <t>C’est d’l’homme, dehors.</t>
+        </is>
+      </c>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t>Refoule Rico une fois de trop</t>
+        </is>
+      </c>
+      <c r="H106" s="18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="19" t="inlineStr">
+        <is>
+          <t>Paule Desbiens</t>
+        </is>
+      </c>
+      <c r="B107" s="19" t="n"/>
+      <c r="C107" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D107" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
+        <is>
+          <t>Notaire de La Baie</t>
+        </is>
+      </c>
+      <c r="F107" s="19" t="inlineStr">
+        <is>
+          <t>Signez ici, et priez un peu.</t>
+        </is>
+      </c>
+      <c r="G107" s="19" t="inlineStr">
+        <is>
+          <t>Trouve l’irrégularité dans le bail</t>
+        </is>
+      </c>
+      <c r="H107" s="19" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="inlineStr">
+        <is>
+          <t>Pauline Fortin</t>
+        </is>
+      </c>
+      <c r="B108" s="18" t="n"/>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D108" s="18" t="inlineStr">
+        <is>
+          <t>Campagne / Neutre</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>Maraîchère, épouse d’Yves</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr">
+        <is>
+          <t>Des bleuets, du temps, c’est tout c’que j’vends.</t>
+        </is>
+      </c>
+      <c r="G108" s="18" t="inlineStr">
+        <is>
+          <t>Son kiosque voit les boîtes passer</t>
+        </is>
+      </c>
+      <c r="H108" s="18" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>Philippe Villeneuve</t>
+        </is>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>Dr Phil</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>Hôpital</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t>Médecin à l’Hôpital de La Baie</t>
+        </is>
+      </c>
+      <c r="F109" s="19" t="inlineStr">
+        <is>
+          <t>J'suis médecin, pas juge.</t>
+        </is>
+      </c>
+      <c r="G109" s="19" t="inlineStr">
+        <is>
+          <t>Soigne un blessé non déclaré</t>
+        </is>
+      </c>
+      <c r="H109" s="19" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>Pierrette Simard</t>
+        </is>
+      </c>
+      <c r="B110" s="18" t="n"/>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D110" s="18" t="inlineStr">
+        <is>
+          <t>Bloc d'en Face / Famille</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>Mère de Marc-André, ex-caissière IGA</t>
+        </is>
+      </c>
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>À la caisse, on sait tout l’monde.</t>
+        </is>
+      </c>
+      <c r="G110" s="18" t="inlineStr">
+        <is>
+          <t>Se souvient des achats suspects</t>
+        </is>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="19" t="inlineStr">
+        <is>
+          <t>Pisse-Feu</t>
+        </is>
+      </c>
+      <c r="B111" s="19" t="n"/>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>Neutre</t>
+        </is>
+      </c>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t>427 / Chat</t>
+        </is>
+      </c>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t>Le vrai concierge du 427 a quatre pattes</t>
+        </is>
+      </c>
+      <c r="F111" s="19" t="inlineStr">
+        <is>
+          <t>Miaou. (Rien à déclarer.)</t>
+        </is>
+      </c>
+      <c r="G111" s="19" t="inlineStr">
+        <is>
+          <t>Dort sur le clavier d’Alex au pire moment</t>
+        </is>
+      </c>
+      <c r="H111" s="19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t>Raymond Gagnon</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>Antenna</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D112" s="18" t="inlineStr">
+        <is>
+          <t>Radio pirate / Marge</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>Pirate radio, écoute Alex T.</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>Ils m’écoutent ? Parfait, j’ai des choses à dire.</t>
+        </is>
+      </c>
+      <c r="G112" s="18" t="inlineStr">
+        <is>
+          <t>Diffuse les bandes d’Alex en direct</t>
+        </is>
+      </c>
+      <c r="H112" s="18" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t>Richard Villeneuve</t>
+        </is>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>Rich</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D113" s="19" t="inlineStr">
+        <is>
+          <t>STS / Neutre</t>
+        </is>
+      </c>
+      <c r="E113" s="19" t="inlineStr">
+        <is>
+          <t>Chauffeur d’autobus</t>
+        </is>
+      </c>
+      <c r="F113" s="19" t="inlineStr">
+        <is>
+          <t>Prochain arrêt : tes conséquences.</t>
+        </is>
+      </c>
+      <c r="G113" s="19" t="inlineStr">
+        <is>
+          <t>La caméra du bus filme la mauvaise course</t>
+        </is>
+      </c>
+      <c r="H113" s="19" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t>Rico Leduc</t>
+        </is>
+      </c>
+      <c r="B114" s="18" t="inlineStr">
+        <is>
+          <t>Rico</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D114" s="18" t="inlineStr">
+        <is>
+          <t>Santini / Ruelle</t>
+        </is>
+      </c>
+      <c r="E114" s="18" t="inlineStr">
+        <is>
+          <t>Recouvre pour Tony à La Baie</t>
+        </is>
+      </c>
+      <c r="F114" s="18" t="inlineStr">
+        <is>
+          <t>Tu payes, ou tu comprends.</t>
+        </is>
+      </c>
+      <c r="G114" s="18" t="inlineStr">
+        <is>
+          <t>Envoyé appuyer Dévon au Spot</t>
+        </is>
+      </c>
+      <c r="H114" s="18" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="19" t="inlineStr">
+        <is>
+          <t>Robert Lavoie</t>
+        </is>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="C115" s="19" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D115" s="19" t="inlineStr">
+        <is>
+          <t>Famille JP</t>
+        </is>
+      </c>
+      <c r="E115" s="19" t="inlineStr">
+        <is>
+          <t>Ses anciens contacts de route servent l’enquête de son fils</t>
+        </is>
+      </c>
+      <c r="F115" s="19" t="inlineStr">
+        <is>
+          <t>Sur la route, on voit les gens pour de vrai.</t>
+        </is>
+      </c>
+      <c r="G115" s="19" t="inlineStr">
+        <is>
+          <t>Remorque JP hors de sa spirale</t>
+        </is>
+      </c>
+      <c r="H115" s="19" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>Rock Côté</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Rock</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D116" s="18" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>Débardeur, filleul de Fernand</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>Un conteneur, ça s’ouvre toujours.</t>
+        </is>
+      </c>
+      <c r="G116" s="18" t="inlineStr">
+        <is>
+          <t>Repère le conteneur de Sal</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>Rock Gagnon</t>
+        </is>
+      </c>
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t>Rocky</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>Motards</t>
+        </is>
+      </c>
+      <c r="D117" s="19" t="inlineStr">
+        <is>
+          <t>Motards</t>
+        </is>
+      </c>
+      <c r="E117" s="19" t="inlineStr">
+        <is>
+          <t>Mécano moto, frère de Karine</t>
+        </is>
+      </c>
+      <c r="F117" s="19" t="inlineStr">
+        <is>
+          <t>Une moto, ça ment jamais.</t>
+        </is>
+      </c>
+      <c r="G117" s="19" t="inlineStr">
+        <is>
+          <t>Prépare les bécanes de repli</t>
+        </is>
+      </c>
+      <c r="H117" s="19" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
+        <is>
+          <t>Roger Bontemps</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="n"/>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>Neutre</t>
+        </is>
+      </c>
+      <c r="D118" s="18" t="inlineStr">
+        <is>
+          <t>Rue / Curieux</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>Sa boîte aux lettres à lui, c’est son journal</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>J’lis pas les lettres, juste les envelopes.</t>
+        </is>
+      </c>
+      <c r="G118" s="18" t="inlineStr">
+        <is>
+          <t>Se fait prendre par Alain et joue l’innocent</t>
+        </is>
+      </c>
+      <c r="H118" s="18" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="19" t="inlineStr">
+        <is>
+          <t>Rosalie Girard</t>
+        </is>
+      </c>
+      <c r="B119" s="19" t="n"/>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D119" s="19" t="inlineStr">
+        <is>
+          <t>Aide / Université</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="inlineStr">
+        <is>
+          <t>Ses stages la ramènent toujours au quartier</t>
+        </is>
+      </c>
+      <c r="F119" s="19" t="inlineStr">
+        <is>
+          <t>Un pouls, ça ment pas.</t>
+        </is>
+      </c>
+      <c r="G119" s="19" t="inlineStr">
+        <is>
+          <t>Reconnaît un patient qui devrait être à l’hôpital</t>
+        </is>
+      </c>
+      <c r="H119" s="19" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>Réal Chicoine</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="inlineStr">
+        <is>
+          <t>Chicoine</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D120" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle / Disparu</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>Rôde autour du Spot avec ses trésors</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>Une scrap, c’est une vie qui a mal tourné.</t>
+        </is>
+      </c>
+      <c r="G120" s="18" t="inlineStr">
+        <is>
+          <t>Trois jours disparus, personne saura jamais</t>
+        </is>
+      </c>
+      <c r="H120" s="18" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>Réal Gravel</t>
+        </is>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>Le Charrue</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D121" s="19" t="inlineStr">
+        <is>
+          <t>Ville / Neutre</t>
+        </is>
+      </c>
+      <c r="E121" s="19" t="inlineStr">
+        <is>
+          <t>Ses niveleuses connaissent la ruelle de la descente</t>
+        </is>
+      </c>
+      <c r="F121" s="19" t="inlineStr">
+        <is>
+          <t>L’hiver efface tout, sauf mes feuilles de route.</t>
+        </is>
+      </c>
+      <c r="G121" s="19" t="inlineStr">
+        <is>
+          <t>Ses feuilles de route contredisent un alibi</t>
+        </is>
+      </c>
+      <c r="H121" s="19" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="18" t="inlineStr">
+        <is>
+          <t>Réjean Pedneault</t>
+        </is>
+      </c>
+      <c r="B122" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Peche</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D122" s="18" t="inlineStr">
+        <is>
+          <t>Port / Neutre</t>
+        </is>
+      </c>
+      <c r="E122" s="18" t="inlineStr">
+        <is>
+          <t>Pêche la baie des Ha! Ha! avec Céline</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>Le fjord parle à qui sait r’garder.</t>
+        </is>
+      </c>
+      <c r="G122" s="18" t="inlineStr">
+        <is>
+          <t>Repêche le ballot tombé d’un conteneur</t>
+        </is>
+      </c>
+      <c r="H122" s="18" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="19" t="inlineStr">
+        <is>
+          <t>Réjean Roy</t>
+        </is>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t>Ti-Jean</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D123" s="19" t="inlineStr">
+        <is>
+          <t>Aide / Famille</t>
+        </is>
+      </c>
+      <c r="E123" s="19" t="inlineStr">
+        <is>
+          <t>Mari de Gigi, ex-papetier</t>
+        </is>
+      </c>
+      <c r="F123" s="19" t="inlineStr">
+        <is>
+          <t>À l’usine, on s’occupait des nôtres.</t>
+        </is>
+      </c>
+      <c r="G123" s="19" t="inlineStr">
+        <is>
+          <t>Accompagne Ginette quand elle doit parler</t>
+        </is>
+      </c>
+      <c r="H123" s="19" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="18" t="inlineStr">
+        <is>
+          <t>Salvatore Martel</t>
+        </is>
+      </c>
+      <c r="B124" s="18" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D124" s="18" t="inlineStr">
+        <is>
+          <t>Santini / Port</t>
+        </is>
+      </c>
+      <c r="E124" s="18" t="inlineStr">
+        <is>
+          <t>Relais conteneurs, croise Yvan</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>Le quai dort jamais.</t>
+        </is>
+      </c>
+      <c r="G124" s="18" t="inlineStr">
+        <is>
+          <t>Reçoit le mauvais conteneur</t>
+        </is>
+      </c>
+      <c r="H124" s="18" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
+          <t>Samuel Desgagné</t>
+        </is>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t>Sam Soudure</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>Industrie</t>
+        </is>
+      </c>
+      <c r="D125" s="19" t="inlineStr">
+        <is>
+          <t>Chantier / Naval</t>
+        </is>
+      </c>
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t>Soude les coques que le port répare</t>
+        </is>
+      </c>
+      <c r="F125" s="19" t="inlineStr">
+        <is>
+          <t>Une belle soudure, ça se voit pas.</t>
+        </is>
+      </c>
+      <c r="G125" s="19" t="inlineStr">
+        <is>
+          <t>Remarque une coque repeinte à la hâte</t>
+        </is>
+      </c>
+      <c r="H125" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t>Samuel Joseph</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>Samy</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D126" s="18" t="inlineStr">
+        <is>
+          <t>Aide / CHSLD</t>
+        </is>
+      </c>
+      <c r="E126" s="18" t="inlineStr">
+        <is>
+          <t>Préposé, fils de Mireille</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>Mamie, t’es où encore ?</t>
+        </is>
+      </c>
+      <c r="G126" s="18" t="inlineStr">
+        <is>
+          <t>Retrouve Mireille qui cache Ti-Coune</t>
+        </is>
+      </c>
+      <c r="H126" s="18" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>Sarah Pelletier</t>
+        </is>
+      </c>
+      <c r="B127" s="19" t="n"/>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="D127" s="19" t="inlineStr">
+        <is>
+          <t>Bar du Coin</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
+          <t>Barmaid, épouse d’Hugo</t>
+        </is>
+      </c>
+      <c r="F127" s="19" t="inlineStr">
+        <is>
+          <t>Pas de mains sur le comptoir, pas d’mains sur moi.</t>
+        </is>
+      </c>
+      <c r="G127" s="19" t="inlineStr">
+        <is>
+          <t>Tient la barre pendant la tempête</t>
+        </is>
+      </c>
+      <c r="H127" s="19" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="18" t="inlineStr">
+        <is>
+          <t>Serge Potvin</t>
+        </is>
+      </c>
+      <c r="B128" s="18" t="inlineStr">
+        <is>
+          <t>Pelle</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D128" s="18" t="inlineStr">
+        <is>
+          <t>Ville / Neutre</t>
+        </is>
+      </c>
+      <c r="E128" s="18" t="inlineStr">
+        <is>
+          <t>Opérateur de déneigement</t>
+        </is>
+      </c>
+      <c r="F128" s="18" t="inlineStr">
+        <is>
+          <t>La neige tombe pour tout le monde, sauf mon horaire.</t>
+        </is>
+      </c>
+      <c r="G128" s="18" t="inlineStr">
+        <is>
+          <t>Sa niveleuse ouvre la ruelle de la descente</t>
+        </is>
+      </c>
+      <c r="H128" s="18" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="19" t="inlineStr">
+        <is>
+          <t>Solange Bouchard</t>
+        </is>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t>La Reine de Grande-Baie</t>
+        </is>
+      </c>
+      <c r="C129" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="inlineStr">
+        <is>
+          <t>Quartier / Marge</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
+          <t>Souverainiste de Grande-Baie</t>
+        </is>
+      </c>
+      <c r="F129" s="19" t="inlineStr">
+        <is>
+          <t>La Grande-Baie est souveraine !</t>
+        </is>
+      </c>
+      <c r="G129" s="19" t="inlineStr">
+        <is>
+          <t>Mobilise le quartier contre l’expulsion</t>
+        </is>
+      </c>
+      <c r="H129" s="19" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="18" t="inlineStr">
+        <is>
+          <t>Sonia Tremblay</t>
+        </is>
+      </c>
+      <c r="B130" s="18" t="n"/>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D130" s="18" t="inlineStr">
+        <is>
+          <t>Famille / Alex</t>
+        </is>
+      </c>
+      <c r="E130" s="18" t="inlineStr">
+        <is>
+          <t>Mère d’Alex Tremblay, préposée aux bénéficiaires</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>Mon fils sortira de sa chambre, un jour.</t>
+        </is>
+      </c>
+      <c r="G130" s="18" t="inlineStr">
+        <is>
+          <t>Débranche l'ordinateur, trouve les preuves</t>
+        </is>
+      </c>
+      <c r="H130" s="18" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="19" t="inlineStr">
+        <is>
+          <t>Steve Gauthier</t>
+        </is>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t>Stevie Chop</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D131" s="19" t="inlineStr">
+        <is>
+          <t>Casse</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t>Dépeceur, fournit Bobby</t>
+        </is>
+      </c>
+      <c r="F131" s="19" t="inlineStr">
+        <is>
+          <t>J'enlève juste ce qui dérange.</t>
+        </is>
+      </c>
+      <c r="G131" s="19" t="inlineStr">
+        <is>
+          <t>Démontre la voiture d’Antoine</t>
+        </is>
+      </c>
+      <c r="H131" s="19" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t>Steve Langlois</t>
+        </is>
+      </c>
+      <c r="B132" s="18" t="inlineStr">
+        <is>
+          <t>Le Plombier</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D132" s="18" t="inlineStr">
+        <is>
+          <t>Plomberie / Urgences</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>Ses urgences au 427 l’envoient sous tous les éviers</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>C’est là que ça perce, là que ça fait mal.</t>
+        </is>
+      </c>
+      <c r="G132" s="18" t="inlineStr">
+        <is>
+          <t>Règle une fuite au sous-sol et voit trop</t>
+        </is>
+      </c>
+      <c r="H132" s="18" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="19" t="inlineStr">
+        <is>
+          <t>Stéphanie Lapointe</t>
+        </is>
+      </c>
+      <c r="B133" s="19" t="inlineStr">
+        <is>
+          <t>Steph</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D133" s="19" t="inlineStr">
+        <is>
+          <t>Commerce / Neutre</t>
+        </is>
+      </c>
+      <c r="E133" s="19" t="inlineStr">
+        <is>
+          <t>Sa caisse du Dollarama voit les poches vides</t>
+        </is>
+      </c>
+      <c r="F133" s="19" t="inlineStr">
+        <is>
+          <t>Carte, comptant, ou on se revoit vendredi.</t>
+        </is>
+      </c>
+      <c r="G133" s="19" t="inlineStr">
+        <is>
+          <t>Reconnaît le même visage avec des billets neufs</t>
+        </is>
+      </c>
+      <c r="H133" s="19" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="18" t="inlineStr">
+        <is>
+          <t>Sylvain Bouchard</t>
+        </is>
+      </c>
+      <c r="B134" s="18" t="inlineStr">
+        <is>
+          <t>Coach Bouche</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D134" s="18" t="inlineStr">
+        <is>
+          <t>Aréna</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>Entraîneur hockey junior</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
+        <is>
+          <t>Sur glace, pas de gang, juste une équipe.</t>
+        </is>
+      </c>
+      <c r="G134" s="18" t="inlineStr">
+        <is>
+          <t>Sort les jeunes du recrutement de Dévon</t>
+        </is>
+      </c>
+      <c r="H134" s="18" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="19" t="inlineStr">
+        <is>
+          <t>Sylvain Gagné</t>
+        </is>
+      </c>
+      <c r="B135" s="19" t="n"/>
+      <c r="C135" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D135" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle / Salon</t>
+        </is>
+      </c>
+      <c r="E135" s="19" t="inlineStr">
+        <is>
+          <t>Coiffeur à domicile, conjoint de Johanne</t>
+        </is>
+      </c>
+      <c r="F135" s="19" t="inlineStr">
+        <is>
+          <t>J’entends tout sous le casque-séchoir.</t>
+        </is>
+      </c>
+      <c r="G135" s="19" t="inlineStr">
+        <is>
+          <t>Coiffe les dames et capte les rumeurs</t>
+        </is>
+      </c>
+      <c r="H135" s="19" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>Sylvie Gagnon</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>La Proprio</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="inlineStr">
+        <is>
+          <t>Bloc</t>
+        </is>
+      </c>
+      <c r="D136" s="18" t="inlineStr">
+        <is>
+          <t>Bloc / Proprio</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
+          <t>Signe les baux du 425 au 431, un à un</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>Un bail, c’est un pacte, pas une prison.</t>
+        </is>
+      </c>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t>Hérite du bloc de sa mère et choisit son camp</t>
+        </is>
+      </c>
+      <c r="H136" s="18" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="19" t="inlineStr">
+        <is>
+          <t>Thomas Bergeron</t>
+        </is>
+      </c>
+      <c r="B137" s="19" t="inlineStr">
+        <is>
+          <t>Tom-Tom</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D137" s="19" t="inlineStr">
+        <is>
+          <t>Aréna</t>
+        </is>
+      </c>
+      <c r="E137" s="19" t="inlineStr">
+        <is>
+          <t>Bloque les tirs à l’aréna, voit ceux du quartier</t>
+        </is>
+      </c>
+      <c r="F137" s="19" t="inlineStr">
+        <is>
+          <t>Un gardien, c’est un mur avec des opinions.</t>
+        </is>
+      </c>
+      <c r="G137" s="19" t="inlineStr">
+        <is>
+          <t>Voit Lio souffrir et parle à sa mère</t>
+        </is>
+      </c>
+      <c r="H137" s="19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>Thérèse Gagnon</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>Maman Louve</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>Motards</t>
+        </is>
+      </c>
+      <c r="D138" s="18" t="inlineStr">
+        <is>
+          <t>Motards / Aînée</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>Mère de Karine et Rock, ex-Louve</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>Les Louves, c’était moi la première.</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>Protège les gamins du quartier</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="19" t="inlineStr">
+        <is>
+          <t>Thérèse Lacroix</t>
+        </is>
+      </c>
+      <c r="B139" s="19" t="n"/>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
+      <c r="D139" s="19" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
+      <c r="E139" s="19" t="inlineStr">
+        <is>
+          <t>Ex-sacristine, sœur de Lucien</t>
+        </is>
+      </c>
+      <c r="F139" s="19" t="inlineStr">
+        <is>
+          <t>Les cierges coûtent cher, les péchés itou.</t>
+        </is>
+      </c>
+      <c r="G139" s="19" t="inlineStr">
+        <is>
+          <t>Ouvre la sacristie aux sans-logis</t>
+        </is>
+      </c>
+      <c r="H139" s="19" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Paul Côté</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="inlineStr">
+        <is>
+          <t>Le Panier</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D140" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>Chiffonnier, copain de Réal</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="inlineStr">
+        <is>
+          <t>Une canette, c’est cinq cennes. Un secret, c’est gratuit.</t>
+        </is>
+      </c>
+      <c r="G140" s="18" t="inlineStr">
+        <is>
+          <t>Récupère une preuve dans ses chariots</t>
+        </is>
+      </c>
+      <c r="H140" s="18" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="19" t="inlineStr">
+        <is>
+          <t>Tommy Fortin</t>
+        </is>
+      </c>
+      <c r="B141" s="19" t="n"/>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D141" s="19" t="inlineStr">
+        <is>
+          <t>Campagne</t>
+        </is>
+      </c>
+      <c r="E141" s="19" t="inlineStr">
+        <is>
+          <t>Journalier à la bleuetière, fils d’Yves</t>
+        </is>
+      </c>
+      <c r="F141" s="19" t="inlineStr">
+        <is>
+          <t>Aux bleuets, pas de Wi-Fi, pas d’mensonge.</t>
+        </is>
+      </c>
+      <c r="G141" s="19" t="inlineStr">
+        <is>
+          <t>Voit les boîtes de contrebande aux champs</t>
+        </is>
+      </c>
+      <c r="H141" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="18" t="inlineStr">
+        <is>
+          <t>Tony Santini</t>
+        </is>
+      </c>
+      <c r="B142" s="18" t="inlineStr">
+        <is>
+          <t>Tony Capo</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D142" s="18" t="inlineStr">
+        <is>
+          <t>Santini / Quai</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>Lieutenant, neveu de Vittorio</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="inlineStr">
+        <is>
+          <t>Le quai et la casse, même famille.</t>
+        </is>
+      </c>
+      <c r="G142" s="18" t="inlineStr">
+        <is>
+          <t>Ordonne la pression sur Dévon</t>
+        </is>
+      </c>
+      <c r="H142" s="18" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="19" t="inlineStr">
+        <is>
+          <t>Valette Bontemps</t>
+        </is>
+      </c>
+      <c r="B143" s="19" t="n"/>
+      <c r="C143" s="19" t="inlineStr">
+        <is>
+          <t>Neutre</t>
+        </is>
+      </c>
+      <c r="D143" s="19" t="inlineStr">
+        <is>
+          <t>Rue / Neutre</t>
+        </is>
+      </c>
+      <c r="E143" s="19" t="inlineStr">
+        <is>
+          <t>Rogne les plates-bandes et interroge le quartier</t>
+        </is>
+      </c>
+      <c r="F143" s="19" t="inlineStr">
+        <is>
+          <t>Ce que je sais, je le dis. D’où mes ennuis.</t>
+        </is>
+      </c>
+      <c r="G143" s="19" t="inlineStr">
+        <is>
+          <t>Répète ce que Roger n’aurait pas dû trouver</t>
+        </is>
+      </c>
+      <c r="H143" s="19" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>Véronique Côté</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t>Véro</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D144" s="18" t="inlineStr">
+        <is>
+          <t>CPE / Aide</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>Éducatrice, collègue de Mélo</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>Un coco, ça sent quand ça va mal chez nous.</t>
+        </is>
+      </c>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t>Porte plainte après avoir vu Lio</t>
+        </is>
+      </c>
+      <c r="H144" s="18" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="19" t="inlineStr">
+        <is>
+          <t>William McKenzie</t>
+        </is>
+      </c>
+      <c r="B145" s="19" t="inlineStr">
+        <is>
+          <t>Will</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D145" s="19" t="inlineStr">
+        <is>
+          <t>Armée / Bagotville</t>
+        </is>
+      </c>
+      <c r="E145" s="19" t="inlineStr">
+        <is>
+          <t>Militaire de la 3e Escadre</t>
+        </is>
+      </c>
+      <c r="F145" s="19" t="inlineStr">
+        <is>
+          <t>Règlements, monsieur. Rien que les règlements.</t>
+        </is>
+      </c>
+      <c r="G145" s="19" t="inlineStr">
+        <is>
+          <t>Confond un vol de nuit avec un exercice</t>
+        </is>
+      </c>
+      <c r="H145" s="19" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>Yan Couture</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="n"/>
+      <c r="C146" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D146" s="18" t="inlineStr">
+        <is>
+          <t>Art / Musique</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>Guitariste de bar, joue au bingo</t>
+        </is>
+      </c>
+      <c r="F146" s="18" t="inlineStr">
+        <is>
+          <t>Une toune pour t’souler, une autre pour t’garder.</t>
+        </is>
+      </c>
+      <c r="G146" s="18" t="inlineStr">
+        <is>
+          <t>Sa chanson devient l’hymne du bloc</t>
+        </is>
+      </c>
+      <c r="H146" s="18" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="19" t="inlineStr">
+        <is>
+          <t>Yvan Truchon</t>
+        </is>
+      </c>
+      <c r="B147" s="19" t="inlineStr">
+        <is>
+          <t>Cartoune</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D147" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle / Contrebande</t>
+        </is>
+      </c>
+      <c r="E147" s="19" t="inlineStr">
+        <is>
+          <t>Sa route du Petit-Parc est une autoroute, la nuit</t>
+        </is>
+      </c>
+      <c r="F147" s="19" t="inlineStr">
+        <is>
+          <t>Du vrai stock à bon prix, le silence est inclus.</t>
+        </is>
+      </c>
+      <c r="G147" s="19" t="inlineStr">
+        <is>
+          <t>Cherche qui a parlé après la pincée de Guy</t>
+        </is>
+      </c>
+      <c r="H147" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>Yves Fortin</t>
+        </is>
+      </c>
+      <c r="B148" s="18" t="n"/>
+      <c r="C148" s="18" t="inlineStr">
+        <is>
+          <t>Plein air / Port</t>
+        </is>
+      </c>
+      <c r="D148" s="18" t="inlineStr">
+        <is>
+          <t>Campagne</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="inlineStr">
+        <is>
+          <t>Producteur de bleuets</t>
+        </is>
+      </c>
+      <c r="F148" s="18" t="inlineStr">
+        <is>
+          <t>Les bleuets poussent seuls, les hommes non.</t>
+        </is>
+      </c>
+      <c r="G148" s="18" t="inlineStr">
+        <is>
+          <t>Compte les passages sur son chemin</t>
+        </is>
+      </c>
+      <c r="H148" s="18" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="19" t="inlineStr">
+        <is>
+          <t>Yvette Desgagné</t>
+        </is>
+      </c>
+      <c r="B149" s="19" t="inlineStr">
+        <is>
+          <t>Mémère Yvette</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
+      <c r="D149" s="19" t="inlineStr">
+        <is>
+          <t>Église / Orgue</t>
+        </is>
+      </c>
+      <c r="E149" s="19" t="inlineStr">
+        <is>
+          <t>Ses cantiques couvrent les silences de famille</t>
+        </is>
+      </c>
+      <c r="F149" s="19" t="inlineStr">
+        <is>
+          <t>Le bon Dieu écrit droit, mais en mineur.</t>
+        </is>
+      </c>
+      <c r="G149" s="19" t="inlineStr">
+        <is>
+          <t>Se souvient de la crypte de la vieille église</t>
+        </is>
+      </c>
+      <c r="H149" s="19" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>Zack Bérubé</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Zack</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D150" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle / Bérubé</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>La beignerie de nuit, c’est le Spot des petits creux</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>Deux heures du matin, tout le monde est honnête.</t>
+        </is>
+      </c>
+      <c r="G150" s="18" t="inlineStr">
+        <is>
+          <t>Voit les nuits de Kevin depuis la beignerie</t>
+        </is>
+      </c>
+      <c r="H150" s="18" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="19" t="inlineStr">
+        <is>
+          <t>Élodie Martel</t>
+        </is>
+      </c>
+      <c r="B151" s="19" t="n"/>
+      <c r="C151" s="19" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D151" s="19" t="inlineStr">
+        <is>
+          <t>Culture / Neutre</t>
+        </is>
+      </c>
+      <c r="E151" s="19" t="inlineStr">
+        <is>
+          <t>Éducatrice au Musée du Fjord</t>
+        </is>
+      </c>
+      <c r="F151" s="19" t="inlineStr">
+        <is>
+          <t>Le fjord s’en fiche de nos chicanes.</t>
+        </is>
+      </c>
+      <c r="G151" s="19" t="inlineStr">
+        <is>
+          <t>Archive une photo qui gêne</t>
+        </is>
+      </c>
+      <c r="H151" s="19" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="18" t="inlineStr">
+        <is>
+          <t>Émile Brassard</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="n"/>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D152" s="18" t="inlineStr">
+        <is>
+          <t>Caserne / Urgences</t>
+        </is>
+      </c>
+      <c r="E152" s="18" t="inlineStr">
+        <is>
+          <t>Pompier, époux de MC</t>
+        </is>
+      </c>
+      <c r="F152" s="18" t="inlineStr">
+        <is>
+          <t>On éteint tout, sauf les dettes.</t>
+        </is>
+      </c>
+      <c r="G152" s="18" t="inlineStr">
+        <is>
+          <t>Premier sur la fausse alerte du Spot</t>
+        </is>
+      </c>
+      <c r="H152" s="18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="19" t="inlineStr">
+        <is>
+          <t>Émilie Gauthier</t>
+        </is>
+      </c>
+      <c r="B153" s="19" t="n"/>
+      <c r="C153" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D153" s="19" t="inlineStr">
+        <is>
+          <t>Commerce / Neutre</t>
+        </is>
+      </c>
+      <c r="E153" s="19" t="inlineStr">
+        <is>
+          <t>Gérante du Dollarama</t>
+        </is>
+      </c>
+      <c r="F153" s="19" t="inlineStr">
+        <is>
+          <t>Tout est à 1,25, la morale de même.</t>
+        </is>
+      </c>
+      <c r="G153" s="19" t="inlineStr">
+        <is>
+          <t>La couronne de Solange sort de son magasin</t>
+        </is>
+      </c>
+      <c r="H153" s="19" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="18" t="inlineStr">
+        <is>
+          <t>Éric Boucher</t>
+        </is>
+      </c>
+      <c r="B154" s="18" t="inlineStr">
+        <is>
+          <t>Boubou</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D154" s="18" t="inlineStr">
+        <is>
+          <t>Ruelle d'en Face</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
+          <t>Frère de Dévon, ferrailleur</t>
+        </is>
+      </c>
+      <c r="F154" s="18" t="inlineStr">
+        <is>
+          <t>La ferraille pèse, les secrets itou.</t>
+        </is>
+      </c>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t>Exécute la casse sans poser de question</t>
+        </is>
+      </c>
+      <c r="H154" s="18" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="19" t="inlineStr">
+        <is>
+          <t>Albert Dufour</t>
+        </is>
+      </c>
+      <c r="B155" s="19" t="n"/>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D155" s="19" t="inlineStr">
+        <is>
+          <t>Ville / Famille</t>
+        </is>
+      </c>
+      <c r="E155" s="19" t="inlineStr">
+        <is>
+          <t>Ex-conseiller, père du maire</t>
+        </is>
+      </c>
+      <c r="F155" s="19" t="inlineStr">
+        <is>
+          <t>Mon fils m’a dépassé, comme le progrès.</t>
+        </is>
+      </c>
+      <c r="G155" s="19" t="inlineStr">
+        <is>
+          <t>Lâche une vieille combine immobilière</t>
+        </is>
+      </c>
+      <c r="H155" s="19" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="18" t="inlineStr">
+        <is>
+          <t>André Simard</t>
+        </is>
+      </c>
+      <c r="B156" s="18" t="inlineStr">
+        <is>
+          <t>Le Chef</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="inlineStr">
+        <is>
+          <t>Loi / Sécurité</t>
+        </is>
+      </c>
+      <c r="D156" s="18" t="inlineStr">
+        <is>
+          <t>Loi / Direction</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr">
+        <is>
+          <t>Directeur du Service de police</t>
+        </is>
+      </c>
+      <c r="F156" s="18" t="inlineStr">
+        <is>
+          <t>La loi, c’est un édredon : ça cache rien longtemps.</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>Retient Samson ou le lâche ?</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="19" t="inlineStr">
+        <is>
+          <t>Caroline Otis</t>
+        </is>
+      </c>
+      <c r="B157" s="19" t="n"/>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D157" s="19" t="inlineStr">
+        <is>
+          <t>Argent / Chambre</t>
+        </is>
+      </c>
+      <c r="E157" s="19" t="inlineStr">
+        <is>
+          <t>Présidente de la Chambre de commerce</t>
+        </is>
+      </c>
+      <c r="F157" s="19" t="inlineStr">
+        <is>
+          <t>Un commerce qui dérange, c’est un commerce.</t>
+        </is>
+      </c>
+      <c r="G157" s="19" t="inlineStr">
+        <is>
+          <t>Fait pression sur les permis du Néon</t>
+        </is>
+      </c>
+      <c r="H157" s="19" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="18" t="inlineStr">
+        <is>
+          <t>Catherine Samson</t>
+        </is>
+      </c>
+      <c r="B158" s="18" t="n"/>
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>Loi / Sécurité</t>
+        </is>
+      </c>
+      <c r="D158" s="18" t="inlineStr">
+        <is>
+          <t>Loi / Famille</t>
+        </is>
+      </c>
+      <c r="E158" s="18" t="inlineStr">
+        <is>
+          <t>Adjointe au palais, épouse de Pierre</t>
+        </is>
+      </c>
+      <c r="F158" s="18" t="inlineStr">
+        <is>
+          <t>Au palais, les dossiers ont des yeux.</t>
+        </is>
+      </c>
+      <c r="G158" s="18" t="inlineStr">
+        <is>
+          <t>Trouve les sociétés-écrans au greffe</t>
+        </is>
+      </c>
+      <c r="H158" s="18" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="19" t="inlineStr">
+        <is>
+          <t>Danny Fortin</t>
+        </is>
+      </c>
+      <c r="B159" s="19" t="inlineStr">
+        <is>
+          <t>Néon</t>
+        </is>
+      </c>
+      <c r="C159" s="19" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D159" s="19" t="inlineStr">
+        <is>
+          <t>Santini / Façade</t>
+        </is>
+      </c>
+      <c r="E159" s="19" t="inlineStr">
+        <is>
+          <t>Gérant de façade du Néon</t>
+        </is>
+      </c>
+      <c r="F159" s="19" t="inlineStr">
+        <is>
+          <t>Bienvenue au Néon : lumière pis oubli.</t>
+        </is>
+      </c>
+      <c r="G159" s="19" t="inlineStr">
+        <is>
+          <t>Sa porte d’en arrière filtre les rencontres</t>
+        </is>
+      </c>
+      <c r="H159" s="19" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="18" t="inlineStr">
+        <is>
+          <t>Denis Pedneault</t>
+        </is>
+      </c>
+      <c r="B160" s="18" t="inlineStr">
+        <is>
+          <t>Den</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D160" s="18" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E160" s="18" t="inlineStr">
+        <is>
+          <t>Propriétaire de CKRS, cousin de Réjean</t>
+        </is>
+      </c>
+      <c r="F160" s="18" t="inlineStr">
+        <is>
+          <t>En onde, tout le monde est innocent.</t>
+        </is>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>Vend du temps d’antenne au plus offrant</t>
+        </is>
+      </c>
+      <c r="H160" s="18" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="19" t="inlineStr">
+        <is>
+          <t>Diane Perron</t>
+        </is>
+      </c>
+      <c r="B161" s="19" t="inlineStr">
+        <is>
+          <t>La Prof</t>
+        </is>
+      </c>
+      <c r="C161" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D161" s="19" t="inlineStr">
+        <is>
+          <t>Aide / Université</t>
+        </is>
+      </c>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>Son séminaire sur le Saguenay devient une enquête</t>
+        </is>
+      </c>
+      <c r="F161" s="19" t="inlineStr">
+        <is>
+          <t>Le terrain, c’est quand le terrain vous choisit.</t>
+        </is>
+      </c>
+      <c r="G161" s="19" t="inlineStr">
+        <is>
+          <t>Pousse Laurie à publier, ou à se taire</t>
+        </is>
+      </c>
+      <c r="H161" s="19" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="18" t="inlineStr">
+        <is>
+          <t>Emma Boucher</t>
+        </is>
+      </c>
+      <c r="B162" s="18" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D162" s="18" t="inlineStr">
+        <is>
+          <t>Cégep / Relève</t>
+        </is>
+      </c>
+      <c r="E162" s="18" t="inlineStr">
+        <is>
+          <t>Sa coloc du 318 devient un avant-poste d’enquête</t>
+        </is>
+      </c>
+      <c r="F162" s="18" t="inlineStr">
+        <is>
+          <t>C’est pas des nouvelles, c’est de la sociologie.</t>
+        </is>
+      </c>
+      <c r="G162" s="18" t="inlineStr">
+        <is>
+          <t>Rapporte à Fernande ce que Dévon cache</t>
+        </is>
+      </c>
+      <c r="H162" s="18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="19" t="inlineStr">
+        <is>
+          <t>Enzo Bianchi</t>
+        </is>
+      </c>
+      <c r="B163" s="19" t="inlineStr">
+        <is>
+          <t>Le Conseiller</t>
+        </is>
+      </c>
+      <c r="C163" s="19" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D163" s="19" t="inlineStr">
+        <is>
+          <t>Santini / Conseiller</t>
+        </is>
+      </c>
+      <c r="E163" s="19" t="inlineStr">
+        <is>
+          <t>Conseiller de Vittorio</t>
+        </is>
+      </c>
+      <c r="F163" s="19" t="inlineStr">
+        <is>
+          <t>Je suggère, jamais j’ordonne.</t>
+        </is>
+      </c>
+      <c r="G163" s="19" t="inlineStr">
+        <is>
+          <t>Négocie la sortie de Vittorio</t>
+        </is>
+      </c>
+      <c r="H163" s="19" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="18" t="inlineStr">
+        <is>
+          <t>François Côté</t>
+        </is>
+      </c>
+      <c r="B164" s="18" t="n"/>
+      <c r="C164" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D164" s="18" t="inlineStr">
+        <is>
+          <t>Presse</t>
+        </is>
+      </c>
+      <c r="E164" s="18" t="inlineStr">
+        <is>
+          <t>Rédacteur en chef du Quotidien</t>
+        </is>
+      </c>
+      <c r="F164" s="18" t="inlineStr">
+        <is>
+          <t>Une nouvelle, ça se prouve. Une rumeur, ça se vend.</t>
+        </is>
+      </c>
+      <c r="G164" s="18" t="inlineStr">
+        <is>
+          <t>Enterre ou publie le dossier</t>
+        </is>
+      </c>
+      <c r="H164" s="18" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="19" t="inlineStr">
+        <is>
+          <t>Gaétan Bossé</t>
+        </is>
+      </c>
+      <c r="B165" s="19" t="inlineStr">
+        <is>
+          <t>Le Bouquiniste</t>
+        </is>
+      </c>
+      <c r="C165" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D165" s="19" t="inlineStr">
+        <is>
+          <t>Commerce / Neutre</t>
+        </is>
+      </c>
+      <c r="E165" s="19" t="inlineStr">
+        <is>
+          <t>Sa cave à livres de la rue Bossé prête à tout le monde</t>
+        </is>
+      </c>
+      <c r="F165" s="19" t="inlineStr">
+        <is>
+          <t>Un livre usagé, c’est une vie qu’on garde.</t>
+        </is>
+      </c>
+      <c r="G165" s="19" t="inlineStr">
+        <is>
+          <t>Reconnaît un livre volé dans un lot</t>
+        </is>
+      </c>
+      <c r="H165" s="19" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="18" t="inlineStr">
+        <is>
+          <t>Gilles Dufour</t>
+        </is>
+      </c>
+      <c r="B166" s="18" t="inlineStr">
+        <is>
+          <t>Monsieur le Maire</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D166" s="18" t="inlineStr">
+        <is>
+          <t>Ville</t>
+        </is>
+      </c>
+      <c r="E166" s="18" t="inlineStr">
+        <is>
+          <t>Maire de Saguenay, fils d’Albert</t>
+        </is>
+      </c>
+      <c r="F166" s="18" t="inlineStr">
+        <is>
+          <t>Saguenay regarde en avant, surtout en arrière.</t>
+        </is>
+      </c>
+      <c r="G166" s="18" t="inlineStr">
+        <is>
+          <t>Pris entre la police et la Chambre</t>
+        </is>
+      </c>
+      <c r="H166" s="18" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="19" t="inlineStr">
+        <is>
+          <t>Hélène Samson</t>
+        </is>
+      </c>
+      <c r="B167" s="19" t="n"/>
+      <c r="C167" s="19" t="inlineStr">
+        <is>
+          <t>Loi / Sécurité</t>
+        </is>
+      </c>
+      <c r="D167" s="19" t="inlineStr">
+        <is>
+          <t>Loi / Famille</t>
+        </is>
+      </c>
+      <c r="E167" s="19" t="inlineStr">
+        <is>
+          <t>Ex-secrétaire de palais, mère de Pierre</t>
+        </is>
+      </c>
+      <c r="F167" s="19" t="inlineStr">
+        <is>
+          <t>J'ai tapé les aveux de trois générations.</t>
+        </is>
+      </c>
+      <c r="G167" s="19" t="inlineStr">
+        <is>
+          <t>Ressort les vieux dossiers Santini</t>
+        </is>
+      </c>
+      <c r="H167" s="19" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>Isabelle Gagné</t>
+        </is>
+      </c>
+      <c r="B168" s="18" t="n"/>
+      <c r="C168" s="18" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D168" s="18" t="inlineStr">
+        <is>
+          <t>Politique</t>
+        </is>
+      </c>
+      <c r="E168" s="18" t="inlineStr">
+        <is>
+          <t>Députée à l’Assemblée nationale</t>
+        </is>
+      </c>
+      <c r="F168" s="18" t="inlineStr">
+        <is>
+          <t>À Québec, vos ruelles, c’est abstrait.</t>
+        </is>
+      </c>
+      <c r="G168" s="18" t="inlineStr">
+        <is>
+          <t>Promet des fonds puis disparaît</t>
+        </is>
+      </c>
+      <c r="H168" s="18" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="19" t="inlineStr">
+        <is>
+          <t>Jonathan Roy</t>
+        </is>
+      </c>
+      <c r="B169" s="19" t="inlineStr">
+        <is>
+          <t>Johnny Fake</t>
+        </is>
+      </c>
+      <c r="C169" s="19" t="inlineStr">
+        <is>
+          <t>Ruelle</t>
+        </is>
+      </c>
+      <c r="D169" s="19" t="inlineStr">
+        <is>
+          <t>Réseau / Louche</t>
+        </is>
+      </c>
+      <c r="E169" s="19" t="inlineStr">
+        <is>
+          <t>Fausses identités, boulevard Talbot</t>
+        </is>
+      </c>
+      <c r="F169" s="19" t="inlineStr">
+        <is>
+          <t>Qui tu veux être aujourd’hui ? J’ai le papier.</t>
+        </is>
+      </c>
+      <c r="G169" s="19" t="inlineStr">
+        <is>
+          <t>Fabrique l’identité du témoin</t>
+        </is>
+      </c>
+      <c r="H169" s="19" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="18" t="inlineStr">
+        <is>
+          <t>Julien Gagné</t>
+        </is>
+      </c>
+      <c r="B170" s="18" t="inlineStr">
+        <is>
+          <t>Le Volant</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D170" s="18" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="E170" s="18" t="inlineStr">
+        <is>
+          <t>Chauffeur de Vittorio</t>
+        </is>
+      </c>
+      <c r="F170" s="18" t="inlineStr">
+        <is>
+          <t>J'demande pas où on va, c'est mieux.</t>
+        </is>
+      </c>
+      <c r="G170" s="18" t="inlineStr">
+        <is>
+          <t>Conduit la mauvaise nuit</t>
+        </is>
+      </c>
+      <c r="H170" s="18" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="19" t="inlineStr">
+        <is>
+          <t>Justin Chen</t>
+        </is>
+      </c>
+      <c r="B171" s="19" t="inlineStr">
+        <is>
+          <t>Junior Talbot</t>
+        </is>
+      </c>
+      <c r="C171" s="19" t="inlineStr">
+        <is>
+          <t>Neutre</t>
+        </is>
+      </c>
+      <c r="D171" s="19" t="inlineStr">
+        <is>
+          <t>Talbot / Naïf</t>
+        </is>
+      </c>
+      <c r="E171" s="19" t="inlineStr">
+        <is>
+          <t>Sa coloc du Talbot a hébergé la fête qui coûte cher</t>
+        </is>
+      </c>
+      <c r="F171" s="19" t="inlineStr">
+        <is>
+          <t>C’était juste une party, j’te jure.</t>
+        </is>
+      </c>
+      <c r="G171" s="19" t="inlineStr">
+        <is>
+          <t>Se souvient enfin de ce qu’il a filmé</t>
+        </is>
+      </c>
+      <c r="H171" s="19" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="18" t="inlineStr">
+        <is>
+          <t>Jérémie Côté</t>
+        </is>
+      </c>
+      <c r="B172" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Poste</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D172" s="18" t="inlineStr">
+        <is>
+          <t>Poste / Neutre</t>
+        </is>
+      </c>
+      <c r="E172" s="18" t="inlineStr">
+        <is>
+          <t>Sa route Sainte-Anne croise les enveloppes discrètes</t>
+        </is>
+      </c>
+      <c r="F172" s="18" t="inlineStr">
+        <is>
+          <t>Le courrier arrive, les excuses itou.</t>
+        </is>
+      </c>
+      <c r="G172" s="18" t="inlineStr">
+        <is>
+          <t>Remarque le même expéditeur sur trois adresses</t>
+        </is>
+      </c>
+      <c r="H172" s="18" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="19" t="inlineStr">
+        <is>
+          <t>Laurie Lavoie</t>
+        </is>
+      </c>
+      <c r="B173" s="19" t="n"/>
+      <c r="C173" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D173" s="19" t="inlineStr">
+        <is>
+          <t>Aide / Université</t>
+        </is>
+      </c>
+      <c r="E173" s="19" t="inlineStr">
+        <is>
+          <t>Écoute le quartier pour sa recherche de maîtrise</t>
+        </is>
+      </c>
+      <c r="F173" s="19" t="inlineStr">
+        <is>
+          <t>Écouter, c’est être là en entier.</t>
+        </is>
+      </c>
+      <c r="G173" s="19" t="inlineStr">
+        <is>
+          <t>Identifie le lien entre trois dossiers du 427</t>
+        </is>
+      </c>
+      <c r="H173" s="19" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="18" t="inlineStr">
+        <is>
+          <t>Lise Gauthier</t>
+        </is>
+      </c>
+      <c r="B174" s="18" t="n"/>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D174" s="18" t="inlineStr">
+        <is>
+          <t>CLSC / Aide</t>
+        </is>
+      </c>
+      <c r="E174" s="18" t="inlineStr">
+        <is>
+          <t>Sa clinique de soir voit les urgences non déclarées</t>
+        </is>
+      </c>
+      <c r="F174" s="18" t="inlineStr">
+        <is>
+          <t>Assis. Je prends ta tension pis tes nouvelles.</t>
+        </is>
+      </c>
+      <c r="G174" s="18" t="inlineStr">
+        <is>
+          <t>Dresse la liste des visites qui se cachent</t>
+        </is>
+      </c>
+      <c r="H174" s="18" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="19" t="inlineStr">
+        <is>
+          <t>Louise Villeneuve</t>
+        </is>
+      </c>
+      <c r="B175" s="19" t="n"/>
+      <c r="C175" s="19" t="inlineStr">
+        <is>
+          <t>Loi / Sécurité</t>
+        </is>
+      </c>
+      <c r="D175" s="19" t="inlineStr">
+        <is>
+          <t>Loi / Magistrature</t>
+        </is>
+      </c>
+      <c r="E175" s="19" t="inlineStr">
+        <is>
+          <t>Juge à la Cour du Québec</t>
+        </is>
+      </c>
+      <c r="F175" s="19" t="inlineStr">
+        <is>
+          <t>La balance penche du côté des preuves.</t>
+        </is>
+      </c>
+      <c r="G175" s="19" t="inlineStr">
+        <is>
+          <t>Signe les mandats du bloc</t>
+        </is>
+      </c>
+      <c r="H175" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="18" t="inlineStr">
+        <is>
+          <t>Lucien Gagné</t>
+        </is>
+      </c>
+      <c r="B176" s="18" t="inlineStr">
+        <is>
+          <t>Le Proprio des étudiants</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D176" s="18" t="inlineStr">
+        <is>
+          <t>Logements / Étudiants</t>
+        </is>
+      </c>
+      <c r="E176" s="18" t="inlineStr">
+        <is>
+          <t>Le 318 Saint-Vallier, ses loyers patients et ses soupers</t>
+        </is>
+      </c>
+      <c r="F176" s="18" t="inlineStr">
+        <is>
+          <t>Un loyer en retard, ça se parle. Un silence, non.</t>
+        </is>
+      </c>
+      <c r="G176" s="18" t="inlineStr">
+        <is>
+          <t>Héberge le témoin que tout le monde cherche</t>
+        </is>
+      </c>
+      <c r="H176" s="18" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="19" t="inlineStr">
+        <is>
+          <t>Maria Santini</t>
+        </is>
+      </c>
+      <c r="B177" s="19" t="inlineStr">
+        <is>
+          <t>Donna Maria</t>
+        </is>
+      </c>
+      <c r="C177" s="19" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D177" s="19" t="inlineStr">
+        <is>
+          <t>Santini / Famille</t>
+        </is>
+      </c>
+      <c r="E177" s="19" t="inlineStr">
+        <is>
+          <t>Matriarche, restaurant familial</t>
+        </is>
+      </c>
+      <c r="F177" s="19" t="inlineStr">
+        <is>
+          <t>Mange. Les affaires attendent, les pâtes non.</t>
+        </is>
+      </c>
+      <c r="G177" s="19" t="inlineStr">
+        <is>
+          <t>Négocie la clémence en cuisine</t>
+        </is>
+      </c>
+      <c r="H177" s="19" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="18" t="inlineStr">
+        <is>
+          <t>Marie-Ève Boucher</t>
+        </is>
+      </c>
+      <c r="B178" s="18" t="inlineStr">
+        <is>
+          <t>La Plume</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D178" s="18" t="inlineStr">
+        <is>
+          <t>Presse</t>
+        </is>
+      </c>
+      <c r="E178" s="18" t="inlineStr">
+        <is>
+          <t>Sa meilleure source signe au 427</t>
+        </is>
+      </c>
+      <c r="F178" s="18" t="inlineStr">
+        <is>
+          <t>On n’écrit pas les faits divers, on les exhume.</t>
+        </is>
+      </c>
+      <c r="G178" s="18" t="inlineStr">
+        <is>
+          <t>Relie la soirée Chen au port</t>
+        </is>
+      </c>
+      <c r="H178" s="18" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="19" t="inlineStr">
+        <is>
+          <t>Maïka Gauthier</t>
+        </is>
+      </c>
+      <c r="B179" s="19" t="n"/>
+      <c r="C179" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D179" s="19" t="inlineStr">
+        <is>
+          <t>Pharmacie / Étudiante</t>
+        </is>
+      </c>
+      <c r="E179" s="19" t="inlineStr">
+        <is>
+          <t>Encaisse les ordonnances qu’Amina surveille</t>
+        </is>
+      </c>
+      <c r="F179" s="19" t="inlineStr">
+        <is>
+          <t>La relève, c’est moé. La relève est fatiguée.</t>
+        </is>
+      </c>
+      <c r="G179" s="19" t="inlineStr">
+        <is>
+          <t>Voit la même ordonnance revenir trop vite</t>
+        </is>
+      </c>
+      <c r="H179" s="19" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="18" t="inlineStr">
+        <is>
+          <t>Mei Chen</t>
+        </is>
+      </c>
+      <c r="B180" s="18" t="n"/>
+      <c r="C180" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D180" s="18" t="inlineStr">
+        <is>
+          <t>Commerces / Famille</t>
+        </is>
+      </c>
+      <c r="E180" s="18" t="inlineStr">
+        <is>
+          <t>Préposée d’hôtel, mère de Justin</t>
+        </is>
+      </c>
+      <c r="F180" s="18" t="inlineStr">
+        <is>
+          <t>Mon fils se croit riche, il est juste jeune.</t>
+        </is>
+      </c>
+      <c r="G180" s="18" t="inlineStr">
+        <is>
+          <t>Héberge les témoins à l’hôtel</t>
+        </is>
+      </c>
+      <c r="H180" s="18" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="19" t="inlineStr">
+        <is>
+          <t>Mgr Paul Tremblay</t>
+        </is>
+      </c>
+      <c r="B181" s="19" t="inlineStr">
+        <is>
+          <t>Monseigneur</t>
+        </is>
+      </c>
+      <c r="C181" s="19" t="inlineStr">
+        <is>
+          <t>Église</t>
+        </is>
+      </c>
+      <c r="D181" s="19" t="inlineStr">
+        <is>
+          <t>Église / Diocèse</t>
+        </is>
+      </c>
+      <c r="E181" s="19" t="inlineStr">
+        <is>
+          <t>Évêque, supérieur de Lucien</t>
+        </is>
+      </c>
+      <c r="F181" s="19" t="inlineStr">
+        <is>
+          <t>L'Église écoute. L'Église se tait. Parfois.</t>
+        </is>
+      </c>
+      <c r="G181" s="19" t="inlineStr">
+        <is>
+          <t>Doit muter Lucien au mauvais moment</t>
+        </is>
+      </c>
+      <c r="H181" s="19" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="18" t="inlineStr">
+        <is>
+          <t>Moussa Diallo</t>
+        </is>
+      </c>
+      <c r="B182" s="18" t="n"/>
+      <c r="C182" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D182" s="18" t="inlineStr">
+        <is>
+          <t>UQAC / Campus</t>
+        </is>
+      </c>
+      <c r="E182" s="18" t="inlineStr">
+        <is>
+          <t>Coloc du 318, branche les câbles de tout le monde</t>
+        </is>
+      </c>
+      <c r="F182" s="18" t="inlineStr">
+        <is>
+          <t>Ton problème, c’est un problème de permissions.</t>
+        </is>
+      </c>
+      <c r="G182" s="18" t="inlineStr">
+        <is>
+          <t>Nettoie les traces d’Alex, ou les garde</t>
+        </is>
+      </c>
+      <c r="H182" s="18" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="19" t="inlineStr">
+        <is>
+          <t>Nico Santini</t>
+        </is>
+      </c>
+      <c r="B183" s="19" t="inlineStr">
+        <is>
+          <t>Nico</t>
+        </is>
+      </c>
+      <c r="C183" s="19" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D183" s="19" t="inlineStr">
+        <is>
+          <t>Santini / Relève</t>
+        </is>
+      </c>
+      <c r="E183" s="19" t="inlineStr">
+        <is>
+          <t>Fils de Vittorio et Maria</t>
+        </is>
+      </c>
+      <c r="F183" s="19" t="inlineStr">
+        <is>
+          <t>J'suis prêt, parrain. J'suis prêt.</t>
+        </is>
+      </c>
+      <c r="G183" s="19" t="inlineStr">
+        <is>
+          <t>Envoyé en premier, il flanche</t>
+        </is>
+      </c>
+      <c r="H183" s="19" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="inlineStr">
+        <is>
+          <t>Olivier Brassard</t>
+        </is>
+      </c>
+      <c r="B184" s="18" t="inlineStr">
+        <is>
+          <t>Oli</t>
+        </is>
+      </c>
+      <c r="C184" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D184" s="18" t="inlineStr">
+        <is>
+          <t>Art / Musique</t>
+        </is>
+      </c>
+      <c r="E184" s="18" t="inlineStr">
+        <is>
+          <t>Ses livraisons à vélo relient les trois arrondissements</t>
+        </is>
+      </c>
+      <c r="F184" s="18" t="inlineStr">
+        <is>
+          <t>À vélo, tout le monde me parle, personne me voit.</t>
+        </is>
+      </c>
+      <c r="G184" s="18" t="inlineStr">
+        <is>
+          <t>Livre un colis que la police voudrait lire</t>
+        </is>
+      </c>
+      <c r="H184" s="18" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="19" t="inlineStr">
+        <is>
+          <t>Olivier Savard</t>
+        </is>
+      </c>
+      <c r="B185" s="19" t="n"/>
+      <c r="C185" s="19" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D185" s="19" t="inlineStr">
+        <is>
+          <t>Presse</t>
+        </is>
+      </c>
+      <c r="E185" s="19" t="inlineStr">
+        <is>
+          <t>Journaliste, ex-collègue de JP</t>
+        </is>
+      </c>
+      <c r="F185" s="19" t="inlineStr">
+        <is>
+          <t>Ta source, elle s’appelle comment déjà ?</t>
+        </is>
+      </c>
+      <c r="G185" s="19" t="inlineStr">
+        <is>
+          <t>Reçoit les bandes d’Alex</t>
+        </is>
+      </c>
+      <c r="H185" s="19" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="18" t="inlineStr">
+        <is>
+          <t>Patrick Lapointe</t>
+        </is>
+      </c>
+      <c r="B186" s="18" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
+      <c r="C186" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D186" s="18" t="inlineStr">
+        <is>
+          <t>Construction / Entrepreneur</t>
+        </is>
+      </c>
+      <c r="E186" s="18" t="inlineStr">
+        <is>
+          <t>Ses chantiers voient les devis gonflés du bloc</t>
+        </is>
+      </c>
+      <c r="F186" s="18" t="inlineStr">
+        <is>
+          <t>Un bon contrat, ça se relit deux fois.</t>
+        </is>
+      </c>
+      <c r="G186" s="18" t="inlineStr">
+        <is>
+          <t>Refuse le contrat trop beau de Dévon</t>
+        </is>
+      </c>
+      <c r="H186" s="18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="19" t="inlineStr">
+        <is>
+          <t>Paul-André Côté</t>
+        </is>
+      </c>
+      <c r="B187" s="19" t="inlineStr">
+        <is>
+          <t>Le Chiffre</t>
+        </is>
+      </c>
+      <c r="C187" s="19" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D187" s="19" t="inlineStr">
+        <is>
+          <t>Santini / Argent</t>
+        </is>
+      </c>
+      <c r="E187" s="19" t="inlineStr">
+        <is>
+          <t>Comptable des sociétés-écrans</t>
+        </is>
+      </c>
+      <c r="F187" s="19" t="inlineStr">
+        <is>
+          <t>Deux et deux font cinq si je signe.</t>
+        </is>
+      </c>
+      <c r="G187" s="19" t="inlineStr">
+        <is>
+          <t>Les livres basculent entre ses mains</t>
+        </is>
+      </c>
+      <c r="H187" s="19" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="18" t="inlineStr">
+        <is>
+          <t>Pierre Samson</t>
+        </is>
+      </c>
+      <c r="B188" s="18" t="inlineStr">
+        <is>
+          <t>L'Enquêteur</t>
+        </is>
+      </c>
+      <c r="C188" s="18" t="inlineStr">
+        <is>
+          <t>Loi / Sécurité</t>
+        </is>
+      </c>
+      <c r="D188" s="18" t="inlineStr">
+        <is>
+          <t>Loi / Stups</t>
+        </is>
+      </c>
+      <c r="E188" s="18" t="inlineStr">
+        <is>
+          <t>Son enquête remonte du Spot au port</t>
+        </is>
+      </c>
+      <c r="F188" s="18" t="inlineStr">
+        <is>
+          <t>La rue ment mal, le quai ment mieux.</t>
+        </is>
+      </c>
+      <c r="G188" s="18" t="inlineStr">
+        <is>
+          <t>Monte le dossier que Vittorio veut étouffer</t>
+        </is>
+      </c>
+      <c r="H188" s="18" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="19" t="inlineStr">
+        <is>
+          <t>Sofia Santini</t>
+        </is>
+      </c>
+      <c r="B189" s="19" t="inlineStr">
+        <is>
+          <t>Sofi</t>
+        </is>
+      </c>
+      <c r="C189" s="19" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D189" s="19" t="inlineStr">
+        <is>
+          <t>Santini / Relève</t>
+        </is>
+      </c>
+      <c r="E189" s="19" t="inlineStr">
+        <is>
+          <t>Fait les tables du resto, entend les affaires</t>
+        </is>
+      </c>
+      <c r="F189" s="19" t="inlineStr">
+        <is>
+          <t>Chez nous, même la sauce a des secrets.</t>
+        </is>
+      </c>
+      <c r="G189" s="19" t="inlineStr">
+        <is>
+          <t>Se voit confier un message qu’elle lit</t>
+        </is>
+      </c>
+      <c r="H189" s="19" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="18" t="inlineStr">
+        <is>
+          <t>Sophie Labbé</t>
+        </is>
+      </c>
+      <c r="B190" s="18" t="n"/>
+      <c r="C190" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D190" s="18" t="inlineStr">
+        <is>
+          <t>Aide / Université</t>
+        </is>
+      </c>
+      <c r="E190" s="18" t="inlineStr">
+        <is>
+          <t>Psychologue, collègue de Laurie</t>
+        </is>
+      </c>
+      <c r="F190" s="18" t="inlineStr">
+        <is>
+          <t>Assieds-toi. On a toute la séance.</t>
+        </is>
+      </c>
+      <c r="G190" s="18" t="inlineStr">
+        <is>
+          <t>Évalue les mineurs de l’affaire</t>
+        </is>
+      </c>
+      <c r="H190" s="18" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="19" t="inlineStr">
+        <is>
+          <t>Stéphane Bossé</t>
+        </is>
+      </c>
+      <c r="B191" s="19" t="inlineStr">
+        <is>
+          <t>Steph Patate</t>
+        </is>
+      </c>
+      <c r="C191" s="19" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D191" s="19" t="inlineStr">
+        <is>
+          <t>Commerce / Neutre</t>
+        </is>
+      </c>
+      <c r="E191" s="19" t="inlineStr">
+        <is>
+          <t>Son comptoir de Jacques-Cartier voit les fins de soirée</t>
+        </is>
+      </c>
+      <c r="F191" s="19" t="inlineStr">
+        <is>
+          <t>Une sauce à spaghetti, ça pardonne presque tout.</t>
+        </is>
+      </c>
+      <c r="G191" s="19" t="inlineStr">
+        <is>
+          <t>Nourrit l’équipe de Marie-Ève à crédit</t>
+        </is>
+      </c>
+      <c r="H191" s="19" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="18" t="inlineStr">
+        <is>
+          <t>Valentina Rojas</t>
+        </is>
+      </c>
+      <c r="B192" s="18" t="n"/>
+      <c r="C192" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D192" s="18" t="inlineStr">
+        <is>
+          <t>Commerces / Famille</t>
+        </is>
+      </c>
+      <c r="E192" s="18" t="inlineStr">
+        <is>
+          <t>Son étal apporte le soleil rue Bossé</t>
+        </is>
+      </c>
+      <c r="F192" s="18" t="inlineStr">
+        <is>
+          <t>Du piment, du courage, tout en vrac.</t>
+        </is>
+      </c>
+      <c r="G192" s="18" t="inlineStr">
+        <is>
+          <t>Traduit plus que des étiquettes</t>
+        </is>
+      </c>
+      <c r="H192" s="18" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="19" t="inlineStr">
+        <is>
+          <t>Vittorio Santini</t>
+        </is>
+      </c>
+      <c r="B193" s="19" t="inlineStr">
+        <is>
+          <t>Don Vittorio</t>
+        </is>
+      </c>
+      <c r="C193" s="19" t="inlineStr">
+        <is>
+          <t>Santini</t>
+        </is>
+      </c>
+      <c r="D193" s="19" t="inlineStr">
+        <is>
+          <t>Santini / Sommet</t>
+        </is>
+      </c>
+      <c r="E193" s="19" t="inlineStr">
+        <is>
+          <t>Patriarche, restauration et bars</t>
+        </is>
+      </c>
+      <c r="F193" s="19" t="inlineStr">
+        <is>
+          <t>La famille, c’est une entreprise avec des tombes.</t>
+        </is>
+      </c>
+      <c r="G193" s="19" t="inlineStr">
+        <is>
+          <t>Propose un deal à Samson</t>
+        </is>
+      </c>
+      <c r="H193" s="19" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
+        <is>
+          <t>William Lavoie</t>
+        </is>
+      </c>
+      <c r="B194" s="18" t="inlineStr">
+        <is>
+          <t>Will</t>
+        </is>
+      </c>
+      <c r="C194" s="18" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D194" s="18" t="inlineStr">
+        <is>
+          <t>Famille JP / Coloc</t>
+        </is>
+      </c>
+      <c r="E194" s="18" t="inlineStr">
+        <is>
+          <t>Nourrit la coloc et rapporte les ragots du bistro</t>
+        </is>
+      </c>
+      <c r="F194" s="18" t="inlineStr">
+        <is>
+          <t>Un bon bouillon répare les familles.</t>
+        </is>
+      </c>
+      <c r="G194" s="18" t="inlineStr">
+        <is>
+          <t>Fait le pont entre JP et Laurie</t>
+        </is>
+      </c>
+      <c r="H194" s="18" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="19" t="inlineStr">
+        <is>
+          <t>Éric Simard</t>
+        </is>
+      </c>
+      <c r="B195" s="19" t="inlineStr">
+        <is>
+          <t>Ti-Eric</t>
+        </is>
+      </c>
+      <c r="C195" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D195" s="19" t="inlineStr">
+        <is>
+          <t>Cégep / Naïf</t>
+        </is>
+      </c>
+      <c r="E195" s="19" t="inlineStr">
+        <is>
+          <t>Coloc de Justin Chen</t>
+        </is>
+      </c>
+      <c r="F195" s="19" t="inlineStr">
+        <is>
+          <t>Wô, c’tait pas supposé aller loin, ça.</t>
+        </is>
+      </c>
+      <c r="G195" s="19" t="inlineStr">
+        <is>
+          <t>Témoin gênant de la soirée Chen</t>
+        </is>
+      </c>
+      <c r="H195" s="19" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="inlineStr">
+        <is>
+          <t>Anthony Simard</t>
+        </is>
+      </c>
+      <c r="B196" s="18" t="inlineStr">
+        <is>
+          <t>Tony Steak</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D196" s="18" t="inlineStr">
+        <is>
+          <t>Boucherie / Famille</t>
+        </is>
+      </c>
+      <c r="E196" s="18" t="inlineStr">
+        <is>
+          <t>Le comptoir de Kénogami entend les commandes spéciales</t>
+        </is>
+      </c>
+      <c r="F196" s="18" t="inlineStr">
+        <is>
+          <t>Un bon steak se défend tout seul.</t>
+        </is>
+      </c>
+      <c r="G196" s="18" t="inlineStr">
+        <is>
+          <t>Sert un client qui paie en billets froissés</t>
+        </is>
+      </c>
+      <c r="H196" s="18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="19" t="inlineStr">
+        <is>
+          <t>Antoine Lefèvre</t>
+        </is>
+      </c>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>Le Français</t>
+        </is>
+      </c>
+      <c r="C197" s="19" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D197" s="19" t="inlineStr">
+        <is>
+          <t>ATM / Art</t>
+        </is>
+      </c>
+      <c r="E197" s="19" t="inlineStr">
+        <is>
+          <t>Ses rushes de fin de session traînent partout</t>
+        </is>
+      </c>
+      <c r="F197" s="19" t="inlineStr">
+        <is>
+          <t>La vérité, vingt-quatre images par seconde.</t>
+        </is>
+      </c>
+      <c r="G197" s="19" t="inlineStr">
+        <is>
+          <t>Doit rendre les images que Benoit exige</t>
+        </is>
+      </c>
+      <c r="H197" s="19" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="18" t="inlineStr">
+        <is>
+          <t>Audrey Lavoie</t>
+        </is>
+      </c>
+      <c r="B198" s="18" t="n"/>
+      <c r="C198" s="18" t="inlineStr">
+        <is>
+          <t>Industrie</t>
+        </is>
+      </c>
+      <c r="D198" s="18" t="inlineStr">
+        <is>
+          <t>Aluminerie / Syndiqué</t>
+        </is>
+      </c>
+      <c r="E198" s="18" t="inlineStr">
+        <is>
+          <t>Ses circuits éclairent des recoins stratégiques</t>
+        </is>
+      </c>
+      <c r="F198" s="18" t="inlineStr">
+        <is>
+          <t>Le courant suit le chemin qu’on lui donne.</t>
+        </is>
+      </c>
+      <c r="G198" s="18" t="inlineStr">
+        <is>
+          <t>Repère une ligne qui ne devrait pas exister</t>
+        </is>
+      </c>
+      <c r="H198" s="18" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="19" t="inlineStr">
+        <is>
+          <t>Benoit Larouche</t>
+        </is>
+      </c>
+      <c r="B199" s="19" t="n"/>
+      <c r="C199" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D199" s="19" t="inlineStr">
+        <is>
+          <t>ATM / École</t>
+        </is>
+      </c>
+      <c r="E199" s="19" t="inlineStr">
+        <is>
+          <t>Prof de cinéma d’Antoine</t>
+        </is>
+      </c>
+      <c r="F199" s="19" t="inlineStr">
+        <is>
+          <t>Le cinéma, c’est regarder deux fois.</t>
+        </is>
+      </c>
+      <c r="G199" s="19" t="inlineStr">
+        <is>
+          <t>Oblige Antoine à rendre les images</t>
+        </is>
+      </c>
+      <c r="H199" s="19" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="inlineStr">
+        <is>
+          <t>Camille Lefèvre</t>
+        </is>
+      </c>
+      <c r="B200" s="18" t="n"/>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D200" s="18" t="inlineStr">
+        <is>
+          <t>ATM / Art</t>
+        </is>
+      </c>
+      <c r="E200" s="18" t="inlineStr">
+        <is>
+          <t>Étudiante en comm, sœur d’Antoine</t>
+        </is>
+      </c>
+      <c r="F200" s="18" t="inlineStr">
+        <is>
+          <t>Une photo, ça trahit pas, ça révèle.</t>
+        </is>
+      </c>
+      <c r="G200" s="18" t="inlineStr">
+        <is>
+          <t>Tire les clichés qui manquent</t>
+        </is>
+      </c>
+      <c r="H200" s="18" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="19" t="inlineStr">
+        <is>
+          <t>Dany Aubin</t>
+        </is>
+      </c>
+      <c r="B201" s="19" t="n"/>
+      <c r="C201" s="19" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D201" s="19" t="inlineStr">
+        <is>
+          <t>Famille / Aubin</t>
+        </is>
+      </c>
+      <c r="E201" s="19" t="inlineStr">
+        <is>
+          <t>Soudeur, frère de Sam</t>
+        </is>
+      </c>
+      <c r="F201" s="19" t="inlineStr">
+        <is>
+          <t>La soudure ferme les trous, les familles non.</t>
+        </is>
+      </c>
+      <c r="G201" s="19" t="inlineStr">
+        <is>
+          <t>Descend à La Baie soutenir Sam</t>
+        </is>
+      </c>
+      <c r="H201" s="19" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="18" t="inlineStr">
+        <is>
+          <t>Fernand Lavoie</t>
+        </is>
+      </c>
+      <c r="B202" s="18" t="inlineStr">
+        <is>
+          <t>Ti-Fer</t>
+        </is>
+      </c>
+      <c r="C202" s="18" t="inlineStr">
+        <is>
+          <t>Industrie</t>
+        </is>
+      </c>
+      <c r="D202" s="18" t="inlineStr">
+        <is>
+          <t>Aluminerie / Syndiqué</t>
+        </is>
+      </c>
+      <c r="E202" s="18" t="inlineStr">
+        <is>
+          <t>Son jardin de la rue Davis nourrit tout Arvida</t>
+        </is>
+      </c>
+      <c r="F202" s="18" t="inlineStr">
+        <is>
+          <t>J’ai donné mon quota aux cuves.</t>
+        </is>
+      </c>
+      <c r="G202" s="18" t="inlineStr">
+        <is>
+          <t>Se souvient d’un camion de 1998</t>
+        </is>
+      </c>
+      <c r="H202" s="18" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="19" t="inlineStr">
+        <is>
+          <t>Gérald Tremblay</t>
+        </is>
+      </c>
+      <c r="B203" s="19" t="inlineStr">
+        <is>
+          <t>Le Syndic</t>
+        </is>
+      </c>
+      <c r="C203" s="19" t="inlineStr">
+        <is>
+          <t>Industrie</t>
+        </is>
+      </c>
+      <c r="D203" s="19" t="inlineStr">
+        <is>
+          <t>Aluminerie / Syndicat</t>
+        </is>
+      </c>
+      <c r="E203" s="19" t="inlineStr">
+        <is>
+          <t>Délégué syndical, collègue de Mathieu</t>
+        </is>
+      </c>
+      <c r="F203" s="19" t="inlineStr">
+        <is>
+          <t>La convention dit ça, et elle a raison.</t>
+        </is>
+      </c>
+      <c r="G203" s="19" t="inlineStr">
+        <is>
+          <t>Son grief devient un levier</t>
+        </is>
+      </c>
+      <c r="H203" s="19" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="18" t="inlineStr">
+        <is>
+          <t>Jade Boivin</t>
+        </is>
+      </c>
+      <c r="B204" s="18" t="n"/>
+      <c r="C204" s="18" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="D204" s="18" t="inlineStr">
+        <is>
+          <t>Aréna / Jeune</t>
+        </is>
+      </c>
+      <c r="E204" s="18" t="inlineStr">
+        <is>
+          <t>Ses figures peuplent la patinoire de Kénogami</t>
+        </is>
+      </c>
+      <c r="F204" s="18" t="inlineStr">
+        <is>
+          <t>Dans ma tête, la musique va plus vite que moé.</t>
+        </is>
+      </c>
+      <c r="G204" s="18" t="inlineStr">
+        <is>
+          <t>Voit la patinoire réservée à d’étranges heures</t>
+        </is>
+      </c>
+      <c r="H204" s="18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="19" t="inlineStr">
+        <is>
+          <t>Jean-Marc Fortin</t>
+        </is>
+      </c>
+      <c r="B205" s="19" t="n"/>
+      <c r="C205" s="19" t="inlineStr">
+        <is>
+          <t>Industrie</t>
+        </is>
+      </c>
+      <c r="D205" s="19" t="inlineStr">
+        <is>
+          <t>Aluminerie / Direction</t>
+        </is>
+      </c>
+      <c r="E205" s="19" t="inlineStr">
+        <is>
+          <t>Directeur d’usine à Arvida</t>
+        </is>
+      </c>
+      <c r="F205" s="19" t="inlineStr">
+        <is>
+          <t>Un four ne négocie pas.</t>
+        </is>
+      </c>
+      <c r="G205" s="19" t="inlineStr">
+        <is>
+          <t>Gère une saisie de conteneurs à l'usine</t>
+        </is>
+      </c>
+      <c r="H205" s="19" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="18" t="inlineStr">
+        <is>
+          <t>Karine Simard</t>
+        </is>
+      </c>
+      <c r="B206" s="18" t="inlineStr">
+        <is>
+          <t>Coach K</t>
+        </is>
+      </c>
+      <c r="C206" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D206" s="18" t="inlineStr">
+        <is>
+          <t>École / Sport</t>
+        </is>
+      </c>
+      <c r="E206" s="18" t="inlineStr">
+        <is>
+          <t>Sa piscine de Kénogami sort les jeunes des rues</t>
+        </is>
+      </c>
+      <c r="F206" s="18" t="inlineStr">
+        <is>
+          <t>Respire, expire, on recommence.</t>
+        </is>
+      </c>
+      <c r="G206" s="18" t="inlineStr">
+        <is>
+          <t>La finale de Léa tombe le pire soir</t>
+        </is>
+      </c>
+      <c r="H206" s="18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="19" t="inlineStr">
+        <is>
+          <t>Ludovic Larouche</t>
+        </is>
+      </c>
+      <c r="B207" s="19" t="inlineStr">
+        <is>
+          <t>Ludo</t>
+        </is>
+      </c>
+      <c r="C207" s="19" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D207" s="19" t="inlineStr">
+        <is>
+          <t>ATM / École</t>
+        </is>
+      </c>
+      <c r="E207" s="19" t="inlineStr">
+        <is>
+          <t>Monte sur les toits pour ses plans séquences</t>
+        </is>
+      </c>
+      <c r="F207" s="19" t="inlineStr">
+        <is>
+          <t>Attends… j’ai une meilleure idée.</t>
+        </is>
+      </c>
+      <c r="G207" s="19" t="inlineStr">
+        <is>
+          <t>Filme un convoi sans le vouloir</t>
+        </is>
+      </c>
+      <c r="H207" s="19" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="18" t="inlineStr">
+        <is>
+          <t>Léa Simard</t>
+        </is>
+      </c>
+      <c r="B208" s="18" t="n"/>
+      <c r="C208" s="18" t="inlineStr">
+        <is>
+          <t>Santé / Enseignement</t>
+        </is>
+      </c>
+      <c r="D208" s="18" t="inlineStr">
+        <is>
+          <t>École / Jeune</t>
+        </is>
+      </c>
+      <c r="E208" s="18" t="inlineStr">
+        <is>
+          <t>Ses entraînements de l’aube croisent les retours de nuit</t>
+        </is>
+      </c>
+      <c r="F208" s="18" t="inlineStr">
+        <is>
+          <t>Dans l’eau, personne me parle.</t>
+        </is>
+      </c>
+      <c r="G208" s="18" t="inlineStr">
+        <is>
+          <t>Part en finale pendant que tout bascule</t>
+        </is>
+      </c>
+      <c r="H208" s="18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="19" t="inlineStr">
+        <is>
+          <t>Marc Picard</t>
+        </is>
+      </c>
+      <c r="B209" s="19" t="inlineStr">
+        <is>
+          <t>L’Arpenteur</t>
+        </is>
+      </c>
+      <c r="C209" s="19" t="inlineStr">
+        <is>
+          <t>Neutre</t>
+        </is>
+      </c>
+      <c r="D209" s="19" t="inlineStr">
+        <is>
+          <t>Terrains / Neutre</t>
+        </is>
+      </c>
+      <c r="E209" s="19" t="inlineStr">
+        <is>
+          <t>Ses relevés du Vieux-Pont datent les glissements</t>
+        </is>
+      </c>
+      <c r="F209" s="19" t="inlineStr">
+        <is>
+          <t>La terre ment jamais, elle bouge juste.</t>
+        </is>
+      </c>
+      <c r="G209" s="19" t="inlineStr">
+        <is>
+          <t>Mesure le terrain que deux familles s’arrachent</t>
+        </is>
+      </c>
+      <c r="H209" s="19" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="18" t="inlineStr">
+        <is>
+          <t>Mathieu Lavoie</t>
+        </is>
+      </c>
+      <c r="B210" s="18" t="inlineStr">
+        <is>
+          <t>Mat</t>
+        </is>
+      </c>
+      <c r="C210" s="18" t="inlineStr">
+        <is>
+          <t>Industrie</t>
+        </is>
+      </c>
+      <c r="D210" s="18" t="inlineStr">
+        <is>
+          <t>Aluminerie / Syndiqué</t>
+        </is>
+      </c>
+      <c r="E210" s="18" t="inlineStr">
+        <is>
+          <t>Son poste de contrôle voit l’usine et le quai</t>
+        </is>
+      </c>
+      <c r="F210" s="18" t="inlineStr">
+        <is>
+          <t>Les fours dorment jamais, moé non plus.</t>
+        </is>
+      </c>
+      <c r="G210" s="18" t="inlineStr">
+        <is>
+          <t>Passe l’info à JP sans le savoir</t>
+        </is>
+      </c>
+      <c r="H210" s="18" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="19" t="inlineStr">
+        <is>
+          <t>Mélissa Harvey</t>
+        </is>
+      </c>
+      <c r="B211" s="19" t="n"/>
+      <c r="C211" s="19" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D211" s="19" t="inlineStr">
+        <is>
+          <t>ATM / Art</t>
+        </is>
+      </c>
+      <c r="E211" s="19" t="inlineStr">
+        <is>
+          <t>Étudiante ATM, nièce de François</t>
+        </is>
+      </c>
+      <c r="F211" s="19" t="inlineStr">
+        <is>
+          <t>Je filme tout, même ce qui faut pas.</t>
+        </is>
+      </c>
+      <c r="G211" s="19" t="inlineStr">
+        <is>
+          <t>Sa perche capte une confession</t>
+        </is>
+      </c>
+      <c r="H211" s="19" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="18" t="inlineStr">
+        <is>
+          <t>Nancy Simard</t>
+        </is>
+      </c>
+      <c r="B212" s="18" t="inlineStr">
+        <is>
+          <t>Nancy Ciseaux</t>
+        </is>
+      </c>
+      <c r="C212" s="18" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="D212" s="18" t="inlineStr">
+        <is>
+          <t>Salon / Voisinage</t>
+        </is>
+      </c>
+      <c r="E212" s="18" t="inlineStr">
+        <is>
+          <t>Son salon de Saint-Hubert sait tout Kénogami</t>
+        </is>
+      </c>
+      <c r="F212" s="18" t="inlineStr">
+        <is>
+          <t>Une coupe, c’est vingt minutes de thérapie.</t>
+        </is>
+      </c>
+      <c r="G212" s="18" t="inlineStr">
+        <is>
+          <t>Coupe les cheveux d’un homme pressé de repartir</t>
+        </is>
+      </c>
+      <c r="H212" s="18" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="19" t="inlineStr">
+        <is>
+          <t>Nicolas Gagné</t>
+        </is>
+      </c>
+      <c r="B213" s="19" t="n"/>
+      <c r="C213" s="19" t="inlineStr">
+        <is>
+          <t>Industrie</t>
+        </is>
+      </c>
+      <c r="D213" s="19" t="inlineStr">
+        <is>
+          <t>Aluminerie / Syndiqué</t>
+        </is>
+      </c>
+      <c r="E213" s="19" t="inlineStr">
+        <is>
+          <t>Technicien, collègue de Mathieu</t>
+        </is>
+      </c>
+      <c r="F213" s="19" t="inlineStr">
+        <is>
+          <t>Le métal pardonne, le contremaître non.</t>
+        </is>
+      </c>
+      <c r="G213" s="19" t="inlineStr">
+        <is>
+          <t>Repère des cargaisons marquées</t>
+        </is>
+      </c>
+      <c r="H213" s="19" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="18" t="inlineStr">
+        <is>
+          <t>Sam Aubin</t>
+        </is>
+      </c>
+      <c r="B214" s="18" t="inlineStr">
+        <is>
+          <t>Ink</t>
+        </is>
+      </c>
+      <c r="C214" s="18" t="inlineStr">
+        <is>
+          <t>Média / Art</t>
+        </is>
+      </c>
+      <c r="D214" s="18" t="inlineStr">
+        <is>
+          <t>Art / Encre</t>
+        </is>
+      </c>
+      <c r="E214" s="18" t="inlineStr">
+        <is>
+          <t>Son studio de Harvey tatoue Jonquière en confidence</t>
+        </is>
+      </c>
+      <c r="F214" s="18" t="inlineStr">
+        <is>
+          <t>Ça va faire mal. Beau, mais mal.</t>
+        </is>
+      </c>
+      <c r="G214" s="18" t="inlineStr">
+        <is>
+          <t>Tatoue le motif qui devient une pièce à dossier</t>
+        </is>
+      </c>
+      <c r="H214" s="18" t="n">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H214"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/base_personnages_fictifs.xlsx
+++ b/base_personnages_fictifs.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Personnages'!$A$1:$Q$214</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Narration'!$A$1:$I$214</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Relations'!$A$1:$H$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Relations'!$A$1:$H$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -17467,7 +17467,7 @@
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>• Relations       : extraction partielle de Parenté dans la feuille Relations ; source data/relations.csv.</t>
+          <t>• Relations       : extraction de Parenté (familles, cousinages, oncles/tantes, grand-parents, parrainage, travail, colocation) dans la feuille Relations ; source data/relations.csv.</t>
         </is>
       </c>
     </row>
@@ -26862,7 +26862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27308,22 +27308,22 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>fratrie</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>P047</t>
+          <t>P117</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
-          <t>Éric Boucher</t>
+          <t>Normand Boucher</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t>P047</t>
+          <t>P117</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -27333,19 +27333,19 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>Fils de Fernande — frère de Dévon</t>
+          <t>Cousin de Dévon et Éric Boucher</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Kevin Bérubé</t>
+          <t>Dévon Boucher</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -27355,17 +27355,17 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>P053</t>
+          <t>P047</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>Jessy Bérubé</t>
+          <t>Éric Boucher</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>P053</t>
+          <t>P047</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -27375,39 +27375,39 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t>Fils de Lucie Bérubé — frère de Kevin</t>
+          <t>Fils de Fernande — frère de Dévon</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>Yvan Truchon</t>
+          <t>Kevin Bérubé</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>P062</t>
+          <t>P120</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>Gisèle Truchon</t>
+          <t>Big Jo Bérubé</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t>P062</t>
+          <t>P120</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -27417,39 +27417,39 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>Conjointe d’Yvan Truchon</t>
+          <t>Cousin de Kevin et Jessy Bérubé — travaille pour Dévon</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>Yvan Truchon</t>
+          <t>Kevin Bérubé</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>P178</t>
+          <t>P053</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>Mathis Truchon</t>
+          <t>Jessy Bérubé</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>P178</t>
+          <t>P053</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -27459,39 +27459,39 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Yvan Truchon et Gisèle</t>
+          <t>Fils de Lucie Bérubé — frère de Kevin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>Sylvie Gagnon</t>
+          <t>Yvan Truchon</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>ex_conjoint_de</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>P061</t>
+          <t>P062</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>Bertrand Gagnon</t>
+          <t>Gisèle Truchon</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>P061</t>
+          <t>P062</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -27501,39 +27501,39 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>Ex-mari de Sylvie Gagnon</t>
+          <t>Conjointe d’Yvan Truchon</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Ahmed Benali</t>
+          <t>Yvan Truchon</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>P041</t>
+          <t>P178</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>Nadia Benali</t>
+          <t>Mathis Truchon</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>P041</t>
+          <t>P178</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -27543,39 +27543,39 @@
       </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t>Épouse d’Ahmed Benali</t>
+          <t>Fils d’Yvan Truchon et Gisèle</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>Ahmed Benali</t>
+          <t>Sylvie Gagnon</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>ex_conjoint_de</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>P103</t>
+          <t>P061</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>Hassan Benali</t>
+          <t>Bertrand Gagnon</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t>P103</t>
+          <t>P061</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -27585,7 +27585,7 @@
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Ahmed et Nadia Benali</t>
+          <t>Ex-mari de Sylvie Gagnon</t>
         </is>
       </c>
     </row>
@@ -27602,22 +27602,22 @@
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>P172</t>
+          <t>P041</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>Nour Benali</t>
+          <t>Nadia Benali</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>P172</t>
+          <t>P041</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -27627,39 +27627,39 @@
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t>Fille d’Ahmed et Nadia Benali — sœur d’Hassan</t>
+          <t>Épouse d’Ahmed Benali</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>Mélanie Dubé</t>
+          <t>Ahmed Benali</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>collegue_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>P085</t>
+          <t>P103</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>Véronique Côté</t>
+          <t>Hassan Benali</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t>P085</t>
+          <t>P103</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -27669,39 +27669,39 @@
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t>Collègue de Mélanie Dubé</t>
+          <t>Fils d’Ahmed et Nadia Benali</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Mélanie Dubé</t>
+          <t>Ahmed Benali</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>fratrie</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>P057</t>
+          <t>P172</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>Carl Dubé</t>
+          <t>Nour Benali</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>P057</t>
+          <t>P172</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -27711,39 +27711,39 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>Frère de Mélanie Dubé</t>
+          <t>Fille d’Ahmed et Nadia Benali — sœur d’Hassan</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>Dave Cloutier</t>
+          <t>Mélanie Dubé</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>fratrie</t>
+          <t>collegue_de</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>P171</t>
+          <t>P085</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>Léo Cloutier</t>
+          <t>Véronique Côté</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>P171</t>
+          <t>P085</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -27753,39 +27753,39 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>Fils de Manon Cloutier — petit frère de Dave</t>
+          <t>Collègue de Mélanie Dubé</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Ginette Roy</t>
+          <t>Mélanie Dubé</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>collegue_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>P089</t>
+          <t>P057</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>Lise Blackburn</t>
+          <t>Carl Dubé</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>P089</t>
+          <t>P057</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -27795,39 +27795,39 @@
       </c>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t>Collègue de Ginette Roy</t>
+          <t>Frère de Mélanie Dubé</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>Ginette Roy</t>
+          <t>Dave Cloutier</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>P050</t>
+          <t>P171</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>Réjean Roy</t>
+          <t>Léo Cloutier</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>P050</t>
+          <t>P171</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -27837,39 +27837,39 @@
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>Mari de Ginette Roy</t>
+          <t>Fils de Manon Cloutier — petit frère de Dave</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Steve Langlois</t>
+          <t>Ginette Roy</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>collegue_de</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>P060</t>
+          <t>P089</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>Josée Langlois</t>
+          <t>Lise Blackburn</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>P060</t>
+          <t>P089</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -27879,19 +27879,19 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
-          <t>Épouse de Steve Langlois</t>
+          <t>Collègue de Ginette Roy</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>Anik Desrosiers</t>
+          <t>Ginette Roy</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -27901,17 +27901,17 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>P043</t>
+          <t>P050</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>Marc-André Simard</t>
+          <t>Réjean Roy</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>P043</t>
+          <t>P050</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -27921,39 +27921,39 @@
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t>Conjoint d’Anik Desrosiers</t>
+          <t>Mari de Ginette Roy</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>P020</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>Antoine Lefèvre</t>
+          <t>Steve Langlois</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>fratrie</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>P065</t>
+          <t>P060</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>Camille Lefèvre</t>
+          <t>Josée Langlois</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>P065</t>
+          <t>P060</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -27963,19 +27963,19 @@
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
-          <t>Sœur d’Antoine Lefèvre</t>
+          <t>Épouse de Steve Langlois</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
         <is>
-          <t>P021</t>
+          <t>P019</t>
         </is>
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>Johanne Tremblay</t>
+          <t>Anik Desrosiers</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -27985,17 +27985,17 @@
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>P067</t>
+          <t>P043</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>Sylvain Gagné</t>
+          <t>Marc-André Simard</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
         <is>
-          <t>P067</t>
+          <t>P043</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -28005,39 +28005,39 @@
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t>Conjoint de Johanne Tremblay</t>
+          <t>Conjoint d’Anik Desrosiers</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P019</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>Lucien Lacroix</t>
+          <t>Anik Desrosiers</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>fratrie</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>P054</t>
+          <t>P149</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>Thérèse Lacroix</t>
+          <t>Karine Desrosiers</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t>P054</t>
+          <t>P149</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -28047,19 +28047,19 @@
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
-          <t>Sœur de Lucien Lacroix</t>
+          <t>Cousine d’Anik Desrosiers</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>Sam Aubin</t>
+          <t>Antoine Lefèvre</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -28069,17 +28069,17 @@
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>P066</t>
+          <t>P065</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>Dany Aubin</t>
+          <t>Camille Lefèvre</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
         <is>
-          <t>P066</t>
+          <t>P065</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -28089,39 +28089,39 @@
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>Frère de Sam Aubin</t>
+          <t>Sœur d’Antoine Lefèvre</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P021</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>Karine Gagnon</t>
+          <t>Johanne Tremblay</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>fratrie</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>P052</t>
+          <t>P067</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>Rock Gagnon</t>
+          <t>Sylvain Gagné</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
         <is>
-          <t>P052</t>
+          <t>P067</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -28131,39 +28131,39 @@
       </c>
       <c r="H30" s="21" t="inlineStr">
         <is>
-          <t>Fils de Thérèse Gagnon — frère de Karine</t>
+          <t>Conjoint de Johanne Tremblay</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>Justin Chen</t>
+          <t>Lucien Lacroix</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>colocataire_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>P100</t>
+          <t>P054</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
-          <t>Éric Simard</t>
+          <t>Thérèse Lacroix</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
         <is>
-          <t>P100</t>
+          <t>P054</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -28173,39 +28173,39 @@
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
-          <t>Colocataire de Justin Chen</t>
+          <t>Sœur de Lucien Lacroix</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>Mireille Joseph</t>
+          <t>Lucien Lacroix</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>P056</t>
+          <t>P138</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
-          <t>Samuel Joseph</t>
+          <t>Armand Lacroix</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t>P056</t>
+          <t>P138</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -28215,39 +28215,39 @@
       </c>
       <c r="H32" s="21" t="inlineStr">
         <is>
-          <t>Fils de Mireille Joseph</t>
+          <t>Neveu de Lucien et Thérèse Lacroix</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>Fatima Al-Hassan</t>
+          <t>Sam Aubin</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>P048</t>
+          <t>P066</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
-          <t>Karim Al-Hassan</t>
+          <t>Dany Aubin</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
         <is>
-          <t>P048</t>
+          <t>P066</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -28257,39 +28257,39 @@
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
-          <t>Époux de Fatima Al-Hassan</t>
+          <t>Frère de Sam Aubin</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>Patrice Dubois</t>
+          <t>Karine Gagnon</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>fratrie</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>P058</t>
+          <t>P111</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>Nancy Dubois</t>
+          <t>Bobby Gagnon</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
         <is>
-          <t>P058</t>
+          <t>P111</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -28299,39 +28299,39 @@
       </c>
       <c r="H34" s="21" t="inlineStr">
         <is>
-          <t>Sœur de Patrice Dubois</t>
+          <t>Cousin de Karine et Rock Gagnon</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="21" t="inlineStr">
         <is>
-          <t>P033</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>Robert Lavoie</t>
+          <t>Karine Gagnon</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>P052</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
-          <t>Jean-Philippe Lavoie</t>
+          <t>Rock Gagnon</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>P052</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -28341,39 +28341,39 @@
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t>Fils de Robert et Diane</t>
+          <t>Fils de Thérèse Gagnon — frère de Karine</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
         <is>
-          <t>P033</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>Robert Lavoie</t>
+          <t>Justin Chen</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>colocataire_de</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>P173</t>
+          <t>P100</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>Alexandre Lavoie</t>
+          <t>Éric Simard</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>P173</t>
+          <t>P100</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -28383,19 +28383,19 @@
       </c>
       <c r="H36" s="21" t="inlineStr">
         <is>
-          <t>Fils cadet de Robert et Diane — petit frère de JP</t>
+          <t>Colocataire de Justin Chen</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="inlineStr">
         <is>
-          <t>P034</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>Diane Tremblay</t>
+          <t>Mireille Joseph</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
@@ -28405,17 +28405,17 @@
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>P056</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>Jean-Philippe Lavoie</t>
+          <t>Samuel Joseph</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>P056</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -28425,39 +28425,39 @@
       </c>
       <c r="H37" s="21" t="inlineStr">
         <is>
-          <t>Fils de Robert et Diane</t>
+          <t>Fils de Mireille Joseph</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
         <is>
-          <t>P034</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>Diane Tremblay</t>
+          <t>Fatima Al-Hassan</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>P173</t>
+          <t>P048</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>Alexandre Lavoie</t>
+          <t>Karim Al-Hassan</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>P173</t>
+          <t>P048</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -28467,39 +28467,39 @@
       </c>
       <c r="H38" s="21" t="inlineStr">
         <is>
-          <t>Fils cadet de Robert et Diane — petit frère de JP</t>
+          <t>Époux de Fatima Al-Hassan</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
         <is>
-          <t>P035</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>Mathieu Lavoie</t>
+          <t>Patrice Dubois</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>collegue_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>P094</t>
+          <t>P058</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
-          <t>Nicolas Gagné</t>
+          <t>Nancy Dubois</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
         <is>
-          <t>P094</t>
+          <t>P058</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
@@ -28509,39 +28509,39 @@
       </c>
       <c r="H39" s="21" t="inlineStr">
         <is>
-          <t>Collègue de Mathieu Lavoie</t>
+          <t>Sœur de Patrice Dubois</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>P035</t>
+          <t>P032</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>Mathieu Lavoie</t>
+          <t>Gilles Bergeron</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>collegue_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>P137</t>
+          <t>P049</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>Gérald Tremblay</t>
+          <t>Isabelle Bergeron</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>P137</t>
+          <t>P049</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
@@ -28551,39 +28551,39 @@
       </c>
       <c r="H40" s="21" t="inlineStr">
         <is>
-          <t>Collègue de Mathieu Lavoie</t>
+          <t>Fille de Gilles Bergeron</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>P036</t>
+          <t>P033</t>
         </is>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>Laurie Lavoie</t>
+          <t>Robert Lavoie</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>collegue_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>P104</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>Sophie Labbé</t>
+          <t>Jean-Philippe Lavoie</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
         <is>
-          <t>P104</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="G41" s="21" t="inlineStr">
@@ -28593,19 +28593,19 @@
       </c>
       <c r="H41" s="21" t="inlineStr">
         <is>
-          <t>Célibataire — collègue de Laurie Lavoie</t>
+          <t>Fils de Robert et Diane</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
-          <t>P037</t>
+          <t>P033</t>
         </is>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>Gérard Lapointe</t>
+          <t>Robert Lavoie</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
@@ -28615,17 +28615,17 @@
       </c>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P173</t>
         </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>Marco Lapointe</t>
+          <t>Alexandre Lavoie</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P173</t>
         </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
@@ -28635,19 +28635,19 @@
       </c>
       <c r="H42" s="21" t="inlineStr">
         <is>
-          <t>Fils de Gérard et Monique</t>
+          <t>Fils cadet de Robert et Diane — petit frère de JP</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
-          <t>P038</t>
+          <t>P034</t>
         </is>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>Monique Bouchard</t>
+          <t>Diane Tremblay</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
@@ -28657,17 +28657,17 @@
       </c>
       <c r="D43" s="21" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
-          <t>Marco Lapointe</t>
+          <t>Jean-Philippe Lavoie</t>
         </is>
       </c>
       <c r="F43" s="21" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="G43" s="21" t="inlineStr">
@@ -28677,19 +28677,19 @@
       </c>
       <c r="H43" s="21" t="inlineStr">
         <is>
-          <t>Fils de Gérard et Monique</t>
+          <t>Fils de Robert et Diane</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
         <is>
-          <t>P039</t>
+          <t>P034</t>
         </is>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>Patrick Lapointe</t>
+          <t>Diane Tremblay</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
@@ -28699,17 +28699,17 @@
       </c>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t>P179</t>
+          <t>P173</t>
         </is>
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
-          <t>Océane Lapointe</t>
+          <t>Alexandre Lavoie</t>
         </is>
       </c>
       <c r="F44" s="21" t="inlineStr">
         <is>
-          <t>P179</t>
+          <t>P173</t>
         </is>
       </c>
       <c r="G44" s="21" t="inlineStr">
@@ -28719,39 +28719,39 @@
       </c>
       <c r="H44" s="21" t="inlineStr">
         <is>
-          <t>Fille de Patrick Lapointe — nièce de Marco</t>
+          <t>Fils cadet de Robert et Diane — petit frère de JP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="inlineStr">
         <is>
-          <t>P041</t>
+          <t>P035</t>
         </is>
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>Nadia Benali</t>
+          <t>Mathieu Lavoie</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>collegue_de</t>
         </is>
       </c>
       <c r="D45" s="21" t="inlineStr">
         <is>
-          <t>P103</t>
+          <t>P094</t>
         </is>
       </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
-          <t>Hassan Benali</t>
+          <t>Nicolas Gagné</t>
         </is>
       </c>
       <c r="F45" s="21" t="inlineStr">
         <is>
-          <t>P103</t>
+          <t>P094</t>
         </is>
       </c>
       <c r="G45" s="21" t="inlineStr">
@@ -28761,39 +28761,39 @@
       </c>
       <c r="H45" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Ahmed et Nadia Benali</t>
+          <t>Collègue de Mathieu Lavoie</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="21" t="inlineStr">
         <is>
-          <t>P041</t>
+          <t>P035</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Nadia Benali</t>
+          <t>Mathieu Lavoie</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>collegue_de</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
         <is>
-          <t>P172</t>
+          <t>P137</t>
         </is>
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
-          <t>Nour Benali</t>
+          <t>Gérald Tremblay</t>
         </is>
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>P172</t>
+          <t>P137</t>
         </is>
       </c>
       <c r="G46" s="21" t="inlineStr">
@@ -28803,39 +28803,39 @@
       </c>
       <c r="H46" s="21" t="inlineStr">
         <is>
-          <t>Fille d’Ahmed et Nadia Benali — sœur d’Hassan</t>
+          <t>Collègue de Mathieu Lavoie</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>P042</t>
+          <t>P036</t>
         </is>
       </c>
       <c r="B47" s="21" t="inlineStr">
         <is>
-          <t>Sonia Tremblay</t>
+          <t>Laurie Lavoie</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>collegue_de</t>
         </is>
       </c>
       <c r="D47" s="21" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P104</t>
         </is>
       </c>
       <c r="E47" s="21" t="inlineStr">
         <is>
-          <t>Alex Tremblay</t>
+          <t>Sophie Labbé</t>
         </is>
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P104</t>
         </is>
       </c>
       <c r="G47" s="21" t="inlineStr">
@@ -28845,19 +28845,19 @@
       </c>
       <c r="H47" s="21" t="inlineStr">
         <is>
-          <t>Fils de Sonia</t>
+          <t>Célibataire — collègue de Laurie Lavoie</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="21" t="inlineStr">
         <is>
-          <t>P044</t>
+          <t>P037</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>Gaétan Lavoie</t>
+          <t>Gérard Lapointe</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
@@ -28867,17 +28867,17 @@
       </c>
       <c r="D48" s="21" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>Chantal Lavoie</t>
+          <t>Marco Lapointe</t>
         </is>
       </c>
       <c r="F48" s="21" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="G48" s="21" t="inlineStr">
@@ -28887,19 +28887,19 @@
       </c>
       <c r="H48" s="21" t="inlineStr">
         <is>
-          <t>Fille de Gaétan</t>
+          <t>Fils de Gérard et Monique</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
-          <t>P045</t>
+          <t>P038</t>
         </is>
       </c>
       <c r="B49" s="21" t="inlineStr">
         <is>
-          <t>Nathalie Bouchard</t>
+          <t>Monique Bouchard</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
@@ -28909,17 +28909,17 @@
       </c>
       <c r="D49" s="21" t="inlineStr">
         <is>
-          <t>P031</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
-          <t>Chloé Bouchard</t>
+          <t>Marco Lapointe</t>
         </is>
       </c>
       <c r="F49" s="21" t="inlineStr">
         <is>
-          <t>P031</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="G49" s="21" t="inlineStr">
@@ -28929,19 +28929,19 @@
       </c>
       <c r="H49" s="21" t="inlineStr">
         <is>
-          <t>Fille de Nathalie</t>
+          <t>Fils de Gérard et Monique</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>P046</t>
+          <t>P039</t>
         </is>
       </c>
       <c r="B50" s="21" t="inlineStr">
         <is>
-          <t>Manon Cloutier</t>
+          <t>Patrick Lapointe</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
@@ -28951,17 +28951,17 @@
       </c>
       <c r="D50" s="21" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P179</t>
         </is>
       </c>
       <c r="E50" s="21" t="inlineStr">
         <is>
-          <t>Dave Cloutier</t>
+          <t>Océane Lapointe</t>
         </is>
       </c>
       <c r="F50" s="21" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P179</t>
         </is>
       </c>
       <c r="G50" s="21" t="inlineStr">
@@ -28971,19 +28971,19 @@
       </c>
       <c r="H50" s="21" t="inlineStr">
         <is>
-          <t>Fils de Manon</t>
+          <t>Fille de Patrick Lapointe — nièce de Marco</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="21" t="inlineStr">
         <is>
-          <t>P046</t>
+          <t>P041</t>
         </is>
       </c>
       <c r="B51" s="21" t="inlineStr">
         <is>
-          <t>Manon Cloutier</t>
+          <t>Nadia Benali</t>
         </is>
       </c>
       <c r="C51" s="21" t="inlineStr">
@@ -28993,17 +28993,17 @@
       </c>
       <c r="D51" s="21" t="inlineStr">
         <is>
-          <t>P171</t>
+          <t>P103</t>
         </is>
       </c>
       <c r="E51" s="21" t="inlineStr">
         <is>
-          <t>Léo Cloutier</t>
+          <t>Hassan Benali</t>
         </is>
       </c>
       <c r="F51" s="21" t="inlineStr">
         <is>
-          <t>P171</t>
+          <t>P103</t>
         </is>
       </c>
       <c r="G51" s="21" t="inlineStr">
@@ -29013,19 +29013,19 @@
       </c>
       <c r="H51" s="21" t="inlineStr">
         <is>
-          <t>Fils de Manon Cloutier — petit frère de Dave</t>
+          <t>Fils d’Ahmed et Nadia Benali</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>P049</t>
+          <t>P041</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
         <is>
-          <t>Isabelle Bergeron</t>
+          <t>Nadia Benali</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
@@ -29035,17 +29035,17 @@
       </c>
       <c r="D52" s="21" t="inlineStr">
         <is>
-          <t>P176</t>
+          <t>P172</t>
         </is>
       </c>
       <c r="E52" s="21" t="inlineStr">
         <is>
-          <t>Thomas Bergeron</t>
+          <t>Nour Benali</t>
         </is>
       </c>
       <c r="F52" s="21" t="inlineStr">
         <is>
-          <t>P176</t>
+          <t>P172</t>
         </is>
       </c>
       <c r="G52" s="21" t="inlineStr">
@@ -29055,19 +29055,19 @@
       </c>
       <c r="H52" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Isabelle Bergeron — petit-fils de Gilles</t>
+          <t>Fille d’Ahmed et Nadia Benali — sœur d’Hassan</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>P055</t>
+          <t>P042</t>
         </is>
       </c>
       <c r="B53" s="21" t="inlineStr">
         <is>
-          <t>Claude Lavoie</t>
+          <t>Sonia Tremblay</t>
         </is>
       </c>
       <c r="C53" s="21" t="inlineStr">
@@ -29077,17 +29077,17 @@
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>P023</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>Michel Lavoie</t>
+          <t>Alex Tremblay</t>
         </is>
       </c>
       <c r="F53" s="21" t="inlineStr">
         <is>
-          <t>P023</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="G53" s="21" t="inlineStr">
@@ -29097,19 +29097,19 @@
       </c>
       <c r="H53" s="21" t="inlineStr">
         <is>
-          <t>Fils de Claude</t>
+          <t>Fils de Sonia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>P059</t>
+          <t>P044</t>
         </is>
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>Hélène Chicoine</t>
+          <t>Gaétan Lavoie</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
@@ -29119,17 +29119,17 @@
       </c>
       <c r="D54" s="21" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="E54" s="21" t="inlineStr">
         <is>
-          <t>Réal Chicoine</t>
+          <t>Chantal Lavoie</t>
         </is>
       </c>
       <c r="F54" s="21" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="G54" s="21" t="inlineStr">
@@ -29139,19 +29139,19 @@
       </c>
       <c r="H54" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Hélène</t>
+          <t>Fille de Gaétan</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="21" t="inlineStr">
         <is>
-          <t>P062</t>
+          <t>P045</t>
         </is>
       </c>
       <c r="B55" s="21" t="inlineStr">
         <is>
-          <t>Gisèle Truchon</t>
+          <t>Nathalie Bouchard</t>
         </is>
       </c>
       <c r="C55" s="21" t="inlineStr">
@@ -29161,17 +29161,17 @@
       </c>
       <c r="D55" s="21" t="inlineStr">
         <is>
-          <t>P178</t>
+          <t>P031</t>
         </is>
       </c>
       <c r="E55" s="21" t="inlineStr">
         <is>
-          <t>Mathis Truchon</t>
+          <t>Chloé Bouchard</t>
         </is>
       </c>
       <c r="F55" s="21" t="inlineStr">
         <is>
-          <t>P178</t>
+          <t>P031</t>
         </is>
       </c>
       <c r="G55" s="21" t="inlineStr">
@@ -29181,19 +29181,19 @@
       </c>
       <c r="H55" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Yvan Truchon et Gisèle</t>
+          <t>Fille de Nathalie</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>P063</t>
+          <t>P046</t>
         </is>
       </c>
       <c r="B56" s="21" t="inlineStr">
         <is>
-          <t>Mei Chen</t>
+          <t>Manon Cloutier</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
@@ -29203,17 +29203,17 @@
       </c>
       <c r="D56" s="21" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="E56" s="21" t="inlineStr">
         <is>
-          <t>Justin Chen</t>
+          <t>Dave Cloutier</t>
         </is>
       </c>
       <c r="F56" s="21" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="G56" s="21" t="inlineStr">
@@ -29223,39 +29223,39 @@
       </c>
       <c r="H56" s="21" t="inlineStr">
         <is>
-          <t>Fils de Mei</t>
+          <t>Fils de Manon</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>P064</t>
+          <t>P046</t>
         </is>
       </c>
       <c r="B57" s="21" t="inlineStr">
         <is>
-          <t>Catherine Samson</t>
+          <t>Manon Cloutier</t>
         </is>
       </c>
       <c r="C57" s="21" t="inlineStr">
         <is>
-          <t>collegue_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D57" s="21" t="inlineStr">
         <is>
-          <t>P127</t>
+          <t>P171</t>
         </is>
       </c>
       <c r="E57" s="21" t="inlineStr">
         <is>
-          <t>Louise Villeneuve</t>
+          <t>Léo Cloutier</t>
         </is>
       </c>
       <c r="F57" s="21" t="inlineStr">
         <is>
-          <t>P127</t>
+          <t>P171</t>
         </is>
       </c>
       <c r="G57" s="21" t="inlineStr">
@@ -29265,39 +29265,39 @@
       </c>
       <c r="H57" s="21" t="inlineStr">
         <is>
-          <t>Collègue de Catherine Samson</t>
+          <t>Fils de Manon Cloutier — petit frère de Dave</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>P068</t>
+          <t>P047</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>Fernand Côté</t>
+          <t>Éric Boucher</t>
         </is>
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
         <is>
-          <t>P069</t>
+          <t>P117</t>
         </is>
       </c>
       <c r="E58" s="21" t="inlineStr">
         <is>
-          <t>Lucie Côté</t>
+          <t>Normand Boucher</t>
         </is>
       </c>
       <c r="F58" s="21" t="inlineStr">
         <is>
-          <t>P068</t>
+          <t>P117</t>
         </is>
       </c>
       <c r="G58" s="21" t="inlineStr">
@@ -29307,39 +29307,39 @@
       </c>
       <c r="H58" s="21" t="inlineStr">
         <is>
-          <t>Époux de Lucie Côté</t>
+          <t>Cousin de Dévon et Éric Boucher</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>P070</t>
+          <t>P049</t>
         </is>
       </c>
       <c r="B59" s="21" t="inlineStr">
         <is>
-          <t>Yves Fortin</t>
+          <t>Isabelle Bergeron</t>
         </is>
       </c>
       <c r="C59" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D59" s="21" t="inlineStr">
         <is>
-          <t>P071</t>
+          <t>P176</t>
         </is>
       </c>
       <c r="E59" s="21" t="inlineStr">
         <is>
-          <t>Pauline Fortin</t>
+          <t>Thomas Bergeron</t>
         </is>
       </c>
       <c r="F59" s="21" t="inlineStr">
         <is>
-          <t>P070</t>
+          <t>P176</t>
         </is>
       </c>
       <c r="G59" s="21" t="inlineStr">
@@ -29349,39 +29349,39 @@
       </c>
       <c r="H59" s="21" t="inlineStr">
         <is>
-          <t>Époux de Pauline Fortin</t>
+          <t>Fils d’Isabelle Bergeron — petit-fils de Gilles</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>P070</t>
+          <t>P052</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
-          <t>Yves Fortin</t>
+          <t>Rock Gagnon</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
         <is>
-          <t>P101</t>
+          <t>P111</t>
         </is>
       </c>
       <c r="E60" s="21" t="inlineStr">
         <is>
-          <t>Tommy Fortin</t>
+          <t>Bobby Gagnon</t>
         </is>
       </c>
       <c r="F60" s="21" t="inlineStr">
         <is>
-          <t>P101</t>
+          <t>P111</t>
         </is>
       </c>
       <c r="G60" s="21" t="inlineStr">
@@ -29391,39 +29391,39 @@
       </c>
       <c r="H60" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Yves et Pauline Fortin</t>
+          <t>Cousin de Karine et Rock Gagnon</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>P071</t>
+          <t>P053</t>
         </is>
       </c>
       <c r="B61" s="21" t="inlineStr">
         <is>
-          <t>Pauline Fortin</t>
+          <t>Jessy Bérubé</t>
         </is>
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D61" s="21" t="inlineStr">
         <is>
-          <t>P101</t>
+          <t>P120</t>
         </is>
       </c>
       <c r="E61" s="21" t="inlineStr">
         <is>
-          <t>Tommy Fortin</t>
+          <t>Big Jo Bérubé</t>
         </is>
       </c>
       <c r="F61" s="21" t="inlineStr">
         <is>
-          <t>P101</t>
+          <t>P120</t>
         </is>
       </c>
       <c r="G61" s="21" t="inlineStr">
@@ -29433,39 +29433,39 @@
       </c>
       <c r="H61" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Yves et Pauline Fortin</t>
+          <t>Cousin de Kevin et Jessy Bérubé — travaille pour Dévon</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>P072</t>
+          <t>P054</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>Hugo Pelletier</t>
+          <t>Thérèse Lacroix</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
         <is>
-          <t>P073</t>
+          <t>P138</t>
         </is>
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
-          <t>Sarah Pelletier</t>
+          <t>Armand Lacroix</t>
         </is>
       </c>
       <c r="F62" s="21" t="inlineStr">
         <is>
-          <t>P073</t>
+          <t>P138</t>
         </is>
       </c>
       <c r="G62" s="21" t="inlineStr">
@@ -29475,19 +29475,19 @@
       </c>
       <c r="H62" s="21" t="inlineStr">
         <is>
-          <t>Épouse d’Hugo Pelletier</t>
+          <t>Neveu de Lucien et Thérèse Lacroix</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>P072</t>
+          <t>P055</t>
         </is>
       </c>
       <c r="B63" s="21" t="inlineStr">
         <is>
-          <t>Hugo Pelletier</t>
+          <t>Claude Lavoie</t>
         </is>
       </c>
       <c r="C63" s="21" t="inlineStr">
@@ -29497,17 +29497,17 @@
       </c>
       <c r="D63" s="21" t="inlineStr">
         <is>
-          <t>P102</t>
+          <t>P023</t>
         </is>
       </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
-          <t>Léa Pelletier</t>
+          <t>Michel Lavoie</t>
         </is>
       </c>
       <c r="F63" s="21" t="inlineStr">
         <is>
-          <t>P102</t>
+          <t>P023</t>
         </is>
       </c>
       <c r="G63" s="21" t="inlineStr">
@@ -29517,19 +29517,19 @@
       </c>
       <c r="H63" s="21" t="inlineStr">
         <is>
-          <t>Fille d’Hugo et Sarah Pelletier</t>
+          <t>Fils de Claude</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>P073</t>
+          <t>P059</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>Sarah Pelletier</t>
+          <t>Hélène Chicoine</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
@@ -29539,17 +29539,17 @@
       </c>
       <c r="D64" s="21" t="inlineStr">
         <is>
-          <t>P102</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="E64" s="21" t="inlineStr">
         <is>
-          <t>Léa Pelletier</t>
+          <t>Réal Chicoine</t>
         </is>
       </c>
       <c r="F64" s="21" t="inlineStr">
         <is>
-          <t>P102</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="G64" s="21" t="inlineStr">
@@ -29559,39 +29559,39 @@
       </c>
       <c r="H64" s="21" t="inlineStr">
         <is>
-          <t>Fille d’Hugo et Sarah Pelletier</t>
+          <t>Fils d’Hélène</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>P074</t>
+          <t>P062</t>
         </is>
       </c>
       <c r="B65" s="21" t="inlineStr">
         <is>
-          <t>Anne Girard</t>
+          <t>Gisèle Truchon</t>
         </is>
       </c>
       <c r="C65" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
-          <t>P075</t>
+          <t>P178</t>
         </is>
       </c>
       <c r="E65" s="21" t="inlineStr">
         <is>
-          <t>Louis Girard</t>
+          <t>Mathis Truchon</t>
         </is>
       </c>
       <c r="F65" s="21" t="inlineStr">
         <is>
-          <t>P074</t>
+          <t>P178</t>
         </is>
       </c>
       <c r="G65" s="21" t="inlineStr">
@@ -29601,19 +29601,19 @@
       </c>
       <c r="H65" s="21" t="inlineStr">
         <is>
-          <t>Épouse de Louis Girard</t>
+          <t>Fils d’Yvan Truchon et Gisèle</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="21" t="inlineStr">
         <is>
-          <t>P074</t>
+          <t>P063</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>Anne Girard</t>
+          <t>Mei Chen</t>
         </is>
       </c>
       <c r="C66" s="21" t="inlineStr">
@@ -29623,17 +29623,17 @@
       </c>
       <c r="D66" s="21" t="inlineStr">
         <is>
-          <t>P181</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="E66" s="21" t="inlineStr">
         <is>
-          <t>Rosalie Girard</t>
+          <t>Justin Chen</t>
         </is>
       </c>
       <c r="F66" s="21" t="inlineStr">
         <is>
-          <t>P181</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="G66" s="21" t="inlineStr">
@@ -29643,39 +29643,39 @@
       </c>
       <c r="H66" s="21" t="inlineStr">
         <is>
-          <t>Fille d’Anne et Louis Girard</t>
+          <t>Fils de Mei</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>P075</t>
+          <t>P064</t>
         </is>
       </c>
       <c r="B67" s="21" t="inlineStr">
         <is>
-          <t>Louis Girard</t>
+          <t>Catherine Samson</t>
         </is>
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>collegue_de</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>P181</t>
+          <t>P127</t>
         </is>
       </c>
       <c r="E67" s="21" t="inlineStr">
         <is>
-          <t>Rosalie Girard</t>
+          <t>Louise Villeneuve</t>
         </is>
       </c>
       <c r="F67" s="21" t="inlineStr">
         <is>
-          <t>P181</t>
+          <t>P127</t>
         </is>
       </c>
       <c r="G67" s="21" t="inlineStr">
@@ -29685,39 +29685,39 @@
       </c>
       <c r="H67" s="21" t="inlineStr">
         <is>
-          <t>Fille d’Anne et Louis Girard</t>
+          <t>Collègue de Catherine Samson</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="21" t="inlineStr">
         <is>
-          <t>P076</t>
+          <t>P068</t>
         </is>
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
-          <t>Émile Brassard</t>
+          <t>Fernand Côté</t>
         </is>
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>collegue_de</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>P197</t>
+          <t>P069</t>
         </is>
       </c>
       <c r="E68" s="21" t="inlineStr">
         <is>
-          <t>Camille Desgagné</t>
+          <t>Lucie Côté</t>
         </is>
       </c>
       <c r="F68" s="21" t="inlineStr">
         <is>
-          <t>P197</t>
+          <t>P068</t>
         </is>
       </c>
       <c r="G68" s="21" t="inlineStr">
@@ -29727,39 +29727,39 @@
       </c>
       <c r="H68" s="21" t="inlineStr">
         <is>
-          <t>Fille de Denis et Johanne — collègue d’Émile Brassard</t>
+          <t>Époux de Lucie Côté</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>P076</t>
+          <t>P068</t>
         </is>
       </c>
       <c r="B69" s="21" t="inlineStr">
         <is>
-          <t>Émile Brassard</t>
+          <t>Fernand Côté</t>
         </is>
       </c>
       <c r="C69" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>parrain_de</t>
         </is>
       </c>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>P077</t>
+          <t>P136</t>
         </is>
       </c>
       <c r="E69" s="21" t="inlineStr">
         <is>
-          <t>Marie-Claude Brassard</t>
+          <t>Rock Côté</t>
         </is>
       </c>
       <c r="F69" s="21" t="inlineStr">
         <is>
-          <t>P076</t>
+          <t>P136</t>
         </is>
       </c>
       <c r="G69" s="21" t="inlineStr">
@@ -29769,39 +29769,39 @@
       </c>
       <c r="H69" s="21" t="inlineStr">
         <is>
-          <t>Époux de Marie-Claude Brassard</t>
+          <t>Filleul de Fernand Côté</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="21" t="inlineStr">
         <is>
-          <t>P086</t>
+          <t>P070</t>
         </is>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>Benoit Larouche</t>
+          <t>Yves Fortin</t>
         </is>
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>enseignant_de</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
         <is>
-          <t>P020</t>
+          <t>P071</t>
         </is>
       </c>
       <c r="E70" s="21" t="inlineStr">
         <is>
-          <t>Antoine Lefèvre</t>
+          <t>Pauline Fortin</t>
         </is>
       </c>
       <c r="F70" s="21" t="inlineStr">
         <is>
-          <t>P086</t>
+          <t>P070</t>
         </is>
       </c>
       <c r="G70" s="21" t="inlineStr">
@@ -29811,39 +29811,39 @@
       </c>
       <c r="H70" s="21" t="inlineStr">
         <is>
-          <t>Prof d’Antoine Lefèvre</t>
+          <t>Époux de Pauline Fortin</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="21" t="inlineStr">
         <is>
-          <t>P086</t>
+          <t>P070</t>
         </is>
       </c>
       <c r="B71" s="21" t="inlineStr">
         <is>
-          <t>Benoit Larouche</t>
+          <t>Yves Fortin</t>
         </is>
       </c>
       <c r="C71" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>P182</t>
+          <t>P139</t>
         </is>
       </c>
       <c r="E71" s="21" t="inlineStr">
         <is>
-          <t>Ludovic Larouche</t>
+          <t>Justine Fortin</t>
         </is>
       </c>
       <c r="F71" s="21" t="inlineStr">
         <is>
-          <t>P182</t>
+          <t>P139</t>
         </is>
       </c>
       <c r="G71" s="21" t="inlineStr">
@@ -29853,39 +29853,39 @@
       </c>
       <c r="H71" s="21" t="inlineStr">
         <is>
-          <t>Fils de Benoit Larouche</t>
+          <t>Nièce d’Yves et Pauline Fortin</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="21" t="inlineStr">
         <is>
-          <t>P087</t>
+          <t>P070</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
-          <t>Émilie Gauthier</t>
+          <t>Yves Fortin</t>
         </is>
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>superieur_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
         <is>
-          <t>P040</t>
+          <t>P101</t>
         </is>
       </c>
       <c r="E72" s="21" t="inlineStr">
         <is>
-          <t>Stéphanie Lapointe</t>
+          <t>Tommy Fortin</t>
         </is>
       </c>
       <c r="F72" s="21" t="inlineStr">
         <is>
-          <t>P087</t>
+          <t>P101</t>
         </is>
       </c>
       <c r="G72" s="21" t="inlineStr">
@@ -29895,39 +29895,39 @@
       </c>
       <c r="H72" s="21" t="inlineStr">
         <is>
-          <t>Supérieure de Stéphanie Lapointe</t>
+          <t>Fils d’Yves et Pauline Fortin</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>P090</t>
+          <t>P071</t>
         </is>
       </c>
       <c r="B73" s="21" t="inlineStr">
         <is>
-          <t>Maxime Boivin</t>
+          <t>Pauline Fortin</t>
         </is>
       </c>
       <c r="C73" s="21" t="inlineStr">
         <is>
-          <t>fratrie</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>P108</t>
+          <t>P139</t>
         </is>
       </c>
       <c r="E73" s="21" t="inlineStr">
         <is>
-          <t>France Boivin</t>
+          <t>Justine Fortin</t>
         </is>
       </c>
       <c r="F73" s="21" t="inlineStr">
         <is>
-          <t>P108</t>
+          <t>P139</t>
         </is>
       </c>
       <c r="G73" s="21" t="inlineStr">
@@ -29937,39 +29937,39 @@
       </c>
       <c r="H73" s="21" t="inlineStr">
         <is>
-          <t>Sœur de Maxime Boivin</t>
+          <t>Nièce d’Yves et Pauline Fortin</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="21" t="inlineStr">
         <is>
-          <t>P093</t>
+          <t>P071</t>
         </is>
       </c>
       <c r="B74" s="21" t="inlineStr">
         <is>
-          <t>Jessica Paradis</t>
+          <t>Pauline Fortin</t>
         </is>
       </c>
       <c r="C74" s="21" t="inlineStr">
         <is>
-          <t>locataire_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P101</t>
         </is>
       </c>
       <c r="E74" s="21" t="inlineStr">
         <is>
-          <t>Sylvie Gagnon</t>
+          <t>Tommy Fortin</t>
         </is>
       </c>
       <c r="F74" s="21" t="inlineStr">
         <is>
-          <t>P093</t>
+          <t>P101</t>
         </is>
       </c>
       <c r="G74" s="21" t="inlineStr">
@@ -29979,39 +29979,39 @@
       </c>
       <c r="H74" s="21" t="inlineStr">
         <is>
-          <t>Locataire de Sylvie Gagnon</t>
+          <t>Fils d’Yves et Pauline Fortin</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="21" t="inlineStr">
         <is>
-          <t>P094</t>
+          <t>P072</t>
         </is>
       </c>
       <c r="B75" s="21" t="inlineStr">
         <is>
-          <t>Nicolas Gagné</t>
+          <t>Hugo Pelletier</t>
         </is>
       </c>
       <c r="C75" s="21" t="inlineStr">
         <is>
-          <t>collegue_de</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D75" s="21" t="inlineStr">
         <is>
-          <t>P191</t>
+          <t>P073</t>
         </is>
       </c>
       <c r="E75" s="21" t="inlineStr">
         <is>
-          <t>Audrey Lavoie</t>
+          <t>Sarah Pelletier</t>
         </is>
       </c>
       <c r="F75" s="21" t="inlineStr">
         <is>
-          <t>P191</t>
+          <t>P073</t>
         </is>
       </c>
       <c r="G75" s="21" t="inlineStr">
@@ -30021,39 +30021,39 @@
       </c>
       <c r="H75" s="21" t="inlineStr">
         <is>
-          <t>Fille de Fernand Lavoie — collègue de Nicolas Gagné</t>
+          <t>Épouse d’Hugo Pelletier</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>P105</t>
+          <t>P072</t>
         </is>
       </c>
       <c r="B76" s="21" t="inlineStr">
         <is>
-          <t>Réjean Pedneault</t>
+          <t>Hugo Pelletier</t>
         </is>
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
         <is>
-          <t>P106</t>
+          <t>P102</t>
         </is>
       </c>
       <c r="E76" s="21" t="inlineStr">
         <is>
-          <t>Céline Pedneault</t>
+          <t>Léa Pelletier</t>
         </is>
       </c>
       <c r="F76" s="21" t="inlineStr">
         <is>
-          <t>P105</t>
+          <t>P102</t>
         </is>
       </c>
       <c r="G76" s="21" t="inlineStr">
@@ -30063,39 +30063,39 @@
       </c>
       <c r="H76" s="21" t="inlineStr">
         <is>
-          <t>Époux de Céline Pedneault</t>
+          <t>Fille d’Hugo et Sarah Pelletier</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="21" t="inlineStr">
         <is>
-          <t>P123</t>
+          <t>P073</t>
         </is>
       </c>
       <c r="B77" s="21" t="inlineStr">
         <is>
-          <t>André Simard</t>
+          <t>Sarah Pelletier</t>
         </is>
       </c>
       <c r="C77" s="21" t="inlineStr">
         <is>
-          <t>superieur_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D77" s="21" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P102</t>
         </is>
       </c>
       <c r="E77" s="21" t="inlineStr">
         <is>
-          <t>Pierre Samson</t>
+          <t>Léa Pelletier</t>
         </is>
       </c>
       <c r="F77" s="21" t="inlineStr">
         <is>
-          <t>P123</t>
+          <t>P102</t>
         </is>
       </c>
       <c r="G77" s="21" t="inlineStr">
@@ -30105,39 +30105,39 @@
       </c>
       <c r="H77" s="21" t="inlineStr">
         <is>
-          <t>Supérieur de Pierre Samson</t>
+          <t>Fille d’Hugo et Sarah Pelletier</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>P125</t>
+          <t>P074</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
         <is>
-          <t>Jean-Marc Fortin</t>
+          <t>Anne Girard</t>
         </is>
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>superieur_de</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
         <is>
-          <t>P035</t>
+          <t>P075</t>
         </is>
       </c>
       <c r="E78" s="21" t="inlineStr">
         <is>
-          <t>Mathieu Lavoie</t>
+          <t>Louis Girard</t>
         </is>
       </c>
       <c r="F78" s="21" t="inlineStr">
         <is>
-          <t>P125</t>
+          <t>P074</t>
         </is>
       </c>
       <c r="G78" s="21" t="inlineStr">
@@ -30147,39 +30147,39 @@
       </c>
       <c r="H78" s="21" t="inlineStr">
         <is>
-          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
+          <t>Épouse de Louis Girard</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="21" t="inlineStr">
         <is>
-          <t>P125</t>
+          <t>P074</t>
         </is>
       </c>
       <c r="B79" s="21" t="inlineStr">
         <is>
-          <t>Jean-Marc Fortin</t>
+          <t>Anne Girard</t>
         </is>
       </c>
       <c r="C79" s="21" t="inlineStr">
         <is>
-          <t>superieur_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>P094</t>
+          <t>P181</t>
         </is>
       </c>
       <c r="E79" s="21" t="inlineStr">
         <is>
-          <t>Nicolas Gagné</t>
+          <t>Rosalie Girard</t>
         </is>
       </c>
       <c r="F79" s="21" t="inlineStr">
         <is>
-          <t>P125</t>
+          <t>P181</t>
         </is>
       </c>
       <c r="G79" s="21" t="inlineStr">
@@ -30189,39 +30189,39 @@
       </c>
       <c r="H79" s="21" t="inlineStr">
         <is>
-          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
+          <t>Fille d’Anne et Louis Girard</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>P126</t>
+          <t>P075</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
         <is>
-          <t>Mgr Paul Tremblay</t>
+          <t>Louis Girard</t>
         </is>
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>superieur_de</t>
+          <t>parent_de</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P181</t>
         </is>
       </c>
       <c r="E80" s="21" t="inlineStr">
         <is>
-          <t>Lucien Lacroix</t>
+          <t>Rosalie Girard</t>
         </is>
       </c>
       <c r="F80" s="21" t="inlineStr">
         <is>
-          <t>P126</t>
+          <t>P181</t>
         </is>
       </c>
       <c r="G80" s="21" t="inlineStr">
@@ -30231,39 +30231,39 @@
       </c>
       <c r="H80" s="21" t="inlineStr">
         <is>
-          <t>Supérieur de Lucien Lacroix</t>
+          <t>Fille d’Anne et Louis Girard</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="21" t="inlineStr">
         <is>
-          <t>P134</t>
+          <t>P076</t>
         </is>
       </c>
       <c r="B81" s="21" t="inlineStr">
         <is>
-          <t>François Côté</t>
+          <t>Émile Brassard</t>
         </is>
       </c>
       <c r="C81" s="21" t="inlineStr">
         <is>
-          <t>superieur_de</t>
+          <t>collegue_de</t>
         </is>
       </c>
       <c r="D81" s="21" t="inlineStr">
         <is>
-          <t>P078</t>
+          <t>P197</t>
         </is>
       </c>
       <c r="E81" s="21" t="inlineStr">
         <is>
-          <t>Olivier Savard</t>
+          <t>Camille Desgagné</t>
         </is>
       </c>
       <c r="F81" s="21" t="inlineStr">
         <is>
-          <t>P134</t>
+          <t>P197</t>
         </is>
       </c>
       <c r="G81" s="21" t="inlineStr">
@@ -30273,19 +30273,19 @@
       </c>
       <c r="H81" s="21" t="inlineStr">
         <is>
-          <t>Patron d’Olivier Savard — ex-patron de JP</t>
+          <t>Fille de Denis et Johanne — collègue d’Émile Brassard</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="21" t="inlineStr">
         <is>
-          <t>P151</t>
+          <t>P076</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
-          <t>Vittorio Santini</t>
+          <t>Émile Brassard</t>
         </is>
       </c>
       <c r="C82" s="21" t="inlineStr">
@@ -30295,17 +30295,17 @@
       </c>
       <c r="D82" s="21" t="inlineStr">
         <is>
-          <t>P152</t>
+          <t>P077</t>
         </is>
       </c>
       <c r="E82" s="21" t="inlineStr">
         <is>
-          <t>Maria Santini</t>
+          <t>Marie-Claude Brassard</t>
         </is>
       </c>
       <c r="F82" s="21" t="inlineStr">
         <is>
-          <t>P152</t>
+          <t>P076</t>
         </is>
       </c>
       <c r="G82" s="21" t="inlineStr">
@@ -30315,39 +30315,39 @@
       </c>
       <c r="H82" s="21" t="inlineStr">
         <is>
-          <t>Épouse de Vittorio</t>
+          <t>Époux de Marie-Claude Brassard</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="21" t="inlineStr">
         <is>
-          <t>P151</t>
+          <t>P076</t>
         </is>
       </c>
       <c r="B83" s="21" t="inlineStr">
         <is>
-          <t>Vittorio Santini</t>
+          <t>Émile Brassard</t>
         </is>
       </c>
       <c r="C83" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D83" s="21" t="inlineStr">
         <is>
-          <t>P160</t>
+          <t>P208</t>
         </is>
       </c>
       <c r="E83" s="21" t="inlineStr">
         <is>
-          <t>Nico Santini</t>
+          <t>Olivier Brassard</t>
         </is>
       </c>
       <c r="F83" s="21" t="inlineStr">
         <is>
-          <t>P160</t>
+          <t>P208</t>
         </is>
       </c>
       <c r="G83" s="21" t="inlineStr">
@@ -30357,39 +30357,39 @@
       </c>
       <c r="H83" s="21" t="inlineStr">
         <is>
-          <t>Fils de Vittorio et Maria</t>
+          <t>Neveu d’Émile Brassard</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="21" t="inlineStr">
         <is>
-          <t>P152</t>
+          <t>P083</t>
         </is>
       </c>
       <c r="B84" s="21" t="inlineStr">
         <is>
-          <t>Maria Santini</t>
+          <t>Amina Traoré</t>
         </is>
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D84" s="21" t="inlineStr">
         <is>
-          <t>P160</t>
+          <t>P180</t>
         </is>
       </c>
       <c r="E84" s="21" t="inlineStr">
         <is>
-          <t>Nico Santini</t>
+          <t>Noah Traoré</t>
         </is>
       </c>
       <c r="F84" s="21" t="inlineStr">
         <is>
-          <t>P160</t>
+          <t>P180</t>
         </is>
       </c>
       <c r="G84" s="21" t="inlineStr">
@@ -30399,39 +30399,39 @@
       </c>
       <c r="H84" s="21" t="inlineStr">
         <is>
-          <t>Fils de Vittorio et Maria</t>
+          <t>Neveu d’Amina Traoré</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>P160</t>
+          <t>P086</t>
         </is>
       </c>
       <c r="B85" s="21" t="inlineStr">
         <is>
-          <t>Nico Santini</t>
+          <t>Benoit Larouche</t>
         </is>
       </c>
       <c r="C85" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>enseignant_de</t>
         </is>
       </c>
       <c r="D85" s="21" t="inlineStr">
         <is>
-          <t>P177</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="E85" s="21" t="inlineStr">
         <is>
-          <t>Sofia Santini</t>
+          <t>Antoine Lefèvre</t>
         </is>
       </c>
       <c r="F85" s="21" t="inlineStr">
         <is>
-          <t>P177</t>
+          <t>P086</t>
         </is>
       </c>
       <c r="G85" s="21" t="inlineStr">
@@ -30441,19 +30441,19 @@
       </c>
       <c r="H85" s="21" t="inlineStr">
         <is>
-          <t>Fille de Nico Santini — petite-fille de Vittorio et Maria</t>
+          <t>Prof d’Antoine Lefèvre</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="21" t="inlineStr">
         <is>
-          <t>P161</t>
+          <t>P086</t>
         </is>
       </c>
       <c r="B86" s="21" t="inlineStr">
         <is>
-          <t>Fernande Boucher</t>
+          <t>Benoit Larouche</t>
         </is>
       </c>
       <c r="C86" s="21" t="inlineStr">
@@ -30463,17 +30463,17 @@
       </c>
       <c r="D86" s="21" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P182</t>
         </is>
       </c>
       <c r="E86" s="21" t="inlineStr">
         <is>
-          <t>Dévon Boucher</t>
+          <t>Ludovic Larouche</t>
         </is>
       </c>
       <c r="F86" s="21" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P182</t>
         </is>
       </c>
       <c r="G86" s="21" t="inlineStr">
@@ -30483,39 +30483,39 @@
       </c>
       <c r="H86" s="21" t="inlineStr">
         <is>
-          <t>Fils de Fernande Boucher — frère d’Éric</t>
+          <t>Fils de Benoit Larouche</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="21" t="inlineStr">
         <is>
-          <t>P161</t>
+          <t>P087</t>
         </is>
       </c>
       <c r="B87" s="21" t="inlineStr">
         <is>
-          <t>Fernande Boucher</t>
+          <t>Émilie Gauthier</t>
         </is>
       </c>
       <c r="C87" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>superieur_de</t>
         </is>
       </c>
       <c r="D87" s="21" t="inlineStr">
         <is>
-          <t>P047</t>
+          <t>P040</t>
         </is>
       </c>
       <c r="E87" s="21" t="inlineStr">
         <is>
-          <t>Éric Boucher</t>
+          <t>Stéphanie Lapointe</t>
         </is>
       </c>
       <c r="F87" s="21" t="inlineStr">
         <is>
-          <t>P047</t>
+          <t>P087</t>
         </is>
       </c>
       <c r="G87" s="21" t="inlineStr">
@@ -30525,39 +30525,39 @@
       </c>
       <c r="H87" s="21" t="inlineStr">
         <is>
-          <t>Fils de Fernande — frère de Dévon</t>
+          <t>Supérieure de Stéphanie Lapointe</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>P162</t>
+          <t>P089</t>
         </is>
       </c>
       <c r="B88" s="21" t="inlineStr">
         <is>
-          <t>Aline Tremblay</t>
+          <t>Lise Blackburn</t>
         </is>
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D88" s="21" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P124</t>
         </is>
       </c>
       <c r="E88" s="21" t="inlineStr">
         <is>
-          <t>Gratien Tremblay</t>
+          <t>Hélène Blackburn</t>
         </is>
       </c>
       <c r="F88" s="21" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P124</t>
         </is>
       </c>
       <c r="G88" s="21" t="inlineStr">
@@ -30567,39 +30567,39 @@
       </c>
       <c r="H88" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Aline Tremblay — conjoint de Linda</t>
+          <t>Sœur de Lise Blackburn</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="21" t="inlineStr">
         <is>
-          <t>P163</t>
+          <t>P090</t>
         </is>
       </c>
       <c r="B89" s="21" t="inlineStr">
         <is>
-          <t>Cécile Truchon</t>
+          <t>Maxime Boivin</t>
         </is>
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P108</t>
         </is>
       </c>
       <c r="E89" s="21" t="inlineStr">
         <is>
-          <t>Yvan Truchon</t>
+          <t>France Boivin</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P108</t>
         </is>
       </c>
       <c r="G89" s="21" t="inlineStr">
@@ -30609,39 +30609,39 @@
       </c>
       <c r="H89" s="21" t="inlineStr">
         <is>
-          <t>Fils de Cécile Truchon — conjoint de Gisèle</t>
+          <t>Sœur de Maxime Boivin</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="21" t="inlineStr">
         <is>
-          <t>P164</t>
+          <t>P090</t>
         </is>
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>Thérèse Gagnon</t>
+          <t>Maxime Boivin</t>
         </is>
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P183</t>
         </is>
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>Karine Gagnon</t>
+          <t>Jade Boivin</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P183</t>
         </is>
       </c>
       <c r="G90" s="21" t="inlineStr">
@@ -30651,19 +30651,19 @@
       </c>
       <c r="H90" s="21" t="inlineStr">
         <is>
-          <t>Fille de Thérèse Gagnon — sœur de Rock</t>
+          <t>Nièce de France et Maxime Boivin</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>P164</t>
+          <t>P092</t>
         </is>
       </c>
       <c r="B91" s="21" t="inlineStr">
         <is>
-          <t>Thérèse Gagnon</t>
+          <t>Pierrette Simard</t>
         </is>
       </c>
       <c r="C91" s="21" t="inlineStr">
@@ -30673,17 +30673,17 @@
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>P052</t>
+          <t>P043</t>
         </is>
       </c>
       <c r="E91" s="21" t="inlineStr">
         <is>
-          <t>Rock Gagnon</t>
+          <t>Marc-André Simard</t>
         </is>
       </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>P052</t>
+          <t>P092</t>
         </is>
       </c>
       <c r="G91" s="21" t="inlineStr">
@@ -30693,39 +30693,39 @@
       </c>
       <c r="H91" s="21" t="inlineStr">
         <is>
-          <t>Fils de Thérèse Gagnon — frère de Karine</t>
+          <t>Mère de Marc-André Simard</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="21" t="inlineStr">
         <is>
-          <t>P165</t>
+          <t>P093</t>
         </is>
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>Lucie Bérubé</t>
+          <t>Jessica Paradis</t>
         </is>
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>locataire_de</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>Kevin Bérubé</t>
+          <t>Sylvie Gagnon</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P093</t>
         </is>
       </c>
       <c r="G92" s="21" t="inlineStr">
@@ -30735,39 +30735,39 @@
       </c>
       <c r="H92" s="21" t="inlineStr">
         <is>
-          <t>Fils de Lucie Bérubé — frère de Jessy</t>
+          <t>Locataire de Sylvie Gagnon</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="21" t="inlineStr">
         <is>
-          <t>P165</t>
+          <t>P094</t>
         </is>
       </c>
       <c r="B93" s="21" t="inlineStr">
         <is>
-          <t>Lucie Bérubé</t>
+          <t>Nicolas Gagné</t>
         </is>
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>collegue_de</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>P053</t>
+          <t>P191</t>
         </is>
       </c>
       <c r="E93" s="21" t="inlineStr">
         <is>
-          <t>Jessy Bérubé</t>
+          <t>Audrey Lavoie</t>
         </is>
       </c>
       <c r="F93" s="21" t="inlineStr">
         <is>
-          <t>P053</t>
+          <t>P191</t>
         </is>
       </c>
       <c r="G93" s="21" t="inlineStr">
@@ -30777,39 +30777,39 @@
       </c>
       <c r="H93" s="21" t="inlineStr">
         <is>
-          <t>Fils de Lucie Bérubé — frère de Kevin</t>
+          <t>Fille de Fernand Lavoie — collègue de Nicolas Gagné</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="21" t="inlineStr">
         <is>
-          <t>P165</t>
+          <t>P096</t>
         </is>
       </c>
       <c r="B94" s="21" t="inlineStr">
         <is>
-          <t>Lucie Bérubé</t>
+          <t>Julie Martel</t>
         </is>
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>P175</t>
+          <t>P140</t>
         </is>
       </c>
       <c r="E94" s="21" t="inlineStr">
         <is>
-          <t>Zack Bérubé</t>
+          <t>Élodie Martel</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr">
         <is>
-          <t>P175</t>
+          <t>P140</t>
         </is>
       </c>
       <c r="G94" s="21" t="inlineStr">
@@ -30819,39 +30819,39 @@
       </c>
       <c r="H94" s="21" t="inlineStr">
         <is>
-          <t>Fils de Lucie Bérubé — cadet de Kevin et Jessy</t>
+          <t>Cousine de Julie et Amélie Martel</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>P166</t>
+          <t>P096</t>
         </is>
       </c>
       <c r="B95" s="21" t="inlineStr">
         <is>
-          <t>Jeanne Gagnon</t>
+          <t>Julie Martel</t>
         </is>
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>fratrie</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P130</t>
         </is>
       </c>
       <c r="E95" s="21" t="inlineStr">
         <is>
-          <t>Sylvie Gagnon</t>
+          <t>Amélie Martel</t>
         </is>
       </c>
       <c r="F95" s="21" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P130</t>
         </is>
       </c>
       <c r="G95" s="21" t="inlineStr">
@@ -30861,39 +30861,39 @@
       </c>
       <c r="H95" s="21" t="inlineStr">
         <is>
-          <t>Fille de Jeanne Gagnon — ex-épouse de Bertrand</t>
+          <t>Sœur de Julie Martel</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="21" t="inlineStr">
         <is>
-          <t>P167</t>
+          <t>P099</t>
         </is>
       </c>
       <c r="B96" s="21" t="inlineStr">
         <is>
-          <t>Gaston Pelletier</t>
+          <t>Jeanne Otis</t>
         </is>
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
         <is>
-          <t>P072</t>
+          <t>P128</t>
         </is>
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>Hugo Pelletier</t>
+          <t>Caroline Otis</t>
         </is>
       </c>
       <c r="F96" s="21" t="inlineStr">
         <is>
-          <t>P072</t>
+          <t>P128</t>
         </is>
       </c>
       <c r="G96" s="21" t="inlineStr">
@@ -30903,39 +30903,39 @@
       </c>
       <c r="H96" s="21" t="inlineStr">
         <is>
-          <t>Fils de Gaston Pelletier — époux de Sarah</t>
+          <t>Nièce de Jeanne Otis</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="21" t="inlineStr">
         <is>
-          <t>P168</t>
+          <t>P099</t>
         </is>
       </c>
       <c r="B97" s="21" t="inlineStr">
         <is>
-          <t>Hélène Samson</t>
+          <t>Jeanne Otis</t>
         </is>
       </c>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D97" s="21" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P147</t>
         </is>
       </c>
       <c r="E97" s="21" t="inlineStr">
         <is>
-          <t>Pierre Samson</t>
+          <t>Félix Otis</t>
         </is>
       </c>
       <c r="F97" s="21" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P147</t>
         </is>
       </c>
       <c r="G97" s="21" t="inlineStr">
@@ -30945,39 +30945,39 @@
       </c>
       <c r="H97" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Hélène Samson — époux de Catherine</t>
+          <t>Neveu de Jeanne Otis</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="21" t="inlineStr">
         <is>
-          <t>P169</t>
+          <t>P105</t>
         </is>
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>Albert Dufour</t>
+          <t>Réjean Pedneault</t>
         </is>
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D98" s="21" t="inlineStr">
         <is>
-          <t>P121</t>
+          <t>P106</t>
         </is>
       </c>
       <c r="E98" s="21" t="inlineStr">
         <is>
-          <t>Gilles Dufour</t>
+          <t>Céline Pedneault</t>
         </is>
       </c>
       <c r="F98" s="21" t="inlineStr">
         <is>
-          <t>P121</t>
+          <t>P105</t>
         </is>
       </c>
       <c r="G98" s="21" t="inlineStr">
@@ -30987,39 +30987,39 @@
       </c>
       <c r="H98" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Albert Dufour — maire de Saguenay</t>
+          <t>Époux de Céline Pedneault</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="21" t="inlineStr">
         <is>
-          <t>P170</t>
+          <t>P105</t>
         </is>
       </c>
       <c r="B99" s="21" t="inlineStr">
         <is>
-          <t>Manon Lavoie</t>
+          <t>Réjean Pedneault</t>
         </is>
       </c>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D99" s="21" t="inlineStr">
         <is>
-          <t>P116</t>
+          <t>P129</t>
         </is>
       </c>
       <c r="E99" s="21" t="inlineStr">
         <is>
-          <t>Cindy Lavoie</t>
+          <t>Denis Pedneault</t>
         </is>
       </c>
       <c r="F99" s="21" t="inlineStr">
         <is>
-          <t>P116</t>
+          <t>P129</t>
         </is>
       </c>
       <c r="G99" s="21" t="inlineStr">
@@ -31029,39 +31029,39 @@
       </c>
       <c r="H99" s="21" t="inlineStr">
         <is>
-          <t>Fille de Manon Lavoie — estafette de Gratien</t>
+          <t>Cousin de Réjean Pedneault</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="21" t="inlineStr">
         <is>
-          <t>P185</t>
+          <t>P105</t>
         </is>
       </c>
       <c r="B100" s="21" t="inlineStr">
         <is>
-          <t>Marie-Ève Boucher</t>
+          <t>Réjean Pedneault</t>
         </is>
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>grand_parent_de</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
         <is>
-          <t>P186</t>
+          <t>P174</t>
         </is>
       </c>
       <c r="E100" s="21" t="inlineStr">
         <is>
-          <t>Stéphane Bossé</t>
+          <t>Maude Pedneault</t>
         </is>
       </c>
       <c r="F100" s="21" t="inlineStr">
         <is>
-          <t>P185</t>
+          <t>P174</t>
         </is>
       </c>
       <c r="G100" s="21" t="inlineStr">
@@ -31071,39 +31071,39 @@
       </c>
       <c r="H100" s="21" t="inlineStr">
         <is>
-          <t>Conjointe de Stéphane Bossé — cousine de Normand Boucher</t>
+          <t>Petite-fille de Réjean et Céline Pedneault</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="21" t="inlineStr">
         <is>
-          <t>P190</t>
+          <t>P106</t>
         </is>
       </c>
       <c r="B101" s="21" t="inlineStr">
         <is>
-          <t>Fernand Lavoie</t>
+          <t>Céline Pedneault</t>
         </is>
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>grand_parent_de</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
         <is>
-          <t>P191</t>
+          <t>P174</t>
         </is>
       </c>
       <c r="E101" s="21" t="inlineStr">
         <is>
-          <t>Audrey Lavoie</t>
+          <t>Maude Pedneault</t>
         </is>
       </c>
       <c r="F101" s="21" t="inlineStr">
         <is>
-          <t>P191</t>
+          <t>P174</t>
         </is>
       </c>
       <c r="G101" s="21" t="inlineStr">
@@ -31113,39 +31113,39 @@
       </c>
       <c r="H101" s="21" t="inlineStr">
         <is>
-          <t>Fille de Fernand Lavoie — collègue de Nicolas Gagné</t>
+          <t>Petite-fille de Réjean et Céline Pedneault</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="21" t="inlineStr">
         <is>
-          <t>P194</t>
+          <t>P108</t>
         </is>
       </c>
       <c r="B102" s="21" t="inlineStr">
         <is>
-          <t>Yvette Desgagné</t>
+          <t>France Boivin</t>
         </is>
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
         <is>
-          <t>P195</t>
+          <t>P183</t>
         </is>
       </c>
       <c r="E102" s="21" t="inlineStr">
         <is>
-          <t>Denis Desgagné</t>
+          <t>Jade Boivin</t>
         </is>
       </c>
       <c r="F102" s="21" t="inlineStr">
         <is>
-          <t>P195</t>
+          <t>P183</t>
         </is>
       </c>
       <c r="G102" s="21" t="inlineStr">
@@ -31155,39 +31155,39 @@
       </c>
       <c r="H102" s="21" t="inlineStr">
         <is>
-          <t>Fils d’Yvette — époux de Johanne Gravel — père de Camille, Samuel et Julien</t>
+          <t>Nièce de France et Maxime Boivin</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="21" t="inlineStr">
         <is>
-          <t>P195</t>
+          <t>P109</t>
         </is>
       </c>
       <c r="B103" s="21" t="inlineStr">
         <is>
-          <t>Denis Desgagné</t>
+          <t>Alain Côté</t>
         </is>
       </c>
       <c r="C103" s="21" t="inlineStr">
         <is>
-          <t>conjoint_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D103" s="21" t="inlineStr">
         <is>
-          <t>P196</t>
+          <t>P187</t>
         </is>
       </c>
       <c r="E103" s="21" t="inlineStr">
         <is>
-          <t>Johanne Gravel</t>
+          <t>Jérémie Côté</t>
         </is>
       </c>
       <c r="F103" s="21" t="inlineStr">
         <is>
-          <t>P196</t>
+          <t>P187</t>
         </is>
       </c>
       <c r="G103" s="21" t="inlineStr">
@@ -31197,39 +31197,39 @@
       </c>
       <c r="H103" s="21" t="inlineStr">
         <is>
-          <t>Épouse de Denis Desgagné — sœur de Réal Gravel</t>
+          <t>Neveu d’Alain Côté</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="21" t="inlineStr">
         <is>
-          <t>P195</t>
+          <t>P118</t>
         </is>
       </c>
       <c r="B104" s="21" t="inlineStr">
         <is>
-          <t>Denis Desgagné</t>
+          <t>Steve Gauthier</t>
         </is>
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D104" s="21" t="inlineStr">
         <is>
-          <t>P197</t>
+          <t>P207</t>
         </is>
       </c>
       <c r="E104" s="21" t="inlineStr">
         <is>
-          <t>Camille Desgagné</t>
+          <t>Maïka Gauthier</t>
         </is>
       </c>
       <c r="F104" s="21" t="inlineStr">
         <is>
-          <t>P197</t>
+          <t>P207</t>
         </is>
       </c>
       <c r="G104" s="21" t="inlineStr">
@@ -31239,39 +31239,39 @@
       </c>
       <c r="H104" s="21" t="inlineStr">
         <is>
-          <t>Fille de Denis et Johanne — collègue d’Émile Brassard</t>
+          <t>Nièce de Lise Gauthier — cousine de Steve et Chantal</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="21" t="inlineStr">
         <is>
-          <t>P195</t>
+          <t>P123</t>
         </is>
       </c>
       <c r="B105" s="21" t="inlineStr">
         <is>
-          <t>Denis Desgagné</t>
+          <t>André Simard</t>
         </is>
       </c>
       <c r="C105" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>superieur_de</t>
         </is>
       </c>
       <c r="D105" s="21" t="inlineStr">
         <is>
-          <t>P198</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="E105" s="21" t="inlineStr">
         <is>
-          <t>Samuel Desgagné</t>
+          <t>Pierre Samson</t>
         </is>
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>P198</t>
+          <t>P123</t>
         </is>
       </c>
       <c r="G105" s="21" t="inlineStr">
@@ -31281,39 +31281,39 @@
       </c>
       <c r="H105" s="21" t="inlineStr">
         <is>
-          <t>Fils de Denis et Johanne — frère de Camille et Julien</t>
+          <t>Supérieur de Pierre Samson</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="21" t="inlineStr">
         <is>
-          <t>P195</t>
+          <t>P125</t>
         </is>
       </c>
       <c r="B106" s="21" t="inlineStr">
         <is>
-          <t>Denis Desgagné</t>
+          <t>Jean-Marc Fortin</t>
         </is>
       </c>
       <c r="C106" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>superieur_de</t>
         </is>
       </c>
       <c r="D106" s="21" t="inlineStr">
         <is>
-          <t>P203</t>
+          <t>P035</t>
         </is>
       </c>
       <c r="E106" s="21" t="inlineStr">
         <is>
-          <t>Julien Desgagné</t>
+          <t>Mathieu Lavoie</t>
         </is>
       </c>
       <c r="F106" s="21" t="inlineStr">
         <is>
-          <t>P203</t>
+          <t>P125</t>
         </is>
       </c>
       <c r="G106" s="21" t="inlineStr">
@@ -31323,39 +31323,39 @@
       </c>
       <c r="H106" s="21" t="inlineStr">
         <is>
-          <t>Fils de Denis et Johanne — aîné de Camille et Samuel</t>
+          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="21" t="inlineStr">
         <is>
-          <t>P196</t>
+          <t>P125</t>
         </is>
       </c>
       <c r="B107" s="21" t="inlineStr">
         <is>
-          <t>Johanne Gravel</t>
+          <t>Jean-Marc Fortin</t>
         </is>
       </c>
       <c r="C107" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>superieur_de</t>
         </is>
       </c>
       <c r="D107" s="21" t="inlineStr">
         <is>
-          <t>P197</t>
+          <t>P094</t>
         </is>
       </c>
       <c r="E107" s="21" t="inlineStr">
         <is>
-          <t>Camille Desgagné</t>
+          <t>Nicolas Gagné</t>
         </is>
       </c>
       <c r="F107" s="21" t="inlineStr">
         <is>
-          <t>P197</t>
+          <t>P125</t>
         </is>
       </c>
       <c r="G107" s="21" t="inlineStr">
@@ -31365,39 +31365,39 @@
       </c>
       <c r="H107" s="21" t="inlineStr">
         <is>
-          <t>Fille de Denis et Johanne — collègue d’Émile Brassard</t>
+          <t>Patron de Mathieu Lavoie et Nicolas Gagné</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="21" t="inlineStr">
         <is>
-          <t>P196</t>
+          <t>P126</t>
         </is>
       </c>
       <c r="B108" s="21" t="inlineStr">
         <is>
-          <t>Johanne Gravel</t>
+          <t>Mgr Paul Tremblay</t>
         </is>
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>superieur_de</t>
         </is>
       </c>
       <c r="D108" s="21" t="inlineStr">
         <is>
-          <t>P198</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="E108" s="21" t="inlineStr">
         <is>
-          <t>Samuel Desgagné</t>
+          <t>Lucien Lacroix</t>
         </is>
       </c>
       <c r="F108" s="21" t="inlineStr">
         <is>
-          <t>P198</t>
+          <t>P126</t>
         </is>
       </c>
       <c r="G108" s="21" t="inlineStr">
@@ -31407,39 +31407,39 @@
       </c>
       <c r="H108" s="21" t="inlineStr">
         <is>
-          <t>Fils de Denis et Johanne — frère de Camille et Julien</t>
+          <t>Supérieur de Lucien Lacroix</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="21" t="inlineStr">
         <is>
-          <t>P196</t>
+          <t>P130</t>
         </is>
       </c>
       <c r="B109" s="21" t="inlineStr">
         <is>
-          <t>Johanne Gravel</t>
+          <t>Amélie Martel</t>
         </is>
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D109" s="21" t="inlineStr">
         <is>
-          <t>P203</t>
+          <t>P140</t>
         </is>
       </c>
       <c r="E109" s="21" t="inlineStr">
         <is>
-          <t>Julien Desgagné</t>
+          <t>Élodie Martel</t>
         </is>
       </c>
       <c r="F109" s="21" t="inlineStr">
         <is>
-          <t>P203</t>
+          <t>P140</t>
         </is>
       </c>
       <c r="G109" s="21" t="inlineStr">
@@ -31449,39 +31449,39 @@
       </c>
       <c r="H109" s="21" t="inlineStr">
         <is>
-          <t>Fils de Denis et Johanne — aîné de Camille et Samuel</t>
+          <t>Cousine de Julie et Amélie Martel</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="21" t="inlineStr">
         <is>
-          <t>P199</t>
+          <t>P131</t>
         </is>
       </c>
       <c r="B110" s="21" t="inlineStr">
         <is>
-          <t>Nathalie Tremblay</t>
+          <t>Sylvain Bouchard</t>
         </is>
       </c>
       <c r="C110" s="21" t="inlineStr">
         <is>
-          <t>superieur_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D110" s="21" t="inlineStr">
         <is>
-          <t>P084</t>
+          <t>P201</t>
         </is>
       </c>
       <c r="E110" s="21" t="inlineStr">
         <is>
-          <t>Jacques Maltais</t>
+          <t>Geneviève Bouchard</t>
         </is>
       </c>
       <c r="F110" s="21" t="inlineStr">
         <is>
-          <t>P199</t>
+          <t>P201</t>
         </is>
       </c>
       <c r="G110" s="21" t="inlineStr">
@@ -31491,39 +31491,39 @@
       </c>
       <c r="H110" s="21" t="inlineStr">
         <is>
-          <t>Célibataire — supérieure de Jacques Maltais</t>
+          <t>Célibataire — cousine de Sylvain Bouchard</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="21" t="inlineStr">
         <is>
-          <t>P204</t>
+          <t>P134</t>
         </is>
       </c>
       <c r="B111" s="21" t="inlineStr">
         <is>
-          <t>Emma Boucher</t>
+          <t>François Côté</t>
         </is>
       </c>
       <c r="C111" s="21" t="inlineStr">
         <is>
-          <t>colocataire_de</t>
+          <t>superieur_de</t>
         </is>
       </c>
       <c r="D111" s="21" t="inlineStr">
         <is>
-          <t>P205</t>
+          <t>P078</t>
         </is>
       </c>
       <c r="E111" s="21" t="inlineStr">
         <is>
-          <t>Moussa Diallo</t>
+          <t>Olivier Savard</t>
         </is>
       </c>
       <c r="F111" s="21" t="inlineStr">
         <is>
-          <t>P205</t>
+          <t>P134</t>
         </is>
       </c>
       <c r="G111" s="21" t="inlineStr">
@@ -31533,39 +31533,39 @@
       </c>
       <c r="H111" s="21" t="inlineStr">
         <is>
-          <t>Célibataire — colocataire d’Emma Boucher et William Lavoie</t>
+          <t>Patron d’Olivier Savard — ex-patron de JP</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="21" t="inlineStr">
         <is>
-          <t>P204</t>
+          <t>P135</t>
         </is>
       </c>
       <c r="B112" s="21" t="inlineStr">
         <is>
-          <t>Emma Boucher</t>
+          <t>Chantal Gauthier</t>
         </is>
       </c>
       <c r="C112" s="21" t="inlineStr">
         <is>
-          <t>colocataire_de</t>
+          <t>cousin_de</t>
         </is>
       </c>
       <c r="D112" s="21" t="inlineStr">
         <is>
-          <t>P206</t>
+          <t>P207</t>
         </is>
       </c>
       <c r="E112" s="21" t="inlineStr">
         <is>
-          <t>William Lavoie</t>
+          <t>Maïka Gauthier</t>
         </is>
       </c>
       <c r="F112" s="21" t="inlineStr">
         <is>
-          <t>P206</t>
+          <t>P207</t>
         </is>
       </c>
       <c r="G112" s="21" t="inlineStr">
@@ -31575,39 +31575,39 @@
       </c>
       <c r="H112" s="21" t="inlineStr">
         <is>
-          <t>Cousin de JP — colocataire d’Emma Boucher et Moussa Diallo</t>
+          <t>Nièce de Lise Gauthier — cousine de Steve et Chantal</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="21" t="inlineStr">
         <is>
-          <t>P205</t>
+          <t>P151</t>
         </is>
       </c>
       <c r="B113" s="21" t="inlineStr">
         <is>
-          <t>Moussa Diallo</t>
+          <t>Vittorio Santini</t>
         </is>
       </c>
       <c r="C113" s="21" t="inlineStr">
         <is>
-          <t>colocataire_de</t>
+          <t>conjoint_de</t>
         </is>
       </c>
       <c r="D113" s="21" t="inlineStr">
         <is>
-          <t>P206</t>
+          <t>P152</t>
         </is>
       </c>
       <c r="E113" s="21" t="inlineStr">
         <is>
-          <t>William Lavoie</t>
+          <t>Maria Santini</t>
         </is>
       </c>
       <c r="F113" s="21" t="inlineStr">
         <is>
-          <t>P205</t>
+          <t>P152</t>
         </is>
       </c>
       <c r="G113" s="21" t="inlineStr">
@@ -31617,39 +31617,39 @@
       </c>
       <c r="H113" s="21" t="inlineStr">
         <is>
-          <t>Célibataire — colocataire d’Emma Boucher et William Lavoie</t>
+          <t>Épouse de Vittorio</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="21" t="inlineStr">
         <is>
-          <t>P213</t>
+          <t>P151</t>
         </is>
       </c>
       <c r="B114" s="21" t="inlineStr">
         <is>
-          <t>Karine Simard</t>
+          <t>Vittorio Santini</t>
         </is>
       </c>
       <c r="C114" s="21" t="inlineStr">
         <is>
-          <t>parent_de</t>
+          <t>oncle_de</t>
         </is>
       </c>
       <c r="D114" s="21" t="inlineStr">
         <is>
-          <t>P211</t>
+          <t>P154</t>
         </is>
       </c>
       <c r="E114" s="21" t="inlineStr">
         <is>
-          <t>Léa Simard</t>
+          <t>Tony Santini</t>
         </is>
       </c>
       <c r="F114" s="21" t="inlineStr">
         <is>
-          <t>P211</t>
+          <t>P154</t>
         </is>
       </c>
       <c r="G114" s="21" t="inlineStr">
@@ -31659,54 +31659,1776 @@
       </c>
       <c r="H114" s="21" t="inlineStr">
         <is>
-          <t>Fille de Karine Simard — sœur d’Anthony</t>
+          <t>Neveu de Vittorio — parle à Bobby Gagnon</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="21" t="inlineStr">
         <is>
+          <t>P151</t>
+        </is>
+      </c>
+      <c r="B115" s="21" t="inlineStr">
+        <is>
+          <t>Vittorio Santini</t>
+        </is>
+      </c>
+      <c r="C115" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D115" s="21" t="inlineStr">
+        <is>
+          <t>P160</t>
+        </is>
+      </c>
+      <c r="E115" s="21" t="inlineStr">
+        <is>
+          <t>Nico Santini</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="inlineStr">
+        <is>
+          <t>P160</t>
+        </is>
+      </c>
+      <c r="G115" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H115" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Vittorio et Maria</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="inlineStr">
+        <is>
+          <t>P152</t>
+        </is>
+      </c>
+      <c r="B116" s="21" t="inlineStr">
+        <is>
+          <t>Maria Santini</t>
+        </is>
+      </c>
+      <c r="C116" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D116" s="21" t="inlineStr">
+        <is>
+          <t>P160</t>
+        </is>
+      </c>
+      <c r="E116" s="21" t="inlineStr">
+        <is>
+          <t>Nico Santini</t>
+        </is>
+      </c>
+      <c r="F116" s="21" t="inlineStr">
+        <is>
+          <t>P160</t>
+        </is>
+      </c>
+      <c r="G116" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H116" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Vittorio et Maria</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="inlineStr">
+        <is>
+          <t>P160</t>
+        </is>
+      </c>
+      <c r="B117" s="21" t="inlineStr">
+        <is>
+          <t>Nico Santini</t>
+        </is>
+      </c>
+      <c r="C117" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D117" s="21" t="inlineStr">
+        <is>
+          <t>P177</t>
+        </is>
+      </c>
+      <c r="E117" s="21" t="inlineStr">
+        <is>
+          <t>Sofia Santini</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="inlineStr">
+        <is>
+          <t>P177</t>
+        </is>
+      </c>
+      <c r="G117" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H117" s="21" t="inlineStr">
+        <is>
+          <t>Fille de Nico Santini — petite-fille de Vittorio et Maria</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="21" t="inlineStr">
+        <is>
+          <t>P161</t>
+        </is>
+      </c>
+      <c r="B118" s="21" t="inlineStr">
+        <is>
+          <t>Fernande Boucher</t>
+        </is>
+      </c>
+      <c r="C118" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D118" s="21" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="E118" s="21" t="inlineStr">
+        <is>
+          <t>Dévon Boucher</t>
+        </is>
+      </c>
+      <c r="F118" s="21" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="G118" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H118" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Fernande Boucher — frère d’Éric</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="21" t="inlineStr">
+        <is>
+          <t>P161</t>
+        </is>
+      </c>
+      <c r="B119" s="21" t="inlineStr">
+        <is>
+          <t>Fernande Boucher</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D119" s="21" t="inlineStr">
+        <is>
+          <t>P047</t>
+        </is>
+      </c>
+      <c r="E119" s="21" t="inlineStr">
+        <is>
+          <t>Éric Boucher</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="inlineStr">
+        <is>
+          <t>P047</t>
+        </is>
+      </c>
+      <c r="G119" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H119" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Fernande — frère de Dévon</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="21" t="inlineStr">
+        <is>
+          <t>P162</t>
+        </is>
+      </c>
+      <c r="B120" s="21" t="inlineStr">
+        <is>
+          <t>Aline Tremblay</t>
+        </is>
+      </c>
+      <c r="C120" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D120" s="21" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="E120" s="21" t="inlineStr">
+        <is>
+          <t>Gratien Tremblay</t>
+        </is>
+      </c>
+      <c r="F120" s="21" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="G120" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H120" s="21" t="inlineStr">
+        <is>
+          <t>Fils d’Aline Tremblay — conjoint de Linda</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="inlineStr">
+        <is>
+          <t>P163</t>
+        </is>
+      </c>
+      <c r="B121" s="21" t="inlineStr">
+        <is>
+          <t>Cécile Truchon</t>
+        </is>
+      </c>
+      <c r="C121" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D121" s="21" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="E121" s="21" t="inlineStr">
+        <is>
+          <t>Yvan Truchon</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="G121" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H121" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Cécile Truchon — conjoint de Gisèle</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="21" t="inlineStr">
+        <is>
+          <t>P164</t>
+        </is>
+      </c>
+      <c r="B122" s="21" t="inlineStr">
+        <is>
+          <t>Thérèse Gagnon</t>
+        </is>
+      </c>
+      <c r="C122" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D122" s="21" t="inlineStr">
+        <is>
+          <t>P025</t>
+        </is>
+      </c>
+      <c r="E122" s="21" t="inlineStr">
+        <is>
+          <t>Karine Gagnon</t>
+        </is>
+      </c>
+      <c r="F122" s="21" t="inlineStr">
+        <is>
+          <t>P025</t>
+        </is>
+      </c>
+      <c r="G122" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H122" s="21" t="inlineStr">
+        <is>
+          <t>Fille de Thérèse Gagnon — sœur de Rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="inlineStr">
+        <is>
+          <t>P164</t>
+        </is>
+      </c>
+      <c r="B123" s="21" t="inlineStr">
+        <is>
+          <t>Thérèse Gagnon</t>
+        </is>
+      </c>
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D123" s="21" t="inlineStr">
+        <is>
+          <t>P052</t>
+        </is>
+      </c>
+      <c r="E123" s="21" t="inlineStr">
+        <is>
+          <t>Rock Gagnon</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t>P052</t>
+        </is>
+      </c>
+      <c r="G123" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H123" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Thérèse Gagnon — frère de Karine</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="21" t="inlineStr">
+        <is>
+          <t>P165</t>
+        </is>
+      </c>
+      <c r="B124" s="21" t="inlineStr">
+        <is>
+          <t>Lucie Bérubé</t>
+        </is>
+      </c>
+      <c r="C124" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D124" s="21" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="E124" s="21" t="inlineStr">
+        <is>
+          <t>Kevin Bérubé</t>
+        </is>
+      </c>
+      <c r="F124" s="21" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="G124" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H124" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Lucie Bérubé — frère de Jessy</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="21" t="inlineStr">
+        <is>
+          <t>P165</t>
+        </is>
+      </c>
+      <c r="B125" s="21" t="inlineStr">
+        <is>
+          <t>Lucie Bérubé</t>
+        </is>
+      </c>
+      <c r="C125" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D125" s="21" t="inlineStr">
+        <is>
+          <t>P053</t>
+        </is>
+      </c>
+      <c r="E125" s="21" t="inlineStr">
+        <is>
+          <t>Jessy Bérubé</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t>P053</t>
+        </is>
+      </c>
+      <c r="G125" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H125" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Lucie Bérubé — frère de Kevin</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="21" t="inlineStr">
+        <is>
+          <t>P165</t>
+        </is>
+      </c>
+      <c r="B126" s="21" t="inlineStr">
+        <is>
+          <t>Lucie Bérubé</t>
+        </is>
+      </c>
+      <c r="C126" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D126" s="21" t="inlineStr">
+        <is>
+          <t>P175</t>
+        </is>
+      </c>
+      <c r="E126" s="21" t="inlineStr">
+        <is>
+          <t>Zack Bérubé</t>
+        </is>
+      </c>
+      <c r="F126" s="21" t="inlineStr">
+        <is>
+          <t>P175</t>
+        </is>
+      </c>
+      <c r="G126" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H126" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Lucie Bérubé — cadet de Kevin et Jessy</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="21" t="inlineStr">
+        <is>
+          <t>P166</t>
+        </is>
+      </c>
+      <c r="B127" s="21" t="inlineStr">
+        <is>
+          <t>Jeanne Gagnon</t>
+        </is>
+      </c>
+      <c r="C127" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D127" s="21" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="E127" s="21" t="inlineStr">
+        <is>
+          <t>Sylvie Gagnon</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="G127" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H127" s="21" t="inlineStr">
+        <is>
+          <t>Fille de Jeanne Gagnon — ex-épouse de Bertrand</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="21" t="inlineStr">
+        <is>
+          <t>P167</t>
+        </is>
+      </c>
+      <c r="B128" s="21" t="inlineStr">
+        <is>
+          <t>Gaston Pelletier</t>
+        </is>
+      </c>
+      <c r="C128" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D128" s="21" t="inlineStr">
+        <is>
+          <t>P072</t>
+        </is>
+      </c>
+      <c r="E128" s="21" t="inlineStr">
+        <is>
+          <t>Hugo Pelletier</t>
+        </is>
+      </c>
+      <c r="F128" s="21" t="inlineStr">
+        <is>
+          <t>P072</t>
+        </is>
+      </c>
+      <c r="G128" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H128" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Gaston Pelletier — époux de Sarah</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="21" t="inlineStr">
+        <is>
+          <t>P168</t>
+        </is>
+      </c>
+      <c r="B129" s="21" t="inlineStr">
+        <is>
+          <t>Hélène Samson</t>
+        </is>
+      </c>
+      <c r="C129" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D129" s="21" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="E129" s="21" t="inlineStr">
+        <is>
+          <t>Pierre Samson</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="G129" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H129" s="21" t="inlineStr">
+        <is>
+          <t>Fils d’Hélène Samson — époux de Catherine</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="21" t="inlineStr">
+        <is>
+          <t>P169</t>
+        </is>
+      </c>
+      <c r="B130" s="21" t="inlineStr">
+        <is>
+          <t>Albert Dufour</t>
+        </is>
+      </c>
+      <c r="C130" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D130" s="21" t="inlineStr">
+        <is>
+          <t>P121</t>
+        </is>
+      </c>
+      <c r="E130" s="21" t="inlineStr">
+        <is>
+          <t>Gilles Dufour</t>
+        </is>
+      </c>
+      <c r="F130" s="21" t="inlineStr">
+        <is>
+          <t>P121</t>
+        </is>
+      </c>
+      <c r="G130" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H130" s="21" t="inlineStr">
+        <is>
+          <t>Fils d’Albert Dufour — maire de Saguenay</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="21" t="inlineStr">
+        <is>
+          <t>P170</t>
+        </is>
+      </c>
+      <c r="B131" s="21" t="inlineStr">
+        <is>
+          <t>Manon Lavoie</t>
+        </is>
+      </c>
+      <c r="C131" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D131" s="21" t="inlineStr">
+        <is>
+          <t>P116</t>
+        </is>
+      </c>
+      <c r="E131" s="21" t="inlineStr">
+        <is>
+          <t>Cindy Lavoie</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>P116</t>
+        </is>
+      </c>
+      <c r="G131" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H131" s="21" t="inlineStr">
+        <is>
+          <t>Fille de Manon Lavoie — estafette de Gratien</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="21" t="inlineStr">
+        <is>
+          <t>P184</t>
+        </is>
+      </c>
+      <c r="B132" s="21" t="inlineStr">
+        <is>
+          <t>Gaétan Bossé</t>
+        </is>
+      </c>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>fratrie</t>
+        </is>
+      </c>
+      <c r="D132" s="21" t="inlineStr">
+        <is>
+          <t>P186</t>
+        </is>
+      </c>
+      <c r="E132" s="21" t="inlineStr">
+        <is>
+          <t>Stéphane Bossé</t>
+        </is>
+      </c>
+      <c r="F132" s="21" t="inlineStr">
+        <is>
+          <t>P184</t>
+        </is>
+      </c>
+      <c r="G132" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H132" s="21" t="inlineStr">
+        <is>
+          <t>Frère de Stéphane Bossé</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="21" t="inlineStr">
+        <is>
+          <t>P185</t>
+        </is>
+      </c>
+      <c r="B133" s="21" t="inlineStr">
+        <is>
+          <t>Marie-Ève Boucher</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>conjoint_de</t>
+        </is>
+      </c>
+      <c r="D133" s="21" t="inlineStr">
+        <is>
+          <t>P186</t>
+        </is>
+      </c>
+      <c r="E133" s="21" t="inlineStr">
+        <is>
+          <t>Stéphane Bossé</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="inlineStr">
+        <is>
+          <t>P185</t>
+        </is>
+      </c>
+      <c r="G133" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H133" s="21" t="inlineStr">
+        <is>
+          <t>Conjointe de Stéphane Bossé — cousine de Normand Boucher</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="21" t="inlineStr">
+        <is>
+          <t>P188</t>
+        </is>
+      </c>
+      <c r="B134" s="21" t="inlineStr">
+        <is>
+          <t>Lise Gauthier</t>
+        </is>
+      </c>
+      <c r="C134" s="21" t="inlineStr">
+        <is>
+          <t>oncle_de</t>
+        </is>
+      </c>
+      <c r="D134" s="21" t="inlineStr">
+        <is>
+          <t>P118</t>
+        </is>
+      </c>
+      <c r="E134" s="21" t="inlineStr">
+        <is>
+          <t>Steve Gauthier</t>
+        </is>
+      </c>
+      <c r="F134" s="21" t="inlineStr">
+        <is>
+          <t>P188</t>
+        </is>
+      </c>
+      <c r="G134" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H134" s="21" t="inlineStr">
+        <is>
+          <t>Tante de Steve et Chantal Gauthier</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="21" t="inlineStr">
+        <is>
+          <t>P188</t>
+        </is>
+      </c>
+      <c r="B135" s="21" t="inlineStr">
+        <is>
+          <t>Lise Gauthier</t>
+        </is>
+      </c>
+      <c r="C135" s="21" t="inlineStr">
+        <is>
+          <t>oncle_de</t>
+        </is>
+      </c>
+      <c r="D135" s="21" t="inlineStr">
+        <is>
+          <t>P135</t>
+        </is>
+      </c>
+      <c r="E135" s="21" t="inlineStr">
+        <is>
+          <t>Chantal Gauthier</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="inlineStr">
+        <is>
+          <t>P188</t>
+        </is>
+      </c>
+      <c r="G135" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H135" s="21" t="inlineStr">
+        <is>
+          <t>Tante de Steve et Chantal Gauthier</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="21" t="inlineStr">
+        <is>
+          <t>P188</t>
+        </is>
+      </c>
+      <c r="B136" s="21" t="inlineStr">
+        <is>
+          <t>Lise Gauthier</t>
+        </is>
+      </c>
+      <c r="C136" s="21" t="inlineStr">
+        <is>
+          <t>oncle_de</t>
+        </is>
+      </c>
+      <c r="D136" s="21" t="inlineStr">
+        <is>
+          <t>P207</t>
+        </is>
+      </c>
+      <c r="E136" s="21" t="inlineStr">
+        <is>
+          <t>Maïka Gauthier</t>
+        </is>
+      </c>
+      <c r="F136" s="21" t="inlineStr">
+        <is>
+          <t>P207</t>
+        </is>
+      </c>
+      <c r="G136" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H136" s="21" t="inlineStr">
+        <is>
+          <t>Nièce de Lise Gauthier — cousine de Steve et Chantal</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="21" t="inlineStr">
+        <is>
+          <t>P190</t>
+        </is>
+      </c>
+      <c r="B137" s="21" t="inlineStr">
+        <is>
+          <t>Fernand Lavoie</t>
+        </is>
+      </c>
+      <c r="C137" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D137" s="21" t="inlineStr">
+        <is>
+          <t>P191</t>
+        </is>
+      </c>
+      <c r="E137" s="21" t="inlineStr">
+        <is>
+          <t>Audrey Lavoie</t>
+        </is>
+      </c>
+      <c r="F137" s="21" t="inlineStr">
+        <is>
+          <t>P191</t>
+        </is>
+      </c>
+      <c r="G137" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H137" s="21" t="inlineStr">
+        <is>
+          <t>Fille de Fernand Lavoie — collègue de Nicolas Gagné</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="21" t="inlineStr">
+        <is>
+          <t>P194</t>
+        </is>
+      </c>
+      <c r="B138" s="21" t="inlineStr">
+        <is>
+          <t>Yvette Desgagné</t>
+        </is>
+      </c>
+      <c r="C138" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D138" s="21" t="inlineStr">
+        <is>
+          <t>P195</t>
+        </is>
+      </c>
+      <c r="E138" s="21" t="inlineStr">
+        <is>
+          <t>Denis Desgagné</t>
+        </is>
+      </c>
+      <c r="F138" s="21" t="inlineStr">
+        <is>
+          <t>P195</t>
+        </is>
+      </c>
+      <c r="G138" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H138" s="21" t="inlineStr">
+        <is>
+          <t>Fils d’Yvette — époux de Johanne Gravel — père de Camille, Samuel et Julien</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="21" t="inlineStr">
+        <is>
+          <t>P195</t>
+        </is>
+      </c>
+      <c r="B139" s="21" t="inlineStr">
+        <is>
+          <t>Denis Desgagné</t>
+        </is>
+      </c>
+      <c r="C139" s="21" t="inlineStr">
+        <is>
+          <t>conjoint_de</t>
+        </is>
+      </c>
+      <c r="D139" s="21" t="inlineStr">
+        <is>
+          <t>P196</t>
+        </is>
+      </c>
+      <c r="E139" s="21" t="inlineStr">
+        <is>
+          <t>Johanne Gravel</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="inlineStr">
+        <is>
+          <t>P196</t>
+        </is>
+      </c>
+      <c r="G139" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H139" s="21" t="inlineStr">
+        <is>
+          <t>Épouse de Denis Desgagné — sœur de Réal Gravel</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="21" t="inlineStr">
+        <is>
+          <t>P195</t>
+        </is>
+      </c>
+      <c r="B140" s="21" t="inlineStr">
+        <is>
+          <t>Denis Desgagné</t>
+        </is>
+      </c>
+      <c r="C140" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D140" s="21" t="inlineStr">
+        <is>
+          <t>P197</t>
+        </is>
+      </c>
+      <c r="E140" s="21" t="inlineStr">
+        <is>
+          <t>Camille Desgagné</t>
+        </is>
+      </c>
+      <c r="F140" s="21" t="inlineStr">
+        <is>
+          <t>P197</t>
+        </is>
+      </c>
+      <c r="G140" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H140" s="21" t="inlineStr">
+        <is>
+          <t>Fille de Denis et Johanne — collègue d’Émile Brassard</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="21" t="inlineStr">
+        <is>
+          <t>P195</t>
+        </is>
+      </c>
+      <c r="B141" s="21" t="inlineStr">
+        <is>
+          <t>Denis Desgagné</t>
+        </is>
+      </c>
+      <c r="C141" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D141" s="21" t="inlineStr">
+        <is>
+          <t>P198</t>
+        </is>
+      </c>
+      <c r="E141" s="21" t="inlineStr">
+        <is>
+          <t>Samuel Desgagné</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="inlineStr">
+        <is>
+          <t>P198</t>
+        </is>
+      </c>
+      <c r="G141" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H141" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Denis et Johanne — frère de Camille et Julien</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="21" t="inlineStr">
+        <is>
+          <t>P195</t>
+        </is>
+      </c>
+      <c r="B142" s="21" t="inlineStr">
+        <is>
+          <t>Denis Desgagné</t>
+        </is>
+      </c>
+      <c r="C142" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D142" s="21" t="inlineStr">
+        <is>
+          <t>P203</t>
+        </is>
+      </c>
+      <c r="E142" s="21" t="inlineStr">
+        <is>
+          <t>Julien Desgagné</t>
+        </is>
+      </c>
+      <c r="F142" s="21" t="inlineStr">
+        <is>
+          <t>P203</t>
+        </is>
+      </c>
+      <c r="G142" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H142" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Denis et Johanne — aîné de Camille et Samuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="21" t="inlineStr">
+        <is>
+          <t>P196</t>
+        </is>
+      </c>
+      <c r="B143" s="21" t="inlineStr">
+        <is>
+          <t>Johanne Gravel</t>
+        </is>
+      </c>
+      <c r="C143" s="21" t="inlineStr">
+        <is>
+          <t>fratrie</t>
+        </is>
+      </c>
+      <c r="D143" s="21" t="inlineStr">
+        <is>
+          <t>P202</t>
+        </is>
+      </c>
+      <c r="E143" s="21" t="inlineStr">
+        <is>
+          <t>Réal Gravel</t>
+        </is>
+      </c>
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t>P202</t>
+        </is>
+      </c>
+      <c r="G143" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H143" s="21" t="inlineStr">
+        <is>
+          <t>Frère de Johanne Gravel — oncle de Camille, Samuel et Julien</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="21" t="inlineStr">
+        <is>
+          <t>P196</t>
+        </is>
+      </c>
+      <c r="B144" s="21" t="inlineStr">
+        <is>
+          <t>Johanne Gravel</t>
+        </is>
+      </c>
+      <c r="C144" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D144" s="21" t="inlineStr">
+        <is>
+          <t>P197</t>
+        </is>
+      </c>
+      <c r="E144" s="21" t="inlineStr">
+        <is>
+          <t>Camille Desgagné</t>
+        </is>
+      </c>
+      <c r="F144" s="21" t="inlineStr">
+        <is>
+          <t>P197</t>
+        </is>
+      </c>
+      <c r="G144" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H144" s="21" t="inlineStr">
+        <is>
+          <t>Fille de Denis et Johanne — collègue d’Émile Brassard</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="21" t="inlineStr">
+        <is>
+          <t>P196</t>
+        </is>
+      </c>
+      <c r="B145" s="21" t="inlineStr">
+        <is>
+          <t>Johanne Gravel</t>
+        </is>
+      </c>
+      <c r="C145" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D145" s="21" t="inlineStr">
+        <is>
+          <t>P198</t>
+        </is>
+      </c>
+      <c r="E145" s="21" t="inlineStr">
+        <is>
+          <t>Samuel Desgagné</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="inlineStr">
+        <is>
+          <t>P198</t>
+        </is>
+      </c>
+      <c r="G145" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H145" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Denis et Johanne — frère de Camille et Julien</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="21" t="inlineStr">
+        <is>
+          <t>P196</t>
+        </is>
+      </c>
+      <c r="B146" s="21" t="inlineStr">
+        <is>
+          <t>Johanne Gravel</t>
+        </is>
+      </c>
+      <c r="C146" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D146" s="21" t="inlineStr">
+        <is>
+          <t>P203</t>
+        </is>
+      </c>
+      <c r="E146" s="21" t="inlineStr">
+        <is>
+          <t>Julien Desgagné</t>
+        </is>
+      </c>
+      <c r="F146" s="21" t="inlineStr">
+        <is>
+          <t>P203</t>
+        </is>
+      </c>
+      <c r="G146" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H146" s="21" t="inlineStr">
+        <is>
+          <t>Fils de Denis et Johanne — aîné de Camille et Samuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="21" t="inlineStr">
+        <is>
+          <t>P199</t>
+        </is>
+      </c>
+      <c r="B147" s="21" t="inlineStr">
+        <is>
+          <t>Nathalie Tremblay</t>
+        </is>
+      </c>
+      <c r="C147" s="21" t="inlineStr">
+        <is>
+          <t>superieur_de</t>
+        </is>
+      </c>
+      <c r="D147" s="21" t="inlineStr">
+        <is>
+          <t>P084</t>
+        </is>
+      </c>
+      <c r="E147" s="21" t="inlineStr">
+        <is>
+          <t>Jacques Maltais</t>
+        </is>
+      </c>
+      <c r="F147" s="21" t="inlineStr">
+        <is>
+          <t>P199</t>
+        </is>
+      </c>
+      <c r="G147" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H147" s="21" t="inlineStr">
+        <is>
+          <t>Célibataire — supérieure de Jacques Maltais</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="21" t="inlineStr">
+        <is>
+          <t>P202</t>
+        </is>
+      </c>
+      <c r="B148" s="21" t="inlineStr">
+        <is>
+          <t>Réal Gravel</t>
+        </is>
+      </c>
+      <c r="C148" s="21" t="inlineStr">
+        <is>
+          <t>oncle_de</t>
+        </is>
+      </c>
+      <c r="D148" s="21" t="inlineStr">
+        <is>
+          <t>P197</t>
+        </is>
+      </c>
+      <c r="E148" s="21" t="inlineStr">
+        <is>
+          <t>Camille Desgagné</t>
+        </is>
+      </c>
+      <c r="F148" s="21" t="inlineStr">
+        <is>
+          <t>P202</t>
+        </is>
+      </c>
+      <c r="G148" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H148" s="21" t="inlineStr">
+        <is>
+          <t>Frère de Johanne Gravel — oncle de Camille, Samuel et Julien</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="21" t="inlineStr">
+        <is>
+          <t>P202</t>
+        </is>
+      </c>
+      <c r="B149" s="21" t="inlineStr">
+        <is>
+          <t>Réal Gravel</t>
+        </is>
+      </c>
+      <c r="C149" s="21" t="inlineStr">
+        <is>
+          <t>oncle_de</t>
+        </is>
+      </c>
+      <c r="D149" s="21" t="inlineStr">
+        <is>
+          <t>P198</t>
+        </is>
+      </c>
+      <c r="E149" s="21" t="inlineStr">
+        <is>
+          <t>Samuel Desgagné</t>
+        </is>
+      </c>
+      <c r="F149" s="21" t="inlineStr">
+        <is>
+          <t>P202</t>
+        </is>
+      </c>
+      <c r="G149" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H149" s="21" t="inlineStr">
+        <is>
+          <t>Frère de Johanne Gravel — oncle de Camille, Samuel et Julien</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="21" t="inlineStr">
+        <is>
+          <t>P202</t>
+        </is>
+      </c>
+      <c r="B150" s="21" t="inlineStr">
+        <is>
+          <t>Réal Gravel</t>
+        </is>
+      </c>
+      <c r="C150" s="21" t="inlineStr">
+        <is>
+          <t>oncle_de</t>
+        </is>
+      </c>
+      <c r="D150" s="21" t="inlineStr">
+        <is>
+          <t>P203</t>
+        </is>
+      </c>
+      <c r="E150" s="21" t="inlineStr">
+        <is>
+          <t>Julien Desgagné</t>
+        </is>
+      </c>
+      <c r="F150" s="21" t="inlineStr">
+        <is>
+          <t>P202</t>
+        </is>
+      </c>
+      <c r="G150" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H150" s="21" t="inlineStr">
+        <is>
+          <t>Frère de Johanne Gravel — oncle de Camille, Samuel et Julien</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="21" t="inlineStr">
+        <is>
+          <t>P204</t>
+        </is>
+      </c>
+      <c r="B151" s="21" t="inlineStr">
+        <is>
+          <t>Emma Boucher</t>
+        </is>
+      </c>
+      <c r="C151" s="21" t="inlineStr">
+        <is>
+          <t>colocataire_de</t>
+        </is>
+      </c>
+      <c r="D151" s="21" t="inlineStr">
+        <is>
+          <t>P205</t>
+        </is>
+      </c>
+      <c r="E151" s="21" t="inlineStr">
+        <is>
+          <t>Moussa Diallo</t>
+        </is>
+      </c>
+      <c r="F151" s="21" t="inlineStr">
+        <is>
+          <t>P205</t>
+        </is>
+      </c>
+      <c r="G151" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H151" s="21" t="inlineStr">
+        <is>
+          <t>Célibataire — colocataire d’Emma Boucher et William Lavoie</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="21" t="inlineStr">
+        <is>
+          <t>P204</t>
+        </is>
+      </c>
+      <c r="B152" s="21" t="inlineStr">
+        <is>
+          <t>Emma Boucher</t>
+        </is>
+      </c>
+      <c r="C152" s="21" t="inlineStr">
+        <is>
+          <t>colocataire_de</t>
+        </is>
+      </c>
+      <c r="D152" s="21" t="inlineStr">
+        <is>
+          <t>P206</t>
+        </is>
+      </c>
+      <c r="E152" s="21" t="inlineStr">
+        <is>
+          <t>William Lavoie</t>
+        </is>
+      </c>
+      <c r="F152" s="21" t="inlineStr">
+        <is>
+          <t>P206</t>
+        </is>
+      </c>
+      <c r="G152" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H152" s="21" t="inlineStr">
+        <is>
+          <t>Cousin de JP — colocataire d’Emma Boucher et Moussa Diallo</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="21" t="inlineStr">
+        <is>
+          <t>P205</t>
+        </is>
+      </c>
+      <c r="B153" s="21" t="inlineStr">
+        <is>
+          <t>Moussa Diallo</t>
+        </is>
+      </c>
+      <c r="C153" s="21" t="inlineStr">
+        <is>
+          <t>colocataire_de</t>
+        </is>
+      </c>
+      <c r="D153" s="21" t="inlineStr">
+        <is>
+          <t>P206</t>
+        </is>
+      </c>
+      <c r="E153" s="21" t="inlineStr">
+        <is>
+          <t>William Lavoie</t>
+        </is>
+      </c>
+      <c r="F153" s="21" t="inlineStr">
+        <is>
+          <t>P205</t>
+        </is>
+      </c>
+      <c r="G153" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H153" s="21" t="inlineStr">
+        <is>
+          <t>Célibataire — colocataire d’Emma Boucher et William Lavoie</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="21" t="inlineStr">
+        <is>
+          <t>P210</t>
+        </is>
+      </c>
+      <c r="B154" s="21" t="inlineStr">
+        <is>
+          <t>Lucien Gagné</t>
+        </is>
+      </c>
+      <c r="C154" s="21" t="inlineStr">
+        <is>
+          <t>oncle_de</t>
+        </is>
+      </c>
+      <c r="D154" s="21" t="inlineStr">
+        <is>
+          <t>P122</t>
+        </is>
+      </c>
+      <c r="E154" s="21" t="inlineStr">
+        <is>
+          <t>Isabelle Gagné</t>
+        </is>
+      </c>
+      <c r="F154" s="21" t="inlineStr">
+        <is>
+          <t>P210</t>
+        </is>
+      </c>
+      <c r="G154" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H154" s="21" t="inlineStr">
+        <is>
+          <t>Oncle d’Isabelle Gagné — propriétaire d’Emma, Moussa et William</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="21" t="inlineStr">
+        <is>
           <t>P213</t>
         </is>
       </c>
-      <c r="B115" s="21" t="inlineStr">
+      <c r="B155" s="21" t="inlineStr">
         <is>
           <t>Karine Simard</t>
         </is>
       </c>
-      <c r="C115" s="21" t="inlineStr">
+      <c r="C155" s="21" t="inlineStr">
         <is>
           <t>parent_de</t>
         </is>
       </c>
-      <c r="D115" s="21" t="inlineStr">
+      <c r="D155" s="21" t="inlineStr">
+        <is>
+          <t>P211</t>
+        </is>
+      </c>
+      <c r="E155" s="21" t="inlineStr">
+        <is>
+          <t>Léa Simard</t>
+        </is>
+      </c>
+      <c r="F155" s="21" t="inlineStr">
+        <is>
+          <t>P211</t>
+        </is>
+      </c>
+      <c r="G155" s="21" t="inlineStr">
+        <is>
+          <t>Parenté</t>
+        </is>
+      </c>
+      <c r="H155" s="21" t="inlineStr">
+        <is>
+          <t>Fille de Karine Simard — sœur d’Anthony</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="21" t="inlineStr">
+        <is>
+          <t>P213</t>
+        </is>
+      </c>
+      <c r="B156" s="21" t="inlineStr">
+        <is>
+          <t>Karine Simard</t>
+        </is>
+      </c>
+      <c r="C156" s="21" t="inlineStr">
+        <is>
+          <t>parent_de</t>
+        </is>
+      </c>
+      <c r="D156" s="21" t="inlineStr">
         <is>
           <t>P212</t>
         </is>
       </c>
-      <c r="E115" s="21" t="inlineStr">
+      <c r="E156" s="21" t="inlineStr">
         <is>
           <t>Anthony Simard</t>
         </is>
       </c>
-      <c r="F115" s="21" t="inlineStr">
+      <c r="F156" s="21" t="inlineStr">
         <is>
           <t>P212</t>
         </is>
       </c>
-      <c r="G115" s="21" t="inlineStr">
+      <c r="G156" s="21" t="inlineStr">
         <is>
           <t>Parenté</t>
         </is>
       </c>
-      <c r="H115" s="21" t="inlineStr">
+      <c r="H156" s="21" t="inlineStr">
         <is>
           <t>Fils de Karine Simard — frère de Léa — neveu de Nancy Simard</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H115"/>
+  <autoFilter ref="A1:H156"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/base_personnages_fictifs.xlsx
+++ b/base_personnages_fictifs.xlsx
@@ -17530,7 +17530,7 @@
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>• Portraits            : images générées par IA ; fiction intégrale. Statut distinct dans LICENSE-DONNEES.md.</t>
+          <t>• Portraits            : images générées par IA ; fiction intégrale. Statut distinct dans LICENSE-DONNEES.md ; chaque image porte son étiquette IA en métadonnées XMP (DigitalSourceType = trainedAlgorithmicMedia).</t>
         </is>
       </c>
     </row>
